--- a/reports/screener_2026-09-01.xlsx
+++ b/reports/screener_2026-09-01.xlsx
@@ -1272,16 +1272,16 @@
         <v>0.61</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI2" t="n">
         <v>10.89999961853027</v>
       </c>
       <c r="CJ2" t="n">
-        <v>6.304016002878752</v>
+        <v>6.304015931491178</v>
       </c>
       <c r="CK2" t="n">
-        <v>11.69394968534009</v>
+        <v>11.69394955291613</v>
       </c>
       <c r="CL2" t="n">
         <v>41.26428427015031</v>
@@ -1290,7 +1290,7 @@
         <v>27.77577096127572</v>
       </c>
       <c r="CN2" t="n">
-        <v>71.93034809093047</v>
+        <v>71.93034780538017</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -1352,7 +1352,7 @@
         <v>1.421654006276185</v>
       </c>
       <c r="DL2" t="n">
-        <v>-22.46674000532078</v>
+        <v>-22.46674537978634</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -1628,10 +1628,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.84679448790572</v>
+        <v>14.84679441791949</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.54080377506511</v>
+        <v>27.54080364524066</v>
       </c>
       <c r="CL3" t="n">
         <v>38.77065228379291</v>
@@ -1640,13 +1640,13 @@
         <v>23.46088908480287</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.90049918950116</v>
+        <v>74.90049932001999</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789233750145</v>
+        <v>48.47789238916742</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.49458272838073</v>
+        <v>26.49458294430783</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.883220620076511</v>
@@ -1966,7 +1966,7 @@
         <v>-4.21</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CG4" t="n">
         <v>0.63</v>
@@ -1978,10 +1978,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247025670269</v>
+        <v>16.22247027568049</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268232618348</v>
+        <v>30.0926823613873</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -1990,19 +1990,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726943942</v>
+        <v>125.5537726880124</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311657662</v>
+        <v>25.70896311385998</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944664979132</v>
+        <v>61.89944660907558</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.17744912371742</v>
+        <v>47.17744912234599</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -2023,7 +2023,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479612101903</v>
+        <v>92.95479611540991</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>4.079999923706055</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.706970677717968</v>
+        <v>3.706970691086601</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.87643060716683</v>
+        <v>6.876430631965645</v>
       </c>
       <c r="CL5" t="n">
         <v>12.7199997621424</v>
@@ -2348,25 +2348,25 @@
         <v>8.569713954002083</v>
       </c>
       <c r="CN5" t="n">
-        <v>24.70099967519722</v>
+        <v>24.70099966623111</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21751809501781</v>
+        <v>11.21751808953736</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.41530415973325</v>
+        <v>10.41530412641649</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.322614371521537</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.186930158263985</v>
+        <v>9.186930155930918</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.492509056867668</v>
+        <v>9.492509040209285</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.543258151180902</v>
+        <v>8.543258136188356</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -2378,10 +2378,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.3935860523414</v>
+        <v>109.3935856848771</v>
       </c>
       <c r="CY5" t="n">
-        <v>125.1698610307587</v>
+        <v>125.1698609735757</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>-1.686751085608817</v>
       </c>
       <c r="DL5" t="n">
-        <v>-37.53577031186686</v>
+        <v>-37.53577507999217</v>
       </c>
       <c r="DM5" t="b">
         <v>1</v>
@@ -2696,10 +2696,10 @@
         <v>4.400000095367432</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.210667574853963</v>
+        <v>3.21066757318049</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.955788351354101</v>
+        <v>5.955788348249809</v>
       </c>
       <c r="CL6" t="n">
         <v>12.72925791782063</v>
@@ -2708,7 +2708,7 @@
         <v>8.553414722002886</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.22474835774388</v>
+        <v>24.22474835262846</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -2720,7 +2720,7 @@
         <v>5.312954959486701</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.42510806728737</v>
+        <v>11.42510806611312</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -2741,7 +2741,7 @@
         <v>136.7641763673805</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.6615413557915</v>
+        <v>159.6615413291041</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -2758,7 +2758,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="DC6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da Marcopolo (POMO4) revela uma empresa com excelente eficiência operacional, evidenciada por um ROE de 28,3% e um ROIC de 18,4%, ambos significativamente acima das médias do setor de bens industriais, que são de 14,5% e 12,6%, respectivamente. Essa alta qualidade de retorno convive com múltiplos de preço bastante atrativos, visto que o P/L de 4,58 e o P/VP de 1,3 sugerem que o papel está descontado frente à sua capacidade de geração de valor. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento controlado, com a relação Dívida Líquida/EBITDA em 1,29, patamar confortavelmente abaixo da média setorial de 2,39, o que confere solidez ao balanço. Essa estrutura de capital saudável e a forte lucratividade sustentam um expressivo Dividend Yield de 21,0%, o qual se mostra coerente com a robustez dos lucros recentes, embora o investidor deva monitorar a sustentabilidade desse fluxo no longo prazo. Por outro lado, o crescimento histórico acende um sinal de alerta, dado que o CAGR de receita dos últimos cinco anos contraiu 14,0%, ficando muito abaixo da média de expansão de 21,6% dos seus pares setoriais. Esse descompasso no crescimento e a existência de vendas por parte de insiders explicam por que a companhia atendeu a apenas 5 dos 8 critérios do checklist de qualidade, além de refletirem uma tendência gráfica atual de baixa. No que tange ao valuation, as estimativas de preço-teto apresentam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 3,21 por Bazin até os otimistas R$ 24,22 por Lynch, estabelecendo uma média de R$ 11,43 e um preço-teto ajustado com margem de segurança de R$ 10,42, o que projeta um expressivo potencial de valorização teórica de 136,8% sobre a cotação atual de R$ 4,40. Em suma, POMO4 destaca-se positivamente por seus indicadores de rentabilidade superiores, endividamento sob controle, múltiplos de valuation convidativos e proventos robustos, mas traz como contrapartidas o histórico recente de retração na receita e a falta de momentum gráfico de curto prazo.</t>
+        </is>
+      </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="b">
         <v>0</v>
@@ -3042,10 +3046,10 @@
         <v>49.08000183105469</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.70442476571499</v>
+        <v>18.70442477833754</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.6967079404013</v>
+        <v>34.69670796381614</v>
       </c>
       <c r="CL7" t="n">
         <v>75.52961954256382</v>
@@ -3054,23 +3058,23 @@
         <v>56.52767725678649</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.8003932206363</v>
+        <v>100.8003932007989</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.84536141761207</v>
+        <v>47.84536141459667</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.47113929721691</v>
+        <v>59.4711392718466</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.19402841657305</v>
+        <v>44.19402842482855</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.27103467900669</v>
+        <v>41.2710346892064</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.14393121110602</v>
+        <v>37.14393122028576</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -3082,10 +3086,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.3196213827284</v>
+        <v>-24.31962136402477</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.955120684999875</v>
+        <v>-9.955120668179374</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -3400,10 +3404,10 @@
         <v>15.73999977111816</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.416394726867549</v>
+        <v>6.416394730624279</v>
       </c>
       <c r="CK8" t="n">
-        <v>11.9024122183393</v>
+        <v>11.90241222530804</v>
       </c>
       <c r="CL8" t="n">
         <v>25.40255748688375</v>
@@ -3412,19 +3416,19 @@
         <v>18.61214239569414</v>
       </c>
       <c r="CN8" t="n">
-        <v>35.20098332860089</v>
+        <v>35.20098332248433</v>
       </c>
       <c r="CO8" t="n">
-        <v>12.29650749169001</v>
+        <v>12.29650749097704</v>
       </c>
       <c r="CP8" t="n">
-        <v>20.37042634952579</v>
+        <v>20.37042634165439</v>
       </c>
       <c r="CQ8" t="n">
         <v>18.47023285957259</v>
       </c>
       <c r="CR8" t="n">
-        <v>20.3221803043295</v>
+        <v>20.3221803032249</v>
       </c>
       <c r="CS8" t="n">
         <v>18.61214239569414</v>
@@ -3445,7 +3449,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY8" t="n">
-        <v>29.11169377282539</v>
+        <v>29.1116937658076</v>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
@@ -3770,10 +3774,10 @@
         <v>45.02000045776367</v>
       </c>
       <c r="CJ9" t="n">
-        <v>131.8923109101077</v>
+        <v>131.8923100198635</v>
       </c>
       <c r="CK9" t="n">
-        <v>244.6602367382497</v>
+        <v>244.6602350868468</v>
       </c>
       <c r="CL9" t="n">
         <v>137.1298864518089</v>
@@ -3794,13 +3798,13 @@
         <v>55.34098571876934</v>
       </c>
       <c r="CR9" t="n">
-        <v>144.1214557430111</v>
+        <v>144.1214554253053</v>
       </c>
       <c r="CS9" t="n">
-        <v>128.5601790802194</v>
+        <v>128.5601786350973</v>
       </c>
       <c r="CT9" t="n">
-        <v>115.7041611721975</v>
+        <v>115.7041607715876</v>
       </c>
       <c r="CU9" t="n">
         <v>8</v>
@@ -3812,10 +3816,10 @@
         <v>5.6</v>
       </c>
       <c r="CX9" t="n">
-        <v>157.0061305991043</v>
+        <v>157.0061297092557</v>
       </c>
       <c r="CY9" t="n">
-        <v>220.1276194526503</v>
+        <v>220.127618746951</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -4130,10 +4134,10 @@
         <v>32.72999954223633</v>
       </c>
       <c r="CJ10" t="n">
-        <v>45.70703783561292</v>
+        <v>45.70703776739576</v>
       </c>
       <c r="CK10" t="n">
-        <v>84.78655518506196</v>
+        <v>84.78655505851914</v>
       </c>
       <c r="CL10" t="n">
         <v>68.18749904632567</v>
@@ -4154,7 +4158,7 @@
         <v>25.65248645136637</v>
       </c>
       <c r="CR10" t="n">
-        <v>77.50815036943183</v>
+        <v>77.50815034160897</v>
       </c>
       <c r="CS10" t="n">
         <v>68.18749904632567</v>
@@ -4175,7 +4179,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY10" t="n">
-        <v>136.8107285470984</v>
+        <v>136.8107284620912</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -4486,7 +4490,7 @@
         <v>-1.81</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CG11" t="n">
         <v>0.57</v>
@@ -4498,37 +4502,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ11" t="n">
-        <v>24.21612678734386</v>
+        <v>24.21612667620782</v>
       </c>
       <c r="CK11" t="n">
-        <v>32.67790149621491</v>
+        <v>32.67790232091849</v>
       </c>
       <c r="CL11" t="n">
-        <v>34.37896721817167</v>
+        <v>34.37896824358241</v>
       </c>
       <c r="CM11" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN11" t="n">
-        <v>48.8073900732228</v>
+        <v>48.80739093580195</v>
       </c>
       <c r="CO11" t="n">
-        <v>50.94836373183931</v>
+        <v>50.9483638746774</v>
       </c>
       <c r="CP11" t="n">
-        <v>16.89191248125056</v>
+        <v>16.89191313044504</v>
       </c>
       <c r="CQ11" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR11" t="n">
-        <v>31.61206944099688</v>
+        <v>31.61206986519563</v>
       </c>
       <c r="CS11" t="n">
-        <v>28.44701414177938</v>
+        <v>28.44701449856316</v>
       </c>
       <c r="CT11" t="n">
-        <v>25.60231272760145</v>
+        <v>25.60231304870684</v>
       </c>
       <c r="CU11" t="n">
         <v>8</v>
@@ -4540,10 +4544,10 @@
         <v>3</v>
       </c>
       <c r="CX11" t="n">
-        <v>-21.46529470568728</v>
+        <v>-21.46529372070136</v>
       </c>
       <c r="CY11" t="n">
-        <v>-3.030457298666644</v>
+        <v>-3.030455997443415</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -4862,16 +4866,16 @@
         <v>0.23</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="CI12" t="n">
         <v>50.29000091552734</v>
       </c>
       <c r="CJ12" t="n">
-        <v>139.5836066576344</v>
+        <v>139.5836077150498</v>
       </c>
       <c r="CK12" t="n">
-        <v>258.9275903499119</v>
+        <v>258.9275923114173</v>
       </c>
       <c r="CL12" t="n">
         <v>137.1075127841023</v>
@@ -4892,7 +4896,7 @@
         <v>54.15143544791205</v>
       </c>
       <c r="CR12" t="n">
-        <v>146.7120320536963</v>
+        <v>146.7120324310614</v>
       </c>
       <c r="CS12" t="n">
         <v>131.157564116113</v>
@@ -4913,7 +4917,7 @@
         <v>134.7222222222222</v>
       </c>
       <c r="CY12" t="n">
-        <v>191.7320130896996</v>
+        <v>191.7320138400776</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -5210,10 +5214,10 @@
         <v>19.34000015258789</v>
       </c>
       <c r="CJ13" t="n">
-        <v>13.29214280561541</v>
+        <v>13.29214273283289</v>
       </c>
       <c r="CK13" t="n">
-        <v>24.65692490441659</v>
+        <v>24.65692476940502</v>
       </c>
       <c r="CL13" t="n">
         <v>19.97311005625795</v>
@@ -5222,7 +5226,7 @@
         <v>12.48226378298752</v>
       </c>
       <c r="CN13" t="n">
-        <v>33.79906478813256</v>
+        <v>33.79906470871283</v>
       </c>
       <c r="CO13" t="n">
         <v>22.8984489302328</v>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
-        <v>20.20515667413068</v>
+        <v>20.20515662218217</v>
       </c>
       <c r="CS13" t="n">
         <v>21.43577949324537</v>
@@ -5253,7 +5257,7 @@
         <v>-0.2471489570317398</v>
       </c>
       <c r="CY13" t="n">
-        <v>4.473404936488734</v>
+        <v>4.473404667882108</v>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
@@ -5270,7 +5274,11 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="DC13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr">
+        <is>
+          <t>A Caixa Seguridade (CXSE3) apresenta-se como uma alternativa robusta no setor de seguros, destacando-se por uma margem líquida expressiva de 75,43% e um crescimento de receita nos últimos cinco anos de 12,8% ao ano, patamar que supera com folga a média negativa de 2,5% de seus pares setoriais. No entanto, essa expansão de receita contrasta com indicadores de eficiência que demandam atenção, uma vez que o ROE de 32,8% e o ROIC de -1,2% situam-se abaixo das médias do setor, de 34,3% e 19,5%, respectivamente, sugerindo que a companhia ainda precisa otimizar a rentabilidade sobre o capital investido frente aos concorrentes. Sob a ótica de preço e qualidade, o papel negocia a múltiplos elevados, com um P/L de 12,83 e um P/VP de 4,21, indicando que o mercado cobra um prêmio considerável por essa operação altamente rentável, embora o PEG ratio em 1,0 sinalize um valuation justo em relação ao crescimento projetado. O retorno em dividendos de 6,99% mostra-se atraente e sustentável, sendo plenamente suportado pela alta geração de caixa e pela ausência de alavancagem financeira preocupante, o que é corroborado pela nota máxima de segurança atribuída à empresa. No checklist de critérios fundamentalistas, a companhia atende a quatro dos seis requisitos avaliados, penalizada justamente por não superar os pares em ROE e ROIC, mas validada pelo porte robusto e pela governança, sem registro de venda de ações por controladores. Quanto ao valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 12,48 por Graham e R$ 13,29 por Bazin até os otimistas R$ 24,66 por Gordon e R$ 33,80 por Lynch. Com uma média de preço-teto de R$ 20,21 e uma mediana de R$ 21,44, o preço-teto ajustado com margem de segurança fica em R$ 19,29, o que coloca a cotação atual de R$ 19,34 em patamar de estabilidade, com um upside ligeiramente negativo de 0,2% em relação a essa métrica ajustada. Em balanço, os prós residem na excelente margem líquida, no forte crescimento histórico de receita frente ao setor e na alta segurança financeira com dividendos consistentes, enquanto os contras ficam por conta da rentabilidade abaixo da média dos pares, dos múltiplos de valuation esticados e de uma tendência gráfica de baixa no curto prazo.</t>
+        </is>
+      </c>
       <c r="DD13" t="inlineStr"/>
       <c r="DE13" t="b">
         <v>1</v>
@@ -5556,10 +5564,10 @@
         <v>-55.81</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="CH14" t="n">
         <v>0.07000000000000001</v>
@@ -5568,10 +5576,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ14" t="n">
-        <v>3.228277651320188</v>
+        <v>3.228277654826922</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.988455043198949</v>
+        <v>5.988455049703941</v>
       </c>
       <c r="CL14" t="n">
         <v>19.81956093381139</v>
@@ -5580,7 +5588,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN14" t="n">
-        <v>31.89244530313685</v>
+        <v>31.89244531340761</v>
       </c>
       <c r="CO14" t="n">
         <v>10.95072400487419</v>
@@ -5912,16 +5920,16 @@
         <v>0.5</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI15" t="n">
         <v>16.75</v>
       </c>
       <c r="CJ15" t="n">
-        <v>10.26720875607003</v>
+        <v>10.26720872277248</v>
       </c>
       <c r="CK15" t="n">
-        <v>19.04567224250991</v>
+        <v>19.04567218074295</v>
       </c>
       <c r="CL15" t="n">
         <v>37.48944256756756</v>
@@ -5930,25 +5938,25 @@
         <v>36.97412590213069</v>
       </c>
       <c r="CN15" t="n">
-        <v>42.62689278589763</v>
+        <v>42.62689276859406</v>
       </c>
       <c r="CO15" t="n">
-        <v>34.59941685514998</v>
+        <v>34.59941686220576</v>
       </c>
       <c r="CP15" t="n">
-        <v>19.0904981639273</v>
+        <v>19.09049820254713</v>
       </c>
       <c r="CQ15" t="n">
         <v>32.11454047621128</v>
       </c>
       <c r="CR15" t="n">
-        <v>31.70579842762777</v>
+        <v>31.70579842285707</v>
       </c>
       <c r="CS15" t="n">
-        <v>34.59941685514998</v>
+        <v>34.59941686220576</v>
       </c>
       <c r="CT15" t="n">
-        <v>31.13947516963498</v>
+        <v>31.13947517598519</v>
       </c>
       <c r="CU15" t="n">
         <v>7</v>
@@ -5960,10 +5968,10 @@
         <v>4.2</v>
       </c>
       <c r="CX15" t="n">
-        <v>85.90731444558195</v>
+        <v>85.90731448349366</v>
       </c>
       <c r="CY15" t="n">
-        <v>89.2883488216583</v>
+        <v>89.28834879317652</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -6002,7 +6010,7 @@
         <v>-4.449518859629698</v>
       </c>
       <c r="DL15" t="n">
-        <v>-26.63753022143262</v>
+        <v>-26.63753640577318</v>
       </c>
       <c r="DM15" t="b">
         <v>1</v>
@@ -6272,43 +6280,43 @@
         <v>0.5</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="CI16" t="n">
         <v>34.11000061035156</v>
       </c>
       <c r="CJ16" t="n">
-        <v>24.52443755055584</v>
+        <v>24.52443740492133</v>
       </c>
       <c r="CK16" t="n">
-        <v>31.40162277937119</v>
+        <v>31.40162301240151</v>
       </c>
       <c r="CL16" t="n">
-        <v>35.21056596633962</v>
+        <v>35.21056643672837</v>
       </c>
       <c r="CM16" t="n">
         <v>36.15779229888242</v>
       </c>
       <c r="CN16" t="n">
-        <v>49.3926378187119</v>
+        <v>49.39263810952428</v>
       </c>
       <c r="CO16" t="n">
-        <v>48.65929057477212</v>
+        <v>48.65929063884296</v>
       </c>
       <c r="CP16" t="n">
-        <v>16.97314174498548</v>
+        <v>16.9731420724301</v>
       </c>
       <c r="CQ16" t="n">
         <v>30.64026112103792</v>
       </c>
       <c r="CR16" t="n">
-        <v>34.11996873183206</v>
+        <v>34.11996888684611</v>
       </c>
       <c r="CS16" t="n">
-        <v>33.30609437285541</v>
+        <v>33.30609472456494</v>
       </c>
       <c r="CT16" t="n">
-        <v>29.97548493556987</v>
+        <v>29.97548525210845</v>
       </c>
       <c r="CU16" t="n">
         <v>8</v>
@@ -6320,10 +6328,10 @@
         <v>2.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>-12.12112459923841</v>
+        <v>-12.12112367124493</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.02922345735014709</v>
+        <v>0.02922391180351092</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -6638,37 +6646,37 @@
         <v>10.10000038146973</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.12472061232733</v>
+        <v>10.12472075949684</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.25250304374272</v>
+        <v>18.2525026437782</v>
       </c>
       <c r="CL17" t="n">
-        <v>23.77636230045178</v>
+        <v>23.77636143383859</v>
       </c>
       <c r="CM17" t="n">
         <v>17.56505572352211</v>
       </c>
       <c r="CN17" t="n">
-        <v>36.59482139902451</v>
+        <v>36.59482126265946</v>
       </c>
       <c r="CO17" t="n">
-        <v>24.18348115246688</v>
+        <v>24.18348108894751</v>
       </c>
       <c r="CP17" t="n">
-        <v>11.6466800429836</v>
+        <v>11.64667972050579</v>
       </c>
       <c r="CQ17" t="n">
         <v>10.10000038146973</v>
       </c>
       <c r="CR17" t="n">
-        <v>19.03045308199858</v>
+        <v>19.03045287677728</v>
       </c>
       <c r="CS17" t="n">
-        <v>17.90877938363242</v>
+        <v>17.90877918365016</v>
       </c>
       <c r="CT17" t="n">
-        <v>16.11790144526918</v>
+        <v>16.11790126528514</v>
       </c>
       <c r="CU17" t="n">
         <v>8</v>
@@ -6680,10 +6688,10 @@
         <v>3.6</v>
       </c>
       <c r="CX17" t="n">
-        <v>59.58317659908583</v>
+        <v>59.58317481706574</v>
       </c>
       <c r="CY17" t="n">
-        <v>88.42032042804063</v>
+        <v>88.4203183961466</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -6998,10 +7006,10 @@
         <v>10.89999961853027</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.401043863156887</v>
+        <v>3.401043865263513</v>
       </c>
       <c r="CK18" t="n">
-        <v>6.308936366156026</v>
+        <v>6.308936370063815</v>
       </c>
       <c r="CL18" t="n">
         <v>19.64965917626206</v>
@@ -7010,13 +7018,13 @@
         <v>18.52341853243414</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.98684412233365</v>
+        <v>20.98684412209636</v>
       </c>
       <c r="CO18" t="n">
-        <v>15.92132131658388</v>
+        <v>15.92132131616827</v>
       </c>
       <c r="CP18" t="n">
-        <v>13.08144275631335</v>
+        <v>13.08144275364198</v>
       </c>
       <c r="CQ18" t="n">
         <v>29.64794112808246</v>
@@ -7342,16 +7350,16 @@
         <v>0.64</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI19" t="n">
         <v>11.11999988555908</v>
       </c>
       <c r="CJ19" t="n">
-        <v>9.626932739675171</v>
+        <v>9.626932757951991</v>
       </c>
       <c r="CK19" t="n">
-        <v>17.85796023209744</v>
+        <v>17.85796026600094</v>
       </c>
       <c r="CL19" t="n">
         <v>21.79585776385471</v>
@@ -7360,25 +7368,25 @@
         <v>12.85650787905083</v>
       </c>
       <c r="CN19" t="n">
-        <v>30.86844381649707</v>
+        <v>30.86844376023747</v>
       </c>
       <c r="CO19" t="n">
-        <v>25.2091716004863</v>
+        <v>25.20917158696246</v>
       </c>
       <c r="CP19" t="n">
-        <v>11.26534095464609</v>
+        <v>11.26534089549061</v>
       </c>
       <c r="CQ19" t="n">
         <v>9.553111101546266</v>
       </c>
       <c r="CR19" t="n">
-        <v>17.37916576098173</v>
+        <v>17.37916575138691</v>
       </c>
       <c r="CS19" t="n">
-        <v>15.35723405557414</v>
+        <v>15.35723407252589</v>
       </c>
       <c r="CT19" t="n">
-        <v>13.82151065001672</v>
+        <v>13.8215106652733</v>
       </c>
       <c r="CU19" t="n">
         <v>8</v>
@@ -7390,10 +7398,10 @@
         <v>3.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>24.29416180090021</v>
+        <v>24.29416193809966</v>
       </c>
       <c r="CY19" t="n">
-        <v>56.28746348775668</v>
+        <v>56.28746340147226</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -7708,10 +7716,10 @@
         <v>27.92000007629395</v>
       </c>
       <c r="CJ20" t="n">
-        <v>7.398493210606342</v>
+        <v>7.398493237326353</v>
       </c>
       <c r="CK20" t="n">
-        <v>13.72420490567476</v>
+        <v>13.72420495524038</v>
       </c>
       <c r="CL20" t="n">
         <v>35.77756296043469</v>
@@ -7720,19 +7728,19 @@
         <v>28.28645183714482</v>
       </c>
       <c r="CN20" t="n">
-        <v>44.17088012759143</v>
+        <v>44.17088008700814</v>
       </c>
       <c r="CO20" t="n">
-        <v>26.42837008433418</v>
+        <v>26.4283700776647</v>
       </c>
       <c r="CP20" t="n">
-        <v>28.68133713647756</v>
+        <v>28.68133708822763</v>
       </c>
       <c r="CQ20" t="n">
         <v>24.48161704504879</v>
       </c>
       <c r="CR20" t="n">
-        <v>28.79291772810089</v>
+        <v>28.79291772153845</v>
       </c>
       <c r="CS20" t="n">
         <v>28.28645183714482</v>
@@ -7753,7 +7761,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY20" t="n">
-        <v>3.126495879017255</v>
+        <v>3.126495855512812</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -8076,10 +8084,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ21" t="n">
-        <v>3.140372322485803</v>
+        <v>3.140372325224375</v>
       </c>
       <c r="CK21" t="n">
-        <v>5.825390658211164</v>
+        <v>5.825390663291215</v>
       </c>
       <c r="CL21" t="n">
         <v>32.87416582383663</v>
@@ -8088,7 +8096,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN21" t="n">
-        <v>42.11194017978662</v>
+        <v>42.1119401840561</v>
       </c>
       <c r="CO21" t="n">
         <v>10.85340539909456</v>
@@ -8406,10 +8414,10 @@
         <v>40.40000152587891</v>
       </c>
       <c r="CJ22" t="n">
-        <v>36.97443496570012</v>
+        <v>36.97443491714012</v>
       </c>
       <c r="CK22" t="n">
-        <v>53.83477731005938</v>
+        <v>53.83477723935603</v>
       </c>
       <c r="CL22" t="n">
         <v>49.19906509006331</v>
@@ -8426,13 +8434,13 @@
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
-        <v>49.87811058741013</v>
+        <v>49.8781105575943</v>
       </c>
       <c r="CS22" t="n">
-        <v>51.51692120006135</v>
+        <v>51.51692116470967</v>
       </c>
       <c r="CT22" t="n">
-        <v>46.36522908005522</v>
+        <v>46.3652290482387</v>
       </c>
       <c r="CU22" t="n">
         <v>4</v>
@@ -8444,10 +8452,10 @@
         <v>1.6</v>
       </c>
       <c r="CX22" t="n">
-        <v>14.76541418038111</v>
+        <v>14.76541410162737</v>
       </c>
       <c r="CY22" t="n">
-        <v>23.46066510779676</v>
+        <v>23.46066503399518</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -8761,7 +8769,7 @@
         <v>0.97</v>
       </c>
       <c r="CG23" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="CH23" t="n">
         <v>-0.03</v>
@@ -8770,10 +8778,10 @@
         <v>35.45000076293945</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.517189250169004</v>
+        <v>3.51718926427456</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.524386059063503</v>
+        <v>6.524386085229309</v>
       </c>
       <c r="CL23" t="n">
         <v>32.59628800200886</v>
@@ -8782,7 +8790,7 @@
         <v>22.8444967389438</v>
       </c>
       <c r="CN23" t="n">
-        <v>40.31857466665218</v>
+        <v>40.3185746803564</v>
       </c>
       <c r="CO23" t="n">
         <v>10.59424454785779</v>
@@ -9100,35 +9108,35 @@
         <v>13.10000038146973</v>
       </c>
       <c r="CJ24" t="n">
-        <v>8.795131836023424</v>
+        <v>8.795131856249405</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.7630574982212</v>
+        <v>13.76305747564655</v>
       </c>
       <c r="CL24" t="n">
-        <v>18.09953100113439</v>
+        <v>18.09953092982379</v>
       </c>
       <c r="CM24" t="n">
         <v>17.43566356412971</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.73124860113306</v>
+        <v>22.73124858131427</v>
       </c>
       <c r="CO24" t="n">
-        <v>17.30064101555901</v>
+        <v>17.30064100996155</v>
       </c>
       <c r="CP24" t="n">
-        <v>9.046996490206137</v>
+        <v>9.046996455747541</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
-        <v>14.4895903377345</v>
+        <v>14.48959031792032</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.5318492568901</v>
+        <v>15.53184924280405</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.9786643312011</v>
+        <v>13.97866431852364</v>
       </c>
       <c r="CU24" t="n">
         <v>4</v>
@@ -9140,10 +9148,10 @@
         <v>2.1</v>
       </c>
       <c r="CX24" t="n">
-        <v>6.707358199578839</v>
+        <v>6.707358102804406</v>
       </c>
       <c r="CY24" t="n">
-        <v>10.60755660916153</v>
+        <v>10.60755645790825</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -9460,16 +9468,16 @@
         <v>0.47</v>
       </c>
       <c r="CH25" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CI25" t="n">
         <v>5.920000076293945</v>
       </c>
       <c r="CJ25" t="n">
-        <v>7.021620230160911</v>
+        <v>7.021620180788066</v>
       </c>
       <c r="CK25" t="n">
-        <v>13.02510552694849</v>
+        <v>13.02510543536186</v>
       </c>
       <c r="CL25" t="n">
         <v>5.692307765667254</v>
@@ -9490,7 +9498,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR25" t="n">
-        <v>7.373583640576677</v>
+        <v>7.373583622956744</v>
       </c>
       <c r="CS25" t="n">
         <v>5.912820549500294</v>
@@ -9511,7 +9519,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY25" t="n">
-        <v>24.55377610725824</v>
+        <v>24.55377580962423</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -9808,10 +9816,10 @@
         <v>39.52000045776367</v>
       </c>
       <c r="CJ26" t="n">
-        <v>20.20396467909244</v>
+        <v>20.20396449452465</v>
       </c>
       <c r="CK26" t="n">
-        <v>37.47835447971648</v>
+        <v>37.47835413734322</v>
       </c>
       <c r="CL26" t="n">
         <v>56.00427872356884</v>
@@ -9820,23 +9828,23 @@
         <v>42.30510206840214</v>
       </c>
       <c r="CN26" t="n">
-        <v>61.64113321511925</v>
+        <v>61.64113351885764</v>
       </c>
       <c r="CO26" t="n">
-        <v>45.15513209307895</v>
+        <v>45.15513215076771</v>
       </c>
       <c r="CP26" t="n">
-        <v>31.02178769744985</v>
+        <v>31.02178806208198</v>
       </c>
       <c r="CQ26" t="inlineStr"/>
       <c r="CR26" t="n">
-        <v>39.71043249386418</v>
+        <v>39.7104323765511</v>
       </c>
       <c r="CS26" t="n">
-        <v>41.31674328639771</v>
+        <v>41.31674314405547</v>
       </c>
       <c r="CT26" t="n">
-        <v>37.18506895775794</v>
+        <v>37.18506882964992</v>
       </c>
       <c r="CU26" t="n">
         <v>4</v>
@@ -9848,10 +9856,10 @@
         <v>2.8</v>
       </c>
       <c r="CX26" t="n">
-        <v>-5.908227411336064</v>
+        <v>-5.90822773549603</v>
       </c>
       <c r="CY26" t="n">
-        <v>0.4818624339441024</v>
+        <v>0.481862137099287</v>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
@@ -10134,7 +10142,7 @@
         <v>-9.109999999999999</v>
       </c>
       <c r="CF27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CG27" t="n">
         <v>0.84</v>
@@ -10146,10 +10154,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.430280394601793</v>
+        <v>9.430280304114609</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.49317013198633</v>
+        <v>17.4931699641326</v>
       </c>
       <c r="CL27" t="n">
         <v>30.9711095548374</v>
@@ -10158,23 +10166,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN27" t="n">
-        <v>34.71574761345398</v>
+        <v>34.71574759725995</v>
       </c>
       <c r="CO27" t="n">
-        <v>25.36137840591655</v>
+        <v>25.36137842421327</v>
       </c>
       <c r="CP27" t="n">
-        <v>15.27881615604266</v>
+        <v>15.27881626855805</v>
       </c>
       <c r="CQ27" t="inlineStr"/>
       <c r="CR27" t="n">
-        <v>20.81398462183552</v>
+        <v>20.81398456182447</v>
       </c>
       <c r="CS27" t="n">
-        <v>21.42727426895144</v>
+        <v>21.42727419417293</v>
       </c>
       <c r="CT27" t="n">
-        <v>19.28454684205629</v>
+        <v>19.28454677475564</v>
       </c>
       <c r="CU27" t="n">
         <v>4</v>
@@ -10186,10 +10194,10 @@
         <v>3.3</v>
       </c>
       <c r="CX27" t="n">
-        <v>27.12291855681743</v>
+        <v>27.12291811317435</v>
       </c>
       <c r="CY27" t="n">
-        <v>37.20490782568544</v>
+        <v>37.20490743009515</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -10228,7 +10236,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL27" t="n">
-        <v>-16.60345638373696</v>
+        <v>-16.60346541872488</v>
       </c>
       <c r="DM27" t="b">
         <v>1</v>
@@ -10492,7 +10500,7 @@
         <v>-8.31</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="CG28" t="n">
         <v>0.68</v>
@@ -10504,37 +10512,37 @@
         <v>26.6299991607666</v>
       </c>
       <c r="CJ28" t="n">
-        <v>17.02888469211387</v>
+        <v>17.02888465585986</v>
       </c>
       <c r="CK28" t="n">
-        <v>28.30221459159857</v>
+        <v>28.30221458715871</v>
       </c>
       <c r="CL28" t="n">
-        <v>47.53961787673538</v>
+        <v>47.53961797048815</v>
       </c>
       <c r="CM28" t="n">
         <v>53.13028264537036</v>
       </c>
       <c r="CN28" t="n">
-        <v>56.44642288305374</v>
+        <v>56.44642287123989</v>
       </c>
       <c r="CO28" t="n">
-        <v>42.94859200147489</v>
+        <v>42.94859200805522</v>
       </c>
       <c r="CP28" t="n">
-        <v>23.6439102219178</v>
+        <v>23.64391026246718</v>
       </c>
       <c r="CQ28" t="n">
         <v>31.11110629796304</v>
       </c>
       <c r="CR28" t="n">
-        <v>37.51887890127846</v>
+        <v>37.51887891232531</v>
       </c>
       <c r="CS28" t="n">
-        <v>37.02984914971897</v>
+        <v>37.02984915300913</v>
       </c>
       <c r="CT28" t="n">
-        <v>33.32686423474708</v>
+        <v>33.32686423770822</v>
       </c>
       <c r="CU28" t="n">
         <v>8</v>
@@ -10546,10 +10554,10 @@
         <v>3.3</v>
       </c>
       <c r="CX28" t="n">
-        <v>25.1478230755892</v>
+        <v>25.1478230867088</v>
       </c>
       <c r="CY28" t="n">
-        <v>40.88952340845058</v>
+        <v>40.88952344993331</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -10864,37 +10872,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ29" t="n">
-        <v>5.830932764418058</v>
+        <v>5.83093274347174</v>
       </c>
       <c r="CK29" t="n">
-        <v>8.573470587989204</v>
+        <v>8.573470605896599</v>
       </c>
       <c r="CL29" t="n">
-        <v>11.02317108330131</v>
+        <v>11.02317114592365</v>
       </c>
       <c r="CM29" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN29" t="n">
-        <v>9.992439949454242</v>
+        <v>9.992439982933714</v>
       </c>
       <c r="CO29" t="n">
-        <v>14.9393663701344</v>
+        <v>14.93936637751284</v>
       </c>
       <c r="CP29" t="n">
-        <v>5.501588119050497</v>
+        <v>5.501588152966776</v>
       </c>
       <c r="CQ29" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.79472366769255</v>
+        <v>9.794723684487252</v>
       </c>
       <c r="CS29" t="n">
-        <v>10.44705002515057</v>
+        <v>10.4470500418903</v>
       </c>
       <c r="CT29" t="n">
-        <v>9.40234502263551</v>
+        <v>9.402345037701274</v>
       </c>
       <c r="CU29" t="n">
         <v>8</v>
@@ -10906,10 +10914,10 @@
         <v>2.7</v>
       </c>
       <c r="CX29" t="n">
-        <v>-37.44281310924005</v>
+        <v>-37.44281300900209</v>
       </c>
       <c r="CY29" t="n">
-        <v>-34.83217670186686</v>
+        <v>-34.83217659012566</v>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
@@ -11224,37 +11232,37 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CJ30" t="n">
-        <v>31.16719164889602</v>
+        <v>31.16719164748666</v>
       </c>
       <c r="CK30" t="n">
-        <v>35.45587111749327</v>
+        <v>35.45587111857558</v>
       </c>
       <c r="CL30" t="n">
-        <v>38.32522055025856</v>
+        <v>38.3252205531615</v>
       </c>
       <c r="CM30" t="n">
         <v>49.84625084152005</v>
       </c>
       <c r="CN30" t="n">
-        <v>59.74639684334014</v>
+        <v>59.74639684493385</v>
       </c>
       <c r="CO30" t="n">
-        <v>16.57961555868113</v>
+        <v>16.57961555881874</v>
       </c>
       <c r="CP30" t="n">
-        <v>17.07014539293028</v>
+        <v>17.07014539542811</v>
       </c>
       <c r="CQ30" t="n">
         <v>28.85483270240698</v>
       </c>
       <c r="CR30" t="n">
-        <v>34.6306905819408</v>
+        <v>34.63069058279143</v>
       </c>
       <c r="CS30" t="n">
-        <v>33.31153138319464</v>
+        <v>33.31153138303112</v>
       </c>
       <c r="CT30" t="n">
-        <v>29.98037824487518</v>
+        <v>29.98037824472801</v>
       </c>
       <c r="CU30" t="n">
         <v>8</v>
@@ -11266,10 +11274,10 @@
         <v>3.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>-23.32383781365586</v>
+        <v>-23.32383781403223</v>
       </c>
       <c r="CY30" t="n">
-        <v>-11.43045541328697</v>
+        <v>-11.43045541111144</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -11566,35 +11574,35 @@
         <v>17.19000053405762</v>
       </c>
       <c r="CJ31" t="n">
-        <v>10.23156219407304</v>
+        <v>10.23156226265194</v>
       </c>
       <c r="CK31" t="n">
-        <v>17.72445288378861</v>
+        <v>17.72445287222933</v>
       </c>
       <c r="CL31" t="n">
-        <v>28.93952544513885</v>
+        <v>28.93952523229304</v>
       </c>
       <c r="CM31" t="n">
         <v>29.49217552957616</v>
       </c>
       <c r="CN31" t="n">
-        <v>32.29551254703937</v>
+        <v>32.29551254200306</v>
       </c>
       <c r="CO31" t="n">
-        <v>27.87164394922435</v>
+        <v>27.87164393389648</v>
       </c>
       <c r="CP31" t="n">
-        <v>14.29787472503851</v>
+        <v>14.29787463976476</v>
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>21.19179611805621</v>
+        <v>21.1917960752677</v>
       </c>
       <c r="CS31" t="n">
-        <v>22.79804841650648</v>
+        <v>22.79804840306291</v>
       </c>
       <c r="CT31" t="n">
-        <v>20.51824357485583</v>
+        <v>20.51824356275662</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -11606,10 +11614,10 @@
         <v>2.8</v>
       </c>
       <c r="CX31" t="n">
-        <v>19.36150632575111</v>
+        <v>19.3615062553659</v>
       </c>
       <c r="CY31" t="n">
-        <v>23.27978743264174</v>
+        <v>23.27978718372661</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -11648,7 +11656,7 @@
         <v>0.05820854891849248</v>
       </c>
       <c r="DL31" t="n">
-        <v>-19.06389685225955</v>
+        <v>-19.06388943634584</v>
       </c>
       <c r="DM31" t="b">
         <v>1</v>
@@ -11920,7 +11928,7 @@
         <v>-21.11</v>
       </c>
       <c r="CF32" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CG32" t="n">
         <v>0.65</v>
@@ -11932,37 +11940,37 @@
         <v>44.54000091552734</v>
       </c>
       <c r="CJ32" t="n">
-        <v>32.31519140066258</v>
+        <v>32.31519152827246</v>
       </c>
       <c r="CK32" t="n">
-        <v>44.48554536094404</v>
+        <v>44.48554511448052</v>
       </c>
       <c r="CL32" t="n">
-        <v>51.22338300983289</v>
+        <v>51.22338252376301</v>
       </c>
       <c r="CM32" t="n">
         <v>48.06226168784099</v>
       </c>
       <c r="CN32" t="n">
-        <v>71.02439355197752</v>
+        <v>71.02439328874729</v>
       </c>
       <c r="CO32" t="n">
-        <v>59.88896249213759</v>
+        <v>59.88896243967735</v>
       </c>
       <c r="CP32" t="n">
-        <v>25.30024916065064</v>
+        <v>25.30024886385048</v>
       </c>
       <c r="CQ32" t="n">
         <v>77.76550794654696</v>
       </c>
       <c r="CR32" t="n">
-        <v>51.25818682632416</v>
+        <v>51.25818667414738</v>
       </c>
       <c r="CS32" t="n">
-        <v>49.64282234883694</v>
+        <v>49.642822105802</v>
       </c>
       <c r="CT32" t="n">
-        <v>44.67854011395325</v>
+        <v>44.6785398952218</v>
       </c>
       <c r="CU32" t="n">
         <v>8</v>
@@ -11974,10 +11982,10 @@
         <v>3.1</v>
       </c>
       <c r="CX32" t="n">
-        <v>0.3110444444953231</v>
+        <v>0.3110439534053988</v>
       </c>
       <c r="CY32" t="n">
-        <v>15.08348848833263</v>
+        <v>15.08348814666947</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -12270,7 +12278,7 @@
         <v>-4.11</v>
       </c>
       <c r="CF33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CG33" t="n">
         <v>0.85</v>
@@ -12282,10 +12290,10 @@
         <v>54.70999908447266</v>
       </c>
       <c r="CJ33" t="n">
-        <v>10.69729567257529</v>
+        <v>10.6972956690376</v>
       </c>
       <c r="CK33" t="n">
-        <v>19.84348347262716</v>
+        <v>19.84348346606475</v>
       </c>
       <c r="CL33" t="n">
         <v>62.01090572021066</v>
@@ -12294,7 +12302,7 @@
         <v>46.36425801252346</v>
       </c>
       <c r="CN33" t="n">
-        <v>83.01215788564106</v>
+        <v>83.01215788140431</v>
       </c>
       <c r="CO33" t="n">
         <v>11.76833333333333</v>
@@ -12304,7 +12312,7 @@
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>14.10303749284526</v>
+        <v>14.10303748947856</v>
       </c>
       <c r="CS33" t="n">
         <v>11.76833333333333</v>
@@ -12325,7 +12333,7 @@
         <v>-80.6406503797475</v>
       </c>
       <c r="CY33" t="n">
-        <v>-74.2221938789104</v>
+        <v>-74.22219388506412</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -12621,7 +12629,7 @@
         <v>1.16</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="CH34" t="n">
         <v>-0.02</v>
@@ -12630,10 +12638,10 @@
         <v>29.55999946594238</v>
       </c>
       <c r="CJ34" t="n">
-        <v>15.45162961219261</v>
+        <v>15.45162960034638</v>
       </c>
       <c r="CK34" t="n">
-        <v>28.66277293061729</v>
+        <v>28.66277290864254</v>
       </c>
       <c r="CL34" t="n">
         <v>54.77901998933378</v>
@@ -12642,23 +12650,23 @@
         <v>49.54885792707731</v>
       </c>
       <c r="CN34" t="n">
-        <v>61.18051769334477</v>
+        <v>61.18051769617078</v>
       </c>
       <c r="CO34" t="n">
-        <v>36.65078487170795</v>
+        <v>36.65078487385424</v>
       </c>
       <c r="CP34" t="n">
-        <v>30.48333052017351</v>
+        <v>30.48333053652983</v>
       </c>
       <c r="CQ34" t="inlineStr"/>
       <c r="CR34" t="n">
-        <v>33.88605185096291</v>
+        <v>33.88605184304424</v>
       </c>
       <c r="CS34" t="n">
-        <v>32.65677890116262</v>
+        <v>32.65677889124839</v>
       </c>
       <c r="CT34" t="n">
-        <v>29.39110101104636</v>
+        <v>29.39110100212355</v>
       </c>
       <c r="CU34" t="n">
         <v>4</v>
@@ -12670,10 +12678,10 @@
         <v>3.5</v>
       </c>
       <c r="CX34" t="n">
-        <v>-0.5713750268859896</v>
+        <v>-0.5713750570713994</v>
       </c>
       <c r="CY34" t="n">
-        <v>14.63481888761464</v>
+        <v>14.63481886082618</v>
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
@@ -12980,16 +12988,16 @@
         <v>0.73</v>
       </c>
       <c r="CH35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI35" t="n">
         <v>10.69999980926514</v>
       </c>
       <c r="CJ35" t="n">
-        <v>13.32483352709585</v>
+        <v>13.32483354254606</v>
       </c>
       <c r="CK35" t="n">
-        <v>19.40095761545156</v>
+        <v>19.40095763794706</v>
       </c>
       <c r="CL35" t="n">
         <v>16.70870841086448</v>
@@ -13008,7 +13016,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR35" t="n">
-        <v>16.27033576537996</v>
+        <v>16.27033577170424</v>
       </c>
       <c r="CS35" t="n">
         <v>15.78776446356376</v>
@@ -13029,7 +13037,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY35" t="n">
-        <v>52.05921547112051</v>
+        <v>52.05921553022599</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -13352,10 +13360,10 @@
         <v>19.68000030517578</v>
       </c>
       <c r="CJ36" t="n">
-        <v>9.229871020670526</v>
+        <v>9.229870995971508</v>
       </c>
       <c r="CK36" t="n">
-        <v>17.12141074334382</v>
+        <v>17.12141069752715</v>
       </c>
       <c r="CL36" t="n">
         <v>17.05428411010982</v>
@@ -13364,7 +13372,7 @@
         <v>16.9233399690805</v>
       </c>
       <c r="CN36" t="n">
-        <v>26.98562450516146</v>
+        <v>26.98562448254627</v>
       </c>
       <c r="CO36" t="n">
         <v>19.94489718117502</v>
@@ -13376,7 +13384,7 @@
         <v>16.90195346323043</v>
       </c>
       <c r="CR36" t="n">
-        <v>17.40625692878056</v>
+        <v>17.4062569171392</v>
       </c>
       <c r="CS36" t="n">
         <v>16.98881203959516</v>
@@ -13397,7 +13405,7 @@
         <v>-22.30726321881998</v>
       </c>
       <c r="CY36" t="n">
-        <v>-11.55357388788879</v>
+        <v>-11.55357394704204</v>
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
@@ -14322,16 +14330,16 @@
         <v>0.61</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI2" t="n">
         <v>10.89999961853027</v>
       </c>
       <c r="CJ2" t="n">
-        <v>6.304016002878752</v>
+        <v>6.304015931491178</v>
       </c>
       <c r="CK2" t="n">
-        <v>11.69394968534009</v>
+        <v>11.69394955291613</v>
       </c>
       <c r="CL2" t="n">
         <v>41.26428427015031</v>
@@ -14340,7 +14348,7 @@
         <v>27.77577096127572</v>
       </c>
       <c r="CN2" t="n">
-        <v>71.93034809093047</v>
+        <v>71.93034780538017</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -14402,7 +14410,7 @@
         <v>1.421654006276185</v>
       </c>
       <c r="DL2" t="n">
-        <v>-22.46674000532078</v>
+        <v>-22.46674537978634</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -14678,10 +14686,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.84679448790572</v>
+        <v>14.84679441791949</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.54080377506511</v>
+        <v>27.54080364524066</v>
       </c>
       <c r="CL3" t="n">
         <v>38.77065228379291</v>
@@ -14690,13 +14698,13 @@
         <v>23.46088908480287</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.90049918950116</v>
+        <v>74.90049932001999</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789233750145</v>
+        <v>48.47789238916742</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.49458272838073</v>
+        <v>26.49458294430783</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.883220620076511</v>
@@ -15016,7 +15024,7 @@
         <v>-4.21</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CG4" t="n">
         <v>0.63</v>
@@ -15028,10 +15036,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247025670269</v>
+        <v>16.22247027568049</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268232618348</v>
+        <v>30.0926823613873</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -15040,19 +15048,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726943942</v>
+        <v>125.5537726880124</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311657662</v>
+        <v>25.70896311385998</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944664979132</v>
+        <v>61.89944660907558</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.17744912371742</v>
+        <v>47.17744912234599</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -15073,7 +15081,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479612101903</v>
+        <v>92.95479611540991</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -15386,10 +15394,10 @@
         <v>4.079999923706055</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.706970677717968</v>
+        <v>3.706970691086601</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.87643060716683</v>
+        <v>6.876430631965645</v>
       </c>
       <c r="CL5" t="n">
         <v>12.7199997621424</v>
@@ -15398,25 +15406,25 @@
         <v>8.569713954002083</v>
       </c>
       <c r="CN5" t="n">
-        <v>24.70099967519722</v>
+        <v>24.70099966623111</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21751809501781</v>
+        <v>11.21751808953736</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.41530415973325</v>
+        <v>10.41530412641649</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.322614371521537</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.186930158263985</v>
+        <v>9.186930155930918</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.492509056867668</v>
+        <v>9.492509040209285</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.543258151180902</v>
+        <v>8.543258136188356</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -15428,10 +15436,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.3935860523414</v>
+        <v>109.3935856848771</v>
       </c>
       <c r="CY5" t="n">
-        <v>125.1698610307587</v>
+        <v>125.1698609735757</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -15470,7 +15478,7 @@
         <v>-1.686751085608817</v>
       </c>
       <c r="DL5" t="n">
-        <v>-37.53577031186686</v>
+        <v>-37.53577507999217</v>
       </c>
       <c r="DM5" t="b">
         <v>1</v>
@@ -15746,10 +15754,10 @@
         <v>4.400000095367432</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.210667574853963</v>
+        <v>3.21066757318049</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.955788351354101</v>
+        <v>5.955788348249809</v>
       </c>
       <c r="CL6" t="n">
         <v>12.72925791782063</v>
@@ -15758,7 +15766,7 @@
         <v>8.553414722002886</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.22474835774388</v>
+        <v>24.22474835262846</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -15770,7 +15778,7 @@
         <v>5.312954959486701</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.42510806728737</v>
+        <v>11.42510806611312</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -15791,7 +15799,7 @@
         <v>136.7641763673805</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.6615413557915</v>
+        <v>159.6615413291041</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -15808,7 +15816,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="DC6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da Marcopolo (POMO4) revela uma empresa com excelente eficiência operacional, evidenciada por um ROE de 28,3% e um ROIC de 18,4%, ambos significativamente acima das médias do setor de bens industriais, que são de 14,5% e 12,6%, respectivamente. Essa alta qualidade de retorno convive com múltiplos de preço bastante atrativos, visto que o P/L de 4,58 e o P/VP de 1,3 sugerem que o papel está descontado frente à sua capacidade de geração de valor. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento controlado, com a relação Dívida Líquida/EBITDA em 1,29, patamar confortavelmente abaixo da média setorial de 2,39, o que confere solidez ao balanço. Essa estrutura de capital saudável e a forte lucratividade sustentam um expressivo Dividend Yield de 21,0%, o qual se mostra coerente com a robustez dos lucros recentes, embora o investidor deva monitorar a sustentabilidade desse fluxo no longo prazo. Por outro lado, o crescimento histórico acende um sinal de alerta, dado que o CAGR de receita dos últimos cinco anos contraiu 14,0%, ficando muito abaixo da média de expansão de 21,6% dos seus pares setoriais. Esse descompasso no crescimento e a existência de vendas por parte de insiders explicam por que a companhia atendeu a apenas 5 dos 8 critérios do checklist de qualidade, além de refletirem uma tendência gráfica atual de baixa. No que tange ao valuation, as estimativas de preço-teto apresentam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 3,21 por Bazin até os otimistas R$ 24,22 por Lynch, estabelecendo uma média de R$ 11,43 e um preço-teto ajustado com margem de segurança de R$ 10,42, o que projeta um expressivo potencial de valorização teórica de 136,8% sobre a cotação atual de R$ 4,40. Em suma, POMO4 destaca-se positivamente por seus indicadores de rentabilidade superiores, endividamento sob controle, múltiplos de valuation convidativos e proventos robustos, mas traz como contrapartidas o histórico recente de retração na receita e a falta de momentum gráfico de curto prazo.</t>
+        </is>
+      </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="b">
         <v>0</v>
@@ -16092,10 +16104,10 @@
         <v>49.08000183105469</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.70442476571499</v>
+        <v>18.70442477833754</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.6967079404013</v>
+        <v>34.69670796381614</v>
       </c>
       <c r="CL7" t="n">
         <v>75.52961954256382</v>
@@ -16104,23 +16116,23 @@
         <v>56.52767725678649</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.8003932206363</v>
+        <v>100.8003932007989</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.84536141761207</v>
+        <v>47.84536141459667</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.47113929721691</v>
+        <v>59.4711392718466</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.19402841657305</v>
+        <v>44.19402842482855</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.27103467900669</v>
+        <v>41.2710346892064</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.14393121110602</v>
+        <v>37.14393122028576</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -16132,10 +16144,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.3196213827284</v>
+        <v>-24.31962136402477</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.955120684999875</v>
+        <v>-9.955120668179374</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -16674,10 +16686,10 @@
         <v>15.73999977111816</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.416394726867549</v>
+        <v>6.416394730624279</v>
       </c>
       <c r="CK9" t="n">
-        <v>11.9024122183393</v>
+        <v>11.90241222530804</v>
       </c>
       <c r="CL9" t="n">
         <v>25.40255748688375</v>
@@ -16686,19 +16698,19 @@
         <v>18.61214239569414</v>
       </c>
       <c r="CN9" t="n">
-        <v>35.20098332860089</v>
+        <v>35.20098332248433</v>
       </c>
       <c r="CO9" t="n">
-        <v>12.29650749169001</v>
+        <v>12.29650749097704</v>
       </c>
       <c r="CP9" t="n">
-        <v>20.37042634952579</v>
+        <v>20.37042634165439</v>
       </c>
       <c r="CQ9" t="n">
         <v>18.47023285957259</v>
       </c>
       <c r="CR9" t="n">
-        <v>20.3221803043295</v>
+        <v>20.3221803032249</v>
       </c>
       <c r="CS9" t="n">
         <v>18.61214239569414</v>
@@ -16719,7 +16731,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY9" t="n">
-        <v>29.11169377282539</v>
+        <v>29.1116937658076</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -17044,10 +17056,10 @@
         <v>45.02000045776367</v>
       </c>
       <c r="CJ10" t="n">
-        <v>131.8923109101077</v>
+        <v>131.8923100198635</v>
       </c>
       <c r="CK10" t="n">
-        <v>244.6602367382497</v>
+        <v>244.6602350868468</v>
       </c>
       <c r="CL10" t="n">
         <v>137.1298864518089</v>
@@ -17068,13 +17080,13 @@
         <v>55.34098571876934</v>
       </c>
       <c r="CR10" t="n">
-        <v>144.1214557430111</v>
+        <v>144.1214554253053</v>
       </c>
       <c r="CS10" t="n">
-        <v>128.5601790802194</v>
+        <v>128.5601786350973</v>
       </c>
       <c r="CT10" t="n">
-        <v>115.7041611721975</v>
+        <v>115.7041607715876</v>
       </c>
       <c r="CU10" t="n">
         <v>8</v>
@@ -17086,10 +17098,10 @@
         <v>5.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>157.0061305991043</v>
+        <v>157.0061297092557</v>
       </c>
       <c r="CY10" t="n">
-        <v>220.1276194526503</v>
+        <v>220.127618746951</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -17404,10 +17416,10 @@
         <v>32.72999954223633</v>
       </c>
       <c r="CJ11" t="n">
-        <v>45.70703783561292</v>
+        <v>45.70703776739576</v>
       </c>
       <c r="CK11" t="n">
-        <v>84.78655518506196</v>
+        <v>84.78655505851914</v>
       </c>
       <c r="CL11" t="n">
         <v>68.18749904632567</v>
@@ -17428,7 +17440,7 @@
         <v>25.65248645136637</v>
       </c>
       <c r="CR11" t="n">
-        <v>77.50815036943183</v>
+        <v>77.50815034160897</v>
       </c>
       <c r="CS11" t="n">
         <v>68.18749904632567</v>
@@ -17449,7 +17461,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY11" t="n">
-        <v>136.8107285470984</v>
+        <v>136.8107284620912</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -17760,7 +17772,7 @@
         <v>-1.81</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CG12" t="n">
         <v>0.57</v>
@@ -17772,37 +17784,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ12" t="n">
-        <v>24.21612678734386</v>
+        <v>24.21612667620782</v>
       </c>
       <c r="CK12" t="n">
-        <v>32.67790149621491</v>
+        <v>32.67790232091849</v>
       </c>
       <c r="CL12" t="n">
-        <v>34.37896721817167</v>
+        <v>34.37896824358241</v>
       </c>
       <c r="CM12" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN12" t="n">
-        <v>48.8073900732228</v>
+        <v>48.80739093580195</v>
       </c>
       <c r="CO12" t="n">
-        <v>50.94836373183931</v>
+        <v>50.9483638746774</v>
       </c>
       <c r="CP12" t="n">
-        <v>16.89191248125056</v>
+        <v>16.89191313044504</v>
       </c>
       <c r="CQ12" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR12" t="n">
-        <v>31.61206944099688</v>
+        <v>31.61206986519563</v>
       </c>
       <c r="CS12" t="n">
-        <v>28.44701414177938</v>
+        <v>28.44701449856316</v>
       </c>
       <c r="CT12" t="n">
-        <v>25.60231272760145</v>
+        <v>25.60231304870684</v>
       </c>
       <c r="CU12" t="n">
         <v>8</v>
@@ -17814,10 +17826,10 @@
         <v>3</v>
       </c>
       <c r="CX12" t="n">
-        <v>-21.46529470568728</v>
+        <v>-21.46529372070136</v>
       </c>
       <c r="CY12" t="n">
-        <v>-3.030457298666644</v>
+        <v>-3.030455997443415</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -18132,10 +18144,10 @@
         <v>7.03000020980835</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.606648461636001</v>
+        <v>6.606648484422949</v>
       </c>
       <c r="CK13" t="n">
-        <v>12.25533289633478</v>
+        <v>12.25533293860457</v>
       </c>
       <c r="CL13" t="n">
         <v>40.49891425215679</v>
@@ -18144,7 +18156,7 @@
         <v>27.27256595484038</v>
       </c>
       <c r="CN13" t="n">
-        <v>86.06220939566491</v>
+        <v>86.06220953436805</v>
       </c>
       <c r="CO13" t="n">
         <v>51.88018214566937</v>
@@ -18482,16 +18494,16 @@
         <v>0.23</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="CI14" t="n">
         <v>50.29000091552734</v>
       </c>
       <c r="CJ14" t="n">
-        <v>139.5836066576344</v>
+        <v>139.5836077150498</v>
       </c>
       <c r="CK14" t="n">
-        <v>258.9275903499119</v>
+        <v>258.9275923114173</v>
       </c>
       <c r="CL14" t="n">
         <v>137.1075127841023</v>
@@ -18512,7 +18524,7 @@
         <v>54.15143544791205</v>
       </c>
       <c r="CR14" t="n">
-        <v>146.7120320536963</v>
+        <v>146.7120324310614</v>
       </c>
       <c r="CS14" t="n">
         <v>131.157564116113</v>
@@ -18533,7 +18545,7 @@
         <v>134.7222222222222</v>
       </c>
       <c r="CY14" t="n">
-        <v>191.7320130896996</v>
+        <v>191.7320138400776</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -18834,7 +18846,7 @@
         <v>-10.01</v>
       </c>
       <c r="CF15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CG15" t="n">
         <v>0.52</v>
@@ -18846,10 +18858,10 @@
         <v>14.0600004196167</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.2071018349132357</v>
+        <v>0.2071018349370626</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.3015402716336712</v>
+        <v>0.3015402716683631</v>
       </c>
       <c r="CL15" t="n">
         <v>75.76373283109515</v>
@@ -19176,10 +19188,10 @@
         <v>19.34000015258789</v>
       </c>
       <c r="CJ16" t="n">
-        <v>13.29214280561541</v>
+        <v>13.29214273283289</v>
       </c>
       <c r="CK16" t="n">
-        <v>24.65692490441659</v>
+        <v>24.65692476940502</v>
       </c>
       <c r="CL16" t="n">
         <v>19.97311005625795</v>
@@ -19188,7 +19200,7 @@
         <v>12.48226378298752</v>
       </c>
       <c r="CN16" t="n">
-        <v>33.79906478813256</v>
+        <v>33.79906470871283</v>
       </c>
       <c r="CO16" t="n">
         <v>22.8984489302328</v>
@@ -19198,7 +19210,7 @@
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
-        <v>20.20515667413068</v>
+        <v>20.20515662218217</v>
       </c>
       <c r="CS16" t="n">
         <v>21.43577949324537</v>
@@ -19219,7 +19231,7 @@
         <v>-0.2471489570317398</v>
       </c>
       <c r="CY16" t="n">
-        <v>4.473404936488734</v>
+        <v>4.473404667882108</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -19236,7 +19248,11 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="DC16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr">
+        <is>
+          <t>A Caixa Seguridade (CXSE3) apresenta-se como uma alternativa robusta no setor de seguros, destacando-se por uma margem líquida expressiva de 75,43% e um crescimento de receita nos últimos cinco anos de 12,8% ao ano, patamar que supera com folga a média negativa de 2,5% de seus pares setoriais. No entanto, essa expansão de receita contrasta com indicadores de eficiência que demandam atenção, uma vez que o ROE de 32,8% e o ROIC de -1,2% situam-se abaixo das médias do setor, de 34,3% e 19,5%, respectivamente, sugerindo que a companhia ainda precisa otimizar a rentabilidade sobre o capital investido frente aos concorrentes. Sob a ótica de preço e qualidade, o papel negocia a múltiplos elevados, com um P/L de 12,83 e um P/VP de 4,21, indicando que o mercado cobra um prêmio considerável por essa operação altamente rentável, embora o PEG ratio em 1,0 sinalize um valuation justo em relação ao crescimento projetado. O retorno em dividendos de 6,99% mostra-se atraente e sustentável, sendo plenamente suportado pela alta geração de caixa e pela ausência de alavancagem financeira preocupante, o que é corroborado pela nota máxima de segurança atribuída à empresa. No checklist de critérios fundamentalistas, a companhia atende a quatro dos seis requisitos avaliados, penalizada justamente por não superar os pares em ROE e ROIC, mas validada pelo porte robusto e pela governança, sem registro de venda de ações por controladores. Quanto ao valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 12,48 por Graham e R$ 13,29 por Bazin até os otimistas R$ 24,66 por Gordon e R$ 33,80 por Lynch. Com uma média de preço-teto de R$ 20,21 e uma mediana de R$ 21,44, o preço-teto ajustado com margem de segurança fica em R$ 19,29, o que coloca a cotação atual de R$ 19,34 em patamar de estabilidade, com um upside ligeiramente negativo de 0,2% em relação a essa métrica ajustada. Em balanço, os prós residem na excelente margem líquida, no forte crescimento histórico de receita frente ao setor e na alta segurança financeira com dividendos consistentes, enquanto os contras ficam por conta da rentabilidade abaixo da média dos pares, dos múltiplos de valuation esticados e de uma tendência gráfica de baixa no curto prazo.</t>
+        </is>
+      </c>
       <c r="DD16" t="inlineStr"/>
       <c r="DE16" t="b">
         <v>1</v>
@@ -19524,10 +19540,10 @@
         <v>14.06999969482422</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.21505899891874</v>
+        <v>10.21505900257557</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.94893444299426</v>
+        <v>18.94893444977768</v>
       </c>
       <c r="CL17" t="n">
         <v>49.58178083947364</v>
@@ -19536,23 +19552,23 @@
         <v>48.67505180787087</v>
       </c>
       <c r="CN17" t="n">
-        <v>68.69075967074541</v>
+        <v>68.69075967757273</v>
       </c>
       <c r="CO17" t="n">
-        <v>33.90958135398201</v>
+        <v>33.90958135341343</v>
       </c>
       <c r="CP17" t="n">
-        <v>29.26600638117898</v>
+        <v>29.2660063769119</v>
       </c>
       <c r="CQ17" t="inlineStr"/>
       <c r="CR17" t="n">
-        <v>34.14676554548331</v>
+        <v>34.14676554755491</v>
       </c>
       <c r="CS17" t="n">
-        <v>33.90958135398201</v>
+        <v>33.90958135341343</v>
       </c>
       <c r="CT17" t="n">
-        <v>30.51862321858381</v>
+        <v>30.51862321807209</v>
       </c>
       <c r="CU17" t="n">
         <v>3</v>
@@ -19564,10 +19580,10 @@
         <v>4.9</v>
       </c>
       <c r="CX17" t="n">
-        <v>116.9056423633781</v>
+        <v>116.9056423597411</v>
       </c>
       <c r="CY17" t="n">
-        <v>142.6920134052633</v>
+        <v>142.6920134199869</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -19866,10 +19882,10 @@
         <v>-55.81</v>
       </c>
       <c r="CF18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="CH18" t="n">
         <v>0.07000000000000001</v>
@@ -19878,10 +19894,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.228277651320188</v>
+        <v>3.228277654826922</v>
       </c>
       <c r="CK18" t="n">
-        <v>5.988455043198949</v>
+        <v>5.988455049703941</v>
       </c>
       <c r="CL18" t="n">
         <v>19.81956093381139</v>
@@ -19890,7 +19906,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN18" t="n">
-        <v>31.89244530313685</v>
+        <v>31.89244531340761</v>
       </c>
       <c r="CO18" t="n">
         <v>10.95072400487419</v>
@@ -20222,16 +20238,16 @@
         <v>0.5</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI19" t="n">
         <v>16.75</v>
       </c>
       <c r="CJ19" t="n">
-        <v>10.26720875607003</v>
+        <v>10.26720872277248</v>
       </c>
       <c r="CK19" t="n">
-        <v>19.04567224250991</v>
+        <v>19.04567218074295</v>
       </c>
       <c r="CL19" t="n">
         <v>37.48944256756756</v>
@@ -20240,25 +20256,25 @@
         <v>36.97412590213069</v>
       </c>
       <c r="CN19" t="n">
-        <v>42.62689278589763</v>
+        <v>42.62689276859406</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.59941685514998</v>
+        <v>34.59941686220576</v>
       </c>
       <c r="CP19" t="n">
-        <v>19.0904981639273</v>
+        <v>19.09049820254713</v>
       </c>
       <c r="CQ19" t="n">
         <v>32.11454047621128</v>
       </c>
       <c r="CR19" t="n">
-        <v>31.70579842762777</v>
+        <v>31.70579842285707</v>
       </c>
       <c r="CS19" t="n">
-        <v>34.59941685514998</v>
+        <v>34.59941686220576</v>
       </c>
       <c r="CT19" t="n">
-        <v>31.13947516963498</v>
+        <v>31.13947517598519</v>
       </c>
       <c r="CU19" t="n">
         <v>7</v>
@@ -20270,10 +20286,10 @@
         <v>4.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>85.90731444558195</v>
+        <v>85.90731448349366</v>
       </c>
       <c r="CY19" t="n">
-        <v>89.2883488216583</v>
+        <v>89.28834879317652</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -20312,7 +20328,7 @@
         <v>-4.449518859629698</v>
       </c>
       <c r="DL19" t="n">
-        <v>-26.63753022143262</v>
+        <v>-26.63753640577318</v>
       </c>
       <c r="DM19" t="b">
         <v>1</v>
@@ -20582,43 +20598,43 @@
         <v>0.5</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="CI20" t="n">
         <v>34.11000061035156</v>
       </c>
       <c r="CJ20" t="n">
-        <v>24.52443755055584</v>
+        <v>24.52443740492133</v>
       </c>
       <c r="CK20" t="n">
-        <v>31.40162277937119</v>
+        <v>31.40162301240151</v>
       </c>
       <c r="CL20" t="n">
-        <v>35.21056596633962</v>
+        <v>35.21056643672837</v>
       </c>
       <c r="CM20" t="n">
         <v>36.15779229888242</v>
       </c>
       <c r="CN20" t="n">
-        <v>49.3926378187119</v>
+        <v>49.39263810952428</v>
       </c>
       <c r="CO20" t="n">
-        <v>48.65929057477212</v>
+        <v>48.65929063884296</v>
       </c>
       <c r="CP20" t="n">
-        <v>16.97314174498548</v>
+        <v>16.9731420724301</v>
       </c>
       <c r="CQ20" t="n">
         <v>30.64026112103792</v>
       </c>
       <c r="CR20" t="n">
-        <v>34.11996873183206</v>
+        <v>34.11996888684611</v>
       </c>
       <c r="CS20" t="n">
-        <v>33.30609437285541</v>
+        <v>33.30609472456494</v>
       </c>
       <c r="CT20" t="n">
-        <v>29.97548493556987</v>
+        <v>29.97548525210845</v>
       </c>
       <c r="CU20" t="n">
         <v>8</v>
@@ -20630,10 +20646,10 @@
         <v>2.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>-12.12112459923841</v>
+        <v>-12.12112367124493</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.02922345735014709</v>
+        <v>0.02922391180351092</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -20948,37 +20964,37 @@
         <v>10.10000038146973</v>
       </c>
       <c r="CJ21" t="n">
-        <v>10.12472061232733</v>
+        <v>10.12472075949684</v>
       </c>
       <c r="CK21" t="n">
-        <v>18.25250304374272</v>
+        <v>18.2525026437782</v>
       </c>
       <c r="CL21" t="n">
-        <v>23.77636230045178</v>
+        <v>23.77636143383859</v>
       </c>
       <c r="CM21" t="n">
         <v>17.56505572352211</v>
       </c>
       <c r="CN21" t="n">
-        <v>36.59482139902451</v>
+        <v>36.59482126265946</v>
       </c>
       <c r="CO21" t="n">
-        <v>24.18348115246688</v>
+        <v>24.18348108894751</v>
       </c>
       <c r="CP21" t="n">
-        <v>11.6466800429836</v>
+        <v>11.64667972050579</v>
       </c>
       <c r="CQ21" t="n">
         <v>10.10000038146973</v>
       </c>
       <c r="CR21" t="n">
-        <v>19.03045308199858</v>
+        <v>19.03045287677728</v>
       </c>
       <c r="CS21" t="n">
-        <v>17.90877938363242</v>
+        <v>17.90877918365016</v>
       </c>
       <c r="CT21" t="n">
-        <v>16.11790144526918</v>
+        <v>16.11790126528514</v>
       </c>
       <c r="CU21" t="n">
         <v>8</v>
@@ -20990,10 +21006,10 @@
         <v>3.6</v>
       </c>
       <c r="CX21" t="n">
-        <v>59.58317659908583</v>
+        <v>59.58317481706574</v>
       </c>
       <c r="CY21" t="n">
-        <v>88.42032042804063</v>
+        <v>88.4203183961466</v>
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
@@ -21310,10 +21326,10 @@
         <v>3.480000019073486</v>
       </c>
       <c r="CJ22" t="n">
-        <v>5.030893696247742</v>
+        <v>5.030893695956821</v>
       </c>
       <c r="CK22" t="n">
-        <v>9.332307806539561</v>
+        <v>9.332307805999902</v>
       </c>
       <c r="CL22" t="n">
         <v>8.507380120428724</v>
@@ -21656,10 +21672,10 @@
         <v>10.89999961853027</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.401043863156887</v>
+        <v>3.401043865263513</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.308936366156026</v>
+        <v>6.308936370063815</v>
       </c>
       <c r="CL23" t="n">
         <v>19.64965917626206</v>
@@ -21668,13 +21684,13 @@
         <v>18.52341853243414</v>
       </c>
       <c r="CN23" t="n">
-        <v>20.98684412233365</v>
+        <v>20.98684412209636</v>
       </c>
       <c r="CO23" t="n">
-        <v>15.92132131658388</v>
+        <v>15.92132131616827</v>
       </c>
       <c r="CP23" t="n">
-        <v>13.08144275631335</v>
+        <v>13.08144275364198</v>
       </c>
       <c r="CQ23" t="n">
         <v>29.64794112808246</v>
@@ -22000,16 +22016,16 @@
         <v>0.64</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI24" t="n">
         <v>11.11999988555908</v>
       </c>
       <c r="CJ24" t="n">
-        <v>9.626932739675171</v>
+        <v>9.626932757951991</v>
       </c>
       <c r="CK24" t="n">
-        <v>17.85796023209744</v>
+        <v>17.85796026600094</v>
       </c>
       <c r="CL24" t="n">
         <v>21.79585776385471</v>
@@ -22018,25 +22034,25 @@
         <v>12.85650787905083</v>
       </c>
       <c r="CN24" t="n">
-        <v>30.86844381649707</v>
+        <v>30.86844376023747</v>
       </c>
       <c r="CO24" t="n">
-        <v>25.2091716004863</v>
+        <v>25.20917158696246</v>
       </c>
       <c r="CP24" t="n">
-        <v>11.26534095464609</v>
+        <v>11.26534089549061</v>
       </c>
       <c r="CQ24" t="n">
         <v>9.553111101546266</v>
       </c>
       <c r="CR24" t="n">
-        <v>17.37916576098173</v>
+        <v>17.37916575138691</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.35723405557414</v>
+        <v>15.35723407252589</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.82151065001672</v>
+        <v>13.8215106652733</v>
       </c>
       <c r="CU24" t="n">
         <v>8</v>
@@ -22048,10 +22064,10 @@
         <v>3.2</v>
       </c>
       <c r="CX24" t="n">
-        <v>24.29416180090021</v>
+        <v>24.29416193809966</v>
       </c>
       <c r="CY24" t="n">
-        <v>56.28746348775668</v>
+        <v>56.28746340147226</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -22362,7 +22378,7 @@
         <v>20.79</v>
       </c>
       <c r="CF25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="CG25" t="n">
         <v>0.48</v>
@@ -22374,10 +22390,10 @@
         <v>14.93000030517578</v>
       </c>
       <c r="CJ25" t="n">
-        <v>4.584303483469895</v>
+        <v>4.584303505989314</v>
       </c>
       <c r="CK25" t="n">
-        <v>8.503882961836654</v>
+        <v>8.503883003610175</v>
       </c>
       <c r="CL25" t="n">
         <v>24.12469561507062</v>
@@ -22386,25 +22402,25 @@
         <v>20.32887248745251</v>
       </c>
       <c r="CN25" t="n">
-        <v>29.1301112771648</v>
+        <v>29.13011125864297</v>
       </c>
       <c r="CO25" t="n">
-        <v>16.68549306818212</v>
+        <v>16.68549306350819</v>
       </c>
       <c r="CP25" t="n">
-        <v>18.2545701394625</v>
+        <v>18.25457010365303</v>
       </c>
       <c r="CQ25" t="n">
         <v>14.67122720766037</v>
       </c>
       <c r="CR25" t="n">
-        <v>18.81412182240422</v>
+        <v>18.81412181994255</v>
       </c>
       <c r="CS25" t="n">
-        <v>18.2545701394625</v>
+        <v>18.25457010365303</v>
       </c>
       <c r="CT25" t="n">
-        <v>16.42911312551625</v>
+        <v>16.42911309328773</v>
       </c>
       <c r="CU25" t="n">
         <v>7</v>
@@ -22416,10 +22432,10 @@
         <v>6.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>10.04094299864666</v>
+        <v>10.04094278278245</v>
       </c>
       <c r="CY25" t="n">
-        <v>26.01554881336428</v>
+        <v>26.0155487968762</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -22719,7 +22735,7 @@
         <v>1.73</v>
       </c>
       <c r="CG26" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="CH26" t="n">
         <v>0.14</v>
@@ -22728,10 +22744,10 @@
         <v>8.319999694824219</v>
       </c>
       <c r="CJ26" t="n">
-        <v>3.85506591507539</v>
+        <v>3.855065919296114</v>
       </c>
       <c r="CK26" t="n">
-        <v>7.151147272464849</v>
+        <v>7.151147280294292</v>
       </c>
       <c r="CL26" t="n">
         <v>24.17543770974142</v>
@@ -22740,13 +22756,13 @@
         <v>22.57848234922987</v>
       </c>
       <c r="CN26" t="n">
-        <v>30.83869137096105</v>
+        <v>30.83869137517999</v>
       </c>
       <c r="CO26" t="n">
-        <v>9.584029438707407</v>
+        <v>9.584029438291648</v>
       </c>
       <c r="CP26" t="n">
-        <v>16.81890468645149</v>
+        <v>16.81890468095813</v>
       </c>
       <c r="CQ26" t="n">
         <v>194.255108804104</v>
@@ -23076,16 +23092,16 @@
         <v>0.45</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI27" t="n">
         <v>14.98999977111816</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.402707639752828</v>
+        <v>9.402707653754039</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.4420226717415</v>
+        <v>17.44202269771374</v>
       </c>
       <c r="CL27" t="n">
         <v>13.59462676025432</v>
@@ -23106,7 +23122,7 @@
         <v>6.241030818750382</v>
       </c>
       <c r="CR27" t="n">
-        <v>11.49757743736391</v>
+        <v>11.4975774430744</v>
       </c>
       <c r="CS27" t="n">
         <v>11.05794841262742</v>
@@ -23127,7 +23143,7 @@
         <v>-33.60804720931423</v>
       </c>
       <c r="CY27" t="n">
-        <v>-23.29834814596358</v>
+        <v>-23.29834810786823</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -23438,10 +23454,10 @@
         <v>27.92000007629395</v>
       </c>
       <c r="CJ28" t="n">
-        <v>7.398493210606342</v>
+        <v>7.398493237326353</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.72420490567476</v>
+        <v>13.72420495524038</v>
       </c>
       <c r="CL28" t="n">
         <v>35.77756296043469</v>
@@ -23450,19 +23466,19 @@
         <v>28.28645183714482</v>
       </c>
       <c r="CN28" t="n">
-        <v>44.17088012759143</v>
+        <v>44.17088008700814</v>
       </c>
       <c r="CO28" t="n">
-        <v>26.42837008433418</v>
+        <v>26.4283700776647</v>
       </c>
       <c r="CP28" t="n">
-        <v>28.68133713647756</v>
+        <v>28.68133708822763</v>
       </c>
       <c r="CQ28" t="n">
         <v>24.48161704504879</v>
       </c>
       <c r="CR28" t="n">
-        <v>28.79291772810089</v>
+        <v>28.79291772153845</v>
       </c>
       <c r="CS28" t="n">
         <v>28.28645183714482</v>
@@ -23483,7 +23499,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY28" t="n">
-        <v>3.126495879017255</v>
+        <v>3.126495855512812</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -23806,10 +23822,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ29" t="n">
-        <v>3.140372322485803</v>
+        <v>3.140372325224375</v>
       </c>
       <c r="CK29" t="n">
-        <v>5.825390658211164</v>
+        <v>5.825390663291215</v>
       </c>
       <c r="CL29" t="n">
         <v>32.87416582383663</v>
@@ -23818,7 +23834,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN29" t="n">
-        <v>42.11194017978662</v>
+        <v>42.1119401840561</v>
       </c>
       <c r="CO29" t="n">
         <v>10.85340539909456</v>
@@ -24136,10 +24152,10 @@
         <v>40.40000152587891</v>
       </c>
       <c r="CJ30" t="n">
-        <v>36.97443496570012</v>
+        <v>36.97443491714012</v>
       </c>
       <c r="CK30" t="n">
-        <v>53.83477731005938</v>
+        <v>53.83477723935603</v>
       </c>
       <c r="CL30" t="n">
         <v>49.19906509006331</v>
@@ -24156,13 +24172,13 @@
       </c>
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="n">
-        <v>49.87811058741013</v>
+        <v>49.8781105575943</v>
       </c>
       <c r="CS30" t="n">
-        <v>51.51692120006135</v>
+        <v>51.51692116470967</v>
       </c>
       <c r="CT30" t="n">
-        <v>46.36522908005522</v>
+        <v>46.3652290482387</v>
       </c>
       <c r="CU30" t="n">
         <v>4</v>
@@ -24174,10 +24190,10 @@
         <v>1.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>14.76541418038111</v>
+        <v>14.76541410162737</v>
       </c>
       <c r="CY30" t="n">
-        <v>23.46066510779676</v>
+        <v>23.46066503399518</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -24486,16 +24502,16 @@
         <v>0.66</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="CI31" t="n">
         <v>24.29000091552734</v>
       </c>
       <c r="CJ31" t="n">
-        <v>12.60225152959778</v>
+        <v>12.60225154395436</v>
       </c>
       <c r="CK31" t="n">
-        <v>23.37717658740388</v>
+        <v>23.37717661403533</v>
       </c>
       <c r="CL31" t="n">
         <v>59.60046520939579</v>
@@ -24504,13 +24520,13 @@
         <v>49.8315404763603</v>
       </c>
       <c r="CN31" t="n">
-        <v>82.59229643638405</v>
+        <v>82.59229643690364</v>
       </c>
       <c r="CO31" t="n">
-        <v>33.6321343420497</v>
+        <v>33.63213433957971</v>
       </c>
       <c r="CP31" t="n">
-        <v>43.39463720173607</v>
+        <v>43.39463717866676</v>
       </c>
       <c r="CQ31" t="n">
         <v>5.427737394613911</v>
@@ -24828,35 +24844,35 @@
         <v>23.10000038146973</v>
       </c>
       <c r="CJ32" t="n">
-        <v>16.58129224999697</v>
+        <v>16.58129223034594</v>
       </c>
       <c r="CK32" t="n">
-        <v>29.63834601132087</v>
+        <v>29.63834601430074</v>
       </c>
       <c r="CL32" t="n">
-        <v>49.98820356173672</v>
+        <v>49.98820362600524</v>
       </c>
       <c r="CM32" t="n">
         <v>49.51516084050021</v>
       </c>
       <c r="CN32" t="n">
-        <v>61.73936032385041</v>
+        <v>61.73936031587442</v>
       </c>
       <c r="CO32" t="n">
-        <v>45.75562700840633</v>
+        <v>45.75562701267919</v>
       </c>
       <c r="CP32" t="n">
-        <v>24.53550117532268</v>
+        <v>24.53550119961923</v>
       </c>
       <c r="CQ32" t="inlineStr"/>
       <c r="CR32" t="n">
-        <v>35.49086720786522</v>
+        <v>35.49086722083278</v>
       </c>
       <c r="CS32" t="n">
-        <v>37.6969865098636</v>
+        <v>37.69698651348997</v>
       </c>
       <c r="CT32" t="n">
-        <v>33.92728785887724</v>
+        <v>33.92728786214097</v>
       </c>
       <c r="CU32" t="n">
         <v>4</v>
@@ -24868,10 +24884,10 @@
         <v>3</v>
       </c>
       <c r="CX32" t="n">
-        <v>46.8713735870451</v>
+        <v>46.87137360117379</v>
       </c>
       <c r="CY32" t="n">
-        <v>53.6401152457779</v>
+        <v>53.64011530191451</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -25182,10 +25198,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="CJ33" t="n">
-        <v>2.170533819521158</v>
+        <v>2.170533820619541</v>
       </c>
       <c r="CK33" t="n">
-        <v>4.026340235211748</v>
+        <v>4.026340237249249</v>
       </c>
       <c r="CL33" t="n">
         <v>27.97222213713006</v>
@@ -25194,7 +25210,7 @@
         <v>23.70514625235032</v>
       </c>
       <c r="CN33" t="n">
-        <v>36.78240284530162</v>
+        <v>36.7824028478904</v>
       </c>
       <c r="CO33" t="n">
         <v>9.158754146</v>
@@ -25516,7 +25532,7 @@
         <v>34.79</v>
       </c>
       <c r="CF34" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CG34" t="n">
         <v>0.5600000000000001</v>
@@ -25528,10 +25544,10 @@
         <v>33.09999847412109</v>
       </c>
       <c r="CJ34" t="n">
-        <v>7.849255785735923</v>
+        <v>7.849255834741833</v>
       </c>
       <c r="CK34" t="n">
-        <v>14.56036948254014</v>
+        <v>14.5603695734461</v>
       </c>
       <c r="CL34" t="n">
         <v>62.56419112440863</v>
@@ -25540,7 +25556,7 @@
         <v>36.49709183960014</v>
       </c>
       <c r="CN34" t="n">
-        <v>86.50350329702131</v>
+        <v>86.50350339489331</v>
       </c>
       <c r="CO34" t="n">
         <v>22.51480113099953</v>
@@ -25874,10 +25890,10 @@
         <v>33.52000045776367</v>
       </c>
       <c r="CJ35" t="n">
-        <v>15.19075447959736</v>
+        <v>15.19075451688022</v>
       </c>
       <c r="CK35" t="n">
-        <v>28.17884955965311</v>
+        <v>28.1788496288128</v>
       </c>
       <c r="CL35" t="n">
         <v>19.96134858720758</v>
@@ -25886,7 +25902,7 @@
         <v>36.77821304906529</v>
       </c>
       <c r="CN35" t="n">
-        <v>26.88317159454586</v>
+        <v>26.88317161800473</v>
       </c>
       <c r="CO35" t="n">
         <v>15.03391666666667</v>
@@ -25898,7 +25914,7 @@
         <v>79.01640001964445</v>
       </c>
       <c r="CR35" t="n">
-        <v>22.42011014204965</v>
+        <v>22.420110160607</v>
       </c>
       <c r="CS35" t="n">
         <v>19.96134858720758</v>
@@ -25919,7 +25935,7 @@
         <v>-46.40449438202248</v>
       </c>
       <c r="CY35" t="n">
-        <v>-33.11423079990782</v>
+        <v>-33.1142307445458</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -26229,7 +26245,7 @@
         <v>0.97</v>
       </c>
       <c r="CG36" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="CH36" t="n">
         <v>-0.03</v>
@@ -26238,10 +26254,10 @@
         <v>35.45000076293945</v>
       </c>
       <c r="CJ36" t="n">
-        <v>3.517189250169004</v>
+        <v>3.51718926427456</v>
       </c>
       <c r="CK36" t="n">
-        <v>6.524386059063503</v>
+        <v>6.524386085229309</v>
       </c>
       <c r="CL36" t="n">
         <v>32.59628800200886</v>
@@ -26250,7 +26266,7 @@
         <v>22.8444967389438</v>
       </c>
       <c r="CN36" t="n">
-        <v>40.31857466665218</v>
+        <v>40.3185746803564</v>
       </c>
       <c r="CO36" t="n">
         <v>10.59424454785779</v>
@@ -26568,35 +26584,35 @@
         <v>13.10000038146973</v>
       </c>
       <c r="CJ37" t="n">
-        <v>8.795131836023424</v>
+        <v>8.795131856249405</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.7630574982212</v>
+        <v>13.76305747564655</v>
       </c>
       <c r="CL37" t="n">
-        <v>18.09953100113439</v>
+        <v>18.09953092982379</v>
       </c>
       <c r="CM37" t="n">
         <v>17.43566356412971</v>
       </c>
       <c r="CN37" t="n">
-        <v>22.73124860113306</v>
+        <v>22.73124858131427</v>
       </c>
       <c r="CO37" t="n">
-        <v>17.30064101555901</v>
+        <v>17.30064100996155</v>
       </c>
       <c r="CP37" t="n">
-        <v>9.046996490206137</v>
+        <v>9.046996455747541</v>
       </c>
       <c r="CQ37" t="inlineStr"/>
       <c r="CR37" t="n">
-        <v>14.4895903377345</v>
+        <v>14.48959031792032</v>
       </c>
       <c r="CS37" t="n">
-        <v>15.5318492568901</v>
+        <v>15.53184924280405</v>
       </c>
       <c r="CT37" t="n">
-        <v>13.9786643312011</v>
+        <v>13.97866431852364</v>
       </c>
       <c r="CU37" t="n">
         <v>4</v>
@@ -26608,10 +26624,10 @@
         <v>2.1</v>
       </c>
       <c r="CX37" t="n">
-        <v>6.707358199578839</v>
+        <v>6.707358102804406</v>
       </c>
       <c r="CY37" t="n">
-        <v>10.60755660916153</v>
+        <v>10.60755645790825</v>
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
@@ -26928,16 +26944,16 @@
         <v>0.47</v>
       </c>
       <c r="CH38" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CI38" t="n">
         <v>5.920000076293945</v>
       </c>
       <c r="CJ38" t="n">
-        <v>7.021620230160911</v>
+        <v>7.021620180788066</v>
       </c>
       <c r="CK38" t="n">
-        <v>13.02510552694849</v>
+        <v>13.02510543536186</v>
       </c>
       <c r="CL38" t="n">
         <v>5.692307765667254</v>
@@ -26958,7 +26974,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR38" t="n">
-        <v>7.373583640576677</v>
+        <v>7.373583622956744</v>
       </c>
       <c r="CS38" t="n">
         <v>5.912820549500294</v>
@@ -26979,7 +26995,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY38" t="n">
-        <v>24.55377610725824</v>
+        <v>24.55377580962423</v>
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
@@ -27276,10 +27292,10 @@
         <v>39.52000045776367</v>
       </c>
       <c r="CJ39" t="n">
-        <v>20.20396467909244</v>
+        <v>20.20396449452465</v>
       </c>
       <c r="CK39" t="n">
-        <v>37.47835447971648</v>
+        <v>37.47835413734322</v>
       </c>
       <c r="CL39" t="n">
         <v>56.00427872356884</v>
@@ -27288,23 +27304,23 @@
         <v>42.30510206840214</v>
       </c>
       <c r="CN39" t="n">
-        <v>61.64113321511925</v>
+        <v>61.64113351885764</v>
       </c>
       <c r="CO39" t="n">
-        <v>45.15513209307895</v>
+        <v>45.15513215076771</v>
       </c>
       <c r="CP39" t="n">
-        <v>31.02178769744985</v>
+        <v>31.02178806208198</v>
       </c>
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="n">
-        <v>39.71043249386418</v>
+        <v>39.7104323765511</v>
       </c>
       <c r="CS39" t="n">
-        <v>41.31674328639771</v>
+        <v>41.31674314405547</v>
       </c>
       <c r="CT39" t="n">
-        <v>37.18506895775794</v>
+        <v>37.18506882964992</v>
       </c>
       <c r="CU39" t="n">
         <v>4</v>
@@ -27316,10 +27332,10 @@
         <v>2.8</v>
       </c>
       <c r="CX39" t="n">
-        <v>-5.908227411336064</v>
+        <v>-5.90822773549603</v>
       </c>
       <c r="CY39" t="n">
-        <v>0.4818624339441024</v>
+        <v>0.481862137099287</v>
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
@@ -27602,7 +27618,7 @@
         <v>-9.109999999999999</v>
       </c>
       <c r="CF40" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CG40" t="n">
         <v>0.84</v>
@@ -27614,10 +27630,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ40" t="n">
-        <v>9.430280394601793</v>
+        <v>9.430280304114609</v>
       </c>
       <c r="CK40" t="n">
-        <v>17.49317013198633</v>
+        <v>17.4931699641326</v>
       </c>
       <c r="CL40" t="n">
         <v>30.9711095548374</v>
@@ -27626,23 +27642,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN40" t="n">
-        <v>34.71574761345398</v>
+        <v>34.71574759725995</v>
       </c>
       <c r="CO40" t="n">
-        <v>25.36137840591655</v>
+        <v>25.36137842421327</v>
       </c>
       <c r="CP40" t="n">
-        <v>15.27881615604266</v>
+        <v>15.27881626855805</v>
       </c>
       <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="n">
-        <v>20.81398462183552</v>
+        <v>20.81398456182447</v>
       </c>
       <c r="CS40" t="n">
-        <v>21.42727426895144</v>
+        <v>21.42727419417293</v>
       </c>
       <c r="CT40" t="n">
-        <v>19.28454684205629</v>
+        <v>19.28454677475564</v>
       </c>
       <c r="CU40" t="n">
         <v>4</v>
@@ -27654,10 +27670,10 @@
         <v>3.3</v>
       </c>
       <c r="CX40" t="n">
-        <v>27.12291855681743</v>
+        <v>27.12291811317435</v>
       </c>
       <c r="CY40" t="n">
-        <v>37.20490782568544</v>
+        <v>37.20490743009515</v>
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
@@ -27696,7 +27712,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL40" t="n">
-        <v>-16.60345638373696</v>
+        <v>-16.60346541872488</v>
       </c>
       <c r="DM40" t="b">
         <v>1</v>
@@ -27960,7 +27976,7 @@
         <v>-29.91</v>
       </c>
       <c r="CF41" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CG41" t="n">
         <v>0.67</v>
@@ -27972,10 +27988,10 @@
         <v>12.77999973297119</v>
       </c>
       <c r="CJ41" t="n">
-        <v>1.574362027791186</v>
+        <v>1.574362027233926</v>
       </c>
       <c r="CK41" t="n">
-        <v>2.92044156155265</v>
+        <v>2.920441560518932</v>
       </c>
       <c r="CL41" t="n">
         <v>12.71283757221233</v>
@@ -27984,7 +28000,7 @@
         <v>9.285279950653386</v>
       </c>
       <c r="CN41" t="n">
-        <v>16.04662645522856</v>
+        <v>16.04662645464285</v>
       </c>
       <c r="CO41" t="n">
         <v>6.104046666666666</v>
@@ -28042,7 +28058,7 @@
         <v>-11.43451515806805</v>
       </c>
       <c r="DL41" t="n">
-        <v>-29.69468656045111</v>
+        <v>-29.69469396946918</v>
       </c>
       <c r="DM41" t="b">
         <v>0</v>
@@ -28306,7 +28322,7 @@
         <v>-8.31</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="CG42" t="n">
         <v>0.68</v>
@@ -28318,37 +28334,37 @@
         <v>26.6299991607666</v>
       </c>
       <c r="CJ42" t="n">
-        <v>17.02888469211387</v>
+        <v>17.02888465585986</v>
       </c>
       <c r="CK42" t="n">
-        <v>28.30221459159857</v>
+        <v>28.30221458715871</v>
       </c>
       <c r="CL42" t="n">
-        <v>47.53961787673538</v>
+        <v>47.53961797048815</v>
       </c>
       <c r="CM42" t="n">
         <v>53.13028264537036</v>
       </c>
       <c r="CN42" t="n">
-        <v>56.44642288305374</v>
+        <v>56.44642287123989</v>
       </c>
       <c r="CO42" t="n">
-        <v>42.94859200147489</v>
+        <v>42.94859200805522</v>
       </c>
       <c r="CP42" t="n">
-        <v>23.6439102219178</v>
+        <v>23.64391026246718</v>
       </c>
       <c r="CQ42" t="n">
         <v>31.11110629796304</v>
       </c>
       <c r="CR42" t="n">
-        <v>37.51887890127846</v>
+        <v>37.51887891232531</v>
       </c>
       <c r="CS42" t="n">
-        <v>37.02984914971897</v>
+        <v>37.02984915300913</v>
       </c>
       <c r="CT42" t="n">
-        <v>33.32686423474708</v>
+        <v>33.32686423770822</v>
       </c>
       <c r="CU42" t="n">
         <v>8</v>
@@ -28360,10 +28376,10 @@
         <v>3.3</v>
       </c>
       <c r="CX42" t="n">
-        <v>25.1478230755892</v>
+        <v>25.1478230867088</v>
       </c>
       <c r="CY42" t="n">
-        <v>40.88952340845058</v>
+        <v>40.88952344993331</v>
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
@@ -28678,37 +28694,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ43" t="n">
-        <v>5.830932764418058</v>
+        <v>5.83093274347174</v>
       </c>
       <c r="CK43" t="n">
-        <v>8.573470587989204</v>
+        <v>8.573470605896599</v>
       </c>
       <c r="CL43" t="n">
-        <v>11.02317108330131</v>
+        <v>11.02317114592365</v>
       </c>
       <c r="CM43" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN43" t="n">
-        <v>9.992439949454242</v>
+        <v>9.992439982933714</v>
       </c>
       <c r="CO43" t="n">
-        <v>14.9393663701344</v>
+        <v>14.93936637751284</v>
       </c>
       <c r="CP43" t="n">
-        <v>5.501588119050497</v>
+        <v>5.501588152966776</v>
       </c>
       <c r="CQ43" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR43" t="n">
-        <v>9.79472366769255</v>
+        <v>9.794723684487252</v>
       </c>
       <c r="CS43" t="n">
-        <v>10.44705002515057</v>
+        <v>10.4470500418903</v>
       </c>
       <c r="CT43" t="n">
-        <v>9.40234502263551</v>
+        <v>9.402345037701274</v>
       </c>
       <c r="CU43" t="n">
         <v>8</v>
@@ -28720,10 +28736,10 @@
         <v>2.7</v>
       </c>
       <c r="CX43" t="n">
-        <v>-37.44281310924005</v>
+        <v>-37.44281300900209</v>
       </c>
       <c r="CY43" t="n">
-        <v>-34.83217670186686</v>
+        <v>-34.83217659012566</v>
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
@@ -29026,10 +29042,10 @@
         <v>-22.21</v>
       </c>
       <c r="CF44" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="CH44" t="n">
         <v>0.07000000000000001</v>
@@ -29038,10 +29054,10 @@
         <v>11.89999961853027</v>
       </c>
       <c r="CJ44" t="n">
-        <v>4.837459967707387</v>
+        <v>4.837459966978797</v>
       </c>
       <c r="CK44" t="n">
-        <v>8.973488240097204</v>
+        <v>8.973488238745668</v>
       </c>
       <c r="CL44" t="n">
         <v>25.39049838092208</v>
@@ -29050,25 +29066,25 @@
         <v>28.53790787901647</v>
       </c>
       <c r="CN44" t="n">
-        <v>23.48175612920273</v>
+        <v>23.48175612859551</v>
       </c>
       <c r="CO44" t="n">
-        <v>14.1572381865218</v>
+        <v>14.15723818659358</v>
       </c>
       <c r="CP44" t="n">
-        <v>13.0241077370618</v>
+        <v>13.02410773771258</v>
       </c>
       <c r="CQ44" t="n">
         <v>4.864443096056768</v>
       </c>
       <c r="CR44" t="n">
-        <v>18.92749942547035</v>
+        <v>18.92749942526431</v>
       </c>
       <c r="CS44" t="n">
-        <v>18.81949715786227</v>
+        <v>18.81949715759454</v>
       </c>
       <c r="CT44" t="n">
-        <v>16.93754744207604</v>
+        <v>16.93754744183509</v>
       </c>
       <c r="CU44" t="n">
         <v>6</v>
@@ -29080,10 +29096,10 @@
         <v>5.9</v>
       </c>
       <c r="CX44" t="n">
-        <v>42.33233600866229</v>
+        <v>42.33233600663746</v>
       </c>
       <c r="CY44" t="n">
-        <v>59.05462211945866</v>
+        <v>59.05462211772725</v>
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
@@ -29394,37 +29410,37 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CJ45" t="n">
-        <v>31.16719164889602</v>
+        <v>31.16719164748666</v>
       </c>
       <c r="CK45" t="n">
-        <v>35.45587111749327</v>
+        <v>35.45587111857558</v>
       </c>
       <c r="CL45" t="n">
-        <v>38.32522055025856</v>
+        <v>38.3252205531615</v>
       </c>
       <c r="CM45" t="n">
         <v>49.84625084152005</v>
       </c>
       <c r="CN45" t="n">
-        <v>59.74639684334014</v>
+        <v>59.74639684493385</v>
       </c>
       <c r="CO45" t="n">
-        <v>16.57961555868113</v>
+        <v>16.57961555881874</v>
       </c>
       <c r="CP45" t="n">
-        <v>17.07014539293028</v>
+        <v>17.07014539542811</v>
       </c>
       <c r="CQ45" t="n">
         <v>28.85483270240698</v>
       </c>
       <c r="CR45" t="n">
-        <v>34.6306905819408</v>
+        <v>34.63069058279143</v>
       </c>
       <c r="CS45" t="n">
-        <v>33.31153138319464</v>
+        <v>33.31153138303112</v>
       </c>
       <c r="CT45" t="n">
-        <v>29.98037824487518</v>
+        <v>29.98037824472801</v>
       </c>
       <c r="CU45" t="n">
         <v>8</v>
@@ -29436,10 +29452,10 @@
         <v>3.6</v>
       </c>
       <c r="CX45" t="n">
-        <v>-23.32383781365586</v>
+        <v>-23.32383781403223</v>
       </c>
       <c r="CY45" t="n">
-        <v>-11.43045541328697</v>
+        <v>-11.43045541111144</v>
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
@@ -29742,10 +29758,10 @@
         <v>-42.81</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="CH46" t="n">
         <v>0.19</v>
@@ -29754,10 +29770,10 @@
         <v>9.279999732971191</v>
       </c>
       <c r="CJ46" t="n">
-        <v>2.530273374163277</v>
+        <v>2.530273363691584</v>
       </c>
       <c r="CK46" t="n">
-        <v>4.693657109072878</v>
+        <v>4.693657089647888</v>
       </c>
       <c r="CL46" t="n">
         <v>13.27861732849549</v>
@@ -29766,25 +29782,25 @@
         <v>15.00003440426151</v>
       </c>
       <c r="CN46" t="n">
-        <v>10.31764099481201</v>
+        <v>10.31764099366976</v>
       </c>
       <c r="CO46" t="n">
-        <v>7.305089436051789</v>
+        <v>7.305089437057424</v>
       </c>
       <c r="CP46" t="n">
-        <v>6.757993209668681</v>
+        <v>6.757993218902199</v>
       </c>
       <c r="CQ46" t="n">
         <v>10.43331654384748</v>
       </c>
       <c r="CR46" t="n">
-        <v>9.683764146601405</v>
+        <v>9.683764145125965</v>
       </c>
       <c r="CS46" t="n">
-        <v>10.31764099481201</v>
+        <v>10.31764099366976</v>
       </c>
       <c r="CT46" t="n">
-        <v>9.285876895330807</v>
+        <v>9.285876894302788</v>
       </c>
       <c r="CU46" t="n">
         <v>7</v>
@@ -29796,10 +29812,10 @@
         <v>5.9</v>
       </c>
       <c r="CX46" t="n">
-        <v>0.06333149276647188</v>
+        <v>0.06333148168868874</v>
       </c>
       <c r="CY46" t="n">
-        <v>4.350909754831855</v>
+        <v>4.350909738932707</v>
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
@@ -29834,7 +29850,7 @@
         <v>-0.2150586812202149</v>
       </c>
       <c r="DL46" t="n">
-        <v>-35.02795298830792</v>
+        <v>-35.02794846614577</v>
       </c>
       <c r="DM46" t="b">
         <v>0</v>
@@ -30044,7 +30060,7 @@
         <v>677</v>
       </c>
       <c r="BN47" t="n">
-        <v>10.25</v>
+        <v>10.46</v>
       </c>
       <c r="BO47" t="n">
         <v>9.710000000000001</v>
@@ -30098,22 +30114,22 @@
         <v>26.69</v>
       </c>
       <c r="CF47" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CG47" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="CH47" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="CI47" t="n">
         <v>34.41999816894531</v>
       </c>
       <c r="CJ47" t="n">
-        <v>14.90406869626761</v>
+        <v>14.9040687867039</v>
       </c>
       <c r="CK47" t="n">
-        <v>27.64704743157641</v>
+        <v>27.64704759933573</v>
       </c>
       <c r="CL47" t="n">
         <v>55.89031565423104</v>
@@ -30122,25 +30138,25 @@
         <v>43.20539681564285</v>
       </c>
       <c r="CN47" t="n">
-        <v>71.37808980256382</v>
+        <v>71.37808968563752</v>
       </c>
       <c r="CO47" t="n">
-        <v>38.39285993080778</v>
+        <v>38.39285990846879</v>
       </c>
       <c r="CP47" t="n">
-        <v>40.06166439671647</v>
+        <v>40.0616642256906</v>
       </c>
       <c r="CQ47" t="n">
         <v>21.74629148659444</v>
       </c>
       <c r="CR47" t="n">
-        <v>42.61738078830469</v>
+        <v>42.617380767943</v>
       </c>
       <c r="CS47" t="n">
-        <v>40.06166439671647</v>
+        <v>40.0616642256906</v>
       </c>
       <c r="CT47" t="n">
-        <v>36.05549795704482</v>
+        <v>36.05549780312154</v>
       </c>
       <c r="CU47" t="n">
         <v>7</v>
@@ -30152,10 +30168,10 @@
         <v>4.8</v>
       </c>
       <c r="CX47" t="n">
-        <v>4.751597545333697</v>
+        <v>4.751597098142257</v>
       </c>
       <c r="CY47" t="n">
-        <v>23.81575553584801</v>
+        <v>23.81575547669144</v>
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
@@ -30452,7 +30468,7 @@
         <v>-43.91</v>
       </c>
       <c r="CF48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CG48" t="n">
         <v>0.5</v>
@@ -30464,10 +30480,10 @@
         <v>6.579999923706055</v>
       </c>
       <c r="CJ48" t="n">
-        <v>7.828833431897523</v>
+        <v>7.828833429520135</v>
       </c>
       <c r="CK48" t="n">
-        <v>11.3987814768428</v>
+        <v>11.39878147338132</v>
       </c>
       <c r="CL48" t="n">
         <v>8.08888879509964</v>
@@ -30486,7 +30502,7 @@
         <v>5.378762847019572</v>
       </c>
       <c r="CR48" t="n">
-        <v>8.398734503624953</v>
+        <v>8.398734502651809</v>
       </c>
       <c r="CS48" t="n">
         <v>8.454774664372401</v>
@@ -30507,7 +30523,7 @@
         <v>15.64281589914329</v>
       </c>
       <c r="CY48" t="n">
-        <v>27.64034348034661</v>
+        <v>27.64034346555719</v>
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
@@ -30800,35 +30816,35 @@
         <v>17.19000053405762</v>
       </c>
       <c r="CJ49" t="n">
-        <v>10.23156219407304</v>
+        <v>10.23156226265194</v>
       </c>
       <c r="CK49" t="n">
-        <v>17.72445288378861</v>
+        <v>17.72445287222933</v>
       </c>
       <c r="CL49" t="n">
-        <v>28.93952544513885</v>
+        <v>28.93952523229304</v>
       </c>
       <c r="CM49" t="n">
         <v>29.49217552957616</v>
       </c>
       <c r="CN49" t="n">
-        <v>32.29551254703937</v>
+        <v>32.29551254200306</v>
       </c>
       <c r="CO49" t="n">
-        <v>27.87164394922435</v>
+        <v>27.87164393389648</v>
       </c>
       <c r="CP49" t="n">
-        <v>14.29787472503851</v>
+        <v>14.29787463976476</v>
       </c>
       <c r="CQ49" t="inlineStr"/>
       <c r="CR49" t="n">
-        <v>21.19179611805621</v>
+        <v>21.1917960752677</v>
       </c>
       <c r="CS49" t="n">
-        <v>22.79804841650648</v>
+        <v>22.79804840306291</v>
       </c>
       <c r="CT49" t="n">
-        <v>20.51824357485583</v>
+        <v>20.51824356275662</v>
       </c>
       <c r="CU49" t="n">
         <v>4</v>
@@ -30840,10 +30856,10 @@
         <v>2.8</v>
       </c>
       <c r="CX49" t="n">
-        <v>19.36150632575111</v>
+        <v>19.3615062553659</v>
       </c>
       <c r="CY49" t="n">
-        <v>23.27978743264174</v>
+        <v>23.27978718372661</v>
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
@@ -30882,7 +30898,7 @@
         <v>0.05820854891849248</v>
       </c>
       <c r="DL49" t="n">
-        <v>-19.06389685225955</v>
+        <v>-19.06388943634584</v>
       </c>
       <c r="DM49" t="b">
         <v>1</v>
@@ -31146,7 +31162,7 @@
         <v>-6.71</v>
       </c>
       <c r="CF50" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="CG50" t="n">
         <v>0.67</v>
@@ -31158,10 +31174,10 @@
         <v>32.7400016784668</v>
       </c>
       <c r="CJ50" t="n">
-        <v>11.12544146697846</v>
+        <v>11.12544153180805</v>
       </c>
       <c r="CK50" t="n">
-        <v>20.63769392124503</v>
+        <v>20.63769404150393</v>
       </c>
       <c r="CL50" t="n">
         <v>55.75900028787725</v>
@@ -31170,19 +31186,19 @@
         <v>52.6103446136404</v>
       </c>
       <c r="CN50" t="n">
-        <v>58.13663201940532</v>
+        <v>58.13663200555031</v>
       </c>
       <c r="CO50" t="n">
-        <v>28.31066647386178</v>
+        <v>28.31066663078114</v>
       </c>
       <c r="CP50" t="n">
-        <v>35.20095527561034</v>
+        <v>35.20095519357238</v>
       </c>
       <c r="CQ50" t="n">
         <v>54.75313563700135</v>
       </c>
       <c r="CR50" t="n">
-        <v>43.62977546123449</v>
+        <v>43.62977548713239</v>
       </c>
       <c r="CS50" t="n">
         <v>52.6103446136404</v>
@@ -31203,7 +31219,7 @@
         <v>44.62219830433958</v>
       </c>
       <c r="CY50" t="n">
-        <v>33.26137209678257</v>
+        <v>33.26137217588425</v>
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
@@ -31510,7 +31526,7 @@
         <v>-21.11</v>
       </c>
       <c r="CF51" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CG51" t="n">
         <v>0.65</v>
@@ -31522,37 +31538,37 @@
         <v>44.54000091552734</v>
       </c>
       <c r="CJ51" t="n">
-        <v>32.31519140066258</v>
+        <v>32.31519152827246</v>
       </c>
       <c r="CK51" t="n">
-        <v>44.48554536094404</v>
+        <v>44.48554511448052</v>
       </c>
       <c r="CL51" t="n">
-        <v>51.22338300983289</v>
+        <v>51.22338252376301</v>
       </c>
       <c r="CM51" t="n">
         <v>48.06226168784099</v>
       </c>
       <c r="CN51" t="n">
-        <v>71.02439355197752</v>
+        <v>71.02439328874729</v>
       </c>
       <c r="CO51" t="n">
-        <v>59.88896249213759</v>
+        <v>59.88896243967735</v>
       </c>
       <c r="CP51" t="n">
-        <v>25.30024916065064</v>
+        <v>25.30024886385048</v>
       </c>
       <c r="CQ51" t="n">
         <v>77.76550794654696</v>
       </c>
       <c r="CR51" t="n">
-        <v>51.25818682632416</v>
+        <v>51.25818667414738</v>
       </c>
       <c r="CS51" t="n">
-        <v>49.64282234883694</v>
+        <v>49.642822105802</v>
       </c>
       <c r="CT51" t="n">
-        <v>44.67854011395325</v>
+        <v>44.6785398952218</v>
       </c>
       <c r="CU51" t="n">
         <v>8</v>
@@ -31564,10 +31580,10 @@
         <v>3.1</v>
       </c>
       <c r="CX51" t="n">
-        <v>0.3110444444953231</v>
+        <v>0.3110439534053988</v>
       </c>
       <c r="CY51" t="n">
-        <v>15.08348848833263</v>
+        <v>15.08348814666947</v>
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
@@ -31873,46 +31889,46 @@
         <v>0.7</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="CI52" t="n">
         <v>10.89000034332275</v>
       </c>
       <c r="CJ52" t="n">
-        <v>8.33236614574025</v>
+        <v>8.332366123371171</v>
       </c>
       <c r="CK52" t="n">
-        <v>11.54775601777823</v>
+        <v>11.54775601196834</v>
       </c>
       <c r="CL52" t="n">
-        <v>16.84415144749038</v>
+        <v>16.84415148423561</v>
       </c>
       <c r="CM52" t="n">
         <v>24.06372840589797</v>
       </c>
       <c r="CN52" t="n">
-        <v>24.25150330569534</v>
+        <v>24.25150329202559</v>
       </c>
       <c r="CO52" t="n">
-        <v>20.99516499384267</v>
+        <v>20.99516499804486</v>
       </c>
       <c r="CP52" t="n">
-        <v>8.33240144935082</v>
+        <v>8.332401471515892</v>
       </c>
       <c r="CQ52" t="n">
         <v>9.730400983158669</v>
       </c>
       <c r="CR52" t="n">
-        <v>15.51218409361929</v>
+        <v>15.51218409627726</v>
       </c>
       <c r="CS52" t="n">
-        <v>14.1959537326343</v>
+        <v>14.19595374810198</v>
       </c>
       <c r="CT52" t="n">
-        <v>12.77635835937087</v>
+        <v>12.77635837329178</v>
       </c>
       <c r="CU52" t="n">
         <v>8</v>
@@ -31924,10 +31940,10 @@
         <v>2.9</v>
       </c>
       <c r="CX52" t="n">
-        <v>17.32192797592287</v>
+        <v>17.32192810375488</v>
       </c>
       <c r="CY52" t="n">
-        <v>42.44429388958329</v>
+        <v>42.44429391399074</v>
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
@@ -32220,7 +32236,7 @@
         <v>-4.11</v>
       </c>
       <c r="CF53" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CG53" t="n">
         <v>0.85</v>
@@ -32232,10 +32248,10 @@
         <v>54.70999908447266</v>
       </c>
       <c r="CJ53" t="n">
-        <v>10.69729567257529</v>
+        <v>10.6972956690376</v>
       </c>
       <c r="CK53" t="n">
-        <v>19.84348347262716</v>
+        <v>19.84348346606475</v>
       </c>
       <c r="CL53" t="n">
         <v>62.01090572021066</v>
@@ -32244,7 +32260,7 @@
         <v>46.36425801252346</v>
       </c>
       <c r="CN53" t="n">
-        <v>83.01215788564106</v>
+        <v>83.01215788140431</v>
       </c>
       <c r="CO53" t="n">
         <v>11.76833333333333</v>
@@ -32254,7 +32270,7 @@
       </c>
       <c r="CQ53" t="inlineStr"/>
       <c r="CR53" t="n">
-        <v>14.10303749284526</v>
+        <v>14.10303748947856</v>
       </c>
       <c r="CS53" t="n">
         <v>11.76833333333333</v>
@@ -32275,7 +32291,7 @@
         <v>-80.6406503797475</v>
       </c>
       <c r="CY53" t="n">
-        <v>-74.2221938789104</v>
+        <v>-74.22219388506412</v>
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
@@ -32571,7 +32587,7 @@
         <v>1.16</v>
       </c>
       <c r="CG54" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="CH54" t="n">
         <v>-0.02</v>
@@ -32580,10 +32596,10 @@
         <v>29.55999946594238</v>
       </c>
       <c r="CJ54" t="n">
-        <v>15.45162961219261</v>
+        <v>15.45162960034638</v>
       </c>
       <c r="CK54" t="n">
-        <v>28.66277293061729</v>
+        <v>28.66277290864254</v>
       </c>
       <c r="CL54" t="n">
         <v>54.77901998933378</v>
@@ -32592,23 +32608,23 @@
         <v>49.54885792707731</v>
       </c>
       <c r="CN54" t="n">
-        <v>61.18051769334477</v>
+        <v>61.18051769617078</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.65078487170795</v>
+        <v>36.65078487385424</v>
       </c>
       <c r="CP54" t="n">
-        <v>30.48333052017351</v>
+        <v>30.48333053652983</v>
       </c>
       <c r="CQ54" t="inlineStr"/>
       <c r="CR54" t="n">
-        <v>33.88605185096291</v>
+        <v>33.88605184304424</v>
       </c>
       <c r="CS54" t="n">
-        <v>32.65677890116262</v>
+        <v>32.65677889124839</v>
       </c>
       <c r="CT54" t="n">
-        <v>29.39110101104636</v>
+        <v>29.39110100212355</v>
       </c>
       <c r="CU54" t="n">
         <v>4</v>
@@ -32620,10 +32636,10 @@
         <v>3.5</v>
       </c>
       <c r="CX54" t="n">
-        <v>-0.5713750268859896</v>
+        <v>-0.5713750570713994</v>
       </c>
       <c r="CY54" t="n">
-        <v>14.63481888761464</v>
+        <v>14.63481886082618</v>
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
@@ -32938,16 +32954,16 @@
         <v>0.51</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="CI55" t="n">
         <v>4.630000114440918</v>
       </c>
       <c r="CJ55" t="n">
-        <v>1.071180595671146</v>
+        <v>1.071180597414208</v>
       </c>
       <c r="CK55" t="n">
-        <v>1.987040004969975</v>
+        <v>1.987040008203355</v>
       </c>
       <c r="CL55" t="n">
         <v>9.337519256673081</v>
@@ -32956,13 +32972,13 @@
         <v>8.790787326279261</v>
       </c>
       <c r="CN55" t="n">
-        <v>10.33759236534468</v>
+        <v>10.33759236551567</v>
       </c>
       <c r="CO55" t="n">
-        <v>4.221651666207287</v>
+        <v>4.221651666016798</v>
       </c>
       <c r="CP55" t="n">
-        <v>6.945757720027977</v>
+        <v>6.945757717800762</v>
       </c>
       <c r="CQ55" t="n">
         <v>6.750867949439122</v>
@@ -33014,7 +33030,7 @@
         <v>-3.138077171202591</v>
       </c>
       <c r="DL55" t="n">
-        <v>-36.06588431068125</v>
+        <v>-36.06588003734091</v>
       </c>
       <c r="DM55" t="b">
         <v>0</v>
@@ -33294,10 +33310,10 @@
         <v>24.53000068664551</v>
       </c>
       <c r="CJ56" t="n">
-        <v>4.302138311121994</v>
+        <v>4.302138311085282</v>
       </c>
       <c r="CK56" t="n">
-        <v>7.980466567131299</v>
+        <v>7.980466567063199</v>
       </c>
       <c r="CL56" t="n">
         <v>28.51074641210991</v>
@@ -33306,13 +33322,13 @@
         <v>28.42351122661583</v>
       </c>
       <c r="CN56" t="n">
-        <v>25.31778196903454</v>
+        <v>25.31778196905591</v>
       </c>
       <c r="CO56" t="n">
-        <v>2.969608790506795</v>
+        <v>2.969608790507634</v>
       </c>
       <c r="CP56" t="n">
-        <v>18.34134381506177</v>
+        <v>18.34134381510354</v>
       </c>
       <c r="CQ56" t="n">
         <v>18.05183245856756</v>
@@ -33632,16 +33648,16 @@
         <v>0.73</v>
       </c>
       <c r="CH57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI57" t="n">
         <v>10.69999980926514</v>
       </c>
       <c r="CJ57" t="n">
-        <v>13.32483352709585</v>
+        <v>13.32483354254606</v>
       </c>
       <c r="CK57" t="n">
-        <v>19.40095761545156</v>
+        <v>19.40095763794706</v>
       </c>
       <c r="CL57" t="n">
         <v>16.70870841086448</v>
@@ -33660,7 +33676,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR57" t="n">
-        <v>16.27033576537996</v>
+        <v>16.27033577170424</v>
       </c>
       <c r="CS57" t="n">
         <v>15.78776446356376</v>
@@ -33681,7 +33697,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY57" t="n">
-        <v>52.05921547112051</v>
+        <v>52.05921553022599</v>
       </c>
       <c r="CZ57" t="inlineStr">
         <is>
@@ -34004,10 +34020,10 @@
         <v>50.15000152587891</v>
       </c>
       <c r="CJ58" t="n">
-        <v>8.346377813723821</v>
+        <v>8.346377809075626</v>
       </c>
       <c r="CK58" t="n">
-        <v>15.48253084445769</v>
+        <v>15.48253083583529</v>
       </c>
       <c r="CL58" t="n">
         <v>19.74116221681211</v>
@@ -34016,25 +34032,25 @@
         <v>12.27363083572354</v>
       </c>
       <c r="CN58" t="n">
-        <v>14.12928603537834</v>
+        <v>14.12928605502382</v>
       </c>
       <c r="CO58" t="n">
-        <v>20.63689395567919</v>
+        <v>20.63689395846857</v>
       </c>
       <c r="CP58" t="n">
-        <v>10.67936480006884</v>
+        <v>10.67936481363265</v>
       </c>
       <c r="CQ58" t="n">
         <v>13.20161376166642</v>
       </c>
       <c r="CR58" t="n">
-        <v>14.31135753293874</v>
+        <v>14.31135753577975</v>
       </c>
       <c r="CS58" t="n">
-        <v>13.66544989852238</v>
+        <v>13.66544990834512</v>
       </c>
       <c r="CT58" t="n">
-        <v>12.29890490867014</v>
+        <v>12.29890491751061</v>
       </c>
       <c r="CU58" t="n">
         <v>8</v>
@@ -34046,10 +34062,10 @@
         <v>2.5</v>
       </c>
       <c r="CX58" t="n">
-        <v>-75.47576364015953</v>
+        <v>-75.47576362253149</v>
       </c>
       <c r="CY58" t="n">
-        <v>-71.46289711366478</v>
+        <v>-71.46289710799975</v>
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
@@ -34356,22 +34372,22 @@
         <v>60.49</v>
       </c>
       <c r="CF59" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="CG59" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="CH59" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="CI59" t="n">
         <v>34.81999969482422</v>
       </c>
       <c r="CJ59" t="n">
-        <v>12.29771087960432</v>
+        <v>12.29771087134512</v>
       </c>
       <c r="CK59" t="n">
-        <v>22.81225368166601</v>
+        <v>22.81225366634519</v>
       </c>
       <c r="CL59" t="n">
         <v>41.04670782530435</v>
@@ -34380,25 +34396,25 @@
         <v>33.52046162339458</v>
       </c>
       <c r="CN59" t="n">
-        <v>41.80899893389934</v>
+        <v>41.80899894587062</v>
       </c>
       <c r="CO59" t="n">
-        <v>23.77591432939287</v>
+        <v>23.77591433096661</v>
       </c>
       <c r="CP59" t="n">
-        <v>24.92756552344322</v>
+        <v>24.9275655374343</v>
       </c>
       <c r="CQ59" t="n">
         <v>27.30596254019629</v>
       </c>
       <c r="CR59" t="n">
-        <v>28.43694691711262</v>
+        <v>28.43694691760713</v>
       </c>
       <c r="CS59" t="n">
-        <v>26.11676403181976</v>
+        <v>26.1167640388153</v>
       </c>
       <c r="CT59" t="n">
-        <v>23.50508762863779</v>
+        <v>23.50508763493377</v>
       </c>
       <c r="CU59" t="n">
         <v>8</v>
@@ -34410,10 +34426,10 @@
         <v>3.4</v>
       </c>
       <c r="CX59" t="n">
-        <v>-32.49543987752627</v>
+        <v>-32.49543985944475</v>
       </c>
       <c r="CY59" t="n">
-        <v>-18.33157045851554</v>
+        <v>-18.33157045709535</v>
       </c>
       <c r="CZ59" t="inlineStr">
         <is>
@@ -34715,7 +34731,7 @@
         <v>1.34</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="CH60" t="n">
         <v>0.1</v>
@@ -34724,10 +34740,10 @@
         <v>4.269999980926514</v>
       </c>
       <c r="CJ60" t="n">
-        <v>2.773787705075276</v>
+        <v>2.773787700734017</v>
       </c>
       <c r="CK60" t="n">
-        <v>5.145376192914636</v>
+        <v>5.145376184861601</v>
       </c>
       <c r="CL60" t="n">
         <v>13.12703010377641</v>
@@ -34736,13 +34752,13 @@
         <v>14.70801820729337</v>
       </c>
       <c r="CN60" t="n">
-        <v>15.2025419216256</v>
+        <v>15.202541913772</v>
       </c>
       <c r="CO60" t="n">
-        <v>9.474628604036438</v>
+        <v>9.4746286045988</v>
       </c>
       <c r="CP60" t="n">
-        <v>6.539101160503703</v>
+        <v>6.539101164430979</v>
       </c>
       <c r="CQ60" t="n">
         <v>1.483476208930862</v>
@@ -35058,7 +35074,7 @@
         <v>7.09</v>
       </c>
       <c r="CF61" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CG61" t="n">
         <v>0.63</v>
@@ -35070,37 +35086,37 @@
         <v>25.46999931335449</v>
       </c>
       <c r="CJ61" t="n">
-        <v>11.25114159108422</v>
+        <v>11.25114160867838</v>
       </c>
       <c r="CK61" t="n">
-        <v>14.23814761208105</v>
+        <v>14.23814760315025</v>
       </c>
       <c r="CL61" t="n">
-        <v>16.86650685549813</v>
+        <v>16.86650681854343</v>
       </c>
       <c r="CM61" t="n">
         <v>21.46890400792605</v>
       </c>
       <c r="CN61" t="n">
-        <v>16.47407045426144</v>
+        <v>16.47407043050653</v>
       </c>
       <c r="CO61" t="n">
-        <v>22.7028061516711</v>
+        <v>22.70280614671631</v>
       </c>
       <c r="CP61" t="n">
-        <v>8.086356218020756</v>
+        <v>8.086356191746342</v>
       </c>
       <c r="CQ61" t="n">
         <v>19.11779586753234</v>
       </c>
       <c r="CR61" t="n">
-        <v>16.27571609475938</v>
+        <v>16.27571608434995</v>
       </c>
       <c r="CS61" t="n">
-        <v>16.67028865487978</v>
+        <v>16.67028862452498</v>
       </c>
       <c r="CT61" t="n">
-        <v>15.00325978939181</v>
+        <v>15.00325976207248</v>
       </c>
       <c r="CU61" t="n">
         <v>8</v>
@@ -35112,10 +35128,10 @@
         <v>2.8</v>
       </c>
       <c r="CX61" t="n">
-        <v>-41.0943847904807</v>
+        <v>-41.0943848977415</v>
       </c>
       <c r="CY61" t="n">
-        <v>-36.09848239679513</v>
+        <v>-36.0984824376645</v>
       </c>
       <c r="CZ61" t="inlineStr">
         <is>
@@ -35426,37 +35442,37 @@
         <v>29.85000038146973</v>
       </c>
       <c r="CJ62" t="n">
-        <v>13.93776506948015</v>
+        <v>13.93776506102995</v>
       </c>
       <c r="CK62" t="n">
-        <v>14.47550351122591</v>
+        <v>14.47550350950391</v>
       </c>
       <c r="CL62" t="n">
-        <v>15.16715023700868</v>
+        <v>15.16715024439996</v>
       </c>
       <c r="CM62" t="n">
         <v>30.56331832909941</v>
       </c>
       <c r="CN62" t="n">
-        <v>14.30197652028888</v>
+        <v>14.30197652407539</v>
       </c>
       <c r="CO62" t="n">
-        <v>30.44422085712622</v>
+        <v>30.44422085888855</v>
       </c>
       <c r="CP62" t="n">
-        <v>6.050759789793193</v>
+        <v>6.050759797266556</v>
       </c>
       <c r="CQ62" t="n">
         <v>38.24989768953186</v>
       </c>
       <c r="CR62" t="n">
-        <v>17.84867061628892</v>
+        <v>17.84867061775196</v>
       </c>
       <c r="CS62" t="n">
-        <v>14.47550351122591</v>
+        <v>14.47550350950391</v>
       </c>
       <c r="CT62" t="n">
-        <v>13.02795316010332</v>
+        <v>13.02795315855352</v>
       </c>
       <c r="CU62" t="n">
         <v>7</v>
@@ -35468,10 +35484,10 @@
         <v>6.3</v>
       </c>
       <c r="CX62" t="n">
-        <v>-56.35526635305905</v>
+        <v>-56.35526635825102</v>
       </c>
       <c r="CY62" t="n">
-        <v>-40.20545933604406</v>
+        <v>-40.20545933114276</v>
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
@@ -35506,7 +35522,7 @@
         <v>-1.934012042004329</v>
       </c>
       <c r="DL62" t="n">
-        <v>-27.3310587051789</v>
+        <v>-27.33106549909805</v>
       </c>
       <c r="DM62" t="b">
         <v>0</v>
@@ -35790,10 +35806,10 @@
         <v>19.68000030517578</v>
       </c>
       <c r="CJ63" t="n">
-        <v>9.229871020670526</v>
+        <v>9.229870995971508</v>
       </c>
       <c r="CK63" t="n">
-        <v>17.12141074334382</v>
+        <v>17.12141069752715</v>
       </c>
       <c r="CL63" t="n">
         <v>17.05428411010982</v>
@@ -35802,7 +35818,7 @@
         <v>16.9233399690805</v>
       </c>
       <c r="CN63" t="n">
-        <v>26.98562450516146</v>
+        <v>26.98562448254627</v>
       </c>
       <c r="CO63" t="n">
         <v>19.94489718117502</v>
@@ -35814,7 +35830,7 @@
         <v>16.90195346323043</v>
       </c>
       <c r="CR63" t="n">
-        <v>17.40625692878056</v>
+        <v>17.4062569171392</v>
       </c>
       <c r="CS63" t="n">
         <v>16.98881203959516</v>
@@ -35835,7 +35851,7 @@
         <v>-22.30726321881998</v>
       </c>
       <c r="CY63" t="n">
-        <v>-11.55357388788879</v>
+        <v>-11.55357394704204</v>
       </c>
       <c r="CZ63" t="inlineStr">
         <is>
@@ -36149,7 +36165,7 @@
         <v>1.52</v>
       </c>
       <c r="CG64" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="CH64" t="n">
         <v>0.17</v>
@@ -36158,35 +36174,35 @@
         <v>3.529999971389771</v>
       </c>
       <c r="CJ64" t="n">
-        <v>2.709629173848352</v>
+        <v>2.70962915526908</v>
       </c>
       <c r="CK64" t="n">
-        <v>3.101291785905935</v>
+        <v>3.101291780074485</v>
       </c>
       <c r="CL64" t="n">
-        <v>3.70936729460187</v>
+        <v>3.709367313061273</v>
       </c>
       <c r="CM64" t="n">
         <v>6.931792131311814</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.590725598313247</v>
+        <v>5.590725589876662</v>
       </c>
       <c r="CO64" t="n">
-        <v>8.464613710247207</v>
+        <v>8.464613714838169</v>
       </c>
       <c r="CP64" t="n">
-        <v>1.66139480421207</v>
+        <v>1.661394819924188</v>
       </c>
       <c r="CQ64" t="inlineStr"/>
       <c r="CR64" t="n">
-        <v>4.595544928348643</v>
+        <v>4.595544929193667</v>
       </c>
       <c r="CS64" t="n">
-        <v>3.70936729460187</v>
+        <v>3.709367313061273</v>
       </c>
       <c r="CT64" t="n">
-        <v>3.338430565141683</v>
+        <v>3.338430581755146</v>
       </c>
       <c r="CU64" t="n">
         <v>7</v>
@@ -36198,10 +36214,10 @@
         <v>5.1</v>
       </c>
       <c r="CX64" t="n">
-        <v>-5.426895405119947</v>
+        <v>-5.426894934483617</v>
       </c>
       <c r="CY64" t="n">
-        <v>30.18540979022626</v>
+        <v>30.18540981416464</v>
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
@@ -36524,10 +36540,10 @@
         <v>35.18000030517578</v>
       </c>
       <c r="CJ65" t="n">
-        <v>10.07312300257284</v>
+        <v>10.07312300570793</v>
       </c>
       <c r="CK65" t="n">
-        <v>18.68564316977261</v>
+        <v>18.68564317558821</v>
       </c>
       <c r="CL65" t="n">
         <v>28.5272340295948</v>
@@ -36536,25 +36552,25 @@
         <v>21.17723585857856</v>
       </c>
       <c r="CN65" t="n">
-        <v>25.90721696276995</v>
+        <v>25.90721695524695</v>
       </c>
       <c r="CO65" t="n">
-        <v>22.89550546133892</v>
+        <v>22.89550546033391</v>
       </c>
       <c r="CP65" t="n">
-        <v>16.61118114621095</v>
+        <v>16.61118113979379</v>
       </c>
       <c r="CQ65" t="n">
         <v>27.23126452034872</v>
       </c>
       <c r="CR65" t="n">
-        <v>21.38855051889842</v>
+        <v>21.38855051814911</v>
       </c>
       <c r="CS65" t="n">
-        <v>22.03637065995874</v>
+        <v>22.03637065945624</v>
       </c>
       <c r="CT65" t="n">
-        <v>19.83273359396287</v>
+        <v>19.83273359351061</v>
       </c>
       <c r="CU65" t="n">
         <v>8</v>
@@ -36566,10 +36582,10 @@
         <v>2.8</v>
       </c>
       <c r="CX65" t="n">
-        <v>-43.62497606048906</v>
+        <v>-43.6249760617746</v>
       </c>
       <c r="CY65" t="n">
-        <v>-39.20252889892194</v>
+        <v>-39.20252890105187</v>
       </c>
       <c r="CZ65" t="inlineStr">
         <is>
@@ -36604,7 +36620,7 @@
         <v>-2.467422781198825</v>
       </c>
       <c r="DL65" t="n">
-        <v>-21.73873559212695</v>
+        <v>-21.73874227621538</v>
       </c>
       <c r="DM65" t="b">
         <v>0</v>
@@ -36858,10 +36874,10 @@
         <v>13.39999961853027</v>
       </c>
       <c r="CJ66" t="n">
-        <v>11.33332649494034</v>
+        <v>11.33332654106458</v>
       </c>
       <c r="CK66" t="n">
-        <v>16.50132337663314</v>
+        <v>16.50132344379003</v>
       </c>
       <c r="CL66" t="n">
         <v>15.80045306493365</v>
@@ -36878,13 +36894,13 @@
       </c>
       <c r="CQ66" t="inlineStr"/>
       <c r="CR66" t="n">
-        <v>12.74210906746012</v>
+        <v>12.7421090957804</v>
       </c>
       <c r="CS66" t="n">
-        <v>13.566889779937</v>
+        <v>13.56688980299912</v>
       </c>
       <c r="CT66" t="n">
-        <v>12.2102008019433</v>
+        <v>12.21020082269921</v>
       </c>
       <c r="CU66" t="n">
         <v>4</v>
@@ -36896,10 +36912,10 @@
         <v>2.3</v>
       </c>
       <c r="CX66" t="n">
-        <v>-8.87909589894058</v>
+        <v>-8.87909574404574</v>
       </c>
       <c r="CY66" t="n">
-        <v>-4.909631117902324</v>
+        <v>-4.909630906556939</v>
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
@@ -37204,16 +37220,16 @@
         <v>0.66</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="CI67" t="n">
         <v>8.229999542236328</v>
       </c>
       <c r="CJ67" t="n">
-        <v>1.587563301376546</v>
+        <v>1.587563301691624</v>
       </c>
       <c r="CK67" t="n">
-        <v>2.944929924053493</v>
+        <v>2.944929924637963</v>
       </c>
       <c r="CL67" t="n">
         <v>24.07229446680603</v>
@@ -37222,13 +37238,13 @@
         <v>23.87899052877524</v>
       </c>
       <c r="CN67" t="n">
-        <v>25.74672793743268</v>
+        <v>25.74672793782991</v>
       </c>
       <c r="CO67" t="n">
-        <v>6.710327659900977</v>
+        <v>6.710327659881873</v>
       </c>
       <c r="CP67" t="n">
-        <v>17.95303920920632</v>
+        <v>17.95303920884393</v>
       </c>
       <c r="CQ67" t="n">
         <v>15.35874199061105</v>
@@ -37544,7 +37560,7 @@
         <v>6.99</v>
       </c>
       <c r="CF68" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CG68" t="n">
         <v>0.62</v>
@@ -37556,10 +37572,10 @@
         <v>8.439999580383301</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.502223222469833</v>
+        <v>0.5022232238494768</v>
       </c>
       <c r="CK68" t="n">
-        <v>0.93162407768154</v>
+        <v>0.9316240802407795</v>
       </c>
       <c r="CL68" t="n">
         <v>9.437130332496094</v>
@@ -37568,13 +37584,13 @@
         <v>8.668386285715835</v>
       </c>
       <c r="CN68" t="n">
-        <v>10.35702314705229</v>
+        <v>10.35702314574443</v>
       </c>
       <c r="CO68" t="n">
-        <v>0.7357683740969124</v>
+        <v>0.7357683740702224</v>
       </c>
       <c r="CP68" t="n">
-        <v>8.039858089648371</v>
+        <v>8.039858087801745</v>
       </c>
       <c r="CQ68" t="inlineStr"/>
       <c r="CR68" t="inlineStr"/>
@@ -37906,25 +37922,25 @@
         <v>2.299999952316284</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.6603398205754561</v>
+        <v>0.6603398183537126</v>
       </c>
       <c r="CK69" t="n">
-        <v>0.9329022581069609</v>
+        <v>0.9329022554341896</v>
       </c>
       <c r="CL69" t="n">
-        <v>3.433379045952449</v>
+        <v>3.433379047667555</v>
       </c>
       <c r="CM69" t="n">
         <v>7.092702042168081</v>
       </c>
       <c r="CN69" t="n">
-        <v>2.633769999518988</v>
+        <v>2.633769996507179</v>
       </c>
       <c r="CO69" t="n">
-        <v>2.230427864201625</v>
+        <v>2.230427864302083</v>
       </c>
       <c r="CP69" t="n">
-        <v>1.704816589741319</v>
+        <v>1.704816590740392</v>
       </c>
       <c r="CQ69" t="n">
         <v>6.812437880468564</v>
@@ -38260,10 +38276,10 @@
         <v>21.70000076293945</v>
       </c>
       <c r="CJ70" t="n">
-        <v>6.001300240443079</v>
+        <v>6.00130026119897</v>
       </c>
       <c r="CK70" t="n">
-        <v>11.13241194602191</v>
+        <v>11.13241198452409</v>
       </c>
       <c r="CL70" t="n">
         <v>32.86000115530831</v>
@@ -38272,25 +38288,25 @@
         <v>33.79823715878612</v>
       </c>
       <c r="CN70" t="n">
-        <v>29.44387883243462</v>
+        <v>29.44387883048357</v>
       </c>
       <c r="CO70" t="n">
-        <v>25.19833803358793</v>
+        <v>25.19833803028006</v>
       </c>
       <c r="CP70" t="n">
-        <v>19.09713068578624</v>
+        <v>19.09713066368537</v>
       </c>
       <c r="CQ70" t="n">
         <v>13.92055056374159</v>
       </c>
       <c r="CR70" t="n">
-        <v>23.63579262509524</v>
+        <v>23.63579262668701</v>
       </c>
       <c r="CS70" t="n">
-        <v>25.19833803358793</v>
+        <v>25.19833803028006</v>
       </c>
       <c r="CT70" t="n">
-        <v>22.67850423022913</v>
+        <v>22.67850422725205</v>
       </c>
       <c r="CU70" t="n">
         <v>7</v>
@@ -38302,10 +38318,10 @@
         <v>5.6</v>
       </c>
       <c r="CX70" t="n">
-        <v>4.509232409617359</v>
+        <v>4.509232395898088</v>
       </c>
       <c r="CY70" t="n">
-        <v>8.920699511964303</v>
+        <v>8.920699519299657</v>
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
@@ -38610,31 +38626,31 @@
         <v>0.4</v>
       </c>
       <c r="CH71" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CI71" t="n">
         <v>17.28000068664551</v>
       </c>
       <c r="CJ71" t="n">
-        <v>4.022695654627861</v>
+        <v>4.022695632508676</v>
       </c>
       <c r="CK71" t="n">
-        <v>6.903155545808813</v>
+        <v>6.903155518588212</v>
       </c>
       <c r="CL71" t="n">
-        <v>23.4822477125908</v>
+        <v>23.48224774911477</v>
       </c>
       <c r="CM71" t="n">
         <v>32.85543339401257</v>
       </c>
       <c r="CN71" t="n">
-        <v>16.59077770085899</v>
+        <v>16.5907776902173</v>
       </c>
       <c r="CO71" t="n">
-        <v>20.29840994350898</v>
+        <v>20.29840994589041</v>
       </c>
       <c r="CP71" t="n">
-        <v>11.62167795227885</v>
+        <v>11.62167796716948</v>
       </c>
       <c r="CQ71" t="n">
         <v>22.25954302628453</v>
@@ -38686,7 +38702,7 @@
         <v>-0.4034564454475809</v>
       </c>
       <c r="DL71" t="n">
-        <v>-40.14819299276235</v>
+        <v>-40.14818897893514</v>
       </c>
       <c r="DM71" t="b">
         <v>0</v>
@@ -38950,7 +38966,7 @@
         <v>-38.81</v>
       </c>
       <c r="CF72" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="CG72" t="n">
         <v>0.33</v>
@@ -38962,10 +38978,10 @@
         <v>3.819999933242798</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.9263872476693884</v>
+        <v>0.9263872449717997</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.718448344426716</v>
+        <v>1.718448339422688</v>
       </c>
       <c r="CL72" t="n">
         <v>6.076230386010452</v>
@@ -38974,7 +38990,7 @@
         <v>4.03575162850128</v>
       </c>
       <c r="CN72" t="n">
-        <v>8.435704737816735</v>
+        <v>8.435704733282973</v>
       </c>
       <c r="CO72" t="n">
         <v>3.760485277130923</v>
@@ -39310,16 +39326,16 @@
         <v>0.64</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="CI73" t="n">
         <v>12.42000007629395</v>
       </c>
       <c r="CJ73" t="n">
-        <v>2.055237991307412</v>
+        <v>2.055237989509821</v>
       </c>
       <c r="CK73" t="n">
-        <v>3.812466473875249</v>
+        <v>3.812466470540718</v>
       </c>
       <c r="CL73" t="n">
         <v>16.11802164651271</v>
@@ -39328,7 +39344,7 @@
         <v>12.7840458343596</v>
       </c>
       <c r="CN73" t="n">
-        <v>21.06496895423241</v>
+        <v>21.06496895176755</v>
       </c>
       <c r="CO73" t="n">
         <v>9.294207014285712</v>
@@ -39662,35 +39678,35 @@
         <v>24.60000038146973</v>
       </c>
       <c r="CJ74" t="n">
-        <v>23.63636236122295</v>
+        <v>23.63636239191129</v>
       </c>
       <c r="CK74" t="n">
-        <v>29.11389157125656</v>
+        <v>29.11389157915331</v>
       </c>
       <c r="CL74" t="n">
-        <v>37.44543331668986</v>
+        <v>37.44543327822903</v>
       </c>
       <c r="CM74" t="n">
         <v>62.14376136419157</v>
       </c>
       <c r="CN74" t="n">
-        <v>67.3169394288627</v>
+        <v>67.31693945752394</v>
       </c>
       <c r="CO74" t="n">
-        <v>41.61751631366096</v>
+        <v>41.6175163092983</v>
       </c>
       <c r="CP74" t="n">
-        <v>17.69709563116624</v>
+        <v>17.69709560245914</v>
       </c>
       <c r="CQ74" t="inlineStr"/>
       <c r="CR74" t="n">
-        <v>39.85299999815012</v>
+        <v>39.85299999753808</v>
       </c>
       <c r="CS74" t="n">
-        <v>37.44543331668986</v>
+        <v>37.44543327822903</v>
       </c>
       <c r="CT74" t="n">
-        <v>33.70088998502087</v>
+        <v>33.70088995040613</v>
       </c>
       <c r="CU74" t="n">
         <v>7</v>
@@ -39702,10 +39718,10 @@
         <v>3.8</v>
       </c>
       <c r="CX74" t="n">
-        <v>36.99548561961205</v>
+        <v>36.99548547890173</v>
       </c>
       <c r="CY74" t="n">
-        <v>62.00406252094985</v>
+        <v>62.00406251846189</v>
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
@@ -40004,7 +40020,7 @@
         <v>-14.81</v>
       </c>
       <c r="CF75" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CG75" t="n">
         <v>0.71</v>
@@ -40016,10 +40032,10 @@
         <v>25.28000068664551</v>
       </c>
       <c r="CJ75" t="n">
-        <v>4.637679035423011</v>
+        <v>4.637679036084639</v>
       </c>
       <c r="CK75" t="n">
-        <v>8.602894610709683</v>
+        <v>8.602894611937005</v>
       </c>
       <c r="CL75" t="n">
         <v>30.23104775253185</v>
@@ -40028,19 +40044,19 @@
         <v>25.66642298400775</v>
       </c>
       <c r="CN75" t="n">
-        <v>34.91506257280638</v>
+        <v>34.91506257199359</v>
       </c>
       <c r="CO75" t="n">
-        <v>11.77719501857461</v>
+        <v>11.77719501849912</v>
       </c>
       <c r="CP75" t="n">
-        <v>24.35835630231654</v>
+        <v>24.35835630128016</v>
       </c>
       <c r="CQ75" t="n">
         <v>25.28000068664551</v>
       </c>
       <c r="CR75" t="n">
-        <v>25.37134755281377</v>
+        <v>25.371347552493</v>
       </c>
       <c r="CS75" t="n">
         <v>25.47321183532663</v>
@@ -40061,7 +40077,7 @@
         <v>-9.312143872271072</v>
       </c>
       <c r="CY75" t="n">
-        <v>0.361340441800384</v>
+        <v>0.3613404405314879</v>
       </c>
       <c r="CZ75" t="inlineStr">
         <is>
@@ -40358,7 +40374,7 @@
         <v>18.39</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="CG76" t="n">
         <v>0.47</v>
@@ -40370,10 +40386,10 @@
         <v>55.22000122070312</v>
       </c>
       <c r="CJ76" t="n">
-        <v>40.15922321596685</v>
+        <v>40.1592235447629</v>
       </c>
       <c r="CK76" t="n">
-        <v>58.47182900244773</v>
+        <v>58.47182948117479</v>
       </c>
       <c r="CL76" t="n">
         <v>35.36256235808575</v>
@@ -40392,13 +40408,13 @@
         <v>48.44534857668784</v>
       </c>
       <c r="CR76" t="n">
-        <v>43.07677508868716</v>
+        <v>43.07677522327433</v>
       </c>
       <c r="CS76" t="n">
-        <v>41.18972129272336</v>
+        <v>41.18972145712138</v>
       </c>
       <c r="CT76" t="n">
-        <v>37.07074916345103</v>
+        <v>37.07074931140924</v>
       </c>
       <c r="CU76" t="n">
         <v>6</v>
@@ -40410,10 +40426,10 @@
         <v>6.4</v>
       </c>
       <c r="CX76" t="n">
-        <v>-32.86717069185353</v>
+        <v>-32.86717042391037</v>
       </c>
       <c r="CY76" t="n">
-        <v>-21.9906299593909</v>
+        <v>-21.99062971566188</v>
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
@@ -40724,10 +40740,10 @@
         <v>29.3799991607666</v>
       </c>
       <c r="CJ77" t="n">
-        <v>13.7272111543367</v>
+        <v>13.72721102294982</v>
       </c>
       <c r="CK77" t="n">
-        <v>25.46397669129458</v>
+        <v>25.46397644757192</v>
       </c>
       <c r="CL77" t="n">
         <v>37.03948514559062</v>
@@ -40736,25 +40752,25 @@
         <v>25.82865525118578</v>
       </c>
       <c r="CN77" t="n">
-        <v>41.32297929430455</v>
+        <v>41.32297960434281</v>
       </c>
       <c r="CO77" t="n">
-        <v>42.02940936123385</v>
+        <v>42.02940942860938</v>
       </c>
       <c r="CP77" t="n">
-        <v>21.94847943027068</v>
+        <v>21.94847973516182</v>
       </c>
       <c r="CQ77" t="n">
         <v>25.37843755022685</v>
       </c>
       <c r="CR77" t="n">
-        <v>29.09232923480545</v>
+        <v>29.09232927320488</v>
       </c>
       <c r="CS77" t="n">
-        <v>25.64631597124018</v>
+        <v>25.64631584937885</v>
       </c>
       <c r="CT77" t="n">
-        <v>23.08168437411617</v>
+        <v>23.08168426444097</v>
       </c>
       <c r="CU77" t="n">
         <v>8</v>
@@ -40766,10 +40782,10 @@
         <v>3.1</v>
       </c>
       <c r="CX77" t="n">
-        <v>-21.43742330347328</v>
+        <v>-21.43742367677214</v>
       </c>
       <c r="CY77" t="n">
-        <v>-0.9791352422681587</v>
+        <v>-0.9791351115689406</v>
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
@@ -40808,7 +40824,7 @@
         <v>1.837084132717348</v>
       </c>
       <c r="DL77" t="n">
-        <v>-22.80233583035372</v>
+        <v>-22.80232771093915</v>
       </c>
       <c r="DM77" t="b">
         <v>0</v>
@@ -41078,16 +41094,16 @@
         <v>0.78</v>
       </c>
       <c r="CH78" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="CI78" t="n">
         <v>15.46000003814697</v>
       </c>
       <c r="CJ78" t="n">
-        <v>2.49476629968139</v>
+        <v>2.494766296551138</v>
       </c>
       <c r="CK78" t="n">
-        <v>4.627791485908977</v>
+        <v>4.627791480102361</v>
       </c>
       <c r="CL78" t="n">
         <v>25.44658391372017</v>
@@ -41096,7 +41112,7 @@
         <v>19.4825803315022</v>
       </c>
       <c r="CN78" t="n">
-        <v>33.14617748667628</v>
+        <v>33.14617748123236</v>
       </c>
       <c r="CO78" t="n">
         <v>10.38593205872702</v>
@@ -41434,10 +41450,10 @@
         <v>14.94999980926514</v>
       </c>
       <c r="CJ79" t="n">
-        <v>9.768326998191464</v>
+        <v>9.768326943679245</v>
       </c>
       <c r="CK79" t="n">
-        <v>18.12024658164517</v>
+        <v>18.120246480525</v>
       </c>
       <c r="CL79" t="n">
         <v>13.9204144394071</v>
@@ -41458,7 +41474,7 @@
         <v>12.34226887232652</v>
       </c>
       <c r="CR79" t="n">
-        <v>15.09537293533789</v>
+        <v>15.09537291588385</v>
       </c>
       <c r="CS79" t="n">
         <v>13.26668799219724</v>
@@ -41479,7 +41495,7 @@
         <v>-20.13364986414387</v>
       </c>
       <c r="CY79" t="n">
-        <v>0.9723955045314758</v>
+        <v>0.9723953744040559</v>
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
@@ -41798,25 +41814,25 @@
         <v>26.69000053405762</v>
       </c>
       <c r="CJ80" t="n">
-        <v>12.15895748631334</v>
+        <v>12.15895746599523</v>
       </c>
       <c r="CK80" t="n">
-        <v>12.772191621796</v>
+        <v>12.77219161249891</v>
       </c>
       <c r="CL80" t="n">
-        <v>13.90679780625699</v>
+        <v>13.90679781937283</v>
       </c>
       <c r="CM80" t="n">
         <v>32.55846683522902</v>
       </c>
       <c r="CN80" t="n">
-        <v>12.92056506285984</v>
+        <v>12.9205650637859</v>
       </c>
       <c r="CO80" t="n">
-        <v>24.65481166746113</v>
+        <v>24.65481167019572</v>
       </c>
       <c r="CP80" t="n">
-        <v>5.642442769968009</v>
+        <v>5.642442782966721</v>
       </c>
       <c r="CQ80" t="n">
         <v>60.74623809393702</v>
@@ -41868,7 +41884,7 @@
         <v>-0.2508191755985822</v>
       </c>
       <c r="DL80" t="n">
-        <v>-17.69193681417648</v>
+        <v>-17.69194660286418</v>
       </c>
       <c r="DM80" t="b">
         <v>0</v>
@@ -42132,7 +42148,7 @@
         <v>8.99</v>
       </c>
       <c r="CF81" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="CG81" t="n">
         <v>0.54</v>
@@ -42144,10 +42160,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="CJ81" t="n">
-        <v>6.368258857793742</v>
+        <v>6.368258880533266</v>
       </c>
       <c r="CK81" t="n">
-        <v>11.81312018120739</v>
+        <v>11.81312022338921</v>
       </c>
       <c r="CL81" t="n">
         <v>7.957659222487079</v>
@@ -42168,7 +42184,7 @@
         <v>39.12743918059205</v>
       </c>
       <c r="CR81" t="n">
-        <v>10.22812763709004</v>
+        <v>10.22812764636452</v>
       </c>
       <c r="CS81" t="n">
         <v>7.957659222487079</v>
@@ -42189,7 +42205,7 @@
         <v>-31.06936416184972</v>
       </c>
       <c r="CY81" t="n">
-        <v>-1.557966322270099</v>
+        <v>-1.557966233006591</v>
       </c>
       <c r="CZ81" t="inlineStr">
         <is>
@@ -42488,7 +42504,7 @@
         <v>-38.51</v>
       </c>
       <c r="CF82" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CG82" t="n">
         <v>0.73</v>
@@ -42500,10 +42516,10 @@
         <v>7.289999961853027</v>
       </c>
       <c r="CJ82" t="n">
-        <v>1.314519039035674</v>
+        <v>1.314519039960138</v>
       </c>
       <c r="CK82" t="n">
-        <v>2.438432817411176</v>
+        <v>2.438432819126056</v>
       </c>
       <c r="CL82" t="n">
         <v>10.38629026823146</v>
@@ -42512,13 +42528,13 @@
         <v>10.2240921491844</v>
       </c>
       <c r="CN82" t="n">
-        <v>9.944698464980533</v>
+        <v>9.944698464653436</v>
       </c>
       <c r="CO82" t="n">
-        <v>1.870903153155057</v>
+        <v>1.870903153117818</v>
       </c>
       <c r="CP82" t="n">
-        <v>7.101162637005492</v>
+        <v>7.101162635925126</v>
       </c>
       <c r="CQ82" t="n">
         <v>11.14780863489649</v>
@@ -42834,7 +42850,7 @@
         <v>-23.51</v>
       </c>
       <c r="CF83" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CG83" t="n">
         <v>0.51</v>
@@ -42846,35 +42862,35 @@
         <v>2.809999942779541</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.292616259899638</v>
+        <v>1.292616257880105</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.753817965197323</v>
+        <v>1.753817963314164</v>
       </c>
       <c r="CL83" t="n">
-        <v>3.690088766222673</v>
+        <v>3.690088768025695</v>
       </c>
       <c r="CM83" t="n">
         <v>7.156826027354137</v>
       </c>
       <c r="CN83" t="n">
-        <v>3.72279801533886</v>
+        <v>3.72279801330596</v>
       </c>
       <c r="CO83" t="n">
-        <v>1.339543244863629</v>
+        <v>1.339543244924848</v>
       </c>
       <c r="CP83" t="n">
-        <v>1.815883361870755</v>
+        <v>1.815883363001047</v>
       </c>
       <c r="CQ83" t="inlineStr"/>
       <c r="CR83" t="n">
-        <v>2.269124602232147</v>
+        <v>2.26912460174197</v>
       </c>
       <c r="CS83" t="n">
-        <v>1.784850663534039</v>
+        <v>1.784850663157605</v>
       </c>
       <c r="CT83" t="n">
-        <v>1.606365597180635</v>
+        <v>1.606365596841845</v>
       </c>
       <c r="CU83" t="n">
         <v>6</v>
@@ -42886,10 +42902,10 @@
         <v>5.5</v>
       </c>
       <c r="CX83" t="n">
-        <v>-42.83396334906392</v>
+        <v>-42.83396336112052</v>
       </c>
       <c r="CY83" t="n">
-        <v>-19.24823315164846</v>
+        <v>-19.24823316909247</v>
       </c>
       <c r="CZ83" t="inlineStr">
         <is>
@@ -43192,16 +43208,16 @@
         <v>0.55</v>
       </c>
       <c r="CH84" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CI84" t="n">
         <v>5.059999942779541</v>
       </c>
       <c r="CJ84" t="n">
-        <v>2.992529737882719</v>
+        <v>2.992529739662723</v>
       </c>
       <c r="CK84" t="n">
-        <v>4.357123298357239</v>
+        <v>4.357123300948926</v>
       </c>
       <c r="CL84" t="n">
         <v>4.345499537977475</v>
@@ -43528,7 +43544,7 @@
         <v>39.59</v>
       </c>
       <c r="CF85" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="CG85" t="n">
         <v>0.06</v>
@@ -43886,22 +43902,22 @@
         <v>24.79</v>
       </c>
       <c r="CF86" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="CG86" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="CH86" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="CI86" t="n">
         <v>19.75</v>
       </c>
       <c r="CJ86" t="n">
-        <v>4.796583153302684</v>
+        <v>4.796583160160012</v>
       </c>
       <c r="CK86" t="n">
-        <v>8.89766174937648</v>
+        <v>8.897661762096821</v>
       </c>
       <c r="CL86" t="n">
         <v>32.34703337453646</v>
@@ -43910,13 +43926,13 @@
         <v>34.91315486946326</v>
       </c>
       <c r="CN86" t="n">
-        <v>27.76804119561196</v>
+        <v>27.7680411969185</v>
       </c>
       <c r="CO86" t="n">
-        <v>11.1128623044606</v>
+        <v>11.1128623040154</v>
       </c>
       <c r="CP86" t="n">
-        <v>18.75837316184987</v>
+        <v>18.75837315521198</v>
       </c>
       <c r="CQ86" t="n">
         <v>43.19279988100329</v>
@@ -44240,7 +44256,7 @@
         <v>-43.51</v>
       </c>
       <c r="CF87" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CG87" t="n">
         <v>0.5600000000000001</v>
@@ -44252,25 +44268,25 @@
         <v>1.539999961853027</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.137366363904497</v>
+        <v>0.1373663639263154</v>
       </c>
       <c r="CK87" t="n">
-        <v>0.1568558709586379</v>
+        <v>0.1568558709826298</v>
       </c>
       <c r="CL87" t="n">
-        <v>0.7489968439946652</v>
+        <v>0.7489968439902622</v>
       </c>
       <c r="CM87" t="n">
         <v>3.105192066391262</v>
       </c>
       <c r="CN87" t="n">
-        <v>0.256971489058553</v>
+        <v>0.2569714890707805</v>
       </c>
       <c r="CO87" t="n">
-        <v>0.5416066536806906</v>
+        <v>0.5416066536803429</v>
       </c>
       <c r="CP87" t="n">
-        <v>0.3347614235010402</v>
+        <v>0.334761423497277</v>
       </c>
       <c r="CQ87" t="inlineStr"/>
       <c r="CR87" t="inlineStr"/>
@@ -44584,7 +44600,7 @@
         <v>7.99</v>
       </c>
       <c r="CF88" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="CG88" t="n">
         <v>0.51</v>
@@ -44596,10 +44612,10 @@
         <v>23.73999977111816</v>
       </c>
       <c r="CJ88" t="n">
-        <v>11.96260239098711</v>
+        <v>11.96260253564058</v>
       </c>
       <c r="CK88" t="n">
-        <v>22.19062743528109</v>
+        <v>22.19062770361327</v>
       </c>
       <c r="CL88" t="n">
         <v>14.98594554394072</v>
@@ -44620,13 +44636,13 @@
         <v>22.59513509081805</v>
       </c>
       <c r="CR88" t="n">
-        <v>19.67984503637958</v>
+        <v>19.67984508800279</v>
       </c>
       <c r="CS88" t="n">
-        <v>18.5882864896109</v>
+        <v>18.58828662377699</v>
       </c>
       <c r="CT88" t="n">
-        <v>16.72945784064981</v>
+        <v>16.72945796139929</v>
       </c>
       <c r="CU88" t="n">
         <v>8</v>
@@ -44638,10 +44654,10 @@
         <v>2.9</v>
       </c>
       <c r="CX88" t="n">
-        <v>-29.53050546781093</v>
+        <v>-29.5305049591779</v>
       </c>
       <c r="CY88" t="n">
-        <v>-17.10258961197685</v>
+        <v>-17.10258939452443</v>
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
@@ -44938,7 +44954,7 @@
         <v>13.99</v>
       </c>
       <c r="CF89" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="CG89" t="n">
         <v>0.38</v>
@@ -44950,10 +44966,10 @@
         <v>13.86999988555908</v>
       </c>
       <c r="CJ89" t="n">
-        <v>5.987465630069805</v>
+        <v>5.987465596009873</v>
       </c>
       <c r="CK89" t="n">
-        <v>8.717749957381638</v>
+        <v>8.717749907790374</v>
       </c>
       <c r="CL89" t="n">
         <v>3.748648617718671</v>
@@ -45269,7 +45285,7 @@
         <v>1.1</v>
       </c>
       <c r="CG90" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="CH90" t="n">
         <v>0.06</v>
@@ -45278,10 +45294,10 @@
         <v>56.88999938964844</v>
       </c>
       <c r="CJ90" t="n">
-        <v>11.93657435517729</v>
+        <v>11.93657438578461</v>
       </c>
       <c r="CK90" t="n">
-        <v>17.37965226113814</v>
+        <v>17.37965230570239</v>
       </c>
       <c r="CL90" t="inlineStr"/>
       <c r="CM90" t="inlineStr"/>
@@ -45292,13 +45308,13 @@
       <c r="CP90" t="inlineStr"/>
       <c r="CQ90" t="inlineStr"/>
       <c r="CR90" t="n">
-        <v>18.54797553877181</v>
+        <v>18.547975563829</v>
       </c>
       <c r="CS90" t="n">
-        <v>17.37965226113814</v>
+        <v>17.37965230570239</v>
       </c>
       <c r="CT90" t="n">
-        <v>15.64168703502433</v>
+        <v>15.64168707513215</v>
       </c>
       <c r="CU90" t="n">
         <v>3</v>
@@ -45310,10 +45326,10 @@
         <v>2.2</v>
       </c>
       <c r="CX90" t="n">
-        <v>-72.50538371798532</v>
+        <v>-72.50538364748466</v>
       </c>
       <c r="CY90" t="n">
-        <v>-67.39677318023183</v>
+        <v>-67.39677313618684</v>
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
@@ -45623,19 +45639,19 @@
         <v>2.34</v>
       </c>
       <c r="CG91" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="CI91" t="n">
         <v>7.300000190734863</v>
       </c>
       <c r="CJ91" t="n">
-        <v>3.038124459502561</v>
+        <v>3.038124462302955</v>
       </c>
       <c r="CK91" t="n">
-        <v>5.63572087237725</v>
+        <v>5.635720877571981</v>
       </c>
       <c r="CL91" t="n">
         <v>14.2452139215371</v>
@@ -45644,23 +45660,23 @@
         <v>15.34435408510034</v>
       </c>
       <c r="CN91" t="n">
-        <v>13.46365965158283</v>
+        <v>13.46365965301287</v>
       </c>
       <c r="CO91" t="n">
-        <v>14.9759088140881</v>
+        <v>14.97590881352097</v>
       </c>
       <c r="CP91" t="n">
-        <v>7.397471757039193</v>
+        <v>7.397471754308697</v>
       </c>
       <c r="CQ91" t="inlineStr"/>
       <c r="CR91" t="n">
-        <v>11.84372151695413</v>
+        <v>11.84372151750866</v>
       </c>
       <c r="CS91" t="n">
-        <v>13.85443678655997</v>
+        <v>13.85443678727498</v>
       </c>
       <c r="CT91" t="n">
-        <v>12.46899310790397</v>
+        <v>12.46899310854749</v>
       </c>
       <c r="CU91" t="n">
         <v>6</v>
@@ -45672,10 +45688,10 @@
         <v>5.1</v>
       </c>
       <c r="CX91" t="n">
-        <v>70.80812030292243</v>
+        <v>70.80812031173768</v>
       </c>
       <c r="CY91" t="n">
-        <v>62.242756267132</v>
+        <v>62.24275627472824</v>
       </c>
       <c r="CZ91" t="inlineStr">
         <is>
@@ -45978,16 +45994,16 @@
         <v>0.45</v>
       </c>
       <c r="CH92" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="CI92" t="n">
         <v>7.559999942779541</v>
       </c>
       <c r="CJ92" t="n">
-        <v>4.86695111414545</v>
+        <v>4.86695112992545</v>
       </c>
       <c r="CK92" t="n">
-        <v>7.086280822195776</v>
+        <v>7.086280845171456</v>
       </c>
       <c r="CL92" t="n">
         <v>5.841307533796971</v>
@@ -46006,13 +46022,13 @@
         <v>7.559999942779542</v>
       </c>
       <c r="CR92" t="n">
-        <v>6.519624763366863</v>
+        <v>6.519624769826144</v>
       </c>
       <c r="CS92" t="n">
-        <v>6.463794177996373</v>
+        <v>6.463794189484213</v>
       </c>
       <c r="CT92" t="n">
-        <v>5.817414760196736</v>
+        <v>5.817414770535792</v>
       </c>
       <c r="CU92" t="n">
         <v>6</v>
@@ -46024,10 +46040,10 @@
         <v>5.9</v>
       </c>
       <c r="CX92" t="n">
-        <v>-23.05006872714498</v>
+        <v>-23.05006859038497</v>
       </c>
       <c r="CY92" t="n">
-        <v>-13.76157655141687</v>
+        <v>-13.76157646597664</v>
       </c>
       <c r="CZ92" t="inlineStr">
         <is>
@@ -46062,7 +46078,7 @@
         <v>-5.735666941749762</v>
       </c>
       <c r="DL92" t="n">
-        <v>-22.08914579674445</v>
+        <v>-22.08913798508859</v>
       </c>
       <c r="DM92" t="b">
         <v>0</v>
@@ -46328,7 +46344,7 @@
         <v>-34.11</v>
       </c>
       <c r="CF93" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="CG93" t="n">
         <v>0.44</v>
@@ -46340,10 +46356,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="CJ93" t="n">
-        <v>33.64104981347511</v>
+        <v>33.64105013375441</v>
       </c>
       <c r="CK93" t="n">
-        <v>62.40414740399633</v>
+        <v>62.40414799811442</v>
       </c>
       <c r="CL93" t="n">
         <v>4.72848169808231</v>
@@ -46672,7 +46688,7 @@
         <v>0.09</v>
       </c>
       <c r="CF94" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="CG94" t="n">
         <v>0.57</v>
@@ -46684,10 +46700,10 @@
         <v>77.84999847412109</v>
       </c>
       <c r="CJ94" t="n">
-        <v>58.20380560785301</v>
+        <v>58.20380565380607</v>
       </c>
       <c r="CK94" t="n">
-        <v>84.74474096503397</v>
+        <v>84.74474103194164</v>
       </c>
       <c r="CL94" t="n">
         <v>24.29162868679446</v>
@@ -47032,10 +47048,10 @@
         <v>35.06999969482422</v>
       </c>
       <c r="CJ95" t="n">
-        <v>8.685425107862285</v>
+        <v>8.685425063697842</v>
       </c>
       <c r="CK95" t="n">
-        <v>16.11146357508454</v>
+        <v>16.1114634931595</v>
       </c>
       <c r="CL95" t="n">
         <v>40.37163301098357</v>
@@ -47044,19 +47060,19 @@
         <v>40.71977393255172</v>
       </c>
       <c r="CN95" t="n">
-        <v>33.68935119010778</v>
+        <v>33.68935121448065</v>
       </c>
       <c r="CO95" t="n">
-        <v>50.04888341890143</v>
+        <v>50.04888343082393</v>
       </c>
       <c r="CP95" t="n">
-        <v>22.67531723123637</v>
+        <v>22.6753172803225</v>
       </c>
       <c r="CQ95" t="n">
         <v>53.59781982634511</v>
       </c>
       <c r="CR95" t="n">
-        <v>36.74489174074436</v>
+        <v>36.74489174123813</v>
       </c>
       <c r="CS95" t="n">
         <v>40.37163301098357</v>
@@ -47077,7 +47093,7 @@
         <v>3.605560382276285</v>
       </c>
       <c r="CY95" t="n">
-        <v>4.775854178770711</v>
+        <v>4.775854180178696</v>
       </c>
       <c r="CZ95" t="inlineStr">
         <is>
@@ -47388,10 +47404,10 @@
         <v>19.60000038146973</v>
       </c>
       <c r="CJ96" t="n">
-        <v>2.02311250687244</v>
+        <v>2.023112509588572</v>
       </c>
       <c r="CK96" t="n">
-        <v>3.752873700248376</v>
+        <v>3.7528737052868</v>
       </c>
       <c r="CL96" t="n">
         <v>10.14849570357459</v>
@@ -47400,19 +47416,19 @@
         <v>8.468407387765433</v>
       </c>
       <c r="CN96" t="n">
-        <v>9.993116425766724</v>
+        <v>9.993116420252131</v>
       </c>
       <c r="CO96" t="n">
-        <v>7.53704755753497</v>
+        <v>7.5370475569177</v>
       </c>
       <c r="CP96" t="n">
-        <v>7.631782581286059</v>
+        <v>7.631782576885709</v>
       </c>
       <c r="CQ96" t="n">
         <v>13.57810210946071</v>
       </c>
       <c r="CR96" t="n">
-        <v>8.729975066519552</v>
+        <v>8.729975065734726</v>
       </c>
       <c r="CS96" t="n">
         <v>8.468407387765433</v>
@@ -47433,7 +47449,7 @@
         <v>-61.11445662932493</v>
       </c>
       <c r="CY96" t="n">
-        <v>-55.45931175198822</v>
+        <v>-55.45931175599244</v>
       </c>
       <c r="CZ96" t="inlineStr">
         <is>
@@ -47720,41 +47736,41 @@
         <v>0.73</v>
       </c>
       <c r="CH97" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="CI97" t="n">
         <v>20.73999977111816</v>
       </c>
       <c r="CJ97" t="n">
-        <v>12.36547793219175</v>
+        <v>12.36547780805222</v>
       </c>
       <c r="CK97" t="n">
-        <v>15.45170008663538</v>
+        <v>15.45170001374955</v>
       </c>
       <c r="CL97" t="n">
-        <v>22.54773478006032</v>
+        <v>22.54773490006369</v>
       </c>
       <c r="CM97" t="n">
         <v>42.26262419215048</v>
       </c>
       <c r="CN97" t="n">
-        <v>27.43829175921822</v>
+        <v>27.43829168639332</v>
       </c>
       <c r="CO97" t="n">
-        <v>15.73774691535128</v>
+        <v>15.73774692378999</v>
       </c>
       <c r="CP97" t="n">
-        <v>10.74135038466847</v>
+        <v>10.74135047195346</v>
       </c>
       <c r="CQ97" t="inlineStr"/>
       <c r="CR97" t="n">
-        <v>16.52566492855968</v>
+        <v>16.52566491141386</v>
       </c>
       <c r="CS97" t="n">
-        <v>15.59472350099333</v>
+        <v>15.59472346876977</v>
       </c>
       <c r="CT97" t="n">
-        <v>14.035251150894</v>
+        <v>14.0352511218928</v>
       </c>
       <c r="CU97" t="n">
         <v>4</v>
@@ -47766,10 +47782,10 @@
         <v>1.8</v>
       </c>
       <c r="CX97" t="n">
-        <v>-32.32762147645237</v>
+        <v>-32.32762161628459</v>
       </c>
       <c r="CY97" t="n">
-        <v>-20.31984035229946</v>
+        <v>-20.31984043496975</v>
       </c>
       <c r="CZ97" t="inlineStr">
         <is>
@@ -48096,10 +48112,10 @@
         <v>16.06999969482422</v>
       </c>
       <c r="CJ98" t="n">
-        <v>8.091824739186727</v>
+        <v>8.091824732257566</v>
       </c>
       <c r="CK98" t="n">
-        <v>15.01033489119138</v>
+        <v>15.01033487833778</v>
       </c>
       <c r="CL98" t="n">
         <v>10.3162546490514</v>
@@ -48120,7 +48136,7 @@
         <v>9.788675943501032</v>
       </c>
       <c r="CR98" t="n">
-        <v>12.35123165400832</v>
+        <v>12.35123165153547</v>
       </c>
       <c r="CS98" t="n">
         <v>10.05246529627622</v>
@@ -48141,7 +48157,7 @@
         <v>-43.70118893304959</v>
       </c>
       <c r="CY98" t="n">
-        <v>-23.14105856525705</v>
+        <v>-23.14105858064501</v>
       </c>
       <c r="CZ98" t="inlineStr">
         <is>
@@ -48448,49 +48464,49 @@
         <v>-13.81</v>
       </c>
       <c r="CF99" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="CG99" t="n">
         <v>0.52</v>
       </c>
       <c r="CH99" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI99" t="n">
         <v>23.02000045776367</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.041728689042804</v>
+        <v>5.041728694974245</v>
       </c>
       <c r="CK99" t="n">
-        <v>7.160497310241811</v>
+        <v>7.16049731156464</v>
       </c>
       <c r="CL99" t="n">
-        <v>10.60050389130764</v>
+        <v>10.60050388079481</v>
       </c>
       <c r="CM99" t="n">
         <v>14.5401656991646</v>
       </c>
       <c r="CN99" t="n">
-        <v>7.144307641829629</v>
+        <v>7.144307635949774</v>
       </c>
       <c r="CO99" t="n">
-        <v>8.435991782087836</v>
+        <v>8.435991781337139</v>
       </c>
       <c r="CP99" t="n">
-        <v>5.268241681168365</v>
+        <v>5.268241675103111</v>
       </c>
       <c r="CQ99" t="n">
         <v>10.72812653727006</v>
       </c>
       <c r="CR99" t="n">
-        <v>8.614945404014094</v>
+        <v>8.614945402019796</v>
       </c>
       <c r="CS99" t="n">
-        <v>7.798244546164824</v>
+        <v>7.798244546450889</v>
       </c>
       <c r="CT99" t="n">
-        <v>7.018420091548342</v>
+        <v>7.0184200918058</v>
       </c>
       <c r="CU99" t="n">
         <v>8</v>
@@ -48502,10 +48518,10 @@
         <v>2.9</v>
       </c>
       <c r="CX99" t="n">
-        <v>-69.51164225897604</v>
+        <v>-69.51164225785762</v>
       </c>
       <c r="CY99" t="n">
-        <v>-62.57625876324152</v>
+        <v>-62.57625877190485</v>
       </c>
       <c r="CZ99" t="inlineStr">
         <is>
@@ -48810,7 +48826,7 @@
         <v>0.34</v>
       </c>
       <c r="CH100" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="CI100" t="n">
         <v>7.46999979019165</v>
@@ -49156,16 +49172,16 @@
         <v>0.26</v>
       </c>
       <c r="CH101" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="CI101" t="n">
         <v>45.29999923706055</v>
       </c>
       <c r="CJ101" t="n">
-        <v>9.911113081611143</v>
+        <v>9.911113141181689</v>
       </c>
       <c r="CK101" t="n">
-        <v>18.38511476638867</v>
+        <v>18.38511487689203</v>
       </c>
       <c r="CL101" t="n">
         <v>85.6241069744725</v>
@@ -49174,13 +49190,13 @@
         <v>75.68006991304929</v>
       </c>
       <c r="CN101" t="n">
-        <v>103.2210458403269</v>
+        <v>103.2210458221905</v>
       </c>
       <c r="CO101" t="n">
-        <v>16.15577153069092</v>
+        <v>16.15577152765509</v>
       </c>
       <c r="CP101" t="n">
-        <v>69.70318642357508</v>
+        <v>69.70318633739319</v>
       </c>
       <c r="CQ101" t="n">
         <v>21.32072017314016</v>
@@ -49520,25 +49536,25 @@
         <v>48</v>
       </c>
       <c r="CJ102" t="n">
-        <v>18.44917489228007</v>
+        <v>18.44917498344724</v>
       </c>
       <c r="CK102" t="n">
-        <v>20.25471222237935</v>
+        <v>20.25471226405904</v>
       </c>
       <c r="CL102" t="n">
-        <v>23.61424223493288</v>
+        <v>23.61424216683523</v>
       </c>
       <c r="CM102" t="n">
         <v>51.21267904692464</v>
       </c>
       <c r="CN102" t="n">
-        <v>19.53680541322071</v>
+        <v>19.53680539399297</v>
       </c>
       <c r="CO102" t="n">
-        <v>23.25457276776683</v>
+        <v>23.25457276018243</v>
       </c>
       <c r="CP102" t="n">
-        <v>10.13948925521774</v>
+        <v>10.13948919280105</v>
       </c>
       <c r="CQ102" t="n">
         <v>119.4939863979636</v>
@@ -49862,7 +49878,7 @@
         <v>-4.31</v>
       </c>
       <c r="CF103" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CG103" t="n">
         <v>0.65</v>
@@ -49874,37 +49890,37 @@
         <v>53.11999893188477</v>
       </c>
       <c r="CJ103" t="n">
-        <v>16.22648838867131</v>
+        <v>16.22648838310892</v>
       </c>
       <c r="CK103" t="n">
-        <v>24.67943852213583</v>
+        <v>24.67943851893409</v>
       </c>
       <c r="CL103" t="n">
-        <v>44.49393104691806</v>
+        <v>44.49393105639813</v>
       </c>
       <c r="CM103" t="n">
         <v>61.84069244222911</v>
       </c>
       <c r="CN103" t="n">
-        <v>35.49872157398222</v>
+        <v>35.49872157565641</v>
       </c>
       <c r="CO103" t="n">
-        <v>26.76189247215356</v>
+        <v>26.76189247263418</v>
       </c>
       <c r="CP103" t="n">
-        <v>22.24510780998028</v>
+        <v>22.24510781480666</v>
       </c>
       <c r="CQ103" t="n">
         <v>21.78028972750627</v>
       </c>
       <c r="CR103" t="n">
-        <v>31.69082024794708</v>
+        <v>31.69082024890922</v>
       </c>
       <c r="CS103" t="n">
-        <v>25.72066549714469</v>
+        <v>25.72066549578414</v>
       </c>
       <c r="CT103" t="n">
-        <v>23.14859894743023</v>
+        <v>23.14859894620573</v>
       </c>
       <c r="CU103" t="n">
         <v>8</v>
@@ -49916,10 +49932,10 @@
         <v>3.8</v>
       </c>
       <c r="CX103" t="n">
-        <v>-56.42206435825905</v>
+        <v>-56.42206436056421</v>
       </c>
       <c r="CY103" t="n">
-        <v>-40.3410751408638</v>
+        <v>-40.34107513905255</v>
       </c>
       <c r="CZ103" t="inlineStr">
         <is>
@@ -50234,7 +50250,7 @@
         <v>-8.609999999999999</v>
       </c>
       <c r="CF104" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CG104" t="n">
         <v>0.6899999999999999</v>
@@ -50246,10 +50262,10 @@
         <v>11.98999977111816</v>
       </c>
       <c r="CJ104" t="n">
-        <v>2.133538110379315</v>
+        <v>2.133538110164374</v>
       </c>
       <c r="CK104" t="n">
-        <v>3.957713194753629</v>
+        <v>3.957713194354913</v>
       </c>
       <c r="CL104" t="n">
         <v>12.12728984483326</v>
@@ -50258,25 +50274,25 @@
         <v>13.42500643241197</v>
       </c>
       <c r="CN104" t="n">
-        <v>8.723292611194086</v>
+        <v>8.723292611278838</v>
       </c>
       <c r="CO104" t="n">
-        <v>5.736755016008477</v>
+        <v>5.73675501602689</v>
       </c>
       <c r="CP104" t="n">
-        <v>6.495066894544941</v>
+        <v>6.495066894742601</v>
       </c>
       <c r="CQ104" t="n">
         <v>11.98999977111816</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.922160537837788</v>
+        <v>8.922160537823805</v>
       </c>
       <c r="CS104" t="n">
-        <v>8.723292611194086</v>
+        <v>8.723292611278838</v>
       </c>
       <c r="CT104" t="n">
-        <v>7.850963350074678</v>
+        <v>7.850963350150955</v>
       </c>
       <c r="CU104" t="n">
         <v>7</v>
@@ -50288,10 +50304,10 @@
         <v>6.3</v>
       </c>
       <c r="CX104" t="n">
-        <v>-34.52073811555617</v>
+        <v>-34.52073811492</v>
       </c>
       <c r="CY104" t="n">
-        <v>-25.58664964006313</v>
+        <v>-25.58664964017976</v>
       </c>
       <c r="CZ104" t="inlineStr">
         <is>
@@ -50596,16 +50612,16 @@
         <v>0.65</v>
       </c>
       <c r="CH105" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CI105" t="n">
         <v>2.990000009536743</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.6261539976464989</v>
+        <v>0.6261539978697558</v>
       </c>
       <c r="CK105" t="n">
-        <v>1.161515665634255</v>
+        <v>1.161515666048397</v>
       </c>
       <c r="CL105" t="n">
         <v>3.424157314292294</v>
@@ -50614,13 +50630,13 @@
         <v>3.957621711457321</v>
       </c>
       <c r="CN105" t="n">
-        <v>2.391887522035988</v>
+        <v>2.391887522007015</v>
       </c>
       <c r="CO105" t="n">
-        <v>2.63593210470331</v>
+        <v>2.635932104674615</v>
       </c>
       <c r="CP105" t="n">
-        <v>1.717596294544028</v>
+        <v>1.71759629435601</v>
       </c>
       <c r="CQ105" t="n">
         <v>9.031114164496099</v>
@@ -50946,10 +50962,10 @@
         <v>55.97999954223633</v>
       </c>
       <c r="CJ106" t="n">
-        <v>63.36141952990894</v>
+        <v>63.36141986344016</v>
       </c>
       <c r="CK106" t="n">
-        <v>92.25422683554743</v>
+        <v>92.25422732116887</v>
       </c>
       <c r="CL106" t="n">
         <v>24.49272171810087</v>
@@ -51564,7 +51580,7 @@
         <v>113.9</v>
       </c>
       <c r="BN108" t="n">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="BO108" t="n">
         <v>3.7</v>
@@ -51618,22 +51634,22 @@
         <v>-4.61</v>
       </c>
       <c r="CF108" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CG108" t="n">
         <v>0.37</v>
       </c>
       <c r="CH108" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="CI108" t="n">
         <v>93.48999786376953</v>
       </c>
       <c r="CJ108" t="n">
-        <v>4.770651245838067</v>
+        <v>4.770651222896008</v>
       </c>
       <c r="CK108" t="n">
-        <v>8.849558061029615</v>
+        <v>8.849558018472095</v>
       </c>
       <c r="CL108" t="n">
         <v>41.68043309875323</v>
@@ -51642,13 +51658,13 @@
         <v>41.35009616132553</v>
       </c>
       <c r="CN108" t="n">
-        <v>34.48348109840035</v>
+        <v>34.48348112937985</v>
       </c>
       <c r="CO108" t="n">
-        <v>17.71052554911851</v>
+        <v>17.71052555125246</v>
       </c>
       <c r="CP108" t="n">
-        <v>28.6662502383411</v>
+        <v>28.66625026460701</v>
       </c>
       <c r="CQ108" t="n">
         <v>43.17568011524377</v>
@@ -51954,7 +51970,7 @@
         <v>0.43</v>
       </c>
       <c r="CH109" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="CI109" t="n">
         <v>3.440000057220459</v>
@@ -52648,10 +52664,10 @@
         <v>16.80999946594238</v>
       </c>
       <c r="CJ111" t="n">
-        <v>3.156562015256176</v>
+        <v>3.156562023749237</v>
       </c>
       <c r="CK111" t="n">
-        <v>5.855422538300205</v>
+        <v>5.855422554054835</v>
       </c>
       <c r="CL111" t="n">
         <v>14.76027123417737</v>
@@ -52660,23 +52676,23 @@
         <v>15.74308637108966</v>
       </c>
       <c r="CN111" t="n">
-        <v>10.52287702166827</v>
+        <v>10.52287701611182</v>
       </c>
       <c r="CO111" t="n">
-        <v>13.03155742470394</v>
+        <v>13.03155742323248</v>
       </c>
       <c r="CP111" t="n">
-        <v>7.749500261327545</v>
+        <v>7.749500252882044</v>
       </c>
       <c r="CQ111" t="inlineStr"/>
       <c r="CR111" t="n">
-        <v>11.27711914187783</v>
+        <v>11.2771191419247</v>
       </c>
       <c r="CS111" t="n">
-        <v>11.7772172231861</v>
+        <v>11.77721721967215</v>
       </c>
       <c r="CT111" t="n">
-        <v>10.59949550086749</v>
+        <v>10.59949549770493</v>
       </c>
       <c r="CU111" t="n">
         <v>6</v>
@@ -52688,10 +52704,10 @@
         <v>5</v>
       </c>
       <c r="CX111" t="n">
-        <v>-36.94529543357557</v>
+        <v>-36.94529545238914</v>
       </c>
       <c r="CY111" t="n">
-        <v>-32.91422070104375</v>
+        <v>-32.91422070076493</v>
       </c>
       <c r="CZ111" t="inlineStr">
         <is>
@@ -53002,25 +53018,25 @@
         <v>14.85999965667725</v>
       </c>
       <c r="CJ112" t="n">
-        <v>3.752078046683459</v>
+        <v>3.75207804173702</v>
       </c>
       <c r="CK112" t="n">
-        <v>4.765173631934386</v>
+        <v>4.765173626483628</v>
       </c>
       <c r="CL112" t="n">
-        <v>14.23467811913275</v>
+        <v>14.23467812161593</v>
       </c>
       <c r="CM112" t="n">
         <v>37.15722486020687</v>
       </c>
       <c r="CN112" t="n">
-        <v>9.753710223925788</v>
+        <v>9.753710219403988</v>
       </c>
       <c r="CO112" t="n">
-        <v>48.40225972060971</v>
+        <v>48.40225972144808</v>
       </c>
       <c r="CP112" t="n">
-        <v>6.836198272962788</v>
+        <v>6.836198274716993</v>
       </c>
       <c r="CQ112" t="n">
         <v>26.75481109869832</v>
@@ -53336,7 +53352,7 @@
         <v>-7.51</v>
       </c>
       <c r="CF113" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CG113" t="n">
         <v>0.58</v>
@@ -53348,25 +53364,25 @@
         <v>15.07999992370605</v>
       </c>
       <c r="CJ113" t="n">
-        <v>1.411262811797934</v>
+        <v>1.411262806999364</v>
       </c>
       <c r="CK113" t="n">
-        <v>2.597759195687962</v>
+        <v>2.597759189848424</v>
       </c>
       <c r="CL113" t="n">
-        <v>8.680968839890916</v>
+        <v>8.680968849893841</v>
       </c>
       <c r="CM113" t="n">
         <v>10.74592199386089</v>
       </c>
       <c r="CN113" t="n">
-        <v>4.788475178546209</v>
+        <v>4.788475181301741</v>
       </c>
       <c r="CO113" t="n">
-        <v>7.68644533851518</v>
+        <v>7.686445339141198</v>
       </c>
       <c r="CP113" t="n">
-        <v>4.229952532585253</v>
+        <v>4.229952536166137</v>
       </c>
       <c r="CQ113" t="n">
         <v>11.59983842664191</v>
@@ -53688,16 +53704,16 @@
         <v>0.49</v>
       </c>
       <c r="CH114" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="CI114" t="n">
         <v>18.61000061035156</v>
       </c>
       <c r="CJ114" t="n">
-        <v>11.90170574698305</v>
+        <v>11.90170574936053</v>
       </c>
       <c r="CK114" t="n">
-        <v>14.8512589103658</v>
+        <v>14.85125891333249</v>
       </c>
       <c r="CL114" t="inlineStr"/>
       <c r="CM114" t="inlineStr"/>
@@ -54020,22 +54036,22 @@
         <v>49.69</v>
       </c>
       <c r="CF115" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="CG115" t="n">
         <v>0.12</v>
       </c>
       <c r="CH115" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="CI115" t="n">
         <v>11.22999954223633</v>
       </c>
       <c r="CJ115" t="n">
-        <v>2.440256526494057</v>
+        <v>2.44025652418362</v>
       </c>
       <c r="CK115" t="n">
-        <v>4.526675856646476</v>
+        <v>4.526675852360615</v>
       </c>
       <c r="CL115" t="n">
         <v>12.16659803226748</v>
@@ -54044,13 +54060,13 @@
         <v>12.69335782761144</v>
       </c>
       <c r="CN115" t="n">
-        <v>9.603046495621939</v>
+        <v>9.603046496797198</v>
       </c>
       <c r="CO115" t="n">
-        <v>0.792228799202753</v>
+        <v>0.7922287992334364</v>
       </c>
       <c r="CP115" t="n">
-        <v>6.733329370753338</v>
+        <v>6.73332937315453</v>
       </c>
       <c r="CQ115" t="n">
         <v>7.252132997019516</v>
@@ -54366,7 +54382,7 @@
         <v>-38.91</v>
       </c>
       <c r="CF116" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CG116" t="n">
         <v>0.58</v>
@@ -54378,25 +54394,25 @@
         <v>8.729999542236328</v>
       </c>
       <c r="CJ116" t="n">
-        <v>2.245062960086118</v>
+        <v>2.245062956253568</v>
       </c>
       <c r="CK116" t="n">
-        <v>2.428788987143962</v>
+        <v>2.428788984056157</v>
       </c>
       <c r="CL116" t="n">
-        <v>3.200197922463793</v>
+        <v>3.20019792385833</v>
       </c>
       <c r="CM116" t="n">
         <v>9.960089719584371</v>
       </c>
       <c r="CN116" t="n">
-        <v>1.879358619930695</v>
+        <v>1.879358619472565</v>
       </c>
       <c r="CO116" t="n">
-        <v>5.908796684173925</v>
+        <v>5.908796684468956</v>
       </c>
       <c r="CP116" t="n">
-        <v>1.350429546044499</v>
+        <v>1.350429547356457</v>
       </c>
       <c r="CQ116" t="n">
         <v>14.4055417732344</v>
@@ -54736,10 +54752,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="CJ117" t="n">
-        <v>1.479717414986534</v>
+        <v>1.4797173986632</v>
       </c>
       <c r="CK117" t="n">
-        <v>1.542194372508188</v>
+        <v>1.542194355495646</v>
       </c>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
@@ -55066,16 +55082,16 @@
         <v>0.49</v>
       </c>
       <c r="CH118" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="CI118" t="n">
         <v>3.299999952316284</v>
       </c>
       <c r="CJ118" t="n">
-        <v>1.626197854239676</v>
+        <v>1.626197854306633</v>
       </c>
       <c r="CK118" t="n">
-        <v>3.016597019614599</v>
+        <v>3.016597019738804</v>
       </c>
       <c r="CL118" t="n">
         <v>1.164757575071677</v>
@@ -55084,7 +55100,7 @@
         <v>4.664417662006795</v>
       </c>
       <c r="CN118" t="n">
-        <v>1.617388636414298</v>
+        <v>1.617388636439268</v>
       </c>
       <c r="CO118" t="n">
         <v>0.7445919647652398</v>
@@ -55742,7 +55758,7 @@
         <v>-24.91</v>
       </c>
       <c r="CF120" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CG120" t="n">
         <v>0.55</v>
@@ -55754,25 +55770,25 @@
         <v>3.579999923706055</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.227444786121344</v>
+        <v>1.227444785702649</v>
       </c>
       <c r="CK120" t="n">
-        <v>1.245483074011054</v>
+        <v>1.245483073737726</v>
       </c>
       <c r="CL120" t="n">
-        <v>1.296712679585207</v>
+        <v>1.29671267974296</v>
       </c>
       <c r="CM120" t="n">
         <v>4.00156132911066</v>
       </c>
       <c r="CN120" t="n">
-        <v>0.8906598608742239</v>
+        <v>0.8906598608456477</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.169812865308901</v>
+        <v>2.169812865340906</v>
       </c>
       <c r="CP120" t="n">
-        <v>0.4979842688587034</v>
+        <v>0.4979842690248753</v>
       </c>
       <c r="CQ120" t="n">
         <v>5.182181461454665</v>
@@ -56092,7 +56108,7 @@
         <v>-20.11</v>
       </c>
       <c r="CF121" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CG121" t="n">
         <v>0.61</v>
@@ -56104,10 +56120,10 @@
         <v>5.480000019073486</v>
       </c>
       <c r="CJ121" t="n">
-        <v>5.433654012781385</v>
+        <v>5.433654021227039</v>
       </c>
       <c r="CK121" t="n">
-        <v>7.911400242609698</v>
+        <v>7.911400254906569</v>
       </c>
       <c r="CL121" t="inlineStr"/>
       <c r="CM121" t="inlineStr"/>
@@ -56116,13 +56132,13 @@
       <c r="CP121" t="inlineStr"/>
       <c r="CQ121" t="inlineStr"/>
       <c r="CR121" t="n">
-        <v>6.672527127695542</v>
+        <v>6.672527138066805</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.672527127695542</v>
+        <v>6.672527138066805</v>
       </c>
       <c r="CT121" t="n">
-        <v>6.005274414925988</v>
+        <v>6.005274424260125</v>
       </c>
       <c r="CU121" t="n">
         <v>2</v>
@@ -56134,10 +56150,10 @@
         <v>1.5</v>
       </c>
       <c r="CX121" t="n">
-        <v>9.585299161026484</v>
+        <v>9.585299331357433</v>
       </c>
       <c r="CY121" t="n">
-        <v>21.76144351225165</v>
+        <v>21.76144370150826</v>
       </c>
       <c r="CZ121" t="inlineStr">
         <is>
@@ -56448,10 +56464,10 @@
         <v>5.320000171661377</v>
       </c>
       <c r="CJ122" t="n">
-        <v>5.856172584950135</v>
+        <v>5.856172586203457</v>
       </c>
       <c r="CK122" t="n">
-        <v>10.44092071230025</v>
+        <v>10.44092071453479</v>
       </c>
       <c r="CL122" t="inlineStr"/>
       <c r="CM122" t="inlineStr"/>
@@ -56460,13 +56476,13 @@
       <c r="CP122" t="inlineStr"/>
       <c r="CQ122" t="inlineStr"/>
       <c r="CR122" t="n">
-        <v>8.148546648625194</v>
+        <v>8.148546650369124</v>
       </c>
       <c r="CS122" t="n">
-        <v>8.148546648625194</v>
+        <v>8.148546650369124</v>
       </c>
       <c r="CT122" t="n">
-        <v>7.333691983762675</v>
+        <v>7.333691985332211</v>
       </c>
       <c r="CU122" t="n">
         <v>2</v>
@@ -56478,10 +56494,10 @@
         <v>1.8</v>
       </c>
       <c r="CX122" t="n">
-        <v>37.85134863017203</v>
+        <v>37.85134865967458</v>
       </c>
       <c r="CY122" t="n">
-        <v>53.16816514463558</v>
+        <v>53.16816517741621</v>
       </c>
       <c r="CZ122" t="inlineStr">
         <is>
@@ -56774,22 +56790,22 @@
         <v>-0.91</v>
       </c>
       <c r="CF123" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="CG123" t="n">
         <v>0.62</v>
       </c>
       <c r="CH123" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="CI123" t="n">
         <v>22</v>
       </c>
       <c r="CJ123" t="n">
-        <v>38.1906839733824</v>
+        <v>38.19068404821391</v>
       </c>
       <c r="CK123" t="n">
-        <v>70.84371877062435</v>
+        <v>70.84371890943679</v>
       </c>
       <c r="CL123" t="n">
         <v>19.69594594594594</v>
@@ -56808,7 +56824,7 @@
       </c>
       <c r="CQ123" t="inlineStr"/>
       <c r="CR123" t="n">
-        <v>25.80022399918462</v>
+        <v>25.80022401165654</v>
       </c>
       <c r="CS123" t="n">
         <v>22.95973920566808</v>
@@ -56829,7 +56845,7 @@
         <v>-6.073794158630585</v>
       </c>
       <c r="CY123" t="n">
-        <v>17.27374545083917</v>
+        <v>17.27374550752971</v>
       </c>
       <c r="CZ123" t="inlineStr">
         <is>
@@ -57128,37 +57144,37 @@
         <v>-17.61</v>
       </c>
       <c r="CF124" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CG124" t="n">
         <v>0.48</v>
       </c>
       <c r="CH124" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="CI124" t="n">
         <v>9.119999885559082</v>
       </c>
       <c r="CJ124" t="n">
-        <v>3.524021699254168</v>
+        <v>3.524021708007403</v>
       </c>
       <c r="CK124" t="n">
-        <v>3.636304816647377</v>
+        <v>3.636304824286649</v>
       </c>
       <c r="CL124" t="n">
-        <v>4.384765274369339</v>
+        <v>4.384765272689786</v>
       </c>
       <c r="CM124" t="n">
         <v>18.94853141028272</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.444738686050912</v>
+        <v>3.444738691311974</v>
       </c>
       <c r="CO124" t="n">
-        <v>7.741903460654555</v>
+        <v>7.741903460300273</v>
       </c>
       <c r="CP124" t="n">
-        <v>1.731607259690655</v>
+        <v>1.73160725797292</v>
       </c>
       <c r="CQ124" t="n">
         <v>21.91904750827104</v>
@@ -57474,7 +57490,7 @@
         <v>-40.51</v>
       </c>
       <c r="CF125" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CG125" t="n">
         <v>0.37</v>
@@ -57486,10 +57502,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.7838805198704599</v>
+        <v>0.7838805201790018</v>
       </c>
       <c r="CK125" t="n">
-        <v>1.454098364359703</v>
+        <v>1.454098364932048</v>
       </c>
       <c r="CL125" t="n">
         <v>15.56199010537595</v>
@@ -57498,13 +57514,13 @@
         <v>16.26314871365512</v>
       </c>
       <c r="CN125" t="n">
-        <v>13.64124870084413</v>
+        <v>13.64124870077692</v>
       </c>
       <c r="CO125" t="n">
-        <v>1.677467519643003</v>
+        <v>1.677467519636447</v>
       </c>
       <c r="CP125" t="n">
-        <v>11.00817213172695</v>
+        <v>11.00817213140765</v>
       </c>
       <c r="CQ125" t="inlineStr"/>
       <c r="CR125" t="inlineStr"/>
@@ -57819,10 +57835,10 @@
         <v>0.95</v>
       </c>
       <c r="CG126" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="CH126" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="CI126" t="n">
         <v>5.639999866485596</v>
@@ -58156,25 +58172,25 @@
         <v>18.89999961853027</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.6514987515067816</v>
+        <v>0.6514987542346277</v>
       </c>
       <c r="CK127" t="n">
-        <v>0.8686880024110349</v>
+        <v>0.868688005772836</v>
       </c>
       <c r="CL127" t="n">
-        <v>4.575616735741728</v>
+        <v>4.575616734290998</v>
       </c>
       <c r="CM127" t="n">
         <v>11.51795868166206</v>
       </c>
       <c r="CN127" t="n">
-        <v>1.753689385904809</v>
+        <v>1.75368938538235</v>
       </c>
       <c r="CO127" t="n">
-        <v>0.6737070722795241</v>
+        <v>0.6737070722592274</v>
       </c>
       <c r="CP127" t="n">
-        <v>2.240011212565463</v>
+        <v>2.240011211626866</v>
       </c>
       <c r="CQ127" t="n">
         <v>18.89999961853027</v>
@@ -58510,10 +58526,10 @@
         <v>5.199999809265137</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.285816888271798</v>
+        <v>1.285816875972246</v>
       </c>
       <c r="CK128" t="n">
-        <v>2.151989901189437</v>
+        <v>2.15198988060446</v>
       </c>
       <c r="CL128" t="inlineStr"/>
       <c r="CM128" t="inlineStr"/>
@@ -58524,13 +58540,13 @@
         <v>5.739109502577318</v>
       </c>
       <c r="CR128" t="n">
-        <v>1.718903394730618</v>
+        <v>1.718903378288353</v>
       </c>
       <c r="CS128" t="n">
-        <v>1.718903394730618</v>
+        <v>1.718903378288353</v>
       </c>
       <c r="CT128" t="n">
-        <v>1.547013055257556</v>
+        <v>1.547013040459517</v>
       </c>
       <c r="CU128" t="n">
         <v>2</v>
@@ -58542,10 +58558,10 @@
         <v>4.5</v>
       </c>
       <c r="CX128" t="n">
-        <v>-70.24974784612195</v>
+        <v>-70.24974813069961</v>
       </c>
       <c r="CY128" t="n">
-        <v>-66.94416427346883</v>
+        <v>-66.94416458966624</v>
       </c>
       <c r="CZ128" t="inlineStr">
         <is>
@@ -58840,10 +58856,10 @@
         <v>-7.11</v>
       </c>
       <c r="CF129" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="CG129" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="CH129" t="n">
         <v>0.16</v>
@@ -58852,10 +58868,10 @@
         <v>17.1299991607666</v>
       </c>
       <c r="CJ129" t="n">
-        <v>1.320220912501634</v>
+        <v>1.320220912227982</v>
       </c>
       <c r="CK129" t="n">
-        <v>1.922241648602379</v>
+        <v>1.922241648203942</v>
       </c>
       <c r="CL129" t="n">
         <v>1.219133588393709</v>
@@ -59194,37 +59210,37 @@
         <v>17.60000038146973</v>
       </c>
       <c r="CJ130" t="n">
-        <v>2.120561565831044</v>
+        <v>2.120561565960465</v>
       </c>
       <c r="CK130" t="n">
-        <v>3.74706914825758</v>
+        <v>3.7470691483819</v>
       </c>
       <c r="CL130" t="n">
-        <v>9.708886929469553</v>
+        <v>9.708886929199128</v>
       </c>
       <c r="CM130" t="n">
         <v>12.04387609297388</v>
       </c>
       <c r="CN130" t="n">
-        <v>5.629015781179113</v>
+        <v>5.629015781092154</v>
       </c>
       <c r="CO130" t="n">
-        <v>5.61396960672481</v>
+        <v>5.61396960671333</v>
       </c>
       <c r="CP130" t="n">
-        <v>4.777582988268952</v>
+        <v>4.777582988164515</v>
       </c>
       <c r="CQ130" t="n">
         <v>16.00722579327991</v>
       </c>
       <c r="CR130" t="n">
-        <v>6.920066757812315</v>
+        <v>6.92006675775415</v>
       </c>
       <c r="CS130" t="n">
-        <v>5.621492693951962</v>
+        <v>5.621492693902742</v>
       </c>
       <c r="CT130" t="n">
-        <v>5.059343424556766</v>
+        <v>5.059343424512468</v>
       </c>
       <c r="CU130" t="n">
         <v>6</v>
@@ -59236,10 +59252,10 @@
         <v>7.5</v>
       </c>
       <c r="CX130" t="n">
-        <v>-71.25373116534971</v>
+        <v>-71.25373116560138</v>
       </c>
       <c r="CY130" t="n">
-        <v>-60.68143972827325</v>
+        <v>-60.68143972860371</v>
       </c>
       <c r="CZ130" t="inlineStr">
         <is>
@@ -59542,10 +59558,10 @@
         <v>4.300000190734863</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.9034764887162958</v>
+        <v>0.9034764882710575</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.675948886568729</v>
+        <v>1.675948885742812</v>
       </c>
       <c r="CL131" t="inlineStr"/>
       <c r="CM131" t="inlineStr"/>
@@ -59554,13 +59570,13 @@
       <c r="CP131" t="inlineStr"/>
       <c r="CQ131" t="inlineStr"/>
       <c r="CR131" t="n">
-        <v>1.289712687642512</v>
+        <v>1.289712687006935</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.289712687642512</v>
+        <v>1.289712687006935</v>
       </c>
       <c r="CT131" t="n">
-        <v>1.160741418878261</v>
+        <v>1.160741418306241</v>
       </c>
       <c r="CU131" t="n">
         <v>2</v>
@@ -59572,10 +59588,10 @@
         <v>1.9</v>
       </c>
       <c r="CX131" t="n">
-        <v>-73.00601471182976</v>
+        <v>-73.00601472513254</v>
       </c>
       <c r="CY131" t="n">
-        <v>-70.00668301314418</v>
+        <v>-70.00668302792505</v>
       </c>
       <c r="CZ131" t="inlineStr">
         <is>
@@ -59876,7 +59892,7 @@
         <v>-55.31</v>
       </c>
       <c r="CF132" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CG132" t="n">
         <v>0.58</v>
@@ -59888,10 +59904,10 @@
         <v>1.159999966621399</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.3412092489664997</v>
+        <v>0.3412092497059581</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.632943156832857</v>
+        <v>0.6329431582045523</v>
       </c>
       <c r="CL132" t="inlineStr"/>
       <c r="CM132" t="inlineStr"/>
@@ -59900,13 +59916,13 @@
       <c r="CP132" t="inlineStr"/>
       <c r="CQ132" t="inlineStr"/>
       <c r="CR132" t="n">
-        <v>0.4870762028996783</v>
+        <v>0.4870762039552552</v>
       </c>
       <c r="CS132" t="n">
-        <v>0.4870762028996783</v>
+        <v>0.4870762039552552</v>
       </c>
       <c r="CT132" t="n">
-        <v>0.4383685826097105</v>
+        <v>0.4383685835597297</v>
       </c>
       <c r="CU132" t="n">
         <v>2</v>
@@ -59918,10 +59934,10 @@
         <v>1.9</v>
       </c>
       <c r="CX132" t="n">
-        <v>-62.20960386003309</v>
+        <v>-62.20960377813489</v>
       </c>
       <c r="CY132" t="n">
-        <v>-58.01067095559234</v>
+        <v>-58.01067086459432</v>
       </c>
       <c r="CZ132" t="inlineStr">
         <is>
@@ -60218,10 +60234,10 @@
         <v>-52.21</v>
       </c>
       <c r="CF133" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="CH133" t="n">
         <v>0.09</v>
@@ -60572,10 +60588,10 @@
         <v>36.66999816894531</v>
       </c>
       <c r="CJ134" t="n">
-        <v>8.259335392706145</v>
+        <v>8.259335376224392</v>
       </c>
       <c r="CK134" t="n">
-        <v>12.02559233178015</v>
+        <v>12.02559230778271</v>
       </c>
       <c r="CL134" t="n">
         <v>7.913840650695814</v>
@@ -60902,10 +60918,10 @@
         <v>-39.11</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CG135" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="CH135" t="n">
         <v>0.06</v>
@@ -60914,10 +60930,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="CJ135" t="n">
-        <v>1.051467708320171</v>
+        <v>1.051467708524754</v>
       </c>
       <c r="CK135" t="n">
-        <v>1.950472598933916</v>
+        <v>1.950472599313419</v>
       </c>
       <c r="CL135" t="inlineStr"/>
       <c r="CM135" t="inlineStr"/>
@@ -60928,13 +60944,13 @@
         <v>3.016723380133466</v>
       </c>
       <c r="CR135" t="n">
-        <v>2.006221229129185</v>
+        <v>2.00622122932388</v>
       </c>
       <c r="CS135" t="n">
-        <v>1.950472598933916</v>
+        <v>1.950472599313419</v>
       </c>
       <c r="CT135" t="n">
-        <v>1.755425339040525</v>
+        <v>1.755425339382077</v>
       </c>
       <c r="CU135" t="n">
         <v>3</v>
@@ -60946,10 +60962,10 @@
         <v>2.9</v>
       </c>
       <c r="CX135" t="n">
-        <v>-68.14110224825237</v>
+        <v>-68.14110224205359</v>
       </c>
       <c r="CY135" t="n">
-        <v>-63.58945288943637</v>
+        <v>-63.58945288590287</v>
       </c>
       <c r="CZ135" t="inlineStr">
         <is>
@@ -61268,25 +61284,25 @@
         <v>5.059999942779541</v>
       </c>
       <c r="CJ136" t="n">
-        <v>1.571374047624458</v>
+        <v>1.571374055208644</v>
       </c>
       <c r="CK136" t="n">
-        <v>1.72616391778095</v>
+        <v>1.726163924234201</v>
       </c>
       <c r="CL136" t="n">
-        <v>2.472176042263926</v>
+        <v>2.472176039574258</v>
       </c>
       <c r="CM136" t="n">
         <v>7.797277570738014</v>
       </c>
       <c r="CN136" t="n">
-        <v>1.720646377183937</v>
+        <v>1.720646379877317</v>
       </c>
       <c r="CO136" t="n">
-        <v>1.780873812301823</v>
+        <v>1.780873812082804</v>
       </c>
       <c r="CP136" t="n">
-        <v>1.062205241003706</v>
+        <v>1.062205238540968</v>
       </c>
       <c r="CQ136" t="n">
         <v>0.3314895236109327</v>
@@ -61600,7 +61616,7 @@
         <v>-24.11</v>
       </c>
       <c r="CF137" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CG137" t="n">
         <v>0.41</v>
@@ -61612,10 +61628,10 @@
         <v>2.160000085830688</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.6064459270512225</v>
+        <v>0.6064459286224482</v>
       </c>
       <c r="CK137" t="n">
-        <v>0.88298526978658</v>
+        <v>0.8829852720742848</v>
       </c>
       <c r="CL137" t="n">
         <v>0.3540983747263424</v>
@@ -61932,7 +61948,7 @@
         <v>-106.31</v>
       </c>
       <c r="CF138" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CG138" t="n">
         <v>0.25</v>
@@ -62270,10 +62286,10 @@
         <v>6.900000095367432</v>
       </c>
       <c r="CJ139" t="n">
-        <v>1.893532151969579</v>
+        <v>1.893532150608669</v>
       </c>
       <c r="CK139" t="n">
-        <v>2.756982813267707</v>
+        <v>2.756982811286222</v>
       </c>
       <c r="CL139" t="n">
         <v>1.700071096702708</v>
@@ -62598,7 +62614,7 @@
         <v>-15.11</v>
       </c>
       <c r="CF140" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="CG140" t="n">
         <v>0.66</v>
@@ -63258,7 +63274,7 @@
         <v>-17.51</v>
       </c>
       <c r="CF142" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CG142" t="n">
         <v>0.31</v>
@@ -63270,10 +63286,10 @@
         <v>18.26000022888184</v>
       </c>
       <c r="CJ142" t="n">
-        <v>27.71516706538424</v>
+        <v>27.71516693967599</v>
       </c>
       <c r="CK142" t="n">
-        <v>37.07673460746958</v>
+        <v>37.07673443929988</v>
       </c>
       <c r="CL142" t="n">
         <v>2.525466010009227</v>
@@ -63282,7 +63298,7 @@
         <v>7.009520407943455</v>
       </c>
       <c r="CN142" t="n">
-        <v>6.461779413052558</v>
+        <v>6.461779387579761</v>
       </c>
       <c r="CO142" t="n">
         <v>3.155500877947406</v>
@@ -63602,7 +63618,7 @@
         <v>-55.51</v>
       </c>
       <c r="CF143" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CG143" t="n">
         <v>0.59</v>
@@ -63614,25 +63630,25 @@
         <v>4.809999942779541</v>
       </c>
       <c r="CJ143" t="n">
-        <v>0.8069513386740899</v>
+        <v>0.8069513405341675</v>
       </c>
       <c r="CK143" t="n">
-        <v>0.8074471860744921</v>
+        <v>0.8074471878170711</v>
       </c>
       <c r="CL143" t="n">
-        <v>0.8152301134035532</v>
+        <v>0.8152301132837682</v>
       </c>
       <c r="CM143" t="n">
         <v>6.116141997685596</v>
       </c>
       <c r="CN143" t="n">
-        <v>0.2687596879002719</v>
+        <v>0.2687596883120737</v>
       </c>
       <c r="CO143" t="n">
-        <v>0.4172981554943293</v>
+        <v>0.4172981554868033</v>
       </c>
       <c r="CP143" t="n">
-        <v>0.3052495648164678</v>
+        <v>0.3052495646871551</v>
       </c>
       <c r="CQ143" t="inlineStr"/>
       <c r="CR143" t="inlineStr"/>
@@ -63952,16 +63968,16 @@
         <v>0.64</v>
       </c>
       <c r="CH144" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="CI144" t="n">
         <v>3.900000095367432</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.7054953886754096</v>
+        <v>0.7054953870063031</v>
       </c>
       <c r="CK144" t="n">
-        <v>1.308693945992885</v>
+        <v>1.308693942896692</v>
       </c>
       <c r="CL144" t="inlineStr"/>
       <c r="CM144" t="inlineStr"/>
@@ -63972,13 +63988,13 @@
         <v>3.536464154706048</v>
       </c>
       <c r="CR144" t="n">
-        <v>1.007094667334147</v>
+        <v>1.007094664951498</v>
       </c>
       <c r="CS144" t="n">
-        <v>1.007094667334147</v>
+        <v>1.007094664951498</v>
       </c>
       <c r="CT144" t="n">
-        <v>0.9063852006007324</v>
+        <v>0.9063851984563478</v>
       </c>
       <c r="CU144" t="n">
         <v>2</v>
@@ -63990,10 +64006,10 @@
         <v>5</v>
       </c>
       <c r="CX144" t="n">
-        <v>-76.75935439905832</v>
+        <v>-76.75935445404254</v>
       </c>
       <c r="CY144" t="n">
-        <v>-74.17706044339813</v>
+        <v>-74.17706050449171</v>
       </c>
       <c r="CZ144" t="inlineStr">
         <is>
@@ -64302,10 +64318,10 @@
         <v>18.89999961853027</v>
       </c>
       <c r="CJ145" t="n">
-        <v>9.581535690849366</v>
+        <v>9.581535674623231</v>
       </c>
       <c r="CK145" t="n">
-        <v>13.95071596587668</v>
+        <v>13.95071594225143</v>
       </c>
       <c r="CL145" t="n">
         <v>4.677772394876603</v>
@@ -64980,13 +64996,13 @@
         <v>-26.01</v>
       </c>
       <c r="CF147" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="CG147" t="n">
         <v>0.29</v>
       </c>
       <c r="CH147" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CI147" t="n">
         <v>1.860000014305115</v>
@@ -65322,22 +65338,22 @@
         <v>-14.31</v>
       </c>
       <c r="CF148" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CG148" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="CH148" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="CI148" t="n">
         <v>11.1899995803833</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.978835466724885</v>
+        <v>5.978835440215578</v>
       </c>
       <c r="CK148" t="n">
-        <v>10.94348328761273</v>
+        <v>10.94348323909088</v>
       </c>
       <c r="CL148" t="inlineStr"/>
       <c r="CM148" t="inlineStr"/>
@@ -65348,13 +65364,13 @@
         <v>3.360116783680318</v>
       </c>
       <c r="CR148" t="n">
-        <v>6.760811846005979</v>
+        <v>6.760811820995592</v>
       </c>
       <c r="CS148" t="n">
-        <v>5.978835466724885</v>
+        <v>5.978835440215578</v>
       </c>
       <c r="CT148" t="n">
-        <v>5.380951920052397</v>
+        <v>5.38095189619402</v>
       </c>
       <c r="CU148" t="n">
         <v>3</v>
@@ -65366,10 +65382,10 @@
         <v>3.3</v>
       </c>
       <c r="CX148" t="n">
-        <v>-51.91284967083012</v>
+        <v>-51.91284988404172</v>
       </c>
       <c r="CY148" t="n">
-        <v>-39.58166130892388</v>
+        <v>-39.58166153243048</v>
       </c>
       <c r="CZ148" t="inlineStr">
         <is>
@@ -65664,7 +65680,7 @@
         <v>20.39</v>
       </c>
       <c r="CF149" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="CG149" t="n">
         <v>0.55</v>
@@ -66026,10 +66042,10 @@
         <v>15.23999977111816</v>
       </c>
       <c r="CJ150" t="n">
-        <v>3.899624962941292</v>
+        <v>3.899624948224281</v>
       </c>
       <c r="CK150" t="n">
-        <v>5.677853946042522</v>
+        <v>5.677853924614553</v>
       </c>
       <c r="CL150" t="inlineStr"/>
       <c r="CM150" t="inlineStr"/>
@@ -66040,7 +66056,7 @@
         <v>5.474834427405684</v>
       </c>
       <c r="CR150" t="n">
-        <v>5.017437778796499</v>
+        <v>5.017437766748173</v>
       </c>
       <c r="CS150" t="n">
         <v>5.474834427405684</v>
@@ -66061,7 +66077,7 @@
         <v>-67.66830013998357</v>
       </c>
       <c r="CY150" t="n">
-        <v>-67.07717943470567</v>
+        <v>-67.07717951376293</v>
       </c>
       <c r="CZ150" t="inlineStr">
         <is>

--- a/reports/screener_2026-09-01.xlsx
+++ b/reports/screener_2026-09-01.xlsx
@@ -1278,10 +1278,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.806389186744216</v>
+        <v>5.806389169061072</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085194141052</v>
+        <v>10.77085190860829</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -1290,10 +1290,10 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.9863169180497</v>
+        <v>66.98631684731713</v>
       </c>
       <c r="CO2" t="n">
-        <v>19.57807411896471</v>
+        <v>19.76753935237404</v>
       </c>
       <c r="CP2" t="n">
         <v>35.30034653799875</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958258126554</v>
+        <v>14.76958268167085</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.39757568824757</v>
+        <v>27.39757587449942</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -1640,13 +1640,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097393955392</v>
+        <v>74.51097375230589</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789240272657</v>
+        <v>48.47789232821682</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.3567960233152</v>
+        <v>26.35679571353672</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -1978,10 +1978,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247029102893</v>
+        <v>16.22247029995932</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268238985866</v>
+        <v>30.09268240642453</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -1990,19 +1990,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.553772682851</v>
+        <v>125.5537726798479</v>
       </c>
       <c r="CO4" t="n">
-        <v>26.09980883464424</v>
+        <v>25.70896311038452</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944657614642</v>
+        <v>61.8994465569868</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.24259007506706</v>
+        <v>47.17744912059148</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -2023,7 +2023,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>93.22122127159973</v>
+        <v>92.95479610823401</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224631188787</v>
+        <v>3.770224629224546</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.9937666908552</v>
+        <v>6.993766687211532</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -2348,25 +2348,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502456754474</v>
+        <v>25.12502456886212</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762152661</v>
+        <v>11.21765762231827</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.5948613080749</v>
+        <v>10.59486131297011</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533149445299</v>
+        <v>9.312533149785834</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802515730468</v>
+        <v>9.655802518178071</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222264157422</v>
+        <v>8.690222266360264</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -2378,10 +2378,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029413121739</v>
+        <v>109.4029413652544</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.398383986562</v>
+        <v>124.3983839947677</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933216131584</v>
+        <v>3.224933225533877</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251115924088</v>
+        <v>5.982251133365341</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -2708,7 +2708,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385724241296</v>
+        <v>24.33385727115359</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -2720,7 +2720,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929365660842</v>
+        <v>11.46929366320583</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -2741,7 +2741,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862773447082</v>
+        <v>159.4862774939709</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418017947997</v>
+        <v>18.62418025063309</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785423293535</v>
+        <v>34.54785436492438</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -3058,23 +3058,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694234461283</v>
+        <v>100.3694233343052</v>
       </c>
       <c r="CO7" t="n">
-        <v>48.35621747253571</v>
+        <v>47.8454123413184</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710168912232</v>
+        <v>59.21710154611024</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.18367405856277</v>
+        <v>44.05597282654397</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.45203585273553</v>
+        <v>41.19663335312139</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.30683226746198</v>
+        <v>37.07697001780925</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -3086,10 +3086,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-23.66107410916782</v>
+        <v>-24.13142863070796</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.589369706870309</v>
+        <v>-9.850677737993419</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.401689195225291</v>
+        <v>6.40168918913402</v>
       </c>
       <c r="CK8" t="n">
-        <v>11.87513345714291</v>
+        <v>11.87513344584361</v>
       </c>
       <c r="CL8" t="n">
         <v>25.33800212822936</v>
@@ -3416,19 +3416,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN8" t="n">
-        <v>35.10892156206317</v>
+        <v>35.10892157198074</v>
       </c>
       <c r="CO8" t="n">
-        <v>12.29620298372775</v>
+        <v>12.29620298488673</v>
       </c>
       <c r="CP8" t="n">
-        <v>20.31530580329477</v>
+        <v>20.31530581605768</v>
       </c>
       <c r="CQ8" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR8" t="n">
-        <v>20.27452914057966</v>
+        <v>20.27452914237111</v>
       </c>
       <c r="CS8" t="n">
         <v>18.56484347595736</v>
@@ -3449,7 +3449,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY8" t="n">
-        <v>29.13712985279737</v>
+        <v>29.13712986420787</v>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ9" t="n">
-        <v>127.5892448772487</v>
+        <v>127.5892443491088</v>
       </c>
       <c r="CK9" t="n">
-        <v>236.6780492472963</v>
+        <v>236.6780482675968</v>
       </c>
       <c r="CL9" t="n">
         <v>132.6522965266787</v>
@@ -3790,13 +3790,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR9" t="n">
-        <v>139.7795671325697</v>
+        <v>139.7795669440898</v>
       </c>
       <c r="CS9" t="n">
-        <v>124.3641616074097</v>
+        <v>124.3641613433398</v>
       </c>
       <c r="CT9" t="n">
-        <v>111.9277454466687</v>
+        <v>111.9277452090058</v>
       </c>
       <c r="CU9" t="n">
         <v>8</v>
@@ -3808,10 +3808,10 @@
         <v>5.6</v>
       </c>
       <c r="CX9" t="n">
-        <v>157.0097529448853</v>
+        <v>157.0097523991609</v>
       </c>
       <c r="CY9" t="n">
-        <v>220.9634203934013</v>
+        <v>220.9634199606116</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL9" t="n">
-        <v>-8.627331177634668</v>
+        <v>-8.627323714303436</v>
       </c>
       <c r="DM9" t="b">
         <v>1</v>
@@ -4130,10 +4130,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ10" t="n">
-        <v>45.30199151837756</v>
+        <v>45.30199113338053</v>
       </c>
       <c r="CK10" t="n">
-        <v>84.03519426659035</v>
+        <v>84.03519355242089</v>
       </c>
       <c r="CL10" t="n">
         <v>67.58333047231037</v>
@@ -4154,7 +4154,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR10" t="n">
-        <v>76.94607072603911</v>
+        <v>76.94607056901533</v>
       </c>
       <c r="CS10" t="n">
         <v>67.58333047231037</v>
@@ -4175,7 +4175,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY10" t="n">
-        <v>137.1950492707072</v>
+        <v>137.1950487866635</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -4498,37 +4498,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ11" t="n">
-        <v>24.2161267267157</v>
+        <v>24.21612672531058</v>
       </c>
       <c r="CK11" t="n">
-        <v>32.67790194611635</v>
+        <v>32.67790195654321</v>
       </c>
       <c r="CL11" t="n">
-        <v>34.37896777756509</v>
+        <v>34.37896779052954</v>
       </c>
       <c r="CM11" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN11" t="n">
-        <v>48.80739054378653</v>
+        <v>48.80739055469227</v>
       </c>
       <c r="CO11" t="n">
-        <v>50.94836380976193</v>
+        <v>50.94836381156785</v>
       </c>
       <c r="CP11" t="n">
-        <v>16.89191283540633</v>
+        <v>16.8919128436142</v>
       </c>
       <c r="CQ11" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR11" t="n">
-        <v>31.61206967241048</v>
+        <v>31.6120696777737</v>
       </c>
       <c r="CS11" t="n">
-        <v>28.44701433641603</v>
+        <v>28.4470143409269</v>
       </c>
       <c r="CT11" t="n">
-        <v>25.60231290277442</v>
+        <v>25.60231290683421</v>
       </c>
       <c r="CU11" t="n">
         <v>8</v>
@@ -4540,10 +4540,10 @@
         <v>3</v>
       </c>
       <c r="CX11" t="n">
-        <v>-21.46529416834684</v>
+        <v>-21.46529415589349</v>
       </c>
       <c r="CY11" t="n">
-        <v>-3.030456588808916</v>
+        <v>-3.030456572357343</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ12" t="n">
-        <v>133.9252033008311</v>
+        <v>133.9252023858741</v>
       </c>
       <c r="CK12" t="n">
-        <v>248.4312521230417</v>
+        <v>248.4312504257963</v>
       </c>
       <c r="CL12" t="n">
         <v>131.5457818930041</v>
@@ -4884,7 +4884,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR12" t="n">
-        <v>141.1793357418161</v>
+        <v>141.1793354152908</v>
       </c>
       <c r="CS12" t="n">
         <v>125.8371913580247</v>
@@ -4905,7 +4905,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY12" t="n">
-        <v>192.5996595685309</v>
+        <v>192.5996588917945</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>0.3954558219285254</v>
       </c>
       <c r="DL12" t="n">
-        <v>-9.168913901075104</v>
+        <v>-9.168920601679343</v>
       </c>
       <c r="DM12" t="b">
         <v>1</v>
@@ -5206,10 +5206,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ13" t="n">
-        <v>13.26532630262742</v>
+        <v>13.2653263333155</v>
       </c>
       <c r="CK13" t="n">
-        <v>24.60718029137386</v>
+        <v>24.60718034830025</v>
       </c>
       <c r="CL13" t="n">
         <v>19.93179967973907</v>
@@ -5218,7 +5218,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN13" t="n">
-        <v>33.72989543812618</v>
+        <v>33.72989547161279</v>
       </c>
       <c r="CO13" t="n">
         <v>22.8984489302328</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
-        <v>20.17568880099329</v>
+        <v>20.1756888228969</v>
       </c>
       <c r="CS13" t="n">
         <v>21.41512430498593</v>
@@ -5249,7 +5249,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY13" t="n">
-        <v>4.537251805954523</v>
+        <v>4.537251919444762</v>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="AV14" t="b">
         <v>1</v>
@@ -5568,10 +5568,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ14" t="n">
-        <v>3.228277665486087</v>
+        <v>3.228277656794087</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.98845506947669</v>
+        <v>5.988455053353031</v>
       </c>
       <c r="CL14" t="n">
         <v>19.81956093381139</v>
@@ -5580,7 +5580,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN14" t="n">
-        <v>31.89244534462692</v>
+        <v>31.89244531916918</v>
       </c>
       <c r="CO14" t="n">
         <v>10.95072400487419</v>
@@ -5926,10 +5926,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ15" t="n">
-        <v>10.67756763704817</v>
+        <v>10.67756767844085</v>
       </c>
       <c r="CK15" t="n">
-        <v>19.80688796672435</v>
+        <v>19.80688804350778</v>
       </c>
       <c r="CL15" t="n">
         <v>38.98902044102951</v>
@@ -5938,25 +5938,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN15" t="n">
-        <v>44.33179745358975</v>
+        <v>44.33179747510008</v>
       </c>
       <c r="CO15" t="n">
-        <v>34.59948399450583</v>
+        <v>34.59948398607202</v>
       </c>
       <c r="CP15" t="n">
-        <v>19.85450036331167</v>
+        <v>19.85450031530278</v>
       </c>
       <c r="CQ15" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR15" t="n">
-        <v>32.77627193818945</v>
+        <v>32.77627194416817</v>
       </c>
       <c r="CS15" t="n">
-        <v>34.59948399450583</v>
+        <v>34.59948398607202</v>
       </c>
       <c r="CT15" t="n">
-        <v>31.13953559505525</v>
+        <v>31.13953558746482</v>
       </c>
       <c r="CU15" t="n">
         <v>7</v>
@@ -5968,10 +5968,10 @@
         <v>4.2</v>
       </c>
       <c r="CX15" t="n">
-        <v>78.75737921167733</v>
+        <v>78.75737916810424</v>
       </c>
       <c r="CY15" t="n">
-        <v>88.15311018737093</v>
+        <v>88.15311022169192</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>-0.6274991787955986</v>
       </c>
       <c r="DL15" t="n">
-        <v>-23.70303752784818</v>
+        <v>-23.70303109613396</v>
       </c>
       <c r="DM15" t="b">
         <v>1</v>
@@ -6286,37 +6286,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ16" t="n">
-        <v>24.99231901236771</v>
+        <v>24.9923191544161</v>
       </c>
       <c r="CK16" t="n">
-        <v>31.99913693845138</v>
+        <v>31.99913671117761</v>
       </c>
       <c r="CL16" t="n">
-        <v>35.87977396685041</v>
+        <v>35.8797735080852</v>
       </c>
       <c r="CM16" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN16" t="n">
-        <v>50.332770974964</v>
+        <v>50.33277069131262</v>
       </c>
       <c r="CO16" t="n">
-        <v>48.65905505261815</v>
+        <v>48.65905499129359</v>
       </c>
       <c r="CP16" t="n">
-        <v>17.29535409769133</v>
+        <v>17.29535377830975</v>
       </c>
       <c r="CQ16" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR16" t="n">
-        <v>34.65367029381299</v>
+        <v>34.65367014276948</v>
       </c>
       <c r="CS16" t="n">
-        <v>33.9394554526509</v>
+        <v>33.9394551096314</v>
       </c>
       <c r="CT16" t="n">
-        <v>30.54550990738581</v>
+        <v>30.54550959866826</v>
       </c>
       <c r="CU16" t="n">
         <v>8</v>
@@ -6328,10 +6328,10 @@
         <v>2.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>-12.12453572397498</v>
+        <v>-12.12453661211524</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0.3058919242074354</v>
+        <v>-0.305892358740012</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -6646,37 +6646,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.03288993429703</v>
+        <v>10.03288994712749</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.09423444451794</v>
+        <v>18.09423440962371</v>
       </c>
       <c r="CL17" t="n">
-        <v>23.57397890982145</v>
+        <v>23.57397883421233</v>
       </c>
       <c r="CM17" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN17" t="n">
-        <v>36.27022042017696</v>
+        <v>36.27022040828844</v>
       </c>
       <c r="CO17" t="n">
-        <v>24.18418239442536</v>
+        <v>24.18418238883785</v>
       </c>
       <c r="CP17" t="n">
-        <v>11.54642594411629</v>
+        <v>11.54642591600218</v>
       </c>
       <c r="CQ17" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR17" t="n">
-        <v>18.89005843022205</v>
+        <v>18.89005841231417</v>
       </c>
       <c r="CS17" t="n">
-        <v>17.75138480502874</v>
+        <v>17.75138478758163</v>
       </c>
       <c r="CT17" t="n">
-        <v>15.97624632452587</v>
+        <v>15.97624630882347</v>
       </c>
       <c r="CU17" t="n">
         <v>8</v>
@@ -6688,10 +6688,10 @@
         <v>3.6</v>
       </c>
       <c r="CX17" t="n">
-        <v>59.60285673550369</v>
+        <v>59.60285657863653</v>
       </c>
       <c r="CY17" t="n">
-        <v>88.71186811483376</v>
+        <v>88.71186793593391</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.337978118893381</v>
+        <v>3.337978094534551</v>
       </c>
       <c r="CK18" t="n">
-        <v>6.191949410547221</v>
+        <v>6.191949365361591</v>
       </c>
       <c r="CL18" t="n">
         <v>19.28911530241674</v>
@@ -7018,13 +7018,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.60183925804898</v>
+        <v>20.60183926079271</v>
       </c>
       <c r="CO18" t="n">
-        <v>15.92145422559568</v>
+        <v>15.92145423049115</v>
       </c>
       <c r="CP18" t="n">
-        <v>12.84225511981982</v>
+        <v>12.84225515070877</v>
       </c>
       <c r="CQ18" t="n">
         <v>29.10394270806049</v>
@@ -7233,13 +7233,13 @@
         <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AV19" t="b">
         <v>1</v>
       </c>
       <c r="AW19" t="n">
-        <v>3638864896</v>
+        <v>5782441984</v>
       </c>
       <c r="AX19" t="n">
         <v>6.76</v>
@@ -7356,10 +7356,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ19" t="n">
-        <v>9.410499907685351</v>
+        <v>9.410499890742297</v>
       </c>
       <c r="CK19" t="n">
-        <v>17.45647732875632</v>
+        <v>17.45647729732696</v>
       </c>
       <c r="CL19" t="n">
         <v>21.3058429709553</v>
@@ -7368,25 +7368,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN19" t="n">
-        <v>30.17445897866877</v>
+        <v>30.17445903082277</v>
       </c>
       <c r="CO19" t="n">
-        <v>25.20917159245645</v>
+        <v>25.20917160528171</v>
       </c>
       <c r="CP19" t="n">
-        <v>11.01207336027179</v>
+        <v>11.01207341511035</v>
       </c>
       <c r="CQ19" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR19" t="n">
-        <v>17.05929121723047</v>
+        <v>17.05929122616115</v>
       </c>
       <c r="CS19" t="n">
-        <v>15.01197250485499</v>
+        <v>15.0119724891403</v>
       </c>
       <c r="CT19" t="n">
-        <v>13.51077525436949</v>
+        <v>13.51077524022627</v>
       </c>
       <c r="CU19" t="n">
         <v>8</v>
@@ -7398,10 +7398,10 @@
         <v>3.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>24.29416188236308</v>
+        <v>24.29416175225072</v>
       </c>
       <c r="CY19" t="n">
-        <v>56.93920328273354</v>
+        <v>56.93920336489246</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ20" t="n">
-        <v>7.255085128776883</v>
+        <v>7.255085112878843</v>
       </c>
       <c r="CK20" t="n">
-        <v>13.45818291388112</v>
+        <v>13.45818288439025</v>
       </c>
       <c r="CL20" t="n">
         <v>35.08558886655294</v>
@@ -7728,19 +7728,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN20" t="n">
-        <v>43.31704739773711</v>
+        <v>43.3170474218836</v>
       </c>
       <c r="CO20" t="n">
-        <v>26.42844994870688</v>
+        <v>26.42844995275339</v>
       </c>
       <c r="CP20" t="n">
-        <v>28.12717779471024</v>
+        <v>28.12717782341828</v>
       </c>
       <c r="CQ20" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR20" t="n">
-        <v>28.30913260239695</v>
+        <v>28.30913260631269</v>
       </c>
       <c r="CS20" t="n">
         <v>27.73936337556392</v>
@@ -7761,7 +7761,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY20" t="n">
-        <v>3.393475055184525</v>
+        <v>3.393475069485996</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -8084,10 +8084,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ21" t="n">
-        <v>3.140372326759291</v>
+        <v>3.14037232458228</v>
       </c>
       <c r="CK21" t="n">
-        <v>5.825390666138484</v>
+        <v>5.825390662100129</v>
       </c>
       <c r="CL21" t="n">
         <v>32.87416582383663</v>
@@ -8096,7 +8096,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN21" t="n">
-        <v>42.11194018644908</v>
+        <v>42.11194018305507</v>
       </c>
       <c r="CO21" t="n">
         <v>10.85340539909456</v>
@@ -8414,10 +8414,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ22" t="n">
-        <v>36.63430045133594</v>
+        <v>36.63430055379242</v>
       </c>
       <c r="CK22" t="n">
-        <v>53.33954145714513</v>
+        <v>53.33954160632177</v>
       </c>
       <c r="CL22" t="n">
         <v>48.73630032327193</v>
@@ -8427,20 +8427,20 @@
       </c>
       <c r="CN22" t="inlineStr"/>
       <c r="CO22" t="n">
-        <v>58.62355366270413</v>
+        <v>59.50416498381771</v>
       </c>
       <c r="CP22" t="n">
         <v>12.51880241820309</v>
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
-        <v>49.33342397361428</v>
+        <v>49.55357686680095</v>
       </c>
       <c r="CS22" t="n">
-        <v>51.03792089020853</v>
+        <v>51.03792096479685</v>
       </c>
       <c r="CT22" t="n">
-        <v>45.93412880118768</v>
+        <v>45.93412886831716</v>
       </c>
       <c r="CU22" t="n">
         <v>4</v>
@@ -8452,10 +8452,10 @@
         <v>1.6</v>
       </c>
       <c r="CX22" t="n">
-        <v>14.77793172357822</v>
+        <v>14.77793189131804</v>
       </c>
       <c r="CY22" t="n">
-        <v>23.27192256201949</v>
+        <v>23.82202973510415</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.414124722491619</v>
+        <v>3.414124724269988</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.333201360221953</v>
+        <v>6.333201363520827</v>
       </c>
       <c r="CL23" t="n">
         <v>31.64000679932063</v>
@@ -8790,7 +8790,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN23" t="n">
-        <v>39.13586008508427</v>
+        <v>39.13586008681204</v>
       </c>
       <c r="CO23" t="n">
         <v>10.59424454785779</v>
@@ -8852,7 +8852,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL23" t="n">
-        <v>-27.83707532184228</v>
+        <v>-27.83708127316356</v>
       </c>
       <c r="DM23" t="b">
         <v>1</v>
@@ -9108,35 +9108,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ24" t="n">
-        <v>8.694392929132208</v>
+        <v>8.694392932746011</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.60549913882544</v>
+        <v>13.60549913479195</v>
       </c>
       <c r="CL24" t="n">
-        <v>17.89239265542053</v>
+        <v>17.89239264267922</v>
       </c>
       <c r="CM24" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.47099643024767</v>
+        <v>22.47099642670662</v>
       </c>
       <c r="CO24" t="n">
-        <v>17.30064966864246</v>
+        <v>17.30064966763078</v>
       </c>
       <c r="CP24" t="n">
-        <v>8.943457194593153</v>
+        <v>8.943457188436387</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
-        <v>14.37323359800516</v>
+        <v>14.37323359446199</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.45307440373395</v>
+        <v>15.45307440121136</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.90776696336056</v>
+        <v>13.90776696109023</v>
       </c>
       <c r="CU24" t="n">
         <v>4</v>
@@ -9148,10 +9148,10 @@
         <v>2.1</v>
       </c>
       <c r="CX24" t="n">
-        <v>7.395885468740948</v>
+        <v>7.395885451209439</v>
       </c>
       <c r="CY24" t="n">
-        <v>10.99022246874293</v>
+        <v>10.99022244138255</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ25" t="n">
-        <v>7.021620190440584</v>
+        <v>7.02162015327599</v>
       </c>
       <c r="CK25" t="n">
-        <v>13.02510545326728</v>
+        <v>13.02510538432696</v>
       </c>
       <c r="CL25" t="n">
         <v>5.692307765667254</v>
@@ -9498,7 +9498,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR25" t="n">
-        <v>7.373583626401485</v>
+        <v>7.373583613138371</v>
       </c>
       <c r="CS25" t="n">
         <v>5.912820549500294</v>
@@ -9519,7 +9519,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY25" t="n">
-        <v>24.55377586781242</v>
+        <v>24.55377564377335</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ26" t="n">
-        <v>20.2039654068213</v>
+        <v>20.20396545957872</v>
       </c>
       <c r="CK26" t="n">
-        <v>37.47835582965351</v>
+        <v>37.47835592751852</v>
       </c>
       <c r="CL26" t="n">
         <v>55.97851442143241</v>
@@ -9828,23 +9828,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN26" t="n">
-        <v>61.5974785395555</v>
+        <v>61.597478452734</v>
       </c>
       <c r="CO26" t="n">
-        <v>45.1522253744618</v>
+        <v>45.15222535796428</v>
       </c>
       <c r="CP26" t="n">
-        <v>30.98915240298335</v>
+        <v>30.9891522987558</v>
       </c>
       <c r="CQ26" t="inlineStr"/>
       <c r="CR26" t="n">
-        <v>39.70326525809226</v>
+        <v>39.70326529162348</v>
       </c>
       <c r="CS26" t="n">
-        <v>41.31529060205766</v>
+        <v>41.3152906427414</v>
       </c>
       <c r="CT26" t="n">
-        <v>37.18376154185189</v>
+        <v>37.18376157846726</v>
       </c>
       <c r="CU26" t="n">
         <v>4</v>
@@ -9856,10 +9856,10 @@
         <v>2.8</v>
       </c>
       <c r="CX26" t="n">
-        <v>-5.868231113389088</v>
+        <v>-5.868231020696224</v>
       </c>
       <c r="CY26" t="n">
-        <v>0.5099654888873095</v>
+        <v>0.5099655737725639</v>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.430280298234226</v>
+        <v>9.4302802537439</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.49316995322449</v>
+        <v>17.49316987069493</v>
       </c>
       <c r="CL27" t="n">
         <v>30.9711095548374</v>
@@ -10166,23 +10166,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN27" t="n">
-        <v>34.71574759620757</v>
+        <v>34.71574758824536</v>
       </c>
       <c r="CO27" t="n">
-        <v>25.47771502368395</v>
+        <v>25.47771503272126</v>
       </c>
       <c r="CP27" t="n">
-        <v>15.27881627586995</v>
+        <v>15.278816331191</v>
       </c>
       <c r="CQ27" t="inlineStr"/>
       <c r="CR27" t="n">
-        <v>20.84306870749501</v>
+        <v>20.84306867799937</v>
       </c>
       <c r="CS27" t="n">
-        <v>21.48544248845422</v>
+        <v>21.4854424517081</v>
       </c>
       <c r="CT27" t="n">
-        <v>19.3368982396088</v>
+        <v>19.33689820653729</v>
       </c>
       <c r="CU27" t="n">
         <v>4</v>
@@ -10194,10 +10194,10 @@
         <v>3.3</v>
       </c>
       <c r="CX27" t="n">
-        <v>27.46801675911943</v>
+        <v>27.46801654111344</v>
       </c>
       <c r="CY27" t="n">
-        <v>37.3966288903738</v>
+        <v>37.39662869593978</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL27" t="n">
-        <v>-16.60347445371087</v>
+        <v>-16.60346541872488</v>
       </c>
       <c r="DM27" t="b">
         <v>1</v>
@@ -10512,37 +10512,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ28" t="n">
-        <v>17.07331069808112</v>
+        <v>17.07331078335307</v>
       </c>
       <c r="CK28" t="n">
-        <v>28.37657058377574</v>
+        <v>28.37657059421937</v>
       </c>
       <c r="CL28" t="n">
-        <v>47.66545656825829</v>
+        <v>47.66545634773779</v>
       </c>
       <c r="CM28" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN28" t="n">
-        <v>56.59469221753312</v>
+        <v>56.5946922453201</v>
       </c>
       <c r="CO28" t="n">
-        <v>42.94865307942731</v>
+        <v>42.9486530639905</v>
       </c>
       <c r="CP28" t="n">
-        <v>23.70643973254973</v>
+        <v>23.70643963717476</v>
       </c>
       <c r="CQ28" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR28" t="n">
-        <v>37.60349437770622</v>
+        <v>37.60349435172751</v>
       </c>
       <c r="CS28" t="n">
-        <v>37.07077017601888</v>
+        <v>37.07077016830048</v>
       </c>
       <c r="CT28" t="n">
-        <v>33.36369315841699</v>
+        <v>33.36369315147043</v>
       </c>
       <c r="CU28" t="n">
         <v>8</v>
@@ -10554,10 +10554,10 @@
         <v>3.3</v>
       </c>
       <c r="CX28" t="n">
-        <v>24.95764870811157</v>
+        <v>24.95764868209449</v>
       </c>
       <c r="CY28" t="n">
-        <v>40.83705357005534</v>
+        <v>40.83705347275676</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -10872,37 +10872,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ29" t="n">
-        <v>5.830932731850884</v>
+        <v>5.830932745051316</v>
       </c>
       <c r="CK29" t="n">
-        <v>8.573470615831482</v>
+        <v>8.573470604546189</v>
       </c>
       <c r="CL29" t="n">
-        <v>11.02317118066605</v>
+        <v>11.02317114120126</v>
       </c>
       <c r="CM29" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN29" t="n">
-        <v>9.992440001507868</v>
+        <v>9.992439980409005</v>
       </c>
       <c r="CO29" t="n">
-        <v>14.93936638160634</v>
+        <v>14.93936637695643</v>
       </c>
       <c r="CP29" t="n">
-        <v>5.501588171783267</v>
+        <v>5.501588150409129</v>
       </c>
       <c r="CQ29" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.794723693804823</v>
+        <v>9.794723683220752</v>
       </c>
       <c r="CS29" t="n">
-        <v>10.44705005117738</v>
+        <v>10.44705004062795</v>
       </c>
       <c r="CT29" t="n">
-        <v>9.402345046059644</v>
+        <v>9.402345036565155</v>
       </c>
       <c r="CU29" t="n">
         <v>8</v>
@@ -10914,10 +10914,10 @@
         <v>2.7</v>
       </c>
       <c r="CX29" t="n">
-        <v>-37.44281295339085</v>
+        <v>-37.4428130165611</v>
       </c>
       <c r="CY29" t="n">
-        <v>-34.8321765281325</v>
+        <v>-34.83217659855213</v>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
@@ -11232,37 +11232,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ30" t="n">
-        <v>30.83210607591968</v>
+        <v>30.83210627958053</v>
       </c>
       <c r="CK30" t="n">
-        <v>35.07524630358477</v>
+        <v>35.07524614717919</v>
       </c>
       <c r="CL30" t="n">
-        <v>37.91416017666519</v>
+        <v>37.91415975715928</v>
       </c>
       <c r="CM30" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN30" t="n">
-        <v>59.10496031981044</v>
+        <v>59.10496008950702</v>
       </c>
       <c r="CO30" t="n">
-        <v>16.57964504833495</v>
+        <v>16.57964502823301</v>
       </c>
       <c r="CP30" t="n">
-        <v>16.88731352844288</v>
+        <v>16.88731316749069</v>
       </c>
       <c r="CQ30" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR30" t="n">
-        <v>34.28114202077357</v>
+        <v>34.28114189782255</v>
       </c>
       <c r="CS30" t="n">
-        <v>32.95367618975222</v>
+        <v>32.95367621337986</v>
       </c>
       <c r="CT30" t="n">
-        <v>29.658308570777</v>
+        <v>29.65830859204187</v>
       </c>
       <c r="CU30" t="n">
         <v>8</v>
@@ -11274,10 +11274,10 @@
         <v>3.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>-23.32391846747629</v>
+        <v>-23.32391841249989</v>
       </c>
       <c r="CY30" t="n">
-        <v>-11.37243601265845</v>
+        <v>-11.37243633052561</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>-0.667689601187782</v>
       </c>
       <c r="DL30" t="n">
-        <v>-11.71364879963919</v>
+        <v>-11.71364092295562</v>
       </c>
       <c r="DM30" t="b">
         <v>1</v>
@@ -11469,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="AW31" t="n">
-        <v>186901528576</v>
+        <v>187227897856</v>
       </c>
       <c r="AX31" t="n">
         <v>7.35</v>
@@ -11574,35 +11574,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ31" t="n">
-        <v>10.16567237167966</v>
+        <v>10.16567239950484</v>
       </c>
       <c r="CK31" t="n">
-        <v>17.61110254244038</v>
+        <v>17.61110253775026</v>
       </c>
       <c r="CL31" t="n">
-        <v>28.75563263571181</v>
+        <v>28.75563254934464</v>
       </c>
       <c r="CM31" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN31" t="n">
-        <v>32.08888080896667</v>
+        <v>32.08888080692324</v>
       </c>
       <c r="CO31" t="n">
-        <v>27.87173774883079</v>
+        <v>27.8717377425716</v>
       </c>
       <c r="CP31" t="n">
-        <v>14.20689962759608</v>
+        <v>14.20689959299714</v>
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>21.10103632466566</v>
+        <v>21.10103630729284</v>
       </c>
       <c r="CS31" t="n">
-        <v>22.74142014563559</v>
+        <v>22.74142014016093</v>
       </c>
       <c r="CT31" t="n">
-        <v>20.46727813107203</v>
+        <v>20.46727812614484</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -11614,10 +11614,10 @@
         <v>2.8</v>
       </c>
       <c r="CX31" t="n">
-        <v>19.83183971016667</v>
+        <v>19.83183968131894</v>
       </c>
       <c r="CY31" t="n">
-        <v>23.54236779227756</v>
+        <v>23.54236769056313</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -11940,37 +11940,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ32" t="n">
-        <v>32.50257829001703</v>
+        <v>32.50257839087045</v>
       </c>
       <c r="CK32" t="n">
-        <v>44.74764057913653</v>
+        <v>44.74764038431965</v>
       </c>
       <c r="CL32" t="n">
-        <v>51.52715738101318</v>
+        <v>51.52715699679499</v>
       </c>
       <c r="CM32" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN32" t="n">
-        <v>71.44157102715603</v>
+        <v>71.44157081911828</v>
       </c>
       <c r="CO32" t="n">
-        <v>59.88947345916158</v>
+        <v>59.88947341794151</v>
       </c>
       <c r="CP32" t="n">
-        <v>25.45084486398652</v>
+        <v>25.45084462941759</v>
       </c>
       <c r="CQ32" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR32" t="n">
-        <v>51.51519296586034</v>
+        <v>51.51519284560929</v>
       </c>
       <c r="CS32" t="n">
-        <v>49.93498913827833</v>
+        <v>49.93498894616923</v>
       </c>
       <c r="CT32" t="n">
-        <v>44.9414902244505</v>
+        <v>44.94149005155231</v>
       </c>
       <c r="CU32" t="n">
         <v>8</v>
@@ -11982,10 +11982,10 @@
         <v>3.1</v>
       </c>
       <c r="CX32" t="n">
-        <v>0.3158281022310971</v>
+        <v>0.3158277162976342</v>
       </c>
       <c r="CY32" t="n">
-        <v>14.98927197133675</v>
+        <v>14.98927170291921</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -12290,10 +12290,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ33" t="n">
-        <v>10.47626030483282</v>
+        <v>10.47626037274054</v>
       </c>
       <c r="CK33" t="n">
-        <v>19.43346286546489</v>
+        <v>19.43346299143371</v>
       </c>
       <c r="CL33" t="n">
         <v>60.73011328156327</v>
@@ -12302,7 +12302,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN33" t="n">
-        <v>81.29749116625149</v>
+        <v>81.29749124757811</v>
       </c>
       <c r="CO33" t="n">
         <v>11.76833333333333</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>13.89268550121035</v>
+        <v>13.89268556583586</v>
       </c>
       <c r="CS33" t="n">
         <v>11.76833333333333</v>
@@ -12333,7 +12333,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY33" t="n">
-        <v>-74.0711365687968</v>
+        <v>-74.07113644818179</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ34" t="n">
-        <v>15.68694277612544</v>
+        <v>15.6869427790179</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.0992788497127</v>
+        <v>29.0992788550782</v>
       </c>
       <c r="CL34" t="n">
         <v>55.61293748708871</v>
@@ -12642,23 +12642,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN34" t="n">
-        <v>62.11186603739112</v>
+        <v>62.11186603670111</v>
       </c>
       <c r="CO34" t="n">
-        <v>36.65076910303291</v>
+        <v>36.65076910251672</v>
       </c>
       <c r="CP34" t="n">
-        <v>30.94726543071105</v>
+        <v>30.94726542671738</v>
       </c>
       <c r="CQ34" t="inlineStr"/>
       <c r="CR34" t="n">
-        <v>34.26248205398994</v>
+        <v>34.26248205592537</v>
       </c>
       <c r="CS34" t="n">
-        <v>32.8750239763728</v>
+        <v>32.87502397879746</v>
       </c>
       <c r="CT34" t="n">
-        <v>29.58752157873552</v>
+        <v>29.58752158091771</v>
       </c>
       <c r="CU34" t="n">
         <v>4</v>
@@ -12670,10 +12670,10 @@
         <v>3.5</v>
       </c>
       <c r="CX34" t="n">
-        <v>-1.4077928921164</v>
+        <v>-1.40779288484485</v>
       </c>
       <c r="CY34" t="n">
-        <v>14.17021590361565</v>
+        <v>14.17021591006493</v>
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
@@ -12990,10 +12990,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ35" t="n">
-        <v>13.32483359075277</v>
+        <v>13.32483359494353</v>
       </c>
       <c r="CK35" t="n">
-        <v>19.40095770813604</v>
+        <v>19.40095771423778</v>
       </c>
       <c r="CL35" t="n">
         <v>16.70870841086448</v>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="CN35" t="inlineStr"/>
       <c r="CO35" t="n">
-        <v>13.95326101288333</v>
+        <v>14.38930041953594</v>
       </c>
       <c r="CP35" t="n">
         <v>4.291934715428101</v>
@@ -13012,7 +13012,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR35" t="n">
-        <v>16.24126649766002</v>
+        <v>16.31393973381754</v>
       </c>
       <c r="CS35" t="n">
         <v>15.78776446356376</v>
@@ -13033,7 +13033,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY35" t="n">
-        <v>51.78754006702593</v>
+        <v>52.46672920210042</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -13348,10 +13348,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ36" t="n">
-        <v>8.850909487110853</v>
+        <v>8.850909473613465</v>
       </c>
       <c r="CK36" t="n">
-        <v>16.41843709859063</v>
+        <v>16.41843707355297</v>
       </c>
       <c r="CL36" t="n">
         <v>16.35235520731475</v>
@@ -13360,7 +13360,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN36" t="n">
-        <v>25.87578449342791</v>
+        <v>25.87578448106929</v>
       </c>
       <c r="CO36" t="n">
         <v>19.94489718117502</v>
@@ -13372,7 +13372,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR36" t="n">
-        <v>16.79289066998749</v>
+        <v>16.79289066362578</v>
       </c>
       <c r="CS36" t="n">
         <v>16.28957786959118</v>
@@ -13393,7 +13393,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY36" t="n">
-        <v>-11.00747258541346</v>
+        <v>-11.0074726191268</v>
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
@@ -14328,10 +14328,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.806389186744216</v>
+        <v>5.806389169061072</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085194141052</v>
+        <v>10.77085190860829</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -14340,10 +14340,10 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.9863169180497</v>
+        <v>66.98631684731713</v>
       </c>
       <c r="CO2" t="n">
-        <v>19.57807411896471</v>
+        <v>19.76753935237404</v>
       </c>
       <c r="CP2" t="n">
         <v>35.30034653799875</v>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr"/>
@@ -14678,10 +14678,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958258126554</v>
+        <v>14.76958268167085</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.39757568824757</v>
+        <v>27.39757587449942</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -14690,13 +14690,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097393955392</v>
+        <v>74.51097375230589</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789240272657</v>
+        <v>48.47789232821682</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.3567960233152</v>
+        <v>26.35679571353672</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -15028,10 +15028,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247029102893</v>
+        <v>16.22247029995932</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268238985866</v>
+        <v>30.09268240642453</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -15040,19 +15040,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.553772682851</v>
+        <v>125.5537726798479</v>
       </c>
       <c r="CO4" t="n">
-        <v>26.09980883464424</v>
+        <v>25.70896311038452</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944657614642</v>
+        <v>61.8994465569868</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.24259007506706</v>
+        <v>47.17744912059148</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -15073,7 +15073,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>93.22122127159973</v>
+        <v>92.95479610823401</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -15386,10 +15386,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224631188787</v>
+        <v>3.770224629224546</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.9937666908552</v>
+        <v>6.993766687211532</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -15398,25 +15398,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502456754474</v>
+        <v>25.12502456886212</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762152661</v>
+        <v>11.21765762231827</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.5948613080749</v>
+        <v>10.59486131297011</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533149445299</v>
+        <v>9.312533149785834</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802515730468</v>
+        <v>9.655802518178071</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222264157422</v>
+        <v>8.690222266360264</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -15428,10 +15428,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029413121739</v>
+        <v>109.4029413652544</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.398383986562</v>
+        <v>124.3983839947677</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -15746,10 +15746,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933216131584</v>
+        <v>3.224933225533877</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251115924088</v>
+        <v>5.982251133365341</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -15758,7 +15758,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385724241296</v>
+        <v>24.33385727115359</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -15770,7 +15770,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929365660842</v>
+        <v>11.46929366320583</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -15791,7 +15791,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862773447082</v>
+        <v>159.4862774939709</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -16096,10 +16096,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418017947997</v>
+        <v>18.62418025063309</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785423293535</v>
+        <v>34.54785436492438</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -16108,23 +16108,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694234461283</v>
+        <v>100.3694233343052</v>
       </c>
       <c r="CO7" t="n">
-        <v>48.35621747253571</v>
+        <v>47.8454123413184</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710168912232</v>
+        <v>59.21710154611024</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.18367405856277</v>
+        <v>44.05597282654397</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.45203585273553</v>
+        <v>41.19663335312139</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.30683226746198</v>
+        <v>37.07697001780925</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -16136,10 +16136,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-23.66107410916782</v>
+        <v>-24.13142863070796</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.589369706870309</v>
+        <v>-9.850677737993419</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -16678,10 +16678,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.401689195225291</v>
+        <v>6.40168918913402</v>
       </c>
       <c r="CK9" t="n">
-        <v>11.87513345714291</v>
+        <v>11.87513344584361</v>
       </c>
       <c r="CL9" t="n">
         <v>25.33800212822936</v>
@@ -16690,19 +16690,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN9" t="n">
-        <v>35.10892156206317</v>
+        <v>35.10892157198074</v>
       </c>
       <c r="CO9" t="n">
-        <v>12.29620298372775</v>
+        <v>12.29620298488673</v>
       </c>
       <c r="CP9" t="n">
-        <v>20.31530580329477</v>
+        <v>20.31530581605768</v>
       </c>
       <c r="CQ9" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR9" t="n">
-        <v>20.27452914057966</v>
+        <v>20.27452914237111</v>
       </c>
       <c r="CS9" t="n">
         <v>18.56484347595736</v>
@@ -16723,7 +16723,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY9" t="n">
-        <v>29.13712985279737</v>
+        <v>29.13712986420787</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ10" t="n">
-        <v>127.5892448772487</v>
+        <v>127.5892443491088</v>
       </c>
       <c r="CK10" t="n">
-        <v>236.6780492472963</v>
+        <v>236.6780482675968</v>
       </c>
       <c r="CL10" t="n">
         <v>132.6522965266787</v>
@@ -17064,13 +17064,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR10" t="n">
-        <v>139.7795671325697</v>
+        <v>139.7795669440898</v>
       </c>
       <c r="CS10" t="n">
-        <v>124.3641616074097</v>
+        <v>124.3641613433398</v>
       </c>
       <c r="CT10" t="n">
-        <v>111.9277454466687</v>
+        <v>111.9277452090058</v>
       </c>
       <c r="CU10" t="n">
         <v>8</v>
@@ -17082,10 +17082,10 @@
         <v>5.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>157.0097529448853</v>
+        <v>157.0097523991609</v>
       </c>
       <c r="CY10" t="n">
-        <v>220.9634203934013</v>
+        <v>220.9634199606116</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL10" t="n">
-        <v>-8.627331177634668</v>
+        <v>-8.627323714303436</v>
       </c>
       <c r="DM10" t="b">
         <v>1</v>
@@ -17404,10 +17404,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ11" t="n">
-        <v>45.30199151837756</v>
+        <v>45.30199113338053</v>
       </c>
       <c r="CK11" t="n">
-        <v>84.03519426659035</v>
+        <v>84.03519355242089</v>
       </c>
       <c r="CL11" t="n">
         <v>67.58333047231037</v>
@@ -17428,7 +17428,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR11" t="n">
-        <v>76.94607072603911</v>
+        <v>76.94607056901533</v>
       </c>
       <c r="CS11" t="n">
         <v>67.58333047231037</v>
@@ -17449,7 +17449,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY11" t="n">
-        <v>137.1950492707072</v>
+        <v>137.1950487866635</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -17772,37 +17772,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ12" t="n">
-        <v>24.2161267267157</v>
+        <v>24.21612672531058</v>
       </c>
       <c r="CK12" t="n">
-        <v>32.67790194611635</v>
+        <v>32.67790195654321</v>
       </c>
       <c r="CL12" t="n">
-        <v>34.37896777756509</v>
+        <v>34.37896779052954</v>
       </c>
       <c r="CM12" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN12" t="n">
-        <v>48.80739054378653</v>
+        <v>48.80739055469227</v>
       </c>
       <c r="CO12" t="n">
-        <v>50.94836380976193</v>
+        <v>50.94836381156785</v>
       </c>
       <c r="CP12" t="n">
-        <v>16.89191283540633</v>
+        <v>16.8919128436142</v>
       </c>
       <c r="CQ12" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR12" t="n">
-        <v>31.61206967241048</v>
+        <v>31.6120696777737</v>
       </c>
       <c r="CS12" t="n">
-        <v>28.44701433641603</v>
+        <v>28.4470143409269</v>
       </c>
       <c r="CT12" t="n">
-        <v>25.60231290277442</v>
+        <v>25.60231290683421</v>
       </c>
       <c r="CU12" t="n">
         <v>8</v>
@@ -17814,10 +17814,10 @@
         <v>3</v>
       </c>
       <c r="CX12" t="n">
-        <v>-21.46529416834684</v>
+        <v>-21.46529415589349</v>
       </c>
       <c r="CY12" t="n">
-        <v>-3.030456588808916</v>
+        <v>-3.030456572357343</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -18132,10 +18132,10 @@
         <v>6.929999828338623</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.512298790662402</v>
+        <v>6.512298822881542</v>
       </c>
       <c r="CK13" t="n">
-        <v>12.08031425667876</v>
+        <v>12.08031431644526</v>
       </c>
       <c r="CL13" t="n">
         <v>39.92282509803772</v>
@@ -18144,7 +18144,7 @@
         <v>26.88461902486203</v>
       </c>
       <c r="CN13" t="n">
-        <v>84.8357306497187</v>
+        <v>84.8357308458352</v>
       </c>
       <c r="CO13" t="n">
         <v>51.88018214566937</v>
@@ -18480,10 +18480,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ14" t="n">
-        <v>133.9252033008311</v>
+        <v>133.9252023858741</v>
       </c>
       <c r="CK14" t="n">
-        <v>248.4312521230417</v>
+        <v>248.4312504257963</v>
       </c>
       <c r="CL14" t="n">
         <v>131.5457818930041</v>
@@ -18504,7 +18504,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR14" t="n">
-        <v>141.1793357418161</v>
+        <v>141.1793354152908</v>
       </c>
       <c r="CS14" t="n">
         <v>125.8371913580247</v>
@@ -18525,7 +18525,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY14" t="n">
-        <v>192.5996595685309</v>
+        <v>192.5996588917945</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>0.3954558219285254</v>
       </c>
       <c r="DL14" t="n">
-        <v>-9.168913901075104</v>
+        <v>-9.168920601679343</v>
       </c>
       <c r="DM14" t="b">
         <v>1</v>
@@ -19172,10 +19172,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ16" t="n">
-        <v>13.26532630262742</v>
+        <v>13.2653263333155</v>
       </c>
       <c r="CK16" t="n">
-        <v>24.60718029137386</v>
+        <v>24.60718034830025</v>
       </c>
       <c r="CL16" t="n">
         <v>19.93179967973907</v>
@@ -19184,7 +19184,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN16" t="n">
-        <v>33.72989543812618</v>
+        <v>33.72989547161279</v>
       </c>
       <c r="CO16" t="n">
         <v>22.8984489302328</v>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
-        <v>20.17568880099329</v>
+        <v>20.1756888228969</v>
       </c>
       <c r="CS16" t="n">
         <v>21.41512430498593</v>
@@ -19215,7 +19215,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY16" t="n">
-        <v>4.537251805954523</v>
+        <v>4.537251919444762</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -19524,10 +19524,10 @@
         <v>13.86999988555908</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.06948873133144</v>
+        <v>10.06948874831884</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.67890159661983</v>
+        <v>18.67890162813145</v>
       </c>
       <c r="CL17" t="n">
         <v>48.87699427756856</v>
@@ -19536,23 +19536,23 @@
         <v>47.98315406169494</v>
       </c>
       <c r="CN17" t="n">
-        <v>67.71366088542058</v>
+        <v>67.71366091713611</v>
       </c>
       <c r="CO17" t="n">
-        <v>33.90963924104684</v>
+        <v>33.90963923836745</v>
       </c>
       <c r="CP17" t="n">
-        <v>28.85042924385775</v>
+        <v>28.8504292240355</v>
       </c>
       <c r="CQ17" t="inlineStr"/>
       <c r="CR17" t="n">
-        <v>33.82184503841174</v>
+        <v>33.82184504802249</v>
       </c>
       <c r="CS17" t="n">
-        <v>33.90963924104684</v>
+        <v>33.90963923836745</v>
       </c>
       <c r="CT17" t="n">
-        <v>30.51867531694216</v>
+        <v>30.5186753145307</v>
       </c>
       <c r="CU17" t="n">
         <v>3</v>
@@ -19564,10 +19564,10 @@
         <v>4.9</v>
       </c>
       <c r="CX17" t="n">
-        <v>120.0337099405246</v>
+        <v>120.0337099231384</v>
       </c>
       <c r="CY17" t="n">
-        <v>143.8489208181304</v>
+        <v>143.848920887422</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="AV18" t="b">
         <v>1</v>
@@ -19878,10 +19878,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.228277665486087</v>
+        <v>3.228277656794087</v>
       </c>
       <c r="CK18" t="n">
-        <v>5.98845506947669</v>
+        <v>5.988455053353031</v>
       </c>
       <c r="CL18" t="n">
         <v>19.81956093381139</v>
@@ -19890,7 +19890,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN18" t="n">
-        <v>31.89244534462692</v>
+        <v>31.89244531916918</v>
       </c>
       <c r="CO18" t="n">
         <v>10.95072400487419</v>
@@ -20236,10 +20236,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ19" t="n">
-        <v>10.67756763704817</v>
+        <v>10.67756767844085</v>
       </c>
       <c r="CK19" t="n">
-        <v>19.80688796672435</v>
+        <v>19.80688804350778</v>
       </c>
       <c r="CL19" t="n">
         <v>38.98902044102951</v>
@@ -20248,25 +20248,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN19" t="n">
-        <v>44.33179745358975</v>
+        <v>44.33179747510008</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.59948399450583</v>
+        <v>34.59948398607202</v>
       </c>
       <c r="CP19" t="n">
-        <v>19.85450036331167</v>
+        <v>19.85450031530278</v>
       </c>
       <c r="CQ19" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR19" t="n">
-        <v>32.77627193818945</v>
+        <v>32.77627194416817</v>
       </c>
       <c r="CS19" t="n">
-        <v>34.59948399450583</v>
+        <v>34.59948398607202</v>
       </c>
       <c r="CT19" t="n">
-        <v>31.13953559505525</v>
+        <v>31.13953558746482</v>
       </c>
       <c r="CU19" t="n">
         <v>7</v>
@@ -20278,10 +20278,10 @@
         <v>4.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>78.75737921167733</v>
+        <v>78.75737916810424</v>
       </c>
       <c r="CY19" t="n">
-        <v>88.15311018737093</v>
+        <v>88.15311022169192</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>-0.6274991787955986</v>
       </c>
       <c r="DL19" t="n">
-        <v>-23.70303752784818</v>
+        <v>-23.70303109613396</v>
       </c>
       <c r="DM19" t="b">
         <v>1</v>
@@ -20596,37 +20596,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ20" t="n">
-        <v>24.99231901236771</v>
+        <v>24.9923191544161</v>
       </c>
       <c r="CK20" t="n">
-        <v>31.99913693845138</v>
+        <v>31.99913671117761</v>
       </c>
       <c r="CL20" t="n">
-        <v>35.87977396685041</v>
+        <v>35.8797735080852</v>
       </c>
       <c r="CM20" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN20" t="n">
-        <v>50.332770974964</v>
+        <v>50.33277069131262</v>
       </c>
       <c r="CO20" t="n">
-        <v>48.65905505261815</v>
+        <v>48.65905499129359</v>
       </c>
       <c r="CP20" t="n">
-        <v>17.29535409769133</v>
+        <v>17.29535377830975</v>
       </c>
       <c r="CQ20" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR20" t="n">
-        <v>34.65367029381299</v>
+        <v>34.65367014276948</v>
       </c>
       <c r="CS20" t="n">
-        <v>33.9394554526509</v>
+        <v>33.9394551096314</v>
       </c>
       <c r="CT20" t="n">
-        <v>30.54550990738581</v>
+        <v>30.54550959866826</v>
       </c>
       <c r="CU20" t="n">
         <v>8</v>
@@ -20638,10 +20638,10 @@
         <v>2.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>-12.12453572397498</v>
+        <v>-12.12453661211524</v>
       </c>
       <c r="CY20" t="n">
-        <v>-0.3058919242074354</v>
+        <v>-0.305892358740012</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -20956,37 +20956,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ21" t="n">
-        <v>10.03288993429703</v>
+        <v>10.03288994712749</v>
       </c>
       <c r="CK21" t="n">
-        <v>18.09423444451794</v>
+        <v>18.09423440962371</v>
       </c>
       <c r="CL21" t="n">
-        <v>23.57397890982145</v>
+        <v>23.57397883421233</v>
       </c>
       <c r="CM21" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN21" t="n">
-        <v>36.27022042017696</v>
+        <v>36.27022040828844</v>
       </c>
       <c r="CO21" t="n">
-        <v>24.18418239442536</v>
+        <v>24.18418238883785</v>
       </c>
       <c r="CP21" t="n">
-        <v>11.54642594411629</v>
+        <v>11.54642591600218</v>
       </c>
       <c r="CQ21" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR21" t="n">
-        <v>18.89005843022205</v>
+        <v>18.89005841231417</v>
       </c>
       <c r="CS21" t="n">
-        <v>17.75138480502874</v>
+        <v>17.75138478758163</v>
       </c>
       <c r="CT21" t="n">
-        <v>15.97624632452587</v>
+        <v>15.97624630882347</v>
       </c>
       <c r="CU21" t="n">
         <v>8</v>
@@ -20998,10 +20998,10 @@
         <v>3.6</v>
       </c>
       <c r="CX21" t="n">
-        <v>59.60285673550369</v>
+        <v>59.60285657863653</v>
       </c>
       <c r="CY21" t="n">
-        <v>88.71186811483376</v>
+        <v>88.71186793593391</v>
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
         <v>3.460000038146973</v>
       </c>
       <c r="CJ22" t="n">
-        <v>5.001737478254582</v>
+        <v>5.001737475679065</v>
       </c>
       <c r="CK22" t="n">
-        <v>9.278223022162249</v>
+        <v>9.278223017384667</v>
       </c>
       <c r="CL22" t="n">
         <v>8.458487178126823</v>
@@ -21664,10 +21664,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.337978118893381</v>
+        <v>3.337978094534551</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.191949410547221</v>
+        <v>6.191949365361591</v>
       </c>
       <c r="CL23" t="n">
         <v>19.28911530241674</v>
@@ -21676,13 +21676,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN23" t="n">
-        <v>20.60183925804898</v>
+        <v>20.60183926079271</v>
       </c>
       <c r="CO23" t="n">
-        <v>15.92145422559568</v>
+        <v>15.92145423049115</v>
       </c>
       <c r="CP23" t="n">
-        <v>12.84225511981982</v>
+        <v>12.84225515070877</v>
       </c>
       <c r="CQ23" t="n">
         <v>29.10394270806049</v>
@@ -21891,13 +21891,13 @@
         <v>1</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AV24" t="b">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>3638864896</v>
+        <v>5782441984</v>
       </c>
       <c r="AX24" t="n">
         <v>6.76</v>
@@ -22014,10 +22014,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ24" t="n">
-        <v>9.410499907685351</v>
+        <v>9.410499890742297</v>
       </c>
       <c r="CK24" t="n">
-        <v>17.45647732875632</v>
+        <v>17.45647729732696</v>
       </c>
       <c r="CL24" t="n">
         <v>21.3058429709553</v>
@@ -22026,25 +22026,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN24" t="n">
-        <v>30.17445897866877</v>
+        <v>30.17445903082277</v>
       </c>
       <c r="CO24" t="n">
-        <v>25.20917159245645</v>
+        <v>25.20917160528171</v>
       </c>
       <c r="CP24" t="n">
-        <v>11.01207336027179</v>
+        <v>11.01207341511035</v>
       </c>
       <c r="CQ24" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR24" t="n">
-        <v>17.05929121723047</v>
+        <v>17.05929122616115</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.01197250485499</v>
+        <v>15.0119724891403</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.51077525436949</v>
+        <v>13.51077524022627</v>
       </c>
       <c r="CU24" t="n">
         <v>8</v>
@@ -22056,10 +22056,10 @@
         <v>3.2</v>
       </c>
       <c r="CX24" t="n">
-        <v>24.29416188236308</v>
+        <v>24.29416175225072</v>
       </c>
       <c r="CY24" t="n">
-        <v>56.93920328273354</v>
+        <v>56.93920336489246</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -22382,10 +22382,10 @@
         <v>14.68000030517578</v>
       </c>
       <c r="CJ25" t="n">
-        <v>4.507867433467572</v>
+        <v>4.507867427855095</v>
       </c>
       <c r="CK25" t="n">
-        <v>8.362094089082346</v>
+        <v>8.3620940786712</v>
       </c>
       <c r="CL25" t="n">
         <v>23.72073220043647</v>
@@ -22394,25 +22394,25 @@
         <v>19.98846940520332</v>
       </c>
       <c r="CN25" t="n">
-        <v>28.64206398913964</v>
+        <v>28.6420639937558</v>
       </c>
       <c r="CO25" t="n">
-        <v>16.68542399358962</v>
+        <v>16.68542399477433</v>
       </c>
       <c r="CP25" t="n">
-        <v>17.94838049709657</v>
+        <v>17.9483805060213</v>
       </c>
       <c r="CQ25" t="n">
         <v>14.42556031369228</v>
       </c>
       <c r="CR25" t="n">
-        <v>18.53896064117718</v>
+        <v>18.53896064179353</v>
       </c>
       <c r="CS25" t="n">
-        <v>17.94838049709657</v>
+        <v>17.9483805060213</v>
       </c>
       <c r="CT25" t="n">
-        <v>16.15354244738691</v>
+        <v>16.15354245541917</v>
       </c>
       <c r="CU25" t="n">
         <v>7</v>
@@ -22424,10 +22424,10 @@
         <v>6.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>10.03775280366714</v>
+        <v>10.03775285838282</v>
       </c>
       <c r="CY25" t="n">
-        <v>26.28719520285587</v>
+        <v>26.28719520705445</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -23090,10 +23090,10 @@
         <v>14.39999961853027</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.032621003521312</v>
+        <v>9.032620984984016</v>
       </c>
       <c r="CK27" t="n">
-        <v>16.75551196153203</v>
+        <v>16.75551192714535</v>
       </c>
       <c r="CL27" t="n">
         <v>13.05954790866024</v>
@@ -23114,7 +23114,7 @@
         <v>5.995386443060455</v>
       </c>
       <c r="CR27" t="n">
-        <v>11.10312102781318</v>
+        <v>11.10312102025261</v>
       </c>
       <c r="CS27" t="n">
         <v>10.62271216510394</v>
@@ -23135,7 +23135,7 @@
         <v>-33.60804720931423</v>
       </c>
       <c r="CY27" t="n">
-        <v>-22.8949908198233</v>
+        <v>-22.89499087232724</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -23446,10 +23446,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ28" t="n">
-        <v>7.255085128776883</v>
+        <v>7.255085112878843</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.45818291388112</v>
+        <v>13.45818288439025</v>
       </c>
       <c r="CL28" t="n">
         <v>35.08558886655294</v>
@@ -23458,19 +23458,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN28" t="n">
-        <v>43.31704739773711</v>
+        <v>43.3170474218836</v>
       </c>
       <c r="CO28" t="n">
-        <v>26.42844994870688</v>
+        <v>26.42844995275339</v>
       </c>
       <c r="CP28" t="n">
-        <v>28.12717779471024</v>
+        <v>28.12717782341828</v>
       </c>
       <c r="CQ28" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR28" t="n">
-        <v>28.30913260239695</v>
+        <v>28.30913260631269</v>
       </c>
       <c r="CS28" t="n">
         <v>27.73936337556392</v>
@@ -23491,7 +23491,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY28" t="n">
-        <v>3.393475055184525</v>
+        <v>3.393475069485996</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -23814,10 +23814,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ29" t="n">
-        <v>3.140372326759291</v>
+        <v>3.14037232458228</v>
       </c>
       <c r="CK29" t="n">
-        <v>5.825390666138484</v>
+        <v>5.825390662100129</v>
       </c>
       <c r="CL29" t="n">
         <v>32.87416582383663</v>
@@ -23826,7 +23826,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN29" t="n">
-        <v>42.11194018644908</v>
+        <v>42.11194018305507</v>
       </c>
       <c r="CO29" t="n">
         <v>10.85340539909456</v>
@@ -24144,10 +24144,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ30" t="n">
-        <v>36.63430045133594</v>
+        <v>36.63430055379242</v>
       </c>
       <c r="CK30" t="n">
-        <v>53.33954145714513</v>
+        <v>53.33954160632177</v>
       </c>
       <c r="CL30" t="n">
         <v>48.73630032327193</v>
@@ -24157,20 +24157,20 @@
       </c>
       <c r="CN30" t="inlineStr"/>
       <c r="CO30" t="n">
-        <v>58.62355366270413</v>
+        <v>59.50416498381771</v>
       </c>
       <c r="CP30" t="n">
         <v>12.51880241820309</v>
       </c>
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="n">
-        <v>49.33342397361428</v>
+        <v>49.55357686680095</v>
       </c>
       <c r="CS30" t="n">
-        <v>51.03792089020853</v>
+        <v>51.03792096479685</v>
       </c>
       <c r="CT30" t="n">
-        <v>45.93412880118768</v>
+        <v>45.93412886831716</v>
       </c>
       <c r="CU30" t="n">
         <v>4</v>
@@ -24182,10 +24182,10 @@
         <v>1.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>14.77793172357822</v>
+        <v>14.77793189131804</v>
       </c>
       <c r="CY30" t="n">
-        <v>23.27192256201949</v>
+        <v>23.82202973510415</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -24508,10 +24508,10 @@
         <v>23.02000045776367</v>
       </c>
       <c r="CJ31" t="n">
-        <v>11.94334397844826</v>
+        <v>11.94334398071796</v>
       </c>
       <c r="CK31" t="n">
-        <v>22.15490308002153</v>
+        <v>22.15490308423182</v>
       </c>
       <c r="CL31" t="n">
         <v>56.48426038247567</v>
@@ -24520,13 +24520,13 @@
         <v>47.22610297818421</v>
       </c>
       <c r="CN31" t="n">
-        <v>78.27396583442825</v>
+        <v>78.27396583451041</v>
       </c>
       <c r="CO31" t="n">
-        <v>33.63213434062392</v>
+        <v>33.63213434021188</v>
       </c>
       <c r="CP31" t="n">
-        <v>41.12575258502071</v>
+        <v>41.12575258137358</v>
       </c>
       <c r="CQ31" t="n">
         <v>5.143948645500518</v>
@@ -24840,35 +24840,35 @@
         <v>23.10000038146973</v>
       </c>
       <c r="CJ32" t="n">
-        <v>16.58090078434925</v>
+        <v>16.58090084571571</v>
       </c>
       <c r="CK32" t="n">
-        <v>29.63840537279216</v>
+        <v>29.63840536348659</v>
       </c>
       <c r="CL32" t="n">
-        <v>49.98948387658403</v>
+        <v>49.98948367587612</v>
       </c>
       <c r="CM32" t="n">
         <v>49.51516084050021</v>
       </c>
       <c r="CN32" t="n">
-        <v>61.73920143524251</v>
+        <v>61.73920146015001</v>
       </c>
       <c r="CO32" t="n">
-        <v>45.75571212746217</v>
+        <v>45.75571211411884</v>
       </c>
       <c r="CP32" t="n">
-        <v>24.53598518344953</v>
+        <v>24.53598510757604</v>
       </c>
       <c r="CQ32" t="inlineStr"/>
       <c r="CR32" t="n">
-        <v>35.49112554029691</v>
+        <v>35.49112549979932</v>
       </c>
       <c r="CS32" t="n">
-        <v>37.69705875012717</v>
+        <v>37.69705873880272</v>
       </c>
       <c r="CT32" t="n">
-        <v>33.92735287511445</v>
+        <v>33.92735286492245</v>
       </c>
       <c r="CU32" t="n">
         <v>4</v>
@@ -24880,10 +24880,10 @@
         <v>3</v>
       </c>
       <c r="CX32" t="n">
-        <v>46.87165504261277</v>
+        <v>46.87165499849155</v>
       </c>
       <c r="CY32" t="n">
-        <v>53.64123356797452</v>
+        <v>53.64123339266027</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -25194,10 +25194,10 @@
         <v>12.17000007629395</v>
       </c>
       <c r="CJ33" t="n">
-        <v>2.107067439001437</v>
+        <v>2.107067437494403</v>
       </c>
       <c r="CK33" t="n">
-        <v>3.908610099347666</v>
+        <v>3.908610096552117</v>
       </c>
       <c r="CL33" t="n">
         <v>27.14688569206982</v>
@@ -25206,7 +25206,7 @@
         <v>23.00571232673531</v>
       </c>
       <c r="CN33" t="n">
-        <v>35.69847563811941</v>
+        <v>35.69847563456747</v>
       </c>
       <c r="CO33" t="n">
         <v>9.158754146</v>
@@ -25540,10 +25540,10 @@
         <v>32.75</v>
       </c>
       <c r="CJ34" t="n">
-        <v>7.767166866965996</v>
+        <v>7.767166859025735</v>
       </c>
       <c r="CK34" t="n">
-        <v>14.40809453822192</v>
+        <v>14.40809452349274</v>
       </c>
       <c r="CL34" t="n">
         <v>61.90263908701854</v>
@@ -25552,7 +25552,7 @@
         <v>36.11117259360064</v>
       </c>
       <c r="CN34" t="n">
-        <v>85.59063282988929</v>
+        <v>85.59063281403144</v>
       </c>
       <c r="CO34" t="n">
         <v>22.51480113099953</v>
@@ -25886,10 +25886,10 @@
         <v>33.20000076293945</v>
       </c>
       <c r="CJ35" t="n">
-        <v>15.04507767425586</v>
+        <v>15.04507767185095</v>
       </c>
       <c r="CK35" t="n">
-        <v>27.90861908574461</v>
+        <v>27.9086190812835</v>
       </c>
       <c r="CL35" t="n">
         <v>19.77078697118866</v>
@@ -25898,7 +25898,7 @@
         <v>36.42710872951999</v>
       </c>
       <c r="CN35" t="n">
-        <v>26.62611668374767</v>
+        <v>26.62611668223447</v>
       </c>
       <c r="CO35" t="n">
         <v>15.03391666666667</v>
@@ -25910,7 +25910,7 @@
         <v>78.26206757492224</v>
       </c>
       <c r="CR35" t="n">
-        <v>22.22625156886419</v>
+        <v>22.22625156766716</v>
       </c>
       <c r="CS35" t="n">
         <v>19.77078697118866</v>
@@ -25931,7 +25931,7 @@
         <v>-46.40449438202248</v>
       </c>
       <c r="CY35" t="n">
-        <v>-33.05346066836557</v>
+        <v>-33.05346067197109</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -26250,10 +26250,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ36" t="n">
-        <v>3.414124722491619</v>
+        <v>3.414124724269988</v>
       </c>
       <c r="CK36" t="n">
-        <v>6.333201360221953</v>
+        <v>6.333201363520827</v>
       </c>
       <c r="CL36" t="n">
         <v>31.64000679932063</v>
@@ -26262,7 +26262,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN36" t="n">
-        <v>39.13586008508427</v>
+        <v>39.13586008681204</v>
       </c>
       <c r="CO36" t="n">
         <v>10.59424454785779</v>
@@ -26324,7 +26324,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL36" t="n">
-        <v>-27.83707532184228</v>
+        <v>-27.83708127316356</v>
       </c>
       <c r="DM36" t="b">
         <v>1</v>
@@ -26580,35 +26580,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ37" t="n">
-        <v>8.694392929132208</v>
+        <v>8.694392932746011</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.60549913882544</v>
+        <v>13.60549913479195</v>
       </c>
       <c r="CL37" t="n">
-        <v>17.89239265542053</v>
+        <v>17.89239264267922</v>
       </c>
       <c r="CM37" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN37" t="n">
-        <v>22.47099643024767</v>
+        <v>22.47099642670662</v>
       </c>
       <c r="CO37" t="n">
-        <v>17.30064966864246</v>
+        <v>17.30064966763078</v>
       </c>
       <c r="CP37" t="n">
-        <v>8.943457194593153</v>
+        <v>8.943457188436387</v>
       </c>
       <c r="CQ37" t="inlineStr"/>
       <c r="CR37" t="n">
-        <v>14.37323359800516</v>
+        <v>14.37323359446199</v>
       </c>
       <c r="CS37" t="n">
-        <v>15.45307440373395</v>
+        <v>15.45307440121136</v>
       </c>
       <c r="CT37" t="n">
-        <v>13.90776696336056</v>
+        <v>13.90776696109023</v>
       </c>
       <c r="CU37" t="n">
         <v>4</v>
@@ -26620,10 +26620,10 @@
         <v>2.1</v>
       </c>
       <c r="CX37" t="n">
-        <v>7.395885468740948</v>
+        <v>7.395885451209439</v>
       </c>
       <c r="CY37" t="n">
-        <v>10.99022246874293</v>
+        <v>10.99022244138255</v>
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
@@ -26946,10 +26946,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ38" t="n">
-        <v>7.021620190440584</v>
+        <v>7.02162015327599</v>
       </c>
       <c r="CK38" t="n">
-        <v>13.02510545326728</v>
+        <v>13.02510538432696</v>
       </c>
       <c r="CL38" t="n">
         <v>5.692307765667254</v>
@@ -26970,7 +26970,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR38" t="n">
-        <v>7.373583626401485</v>
+        <v>7.373583613138371</v>
       </c>
       <c r="CS38" t="n">
         <v>5.912820549500294</v>
@@ -26991,7 +26991,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY38" t="n">
-        <v>24.55377586781242</v>
+        <v>24.55377564377335</v>
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
@@ -27288,10 +27288,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ39" t="n">
-        <v>20.2039654068213</v>
+        <v>20.20396545957872</v>
       </c>
       <c r="CK39" t="n">
-        <v>37.47835582965351</v>
+        <v>37.47835592751852</v>
       </c>
       <c r="CL39" t="n">
         <v>55.97851442143241</v>
@@ -27300,23 +27300,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN39" t="n">
-        <v>61.5974785395555</v>
+        <v>61.597478452734</v>
       </c>
       <c r="CO39" t="n">
-        <v>45.1522253744618</v>
+        <v>45.15222535796428</v>
       </c>
       <c r="CP39" t="n">
-        <v>30.98915240298335</v>
+        <v>30.9891522987558</v>
       </c>
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="n">
-        <v>39.70326525809226</v>
+        <v>39.70326529162348</v>
       </c>
       <c r="CS39" t="n">
-        <v>41.31529060205766</v>
+        <v>41.3152906427414</v>
       </c>
       <c r="CT39" t="n">
-        <v>37.18376154185189</v>
+        <v>37.18376157846726</v>
       </c>
       <c r="CU39" t="n">
         <v>4</v>
@@ -27328,10 +27328,10 @@
         <v>2.8</v>
       </c>
       <c r="CX39" t="n">
-        <v>-5.868231113389088</v>
+        <v>-5.868231020696224</v>
       </c>
       <c r="CY39" t="n">
-        <v>0.5099654888873095</v>
+        <v>0.5099655737725639</v>
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
@@ -27626,10 +27626,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ40" t="n">
-        <v>9.430280298234226</v>
+        <v>9.4302802537439</v>
       </c>
       <c r="CK40" t="n">
-        <v>17.49316995322449</v>
+        <v>17.49316987069493</v>
       </c>
       <c r="CL40" t="n">
         <v>30.9711095548374</v>
@@ -27638,23 +27638,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN40" t="n">
-        <v>34.71574759620757</v>
+        <v>34.71574758824536</v>
       </c>
       <c r="CO40" t="n">
-        <v>25.47771502368395</v>
+        <v>25.47771503272126</v>
       </c>
       <c r="CP40" t="n">
-        <v>15.27881627586995</v>
+        <v>15.278816331191</v>
       </c>
       <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="n">
-        <v>20.84306870749501</v>
+        <v>20.84306867799937</v>
       </c>
       <c r="CS40" t="n">
-        <v>21.48544248845422</v>
+        <v>21.4854424517081</v>
       </c>
       <c r="CT40" t="n">
-        <v>19.3368982396088</v>
+        <v>19.33689820653729</v>
       </c>
       <c r="CU40" t="n">
         <v>4</v>
@@ -27666,10 +27666,10 @@
         <v>3.3</v>
       </c>
       <c r="CX40" t="n">
-        <v>27.46801675911943</v>
+        <v>27.46801654111344</v>
       </c>
       <c r="CY40" t="n">
-        <v>37.3966288903738</v>
+        <v>37.39662869593978</v>
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL40" t="n">
-        <v>-16.60347445371087</v>
+        <v>-16.60346541872488</v>
       </c>
       <c r="DM40" t="b">
         <v>1</v>
@@ -27984,10 +27984,10 @@
         <v>12.77999973297119</v>
       </c>
       <c r="CJ41" t="n">
-        <v>1.574362019634505</v>
+        <v>1.574362026260813</v>
       </c>
       <c r="CK41" t="n">
-        <v>2.920441546422006</v>
+        <v>2.920441558713808</v>
       </c>
       <c r="CL41" t="n">
         <v>12.71283757221233</v>
@@ -27996,7 +27996,7 @@
         <v>9.285279950653386</v>
       </c>
       <c r="CN41" t="n">
-        <v>16.04662644665547</v>
+        <v>16.04662645362006</v>
       </c>
       <c r="CO41" t="n">
         <v>6.104046666666666</v>
@@ -28054,7 +28054,7 @@
         <v>-11.43451515806805</v>
       </c>
       <c r="DL41" t="n">
-        <v>-29.69469396946918</v>
+        <v>-29.69468656045111</v>
       </c>
       <c r="DM41" t="b">
         <v>0</v>
@@ -28330,37 +28330,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ42" t="n">
-        <v>17.07331069808112</v>
+        <v>17.07331078335307</v>
       </c>
       <c r="CK42" t="n">
-        <v>28.37657058377574</v>
+        <v>28.37657059421937</v>
       </c>
       <c r="CL42" t="n">
-        <v>47.66545656825829</v>
+        <v>47.66545634773779</v>
       </c>
       <c r="CM42" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN42" t="n">
-        <v>56.59469221753312</v>
+        <v>56.5946922453201</v>
       </c>
       <c r="CO42" t="n">
-        <v>42.94865307942731</v>
+        <v>42.9486530639905</v>
       </c>
       <c r="CP42" t="n">
-        <v>23.70643973254973</v>
+        <v>23.70643963717476</v>
       </c>
       <c r="CQ42" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR42" t="n">
-        <v>37.60349437770622</v>
+        <v>37.60349435172751</v>
       </c>
       <c r="CS42" t="n">
-        <v>37.07077017601888</v>
+        <v>37.07077016830048</v>
       </c>
       <c r="CT42" t="n">
-        <v>33.36369315841699</v>
+        <v>33.36369315147043</v>
       </c>
       <c r="CU42" t="n">
         <v>8</v>
@@ -28372,10 +28372,10 @@
         <v>3.3</v>
       </c>
       <c r="CX42" t="n">
-        <v>24.95764870811157</v>
+        <v>24.95764868209449</v>
       </c>
       <c r="CY42" t="n">
-        <v>40.83705357005534</v>
+        <v>40.83705347275676</v>
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
@@ -28690,37 +28690,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ43" t="n">
-        <v>5.830932731850884</v>
+        <v>5.830932745051316</v>
       </c>
       <c r="CK43" t="n">
-        <v>8.573470615831482</v>
+        <v>8.573470604546189</v>
       </c>
       <c r="CL43" t="n">
-        <v>11.02317118066605</v>
+        <v>11.02317114120126</v>
       </c>
       <c r="CM43" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN43" t="n">
-        <v>9.992440001507868</v>
+        <v>9.992439980409005</v>
       </c>
       <c r="CO43" t="n">
-        <v>14.93936638160634</v>
+        <v>14.93936637695643</v>
       </c>
       <c r="CP43" t="n">
-        <v>5.501588171783267</v>
+        <v>5.501588150409129</v>
       </c>
       <c r="CQ43" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR43" t="n">
-        <v>9.794723693804823</v>
+        <v>9.794723683220752</v>
       </c>
       <c r="CS43" t="n">
-        <v>10.44705005117738</v>
+        <v>10.44705004062795</v>
       </c>
       <c r="CT43" t="n">
-        <v>9.402345046059644</v>
+        <v>9.402345036565155</v>
       </c>
       <c r="CU43" t="n">
         <v>8</v>
@@ -28732,10 +28732,10 @@
         <v>2.7</v>
       </c>
       <c r="CX43" t="n">
-        <v>-37.44281295339085</v>
+        <v>-37.4428130165611</v>
       </c>
       <c r="CY43" t="n">
-        <v>-34.8321765281325</v>
+        <v>-34.83217659855213</v>
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
@@ -29050,10 +29050,10 @@
         <v>11.73999977111816</v>
       </c>
       <c r="CJ44" t="n">
-        <v>4.772256401015579</v>
+        <v>4.77225638200441</v>
       </c>
       <c r="CK44" t="n">
-        <v>8.852535623883897</v>
+        <v>8.852535588618181</v>
       </c>
       <c r="CL44" t="n">
         <v>25.04911384336806</v>
@@ -29062,25 +29062,25 @@
         <v>28.15420526956483</v>
       </c>
       <c r="CN44" t="n">
-        <v>23.16590019056064</v>
+        <v>23.1659001747162</v>
       </c>
       <c r="CO44" t="n">
-        <v>14.15725437859012</v>
+        <v>14.15725438048856</v>
       </c>
       <c r="CP44" t="n">
-        <v>12.84913867550562</v>
+        <v>12.84913869248639</v>
       </c>
       <c r="CQ44" t="n">
         <v>4.799038879412761</v>
       </c>
       <c r="CR44" t="n">
-        <v>18.70469133024553</v>
+        <v>18.7046913248737</v>
       </c>
       <c r="CS44" t="n">
-        <v>18.66157728457538</v>
+        <v>18.66157727760238</v>
       </c>
       <c r="CT44" t="n">
-        <v>16.79541955611784</v>
+        <v>16.79541954984214</v>
       </c>
       <c r="CU44" t="n">
         <v>6</v>
@@ -29092,10 +29092,10 @@
         <v>5.9</v>
       </c>
       <c r="CX44" t="n">
-        <v>43.06149815638523</v>
+        <v>43.0614981029295</v>
       </c>
       <c r="CY44" t="n">
-        <v>59.32446077436353</v>
+        <v>59.32446072860693</v>
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
@@ -29406,37 +29406,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ45" t="n">
-        <v>30.83210607591968</v>
+        <v>30.83210627958053</v>
       </c>
       <c r="CK45" t="n">
-        <v>35.07524630358477</v>
+        <v>35.07524614717919</v>
       </c>
       <c r="CL45" t="n">
-        <v>37.91416017666519</v>
+        <v>37.91415975715928</v>
       </c>
       <c r="CM45" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN45" t="n">
-        <v>59.10496031981044</v>
+        <v>59.10496008950702</v>
       </c>
       <c r="CO45" t="n">
-        <v>16.57964504833495</v>
+        <v>16.57964502823301</v>
       </c>
       <c r="CP45" t="n">
-        <v>16.88731352844288</v>
+        <v>16.88731316749069</v>
       </c>
       <c r="CQ45" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR45" t="n">
-        <v>34.28114202077357</v>
+        <v>34.28114189782255</v>
       </c>
       <c r="CS45" t="n">
-        <v>32.95367618975222</v>
+        <v>32.95367621337986</v>
       </c>
       <c r="CT45" t="n">
-        <v>29.658308570777</v>
+        <v>29.65830859204187</v>
       </c>
       <c r="CU45" t="n">
         <v>8</v>
@@ -29448,10 +29448,10 @@
         <v>3.6</v>
       </c>
       <c r="CX45" t="n">
-        <v>-23.32391846747629</v>
+        <v>-23.32391841249989</v>
       </c>
       <c r="CY45" t="n">
-        <v>-11.37243601265845</v>
+        <v>-11.37243633052561</v>
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>-0.667689601187782</v>
       </c>
       <c r="DL45" t="n">
-        <v>-11.71364879963919</v>
+        <v>-11.71364092295562</v>
       </c>
       <c r="DM45" t="b">
         <v>1</v>
@@ -29766,10 +29766,10 @@
         <v>9.279999732971191</v>
       </c>
       <c r="CJ46" t="n">
-        <v>2.530273385197774</v>
+        <v>2.530273360000627</v>
       </c>
       <c r="CK46" t="n">
-        <v>4.693657129541871</v>
+        <v>4.693657082801162</v>
       </c>
       <c r="CL46" t="n">
         <v>13.27861732849549</v>
@@ -29778,25 +29778,25 @@
         <v>15.00003440426151</v>
       </c>
       <c r="CN46" t="n">
-        <v>10.31764099601564</v>
+        <v>10.31764099326716</v>
       </c>
       <c r="CO46" t="n">
-        <v>7.305089434992105</v>
+        <v>7.30508943741188</v>
       </c>
       <c r="CP46" t="n">
-        <v>6.757993199938901</v>
+        <v>6.757993222156737</v>
       </c>
       <c r="CQ46" t="n">
         <v>10.43331654384748</v>
       </c>
       <c r="CR46" t="n">
-        <v>9.683764148156143</v>
+        <v>9.683764144605917</v>
       </c>
       <c r="CS46" t="n">
-        <v>10.31764099601564</v>
+        <v>10.31764099326716</v>
       </c>
       <c r="CT46" t="n">
-        <v>9.285876896414077</v>
+        <v>9.285876893940443</v>
       </c>
       <c r="CU46" t="n">
         <v>7</v>
@@ -29808,10 +29808,10 @@
         <v>5.9</v>
       </c>
       <c r="CX46" t="n">
-        <v>0.06333150443964541</v>
+        <v>0.06333147778410098</v>
       </c>
       <c r="CY46" t="n">
-        <v>4.350909771585498</v>
+        <v>4.350909733328745</v>
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>-0.2150586812202149</v>
       </c>
       <c r="DL46" t="n">
-        <v>-35.02795298830792</v>
+        <v>-35.02794846614577</v>
       </c>
       <c r="DM46" t="b">
         <v>0</v>
@@ -30122,10 +30122,10 @@
         <v>33.38000106811523</v>
       </c>
       <c r="CJ47" t="n">
-        <v>14.45460459059842</v>
+        <v>14.45460462227885</v>
       </c>
       <c r="CK47" t="n">
-        <v>26.81329151556006</v>
+        <v>26.81329157432727</v>
       </c>
       <c r="CL47" t="n">
         <v>54.20159487163318</v>
@@ -30134,25 +30134,25 @@
         <v>41.89994969714121</v>
       </c>
       <c r="CN47" t="n">
-        <v>69.22029418046264</v>
+        <v>69.22029413950256</v>
       </c>
       <c r="CO47" t="n">
-        <v>38.39264063381264</v>
+        <v>38.39264062574333</v>
       </c>
       <c r="CP47" t="n">
-        <v>38.84957667101231</v>
+        <v>38.8495766111008</v>
       </c>
       <c r="CQ47" t="n">
         <v>21.08922927558395</v>
       </c>
       <c r="CR47" t="n">
-        <v>41.49522526360086</v>
+        <v>41.49522525643318</v>
       </c>
       <c r="CS47" t="n">
-        <v>38.84957667101231</v>
+        <v>38.8495766111008</v>
       </c>
       <c r="CT47" t="n">
-        <v>34.96461900391107</v>
+        <v>34.96461894999072</v>
       </c>
       <c r="CU47" t="n">
         <v>7</v>
@@ -30164,10 +30164,10 @@
         <v>4.8</v>
       </c>
       <c r="CX47" t="n">
-        <v>4.747207564680034</v>
+        <v>4.747207403145115</v>
       </c>
       <c r="CY47" t="n">
-        <v>24.31163551770323</v>
+        <v>24.31163549623028</v>
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
@@ -30476,10 +30476,10 @@
         <v>6.550000190734863</v>
       </c>
       <c r="CJ48" t="n">
-        <v>7.7931400177036</v>
+        <v>7.793139942703395</v>
       </c>
       <c r="CK48" t="n">
-        <v>11.34681186577644</v>
+        <v>11.34681175657614</v>
       </c>
       <c r="CL48" t="n">
         <v>8.052009690737892</v>
@@ -30498,7 +30498,7 @@
         <v>5.354239830150741</v>
       </c>
       <c r="CR48" t="n">
-        <v>8.367187742540432</v>
+        <v>8.367187711840348</v>
       </c>
       <c r="CS48" t="n">
         <v>8.416227402183392</v>
@@ -30519,7 +30519,7 @@
         <v>15.64281589914329</v>
       </c>
       <c r="CY48" t="n">
-        <v>27.74332059373106</v>
+        <v>27.74332012502749</v>
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>1</v>
       </c>
       <c r="AW49" t="n">
-        <v>186901528576</v>
+        <v>187227897856</v>
       </c>
       <c r="AX49" t="n">
         <v>7.35</v>
@@ -30812,35 +30812,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ49" t="n">
-        <v>10.16567237167966</v>
+        <v>10.16567239950484</v>
       </c>
       <c r="CK49" t="n">
-        <v>17.61110254244038</v>
+        <v>17.61110253775026</v>
       </c>
       <c r="CL49" t="n">
-        <v>28.75563263571181</v>
+        <v>28.75563254934464</v>
       </c>
       <c r="CM49" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN49" t="n">
-        <v>32.08888080896667</v>
+        <v>32.08888080692324</v>
       </c>
       <c r="CO49" t="n">
-        <v>27.87173774883079</v>
+        <v>27.8717377425716</v>
       </c>
       <c r="CP49" t="n">
-        <v>14.20689962759608</v>
+        <v>14.20689959299714</v>
       </c>
       <c r="CQ49" t="inlineStr"/>
       <c r="CR49" t="n">
-        <v>21.10103632466566</v>
+        <v>21.10103630729284</v>
       </c>
       <c r="CS49" t="n">
-        <v>22.74142014563559</v>
+        <v>22.74142014016093</v>
       </c>
       <c r="CT49" t="n">
-        <v>20.46727813107203</v>
+        <v>20.46727812614484</v>
       </c>
       <c r="CU49" t="n">
         <v>4</v>
@@ -30852,10 +30852,10 @@
         <v>2.8</v>
       </c>
       <c r="CX49" t="n">
-        <v>19.83183971016667</v>
+        <v>19.83183968131894</v>
       </c>
       <c r="CY49" t="n">
-        <v>23.54236779227756</v>
+        <v>23.54236769056313</v>
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
@@ -31170,10 +31170,10 @@
         <v>32.70000076293945</v>
       </c>
       <c r="CJ50" t="n">
-        <v>11.11179111257907</v>
+        <v>11.11179111323442</v>
       </c>
       <c r="CK50" t="n">
-        <v>20.61237251383417</v>
+        <v>20.61237251504984</v>
       </c>
       <c r="CL50" t="n">
         <v>55.69087533534032</v>
@@ -31182,19 +31182,19 @@
         <v>52.54606660988762</v>
       </c>
       <c r="CN50" t="n">
-        <v>58.06561443899081</v>
+        <v>58.06561443885076</v>
       </c>
       <c r="CO50" t="n">
-        <v>28.27593786619558</v>
+        <v>28.27593786778185</v>
       </c>
       <c r="CP50" t="n">
-        <v>35.15802047755473</v>
+        <v>35.15802047672543</v>
       </c>
       <c r="CQ50" t="n">
         <v>54.68623962474753</v>
       </c>
       <c r="CR50" t="n">
-        <v>43.57644669522154</v>
+        <v>43.57644669548333</v>
       </c>
       <c r="CS50" t="n">
         <v>52.54606660988762</v>
@@ -31215,7 +31215,7 @@
         <v>44.62219830433958</v>
       </c>
       <c r="CY50" t="n">
-        <v>33.26130176916971</v>
+        <v>33.26130176997029</v>
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
@@ -31534,37 +31534,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ51" t="n">
-        <v>32.50257829001703</v>
+        <v>32.50257839087045</v>
       </c>
       <c r="CK51" t="n">
-        <v>44.74764057913653</v>
+        <v>44.74764038431965</v>
       </c>
       <c r="CL51" t="n">
-        <v>51.52715738101318</v>
+        <v>51.52715699679499</v>
       </c>
       <c r="CM51" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN51" t="n">
-        <v>71.44157102715603</v>
+        <v>71.44157081911828</v>
       </c>
       <c r="CO51" t="n">
-        <v>59.88947345916158</v>
+        <v>59.88947341794151</v>
       </c>
       <c r="CP51" t="n">
-        <v>25.45084486398652</v>
+        <v>25.45084462941759</v>
       </c>
       <c r="CQ51" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR51" t="n">
-        <v>51.51519296586034</v>
+        <v>51.51519284560929</v>
       </c>
       <c r="CS51" t="n">
-        <v>49.93498913827833</v>
+        <v>49.93498894616923</v>
       </c>
       <c r="CT51" t="n">
-        <v>44.9414902244505</v>
+        <v>44.94149005155231</v>
       </c>
       <c r="CU51" t="n">
         <v>8</v>
@@ -31576,10 +31576,10 @@
         <v>3.1</v>
       </c>
       <c r="CX51" t="n">
-        <v>0.3158281022310971</v>
+        <v>0.3158277162976342</v>
       </c>
       <c r="CY51" t="n">
-        <v>14.98927197133675</v>
+        <v>14.98927170291921</v>
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>1</v>
       </c>
       <c r="AW52" t="n">
-        <v>3190868736</v>
+        <v>3196020224</v>
       </c>
       <c r="AX52" t="n">
         <v>6.4</v>
@@ -31894,37 +31894,37 @@
         <v>10.89000034332275</v>
       </c>
       <c r="CJ52" t="n">
-        <v>8.332366121739575</v>
+        <v>8.332366149887951</v>
       </c>
       <c r="CK52" t="n">
-        <v>11.54775601154457</v>
+        <v>11.54775601885551</v>
       </c>
       <c r="CL52" t="n">
-        <v>16.84415148691581</v>
+        <v>16.84415144067704</v>
       </c>
       <c r="CM52" t="n">
         <v>24.06372840589797</v>
       </c>
       <c r="CN52" t="n">
-        <v>24.25150329102852</v>
+        <v>24.25150330823</v>
       </c>
       <c r="CO52" t="n">
-        <v>20.99516499835137</v>
+        <v>20.9951649930635</v>
       </c>
       <c r="CP52" t="n">
-        <v>8.332401473132608</v>
+        <v>8.332401445240945</v>
       </c>
       <c r="CQ52" t="n">
         <v>9.730400983158669</v>
       </c>
       <c r="CR52" t="n">
-        <v>15.51218409647113</v>
+        <v>15.51218409312645</v>
       </c>
       <c r="CS52" t="n">
-        <v>14.19595374923019</v>
+        <v>14.19595372976627</v>
       </c>
       <c r="CT52" t="n">
-        <v>12.77635837430717</v>
+        <v>12.77635835678965</v>
       </c>
       <c r="CU52" t="n">
         <v>8</v>
@@ -31936,10 +31936,10 @@
         <v>2.9</v>
       </c>
       <c r="CX52" t="n">
-        <v>17.32192811307893</v>
+        <v>17.32192795222014</v>
       </c>
       <c r="CY52" t="n">
-        <v>42.44429391577101</v>
+        <v>42.44429388505762</v>
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
@@ -32244,10 +32244,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ53" t="n">
-        <v>10.47626030483282</v>
+        <v>10.47626037274054</v>
       </c>
       <c r="CK53" t="n">
-        <v>19.43346286546489</v>
+        <v>19.43346299143371</v>
       </c>
       <c r="CL53" t="n">
         <v>60.73011328156327</v>
@@ -32256,7 +32256,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN53" t="n">
-        <v>81.29749116625149</v>
+        <v>81.29749124757811</v>
       </c>
       <c r="CO53" t="n">
         <v>11.76833333333333</v>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="CQ53" t="inlineStr"/>
       <c r="CR53" t="n">
-        <v>13.89268550121035</v>
+        <v>13.89268556583586</v>
       </c>
       <c r="CS53" t="n">
         <v>11.76833333333333</v>
@@ -32287,7 +32287,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY53" t="n">
-        <v>-74.0711365687968</v>
+        <v>-74.07113644818179</v>
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
@@ -32584,10 +32584,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ54" t="n">
-        <v>15.68694277612544</v>
+        <v>15.6869427790179</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.0992788497127</v>
+        <v>29.0992788550782</v>
       </c>
       <c r="CL54" t="n">
         <v>55.61293748708871</v>
@@ -32596,23 +32596,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN54" t="n">
-        <v>62.11186603739112</v>
+        <v>62.11186603670111</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.65076910303291</v>
+        <v>36.65076910251672</v>
       </c>
       <c r="CP54" t="n">
-        <v>30.94726543071105</v>
+        <v>30.94726542671738</v>
       </c>
       <c r="CQ54" t="inlineStr"/>
       <c r="CR54" t="n">
-        <v>34.26248205398994</v>
+        <v>34.26248205592537</v>
       </c>
       <c r="CS54" t="n">
-        <v>32.8750239763728</v>
+        <v>32.87502397879746</v>
       </c>
       <c r="CT54" t="n">
-        <v>29.58752157873552</v>
+        <v>29.58752158091771</v>
       </c>
       <c r="CU54" t="n">
         <v>4</v>
@@ -32624,10 +32624,10 @@
         <v>3.5</v>
       </c>
       <c r="CX54" t="n">
-        <v>-1.4077928921164</v>
+        <v>-1.40779288484485</v>
       </c>
       <c r="CY54" t="n">
-        <v>14.17021590361565</v>
+        <v>14.17021591006493</v>
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
@@ -32952,10 +32952,10 @@
         <v>4.78000020980835</v>
       </c>
       <c r="CJ55" t="n">
-        <v>1.105884091399179</v>
+        <v>1.10588409695656</v>
       </c>
       <c r="CK55" t="n">
-        <v>2.051414989545477</v>
+        <v>2.051414999854419</v>
       </c>
       <c r="CL55" t="n">
         <v>9.640030864529775</v>
@@ -32964,13 +32964,13 @@
         <v>9.075586225783375</v>
       </c>
       <c r="CN55" t="n">
-        <v>10.67250376968955</v>
+        <v>10.67250377023472</v>
       </c>
       <c r="CO55" t="n">
-        <v>4.221651666260194</v>
+        <v>4.221651665671916</v>
       </c>
       <c r="CP55" t="n">
-        <v>7.170782406336428</v>
+        <v>7.17078239923543</v>
       </c>
       <c r="CQ55" t="n">
         <v>6.969578707797512</v>
@@ -33294,10 +33294,10 @@
         <v>24.1299991607666</v>
       </c>
       <c r="CJ56" t="n">
-        <v>4.231713754901545</v>
+        <v>4.231713749960219</v>
       </c>
       <c r="CK56" t="n">
-        <v>7.849829015342366</v>
+        <v>7.849829006176207</v>
       </c>
       <c r="CL56" t="n">
         <v>28.04583235790854</v>
@@ -33306,13 +33306,13 @@
         <v>27.96001968388332</v>
       </c>
       <c r="CN56" t="n">
-        <v>24.90509226239773</v>
+        <v>24.90509226527422</v>
       </c>
       <c r="CO56" t="n">
-        <v>2.969615091359295</v>
+        <v>2.969615091474098</v>
       </c>
       <c r="CP56" t="n">
-        <v>18.04256697852469</v>
+        <v>18.04256698414713</v>
       </c>
       <c r="CQ56" t="n">
         <v>17.75746799357721</v>
@@ -33638,10 +33638,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ57" t="n">
-        <v>13.32483359075277</v>
+        <v>13.32483359494353</v>
       </c>
       <c r="CK57" t="n">
-        <v>19.40095770813604</v>
+        <v>19.40095771423778</v>
       </c>
       <c r="CL57" t="n">
         <v>16.70870841086448</v>
@@ -33651,7 +33651,7 @@
       </c>
       <c r="CN57" t="inlineStr"/>
       <c r="CO57" t="n">
-        <v>13.95326101288333</v>
+        <v>14.38930041953594</v>
       </c>
       <c r="CP57" t="n">
         <v>4.291934715428101</v>
@@ -33660,7 +33660,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR57" t="n">
-        <v>16.24126649766002</v>
+        <v>16.31393973381754</v>
       </c>
       <c r="CS57" t="n">
         <v>15.78776446356376</v>
@@ -33681,7 +33681,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY57" t="n">
-        <v>51.78754006702593</v>
+        <v>52.46672920210042</v>
       </c>
       <c r="CZ57" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>1</v>
       </c>
       <c r="AU58" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AV58" t="b">
         <v>1</v>
@@ -34004,10 +34004,10 @@
         <v>49.97999954223633</v>
       </c>
       <c r="CJ58" t="n">
-        <v>8.318203549828779</v>
+        <v>8.318203507580391</v>
       </c>
       <c r="CK58" t="n">
-        <v>15.43026758493238</v>
+        <v>15.43026750656162</v>
       </c>
       <c r="CL58" t="n">
         <v>19.67424224404727</v>
@@ -34016,25 +34016,25 @@
         <v>12.23202482325925</v>
       </c>
       <c r="CN58" t="n">
-        <v>14.08088718543708</v>
+        <v>14.08088736399888</v>
       </c>
       <c r="CO58" t="n">
-        <v>20.63682237815346</v>
+        <v>20.63682240359299</v>
       </c>
       <c r="CP58" t="n">
-        <v>10.6428162655222</v>
+        <v>10.64281638880638</v>
       </c>
       <c r="CQ58" t="n">
         <v>13.15686200775853</v>
       </c>
       <c r="CR58" t="n">
-        <v>14.27151575486737</v>
+        <v>14.27151578070066</v>
       </c>
       <c r="CS58" t="n">
-        <v>13.6188745965978</v>
+        <v>13.6188746858787</v>
       </c>
       <c r="CT58" t="n">
-        <v>12.25698713693802</v>
+        <v>12.25698721729083</v>
       </c>
       <c r="CU58" t="n">
         <v>8</v>
@@ -34046,10 +34046,10 @@
         <v>2.5</v>
       </c>
       <c r="CX58" t="n">
-        <v>-75.47621598799721</v>
+        <v>-75.47621582722728</v>
       </c>
       <c r="CY58" t="n">
-        <v>-71.44554644742041</v>
+        <v>-71.44554639573313</v>
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>1</v>
       </c>
       <c r="AW59" t="n">
-        <v>37049118720</v>
+        <v>37104889856</v>
       </c>
       <c r="AX59" t="n">
         <v>11.24</v>
@@ -34302,7 +34302,7 @@
         <v>44.3</v>
       </c>
       <c r="BN59" t="n">
-        <v>12.74</v>
+        <v>12.93</v>
       </c>
       <c r="BO59" t="n">
         <v>9.73</v>
@@ -34368,10 +34368,10 @@
         <v>34.81999969482422</v>
       </c>
       <c r="CJ59" t="n">
-        <v>12.29771087175807</v>
+        <v>12.29771090237208</v>
       </c>
       <c r="CK59" t="n">
-        <v>22.81225366711122</v>
+        <v>22.8122537239002</v>
       </c>
       <c r="CL59" t="n">
         <v>41.04670782530435</v>
@@ -34380,25 +34380,25 @@
         <v>33.52046162339458</v>
       </c>
       <c r="CN59" t="n">
-        <v>41.80899894527207</v>
+        <v>41.80899890089865</v>
       </c>
       <c r="CO59" t="n">
-        <v>23.77591433088793</v>
+        <v>23.77591432505459</v>
       </c>
       <c r="CP59" t="n">
-        <v>24.92756553673476</v>
+        <v>24.92756548487464</v>
       </c>
       <c r="CQ59" t="n">
         <v>27.30596254019629</v>
       </c>
       <c r="CR59" t="n">
-        <v>28.43694691758241</v>
+        <v>28.43694691574942</v>
       </c>
       <c r="CS59" t="n">
-        <v>26.11676403846553</v>
+        <v>26.11676401253547</v>
       </c>
       <c r="CT59" t="n">
-        <v>23.50508763461898</v>
+        <v>23.50508761128192</v>
       </c>
       <c r="CU59" t="n">
         <v>8</v>
@@ -34410,10 +34410,10 @@
         <v>3.4</v>
       </c>
       <c r="CX59" t="n">
-        <v>-32.49543986034881</v>
+        <v>-32.4954399273708</v>
       </c>
       <c r="CY59" t="n">
-        <v>-18.33157045716635</v>
+        <v>-18.33157046243052</v>
       </c>
       <c r="CZ59" t="inlineStr">
         <is>
@@ -34724,10 +34724,10 @@
         <v>4.25</v>
       </c>
       <c r="CJ60" t="n">
-        <v>2.76051724855626</v>
+        <v>2.760517245314274</v>
       </c>
       <c r="CK60" t="n">
-        <v>5.120759496071861</v>
+        <v>5.120759490057978</v>
       </c>
       <c r="CL60" t="n">
         <v>13.06554524361949</v>
@@ -34736,13 +34736,13 @@
         <v>14.63912825766184</v>
       </c>
       <c r="CN60" t="n">
-        <v>15.13083190065455</v>
+        <v>15.1308318947896</v>
       </c>
       <c r="CO60" t="n">
-        <v>9.474664849062652</v>
+        <v>9.474664849484594</v>
       </c>
       <c r="CP60" t="n">
-        <v>6.508725013355891</v>
+        <v>6.508725016288722</v>
       </c>
       <c r="CQ60" t="n">
         <v>1.476527849208126</v>
@@ -35070,37 +35070,37 @@
         <v>24.77000045776367</v>
       </c>
       <c r="CJ61" t="n">
-        <v>10.94213063200709</v>
+        <v>10.94213059726783</v>
       </c>
       <c r="CK61" t="n">
-        <v>13.84673159218291</v>
+        <v>13.84673160981596</v>
       </c>
       <c r="CL61" t="n">
-        <v>16.40252491526523</v>
+        <v>16.40252498822795</v>
       </c>
       <c r="CM61" t="n">
         <v>20.87886833295617</v>
       </c>
       <c r="CN61" t="n">
-        <v>16.02102938633461</v>
+        <v>16.02102943323814</v>
       </c>
       <c r="CO61" t="n">
-        <v>23.06891947755925</v>
+        <v>23.0689194877811</v>
       </c>
       <c r="CP61" t="n">
-        <v>7.863807290128736</v>
+        <v>7.863807342006963</v>
       </c>
       <c r="CQ61" t="n">
         <v>18.59237633123597</v>
       </c>
       <c r="CR61" t="n">
-        <v>15.95204849470874</v>
+        <v>15.95204851531626</v>
       </c>
       <c r="CS61" t="n">
-        <v>16.21177715079992</v>
+        <v>16.21177721073305</v>
       </c>
       <c r="CT61" t="n">
-        <v>14.59059943571993</v>
+        <v>14.59059948965974</v>
       </c>
       <c r="CU61" t="n">
         <v>8</v>
@@ -35112,10 +35112,10 @@
         <v>2.9</v>
       </c>
       <c r="CX61" t="n">
-        <v>-41.09568362504091</v>
+        <v>-41.09568340727824</v>
       </c>
       <c r="CY61" t="n">
-        <v>-35.59932095314562</v>
+        <v>-35.59932086995016</v>
       </c>
       <c r="CZ61" t="inlineStr">
         <is>
@@ -35426,37 +35426,37 @@
         <v>29.61000061035156</v>
       </c>
       <c r="CJ62" t="n">
-        <v>13.82349765739077</v>
+        <v>13.82349757249801</v>
       </c>
       <c r="CK62" t="n">
-        <v>14.35866822258811</v>
+        <v>14.35866820528189</v>
       </c>
       <c r="CL62" t="n">
-        <v>15.04713239624037</v>
+        <v>15.04713247051169</v>
       </c>
       <c r="CM62" t="n">
         <v>30.31758334384464</v>
       </c>
       <c r="CN62" t="n">
-        <v>14.1879739561542</v>
+        <v>14.1879739941943</v>
       </c>
       <c r="CO62" t="n">
-        <v>30.44468446782902</v>
+        <v>30.44468448567737</v>
       </c>
       <c r="CP62" t="n">
-        <v>6.004060691405561</v>
+        <v>6.004060766484719</v>
       </c>
       <c r="CQ62" t="n">
         <v>37.94236112090656</v>
       </c>
       <c r="CR62" t="n">
-        <v>17.74051439077895</v>
+        <v>17.74051440549894</v>
       </c>
       <c r="CS62" t="n">
-        <v>14.35866822258811</v>
+        <v>14.35866820528189</v>
       </c>
       <c r="CT62" t="n">
-        <v>12.9228014003293</v>
+        <v>12.9228013847537</v>
       </c>
       <c r="CU62" t="n">
         <v>7</v>
@@ -35468,10 +35468,10 @@
         <v>6.3</v>
       </c>
       <c r="CX62" t="n">
-        <v>-56.35663244190703</v>
+        <v>-56.35663249450954</v>
       </c>
       <c r="CY62" t="n">
-        <v>-40.08607218813456</v>
+        <v>-40.08607213842166</v>
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>-2.817918093619187</v>
       </c>
       <c r="DL62" t="n">
-        <v>-27.91534451392703</v>
+        <v>-27.91533777463357</v>
       </c>
       <c r="DM62" t="b">
         <v>0</v>
@@ -35782,10 +35782,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ63" t="n">
-        <v>8.850909487110853</v>
+        <v>8.850909473613465</v>
       </c>
       <c r="CK63" t="n">
-        <v>16.41843709859063</v>
+        <v>16.41843707355297</v>
       </c>
       <c r="CL63" t="n">
         <v>16.35235520731475</v>
@@ -35794,7 +35794,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN63" t="n">
-        <v>25.87578449342791</v>
+        <v>25.87578448106929</v>
       </c>
       <c r="CO63" t="n">
         <v>19.94489718117502</v>
@@ -35806,7 +35806,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR63" t="n">
-        <v>16.79289066998749</v>
+        <v>16.79289066362578</v>
       </c>
       <c r="CS63" t="n">
         <v>16.28957786959118</v>
@@ -35827,7 +35827,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY63" t="n">
-        <v>-11.00747258541346</v>
+        <v>-11.0074726191268</v>
       </c>
       <c r="CZ63" t="inlineStr">
         <is>
@@ -36154,35 +36154,35 @@
         <v>3.410000085830688</v>
       </c>
       <c r="CJ64" t="n">
-        <v>2.617517202431535</v>
+        <v>2.617517221042489</v>
       </c>
       <c r="CK64" t="n">
-        <v>2.995865530089951</v>
+        <v>2.995865535931345</v>
       </c>
       <c r="CL64" t="n">
-        <v>3.583269960555498</v>
+        <v>3.583269942064618</v>
       </c>
       <c r="CM64" t="n">
         <v>6.696150695272573</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.400672774727071</v>
+        <v>5.400672783178041</v>
       </c>
       <c r="CO64" t="n">
-        <v>8.464613715007831</v>
+        <v>8.464613710247207</v>
       </c>
       <c r="CP64" t="n">
-        <v>1.604916863013375</v>
+        <v>1.604916847274464</v>
       </c>
       <c r="CQ64" t="inlineStr"/>
       <c r="CR64" t="n">
-        <v>4.480429534442548</v>
+        <v>4.480429533572962</v>
       </c>
       <c r="CS64" t="n">
-        <v>3.583269960555498</v>
+        <v>3.583269942064618</v>
       </c>
       <c r="CT64" t="n">
-        <v>3.224942964499948</v>
+        <v>3.224942947858156</v>
       </c>
       <c r="CU64" t="n">
         <v>7</v>
@@ -36194,10 +36194,10 @@
         <v>5.3</v>
       </c>
       <c r="CX64" t="n">
-        <v>-5.426894917090874</v>
+        <v>-5.426895405119958</v>
       </c>
       <c r="CY64" t="n">
-        <v>31.39089213105104</v>
+        <v>31.39089210554999</v>
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
@@ -36520,10 +36520,10 @@
         <v>35.18000030517578</v>
       </c>
       <c r="CJ65" t="n">
-        <v>10.07312301375178</v>
+        <v>10.0731230057133</v>
       </c>
       <c r="CK65" t="n">
-        <v>18.68564319050954</v>
+        <v>18.68564317559816</v>
       </c>
       <c r="CL65" t="n">
         <v>28.5272340295948</v>
@@ -36532,25 +36532,25 @@
         <v>21.17723585857856</v>
       </c>
       <c r="CN65" t="n">
-        <v>25.90721693594488</v>
+        <v>25.90721695523408</v>
       </c>
       <c r="CO65" t="n">
-        <v>22.89550545775529</v>
+        <v>22.6873645016019</v>
       </c>
       <c r="CP65" t="n">
-        <v>16.611181123329</v>
+        <v>16.61118113978281</v>
       </c>
       <c r="CQ65" t="n">
         <v>27.23126452034872</v>
       </c>
       <c r="CR65" t="n">
-        <v>21.38855051622657</v>
+        <v>21.36253289830654</v>
       </c>
       <c r="CS65" t="n">
-        <v>22.03637065816693</v>
+        <v>21.93230018009023</v>
       </c>
       <c r="CT65" t="n">
-        <v>19.83273359235024</v>
+        <v>19.73907016208121</v>
       </c>
       <c r="CU65" t="n">
         <v>8</v>
@@ -36562,10 +36562,10 @@
         <v>2.8</v>
       </c>
       <c r="CX65" t="n">
-        <v>-43.62497606507301</v>
+        <v>-43.89121662634795</v>
       </c>
       <c r="CY65" t="n">
-        <v>-39.20252890651673</v>
+        <v>-39.27648461343639</v>
       </c>
       <c r="CZ65" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>-2.467422781198825</v>
       </c>
       <c r="DL65" t="n">
-        <v>-21.73874227621538</v>
+        <v>-21.73873559212695</v>
       </c>
       <c r="DM65" t="b">
         <v>0</v>
@@ -36854,10 +36854,10 @@
         <v>13.14999961853027</v>
       </c>
       <c r="CJ66" t="n">
-        <v>11.12140753920365</v>
+        <v>11.12140753099835</v>
       </c>
       <c r="CK66" t="n">
-        <v>16.19276937708052</v>
+        <v>16.19276936513359</v>
       </c>
       <c r="CL66" t="n">
         <v>15.50566848443479</v>
@@ -36874,13 +36874,13 @@
       </c>
       <c r="CQ66" t="inlineStr"/>
       <c r="CR66" t="n">
-        <v>12.53829468351307</v>
+        <v>12.53829467847502</v>
       </c>
       <c r="CS66" t="n">
-        <v>13.31353801181922</v>
+        <v>13.31353800771657</v>
       </c>
       <c r="CT66" t="n">
-        <v>11.9821842106373</v>
+        <v>11.98218420694491</v>
       </c>
       <c r="CU66" t="n">
         <v>4</v>
@@ -36892,10 +36892,10 @@
         <v>2.2</v>
       </c>
       <c r="CX66" t="n">
-        <v>-8.880725792929701</v>
+        <v>-8.880725821008696</v>
       </c>
       <c r="CY66" t="n">
-        <v>-4.651748690206936</v>
+        <v>-4.651748728519156</v>
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
@@ -37206,10 +37206,10 @@
         <v>8.340000152587891</v>
       </c>
       <c r="CJ67" t="n">
-        <v>1.607882486886066</v>
+        <v>1.607882485612103</v>
       </c>
       <c r="CK67" t="n">
-        <v>2.982622013173653</v>
+        <v>2.98262201081045</v>
       </c>
       <c r="CL67" t="n">
         <v>24.39404018141049</v>
@@ -37218,13 +37218,13 @@
         <v>24.19815257966773</v>
       </c>
       <c r="CN67" t="n">
-        <v>26.08971932102097</v>
+        <v>26.08971931941487</v>
       </c>
       <c r="CO67" t="n">
-        <v>6.710381499757311</v>
+        <v>6.710381499833533</v>
       </c>
       <c r="CP67" t="n">
-        <v>18.19403113111958</v>
+        <v>18.19403113258484</v>
       </c>
       <c r="CQ67" t="n">
         <v>15.56402401821373</v>
@@ -37552,10 +37552,10 @@
         <v>8.439999580383301</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.5022232230790979</v>
+        <v>0.5022232223349544</v>
       </c>
       <c r="CK68" t="n">
-        <v>0.9316240788117267</v>
+        <v>0.9316240774313405</v>
       </c>
       <c r="CL68" t="n">
         <v>9.437130332496094</v>
@@ -37564,13 +37564,13 @@
         <v>8.668386285715835</v>
       </c>
       <c r="CN68" t="n">
-        <v>10.35702314647473</v>
+        <v>10.35702314718015</v>
       </c>
       <c r="CO68" t="n">
-        <v>0.7357683740851259</v>
+        <v>0.7357683740995217</v>
       </c>
       <c r="CP68" t="n">
-        <v>8.039858088832881</v>
+        <v>8.039858089828902</v>
       </c>
       <c r="CQ68" t="inlineStr"/>
       <c r="CR68" t="inlineStr"/>
@@ -37902,25 +37902,25 @@
         <v>2.240000009536743</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.6430659525574216</v>
+        <v>0.6430659547212066</v>
       </c>
       <c r="CK69" t="n">
-        <v>0.908508402864441</v>
+        <v>0.9085084054675461</v>
       </c>
       <c r="CL69" t="n">
-        <v>3.343849487020723</v>
+        <v>3.343849485350326</v>
       </c>
       <c r="CM69" t="n">
         <v>6.907675204991913</v>
       </c>
       <c r="CN69" t="n">
-        <v>2.564998455489631</v>
+        <v>2.56499845842287</v>
       </c>
       <c r="CO69" t="n">
-        <v>2.230430075403012</v>
+        <v>2.230430075302555</v>
       </c>
       <c r="CP69" t="n">
-        <v>1.660364572292551</v>
+        <v>1.66036457131954</v>
       </c>
       <c r="CQ69" t="n">
         <v>6.634722275472289</v>
@@ -38256,10 +38256,10 @@
         <v>21.36000061035156</v>
       </c>
       <c r="CJ70" t="n">
-        <v>5.907198068279585</v>
+        <v>5.90719807467577</v>
       </c>
       <c r="CK70" t="n">
-        <v>10.95785241665863</v>
+        <v>10.95785242852355</v>
       </c>
       <c r="CL70" t="n">
         <v>32.3451437813895</v>
@@ -38268,25 +38268,25 @@
         <v>33.26867930684288</v>
       </c>
       <c r="CN70" t="n">
-        <v>28.98255279703931</v>
+        <v>28.98255279643806</v>
       </c>
       <c r="CO70" t="n">
-        <v>25.19834977900429</v>
+        <v>25.1983497779687</v>
       </c>
       <c r="CP70" t="n">
-        <v>18.79799009132352</v>
+        <v>18.79799008451286</v>
       </c>
       <c r="CQ70" t="n">
         <v>13.70244046469206</v>
       </c>
       <c r="CR70" t="n">
-        <v>23.32185837670717</v>
+        <v>23.32185837719538</v>
       </c>
       <c r="CS70" t="n">
-        <v>25.19834977900429</v>
+        <v>25.1983497779687</v>
       </c>
       <c r="CT70" t="n">
-        <v>22.67851480110386</v>
+        <v>22.67851480017183</v>
       </c>
       <c r="CU70" t="n">
         <v>7</v>
@@ -38298,10 +38298,10 @@
         <v>5.6</v>
       </c>
       <c r="CX70" t="n">
-        <v>6.172819068709723</v>
+        <v>6.172819064346324</v>
       </c>
       <c r="CY70" t="n">
-        <v>9.184727108129609</v>
+        <v>9.184727110415203</v>
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
@@ -38612,25 +38612,25 @@
         <v>17.28000068664551</v>
       </c>
       <c r="CJ71" t="n">
-        <v>4.022695616101089</v>
+        <v>4.022695612443805</v>
       </c>
       <c r="CK71" t="n">
-        <v>6.903155498396494</v>
+        <v>6.903155493895718</v>
       </c>
       <c r="CL71" t="n">
-        <v>23.48224777620755</v>
+        <v>23.48224778224658</v>
       </c>
       <c r="CM71" t="n">
         <v>32.85543339401257</v>
       </c>
       <c r="CN71" t="n">
-        <v>16.59077768232352</v>
+        <v>16.59077768056397</v>
       </c>
       <c r="CO71" t="n">
-        <v>20.29840994765691</v>
+        <v>20.50985171834286</v>
       </c>
       <c r="CP71" t="n">
-        <v>11.62167797821507</v>
+        <v>11.62167798067715</v>
       </c>
       <c r="CQ71" t="n">
         <v>22.25954302628453</v>
@@ -38682,7 +38682,7 @@
         <v>-0.4034564454475809</v>
       </c>
       <c r="DL71" t="n">
-        <v>-40.14819299276235</v>
+        <v>-40.148197006589</v>
       </c>
       <c r="DM71" t="b">
         <v>0</v>
@@ -38958,10 +38958,10 @@
         <v>3.819999933242798</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.9263872465237263</v>
+        <v>0.9263872497989677</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.718448342301512</v>
+        <v>1.718448348377085</v>
       </c>
       <c r="CL72" t="n">
         <v>6.076230386010452</v>
@@ -38970,7 +38970,7 @@
         <v>4.03575162850128</v>
       </c>
       <c r="CN72" t="n">
-        <v>8.435704735891253</v>
+        <v>8.43570474139586</v>
       </c>
       <c r="CO72" t="n">
         <v>3.760485277130923</v>
@@ -39028,7 +39028,7 @@
         <v>-6.829267753723601</v>
       </c>
       <c r="DL72" t="n">
-        <v>-47.77722836921714</v>
+        <v>-47.77722489151894</v>
       </c>
       <c r="DM72" t="b">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>12.57999992370605</v>
       </c>
       <c r="CJ73" t="n">
-        <v>2.081714463359797</v>
+        <v>2.081714462794371</v>
       </c>
       <c r="CK73" t="n">
-        <v>3.861580329532424</v>
+        <v>3.861580328483558</v>
       </c>
       <c r="CL73" t="n">
         <v>16.32566101754214</v>
@@ -39324,7 +39324,7 @@
         <v>12.94873547769632</v>
       </c>
       <c r="CN73" t="n">
-        <v>21.33633705608501</v>
+        <v>21.33633705530969</v>
       </c>
       <c r="CO73" t="n">
         <v>9.294207014285712</v>
@@ -39658,35 +39658,35 @@
         <v>24.09000015258789</v>
       </c>
       <c r="CJ74" t="n">
-        <v>23.14624720677451</v>
+        <v>23.14624711752801</v>
       </c>
       <c r="CK74" t="n">
-        <v>28.51028675244264</v>
+        <v>28.51028672947743</v>
       </c>
       <c r="CL74" t="n">
-        <v>36.66924151484317</v>
+        <v>36.66924162669387</v>
       </c>
       <c r="CM74" t="n">
         <v>60.85541453379113</v>
       </c>
       <c r="CN74" t="n">
-        <v>65.92125707242359</v>
+        <v>65.92125698907222</v>
       </c>
       <c r="CO74" t="n">
-        <v>41.61752978478423</v>
+        <v>41.61752979774013</v>
       </c>
       <c r="CP74" t="n">
-        <v>17.33029126994464</v>
+        <v>17.33029135342939</v>
       </c>
       <c r="CQ74" t="inlineStr"/>
       <c r="CR74" t="n">
-        <v>39.15003830500056</v>
+        <v>39.15003830681889</v>
       </c>
       <c r="CS74" t="n">
-        <v>36.66924151484317</v>
+        <v>36.66924162669387</v>
       </c>
       <c r="CT74" t="n">
-        <v>33.00231736335886</v>
+        <v>33.00231746402449</v>
       </c>
       <c r="CU74" t="n">
         <v>7</v>
@@ -39698,10 +39698,10 @@
         <v>3.8</v>
       </c>
       <c r="CX74" t="n">
-        <v>36.99592010925559</v>
+        <v>36.99592052712867</v>
       </c>
       <c r="CY74" t="n">
-        <v>62.51572460365815</v>
+        <v>62.51572461120618</v>
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
@@ -40012,10 +40012,10 @@
         <v>25.28000068664551</v>
       </c>
       <c r="CJ75" t="n">
-        <v>4.637679040292404</v>
+        <v>4.637679044239077</v>
       </c>
       <c r="CK75" t="n">
-        <v>8.602894619742411</v>
+        <v>8.602894627063487</v>
       </c>
       <c r="CL75" t="n">
         <v>30.23104775253185</v>
@@ -40024,19 +40024,19 @@
         <v>25.66642298400775</v>
       </c>
       <c r="CN75" t="n">
-        <v>34.91506256682452</v>
+        <v>34.91506256197618</v>
       </c>
       <c r="CO75" t="n">
-        <v>11.777195018019</v>
+        <v>11.77719501756868</v>
       </c>
       <c r="CP75" t="n">
-        <v>24.35835629468911</v>
+        <v>24.35835628850705</v>
       </c>
       <c r="CQ75" t="n">
         <v>25.28000068664551</v>
       </c>
       <c r="CR75" t="n">
-        <v>25.37134755045296</v>
+        <v>25.3713475485395</v>
       </c>
       <c r="CS75" t="n">
         <v>25.47321183532663</v>
@@ -40057,7 +40057,7 @@
         <v>-9.312143872271072</v>
       </c>
       <c r="CY75" t="n">
-        <v>0.3613404324617209</v>
+        <v>0.3613404248926644</v>
       </c>
       <c r="CZ75" t="inlineStr">
         <is>
@@ -40366,10 +40366,10 @@
         <v>54.72999954223633</v>
       </c>
       <c r="CJ76" t="n">
-        <v>39.80284393378582</v>
+        <v>39.80284439285852</v>
       </c>
       <c r="CK76" t="n">
-        <v>57.95294076759216</v>
+        <v>57.95294143600201</v>
       </c>
       <c r="CL76" t="n">
         <v>35.04876817975726</v>
@@ -40388,13 +40388,13 @@
         <v>48.01546263696088</v>
       </c>
       <c r="CR76" t="n">
-        <v>42.74450940503169</v>
+        <v>42.74450959294544</v>
       </c>
       <c r="CS76" t="n">
-        <v>40.82420841821244</v>
+        <v>40.82420864774879</v>
       </c>
       <c r="CT76" t="n">
-        <v>36.7417875763912</v>
+        <v>36.74178778297392</v>
       </c>
       <c r="CU76" t="n">
         <v>6</v>
@@ -40406,10 +40406,10 @@
         <v>6.4</v>
       </c>
       <c r="CX76" t="n">
-        <v>-32.86718822638257</v>
+        <v>-32.86718784892465</v>
       </c>
       <c r="CY76" t="n">
-        <v>-21.89930611630132</v>
+        <v>-21.89930577295441</v>
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
@@ -40720,10 +40720,10 @@
         <v>28.80999946594238</v>
       </c>
       <c r="CJ77" t="n">
-        <v>13.46031132377003</v>
+        <v>13.46031126486381</v>
       </c>
       <c r="CK77" t="n">
-        <v>24.9688775055934</v>
+        <v>24.96887739632236</v>
       </c>
       <c r="CL77" t="n">
         <v>36.32088419826228</v>
@@ -40732,25 +40732,25 @@
         <v>25.32755497782173</v>
       </c>
       <c r="CN77" t="n">
-        <v>40.52264077571276</v>
+        <v>40.52264091471584</v>
       </c>
       <c r="CO77" t="n">
-        <v>42.02971214132558</v>
+        <v>42.02971217213049</v>
       </c>
       <c r="CP77" t="n">
-        <v>21.52400180101875</v>
+        <v>21.52400193771418</v>
       </c>
       <c r="CQ77" t="n">
         <v>24.88607192490505</v>
       </c>
       <c r="CR77" t="n">
-        <v>28.6300068310512</v>
+        <v>28.63000684834197</v>
       </c>
       <c r="CS77" t="n">
-        <v>25.14821624170757</v>
+        <v>25.14821618707204</v>
       </c>
       <c r="CT77" t="n">
-        <v>22.63339461753681</v>
+        <v>22.63339456836484</v>
       </c>
       <c r="CU77" t="n">
         <v>8</v>
@@ -40762,10 +40762,10 @@
         <v>3.1</v>
       </c>
       <c r="CX77" t="n">
-        <v>-21.43910087782966</v>
+        <v>-21.43910104850639</v>
       </c>
       <c r="CY77" t="n">
-        <v>-0.6247575086003154</v>
+        <v>-0.624757448583757</v>
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
@@ -41084,10 +41084,10 @@
         <v>15.0600004196167</v>
       </c>
       <c r="CJ78" t="n">
-        <v>2.430224157038172</v>
+        <v>2.430224155283246</v>
       </c>
       <c r="CK78" t="n">
-        <v>4.508065811305809</v>
+        <v>4.508065808050421</v>
       </c>
       <c r="CL78" t="n">
         <v>24.78819944843742</v>
@@ -41096,7 +41096,7 @@
         <v>18.97850370269514</v>
       </c>
       <c r="CN78" t="n">
-        <v>32.2885893779857</v>
+        <v>32.28858937493365</v>
       </c>
       <c r="CO78" t="n">
         <v>10.38593205872702</v>
@@ -41430,10 +41430,10 @@
         <v>14.94999980926514</v>
       </c>
       <c r="CJ79" t="n">
-        <v>9.768326968834137</v>
+        <v>9.768327017563797</v>
       </c>
       <c r="CK79" t="n">
-        <v>18.12024652718732</v>
+        <v>18.12024661758084</v>
       </c>
       <c r="CL79" t="n">
         <v>13.9204144394071</v>
@@ -41445,7 +41445,7 @@
         <v>31.51791948545004</v>
       </c>
       <c r="CO79" t="n">
-        <v>8.56043112128839</v>
+        <v>8.720439179630231</v>
       </c>
       <c r="CP79" t="n">
         <v>12.71222752579818</v>
@@ -41454,7 +41454,7 @@
         <v>12.34226887232652</v>
       </c>
       <c r="CR79" t="n">
-        <v>15.095372924861</v>
+        <v>15.11537394954413</v>
       </c>
       <c r="CS79" t="n">
         <v>13.26668799219724</v>
@@ -41469,13 +41469,13 @@
         <v>1</v>
       </c>
       <c r="CW79" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="CX79" t="n">
         <v>-20.13364986414387</v>
       </c>
       <c r="CY79" t="n">
-        <v>0.9723954344518893</v>
+        <v>1.106181554440555</v>
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
@@ -41794,25 +41794,25 @@
         <v>26.40999984741211</v>
       </c>
       <c r="CJ80" t="n">
-        <v>12.03062440629774</v>
+        <v>12.0306244249184</v>
       </c>
       <c r="CK80" t="n">
-        <v>12.63784573876657</v>
+        <v>12.63784574728765</v>
       </c>
       <c r="CL80" t="n">
-        <v>13.76140424130544</v>
+        <v>13.76140422928458</v>
       </c>
       <c r="CM80" t="n">
         <v>32.21690097207528</v>
       </c>
       <c r="CN80" t="n">
-        <v>12.7850527416906</v>
+        <v>12.78505274084192</v>
       </c>
       <c r="CO80" t="n">
-        <v>24.65491712457276</v>
+        <v>24.65491712204005</v>
       </c>
       <c r="CP80" t="n">
-        <v>5.583744795954193</v>
+        <v>5.58374478404144</v>
       </c>
       <c r="CQ80" t="n">
         <v>60.10895866204905</v>
@@ -42140,10 +42140,10 @@
         <v>10.42000007629395</v>
       </c>
       <c r="CJ81" t="n">
-        <v>6.386823438903594</v>
+        <v>6.386823413548832</v>
       </c>
       <c r="CK81" t="n">
-        <v>11.84755747916617</v>
+        <v>11.84755743213308</v>
       </c>
       <c r="CL81" t="n">
         <v>7.980635896583511</v>
@@ -42164,7 +42164,7 @@
         <v>39.24041441528669</v>
       </c>
       <c r="CR81" t="n">
-        <v>10.25521142632838</v>
+        <v>10.25521141598726</v>
       </c>
       <c r="CS81" t="n">
         <v>7.980635896583511</v>
@@ -42185,7 +42185,7 @@
         <v>-31.06936416184972</v>
       </c>
       <c r="CY81" t="n">
-        <v>-1.581464959299439</v>
+        <v>-1.581465058542453</v>
       </c>
       <c r="CZ81" t="inlineStr">
         <is>
@@ -42496,10 +42496,10 @@
         <v>6.909999847412109</v>
       </c>
       <c r="CJ82" t="n">
-        <v>1.245705649853979</v>
+        <v>1.245705646893949</v>
       </c>
       <c r="CK82" t="n">
-        <v>2.310783980479132</v>
+        <v>2.310783974988275</v>
       </c>
       <c r="CL82" t="n">
         <v>9.844892255721552</v>
@@ -42508,13 +42508,13 @@
         <v>9.691148910902541</v>
       </c>
       <c r="CN82" t="n">
-        <v>9.426422450585946</v>
+        <v>9.426422451633274</v>
       </c>
       <c r="CO82" t="n">
-        <v>1.870915582666675</v>
+        <v>1.870915582792464</v>
       </c>
       <c r="CP82" t="n">
-        <v>6.731347708042676</v>
+        <v>6.731347711501887</v>
       </c>
       <c r="CQ82" t="n">
         <v>10.56671555133091</v>
@@ -42776,7 +42776,7 @@
         <v>205.2</v>
       </c>
       <c r="BN83" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="BO83" t="n">
         <v>6.53</v>
@@ -42842,35 +42842,35 @@
         <v>2.75</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.26483687054076</v>
+        <v>1.264836872829382</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.716202946016668</v>
+        <v>1.716202948150942</v>
       </c>
       <c r="CL83" t="n">
-        <v>3.611456785565154</v>
+        <v>3.611456783521727</v>
       </c>
       <c r="CM83" t="n">
         <v>7.004011379358229</v>
       </c>
       <c r="CN83" t="n">
-        <v>3.643127487268698</v>
+        <v>3.643127489572467</v>
       </c>
       <c r="CO83" t="n">
-        <v>1.339548791459858</v>
+        <v>1.339548791388968</v>
       </c>
       <c r="CP83" t="n">
-        <v>1.777210308580688</v>
+        <v>1.777210307299792</v>
       </c>
       <c r="CQ83" t="inlineStr"/>
       <c r="CR83" t="n">
-        <v>2.225397198238638</v>
+        <v>2.22539719879388</v>
       </c>
       <c r="CS83" t="n">
-        <v>1.746706627298678</v>
+        <v>1.746706627725367</v>
       </c>
       <c r="CT83" t="n">
-        <v>1.57203596456881</v>
+        <v>1.57203596495283</v>
       </c>
       <c r="CU83" t="n">
         <v>6</v>
@@ -42882,10 +42882,10 @@
         <v>5.5</v>
       </c>
       <c r="CX83" t="n">
-        <v>-42.83505583386145</v>
+        <v>-42.83505581989707</v>
       </c>
       <c r="CY83" t="n">
-        <v>-19.07646551859498</v>
+        <v>-19.07646549840437</v>
       </c>
       <c r="CZ83" t="inlineStr">
         <is>
@@ -43194,10 +43194,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ84" t="n">
-        <v>3.069412976604649</v>
+        <v>3.069412991811349</v>
       </c>
       <c r="CK84" t="n">
-        <v>4.469065293936369</v>
+        <v>4.469065316077325</v>
       </c>
       <c r="CL84" t="n">
         <v>4.457142906283466</v>
@@ -43551,7 +43551,7 @@
         <v>60.03558955530804</v>
       </c>
       <c r="CO85" t="n">
-        <v>2.101533458199268</v>
+        <v>2.101533458199269</v>
       </c>
       <c r="CP85" t="n">
         <v>49.08416834166859</v>
@@ -43894,10 +43894,10 @@
         <v>18.57999992370605</v>
       </c>
       <c r="CJ86" t="n">
-        <v>4.512852236067691</v>
+        <v>4.512852214528588</v>
       </c>
       <c r="CK86" t="n">
-        <v>8.371340897905565</v>
+        <v>8.371340857950532</v>
       </c>
       <c r="CL86" t="n">
         <v>30.43077861422808</v>
@@ -43906,13 +43906,13 @@
         <v>32.84488176258051</v>
       </c>
       <c r="CN86" t="n">
-        <v>26.12312850401006</v>
+        <v>26.12312849990618</v>
       </c>
       <c r="CO86" t="n">
-        <v>11.11283324209325</v>
+        <v>11.11283324357972</v>
       </c>
       <c r="CP86" t="n">
-        <v>17.64670992513289</v>
+        <v>17.64670994598274</v>
       </c>
       <c r="CQ86" t="n">
         <v>40.63403637942744</v>
@@ -44248,25 +44248,25 @@
         <v>1.539999961853027</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.1373663638326542</v>
+        <v>0.1373663637954049</v>
       </c>
       <c r="CK87" t="n">
-        <v>0.1568558708796382</v>
+        <v>0.1568558708386782</v>
       </c>
       <c r="CL87" t="n">
-        <v>0.7489968440091629</v>
+        <v>0.7489968440166799</v>
       </c>
       <c r="CM87" t="n">
         <v>3.105192066391262</v>
       </c>
       <c r="CN87" t="n">
-        <v>0.2569714890182906</v>
+        <v>0.2569714889974152</v>
       </c>
       <c r="CO87" t="n">
-        <v>0.5416066536818356</v>
+        <v>0.5416066536824292</v>
       </c>
       <c r="CP87" t="n">
-        <v>0.3347614235134316</v>
+        <v>0.3347614235198564</v>
       </c>
       <c r="CQ87" t="inlineStr"/>
       <c r="CR87" t="inlineStr"/>
@@ -44592,10 +44592,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CJ88" t="n">
-        <v>11.9932523047715</v>
+        <v>11.99325227643426</v>
       </c>
       <c r="CK88" t="n">
-        <v>22.24748302535112</v>
+        <v>22.24748297278554</v>
       </c>
       <c r="CL88" t="n">
         <v>15.02382038547176</v>
@@ -44616,13 +44616,13 @@
         <v>22.65224107444971</v>
       </c>
       <c r="CR88" t="n">
-        <v>19.72597610761357</v>
+        <v>19.72597609750072</v>
       </c>
       <c r="CS88" t="n">
-        <v>18.63565170541144</v>
+        <v>18.63565167912865</v>
       </c>
       <c r="CT88" t="n">
-        <v>16.7720865348703</v>
+        <v>16.77208651121579</v>
       </c>
       <c r="CU88" t="n">
         <v>8</v>
@@ -44634,10 +44634,10 @@
         <v>2.9</v>
       </c>
       <c r="CX88" t="n">
-        <v>-29.52904591377727</v>
+        <v>-29.52904601316598</v>
       </c>
       <c r="CY88" t="n">
-        <v>-17.11774479010505</v>
+        <v>-17.11774483259604</v>
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
@@ -44946,10 +44946,10 @@
         <v>14.02999973297119</v>
       </c>
       <c r="CJ89" t="n">
-        <v>6.056552951888049</v>
+        <v>6.056552957448704</v>
       </c>
       <c r="CK89" t="n">
-        <v>8.818341097949002</v>
+        <v>8.818341106045313</v>
       </c>
       <c r="CL89" t="n">
         <v>3.791891819721943</v>
@@ -45274,10 +45274,10 @@
         <v>56.88999938964844</v>
       </c>
       <c r="CJ90" t="n">
-        <v>11.93657437048095</v>
+        <v>11.93657435517729</v>
       </c>
       <c r="CK90" t="n">
-        <v>17.37965228342026</v>
+        <v>17.37965226113814</v>
       </c>
       <c r="CL90" t="inlineStr"/>
       <c r="CM90" t="inlineStr"/>
@@ -45288,13 +45288,13 @@
       <c r="CP90" t="inlineStr"/>
       <c r="CQ90" t="inlineStr"/>
       <c r="CR90" t="n">
-        <v>18.5479755513004</v>
+        <v>18.54797553877181</v>
       </c>
       <c r="CS90" t="n">
-        <v>17.37965228342026</v>
+        <v>17.37965226113814</v>
       </c>
       <c r="CT90" t="n">
-        <v>15.64168705507824</v>
+        <v>15.64168703502433</v>
       </c>
       <c r="CU90" t="n">
         <v>3</v>
@@ -45306,10 +45306,10 @@
         <v>2.2</v>
       </c>
       <c r="CX90" t="n">
-        <v>-72.505383682735</v>
+        <v>-72.50538371798532</v>
       </c>
       <c r="CY90" t="n">
-        <v>-67.39677315820933</v>
+        <v>-67.39677318023183</v>
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>1.353996627598364</v>
       </c>
       <c r="DL90" t="n">
-        <v>-12.10365646225029</v>
+        <v>-12.10365102226845</v>
       </c>
       <c r="DM90" t="b">
         <v>0</v>
@@ -45505,13 +45505,13 @@
         <v>0</v>
       </c>
       <c r="AU91" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="AV91" t="b">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>2927565056</v>
+        <v>2950389248</v>
       </c>
       <c r="AX91" t="n">
         <v>6.79</v>
@@ -45628,10 +45628,10 @@
         <v>6.980000019073486</v>
       </c>
       <c r="CJ91" t="n">
-        <v>2.904946340527524</v>
+        <v>2.904946337862583</v>
       </c>
       <c r="CK91" t="n">
-        <v>5.388675461678556</v>
+        <v>5.388675456735091</v>
       </c>
       <c r="CL91" t="n">
         <v>13.62076586932602</v>
@@ -45640,23 +45640,23 @@
         <v>14.67172452167963</v>
       </c>
       <c r="CN91" t="n">
-        <v>12.87347153388144</v>
+        <v>12.87347153252058</v>
       </c>
       <c r="CO91" t="n">
-        <v>14.9759088125025</v>
+        <v>14.97590881306693</v>
       </c>
       <c r="CP91" t="n">
-        <v>7.073198849703783</v>
+        <v>7.073198852302207</v>
       </c>
       <c r="CQ91" t="inlineStr"/>
       <c r="CR91" t="n">
-        <v>11.43395750812866</v>
+        <v>11.43395750760508</v>
       </c>
       <c r="CS91" t="n">
-        <v>13.24711870160373</v>
+        <v>13.2471187009233</v>
       </c>
       <c r="CT91" t="n">
-        <v>11.92240683144336</v>
+        <v>11.92240683083097</v>
       </c>
       <c r="CU91" t="n">
         <v>6</v>
@@ -45668,10 +45668,10 @@
         <v>5.2</v>
       </c>
       <c r="CX91" t="n">
-        <v>70.80812032756872</v>
+        <v>70.8081203187952</v>
       </c>
       <c r="CY91" t="n">
-        <v>63.81027903845735</v>
+        <v>63.81027903095624</v>
       </c>
       <c r="CZ91" t="inlineStr">
         <is>
@@ -45980,10 +45980,10 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CJ92" t="n">
-        <v>4.969684070789089</v>
+        <v>4.969684097335415</v>
       </c>
       <c r="CK92" t="n">
-        <v>7.235860007068913</v>
+        <v>7.235860045720364</v>
       </c>
       <c r="CL92" t="n">
         <v>5.964932973104989</v>
@@ -46002,13 +46002,13 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CR92" t="n">
-        <v>6.640162221918384</v>
+        <v>6.64016223278468</v>
       </c>
       <c r="CS92" t="n">
-        <v>6.600396490086951</v>
+        <v>6.600396509412676</v>
       </c>
       <c r="CT92" t="n">
-        <v>5.940356841078255</v>
+        <v>5.940356858471409</v>
       </c>
       <c r="CU92" t="n">
         <v>6</v>
@@ -46020,10 +46020,10 @@
         <v>5.9</v>
       </c>
       <c r="CX92" t="n">
-        <v>-23.0523704336683</v>
+        <v>-23.05237020836838</v>
       </c>
       <c r="CY92" t="n">
-        <v>-13.98753364793108</v>
+        <v>-13.98753350717595</v>
       </c>
       <c r="CZ92" t="inlineStr">
         <is>
@@ -46336,10 +46336,10 @@
         <v>3.670000076293945</v>
       </c>
       <c r="CJ93" t="n">
-        <v>33.45871405045576</v>
+        <v>33.45871388966976</v>
       </c>
       <c r="CK93" t="n">
-        <v>62.06591456359543</v>
+        <v>62.0659142653374</v>
       </c>
       <c r="CL93" t="n">
         <v>4.702853095831215</v>
@@ -46680,10 +46680,10 @@
         <v>78.58000183105469</v>
       </c>
       <c r="CJ94" t="n">
-        <v>58.74948823012014</v>
+        <v>58.74948816122167</v>
       </c>
       <c r="CK94" t="n">
-        <v>85.53925486305492</v>
+        <v>85.53925476273876</v>
       </c>
       <c r="CL94" t="n">
         <v>24.51941251254032</v>
@@ -47028,10 +47028,10 @@
         <v>34.81000137329102</v>
       </c>
       <c r="CJ95" t="n">
-        <v>8.619676356772151</v>
+        <v>8.619676376756265</v>
       </c>
       <c r="CK95" t="n">
-        <v>15.98949964181234</v>
+        <v>15.98949967888287</v>
       </c>
       <c r="CL95" t="n">
         <v>40.07232999097358</v>
@@ -47040,19 +47040,19 @@
         <v>40.41788990153368</v>
       </c>
       <c r="CN95" t="n">
-        <v>33.4403378176041</v>
+        <v>33.44033780657554</v>
       </c>
       <c r="CO95" t="n">
-        <v>50.04925266333676</v>
+        <v>50.0492526579016</v>
       </c>
       <c r="CP95" t="n">
-        <v>22.50871826409482</v>
+        <v>22.50871824188368</v>
       </c>
       <c r="CQ95" t="n">
         <v>53.2004618761326</v>
       </c>
       <c r="CR95" t="n">
-        <v>36.52549859364113</v>
+        <v>36.52549859341194</v>
       </c>
       <c r="CS95" t="n">
         <v>40.07232999097358</v>
@@ -47073,7 +47073,7 @@
         <v>3.605560382276285</v>
       </c>
       <c r="CY95" t="n">
-        <v>4.928173377397171</v>
+        <v>4.928173376738765</v>
       </c>
       <c r="CZ95" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>1</v>
       </c>
       <c r="AU96" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AV96" t="b">
         <v>1</v>
@@ -47384,10 +47384,10 @@
         <v>19.60000038146973</v>
       </c>
       <c r="CJ96" t="n">
-        <v>2.023112505378596</v>
+        <v>2.023112504224832</v>
       </c>
       <c r="CK96" t="n">
-        <v>3.752873697477296</v>
+        <v>3.752873695337063</v>
       </c>
       <c r="CL96" t="n">
         <v>10.14849570357459</v>
@@ -47396,19 +47396,19 @@
         <v>8.468407387765433</v>
       </c>
       <c r="CN96" t="n">
-        <v>9.993116428799691</v>
+        <v>9.993116431142193</v>
       </c>
       <c r="CO96" t="n">
-        <v>7.537047557874462</v>
+        <v>7.537047558136668</v>
       </c>
       <c r="CP96" t="n">
-        <v>7.631782583706205</v>
+        <v>7.631782585575396</v>
       </c>
       <c r="CQ96" t="n">
         <v>13.57810210946071</v>
       </c>
       <c r="CR96" t="n">
-        <v>8.729975066951198</v>
+        <v>8.729975067284579</v>
       </c>
       <c r="CS96" t="n">
         <v>8.468407387765433</v>
@@ -47429,7 +47429,7 @@
         <v>-61.11445662932493</v>
       </c>
       <c r="CY96" t="n">
-        <v>-55.45931174978593</v>
+        <v>-55.45931174808501</v>
       </c>
       <c r="CZ96" t="inlineStr">
         <is>
@@ -47722,35 +47722,35 @@
         <v>20.17000007629395</v>
       </c>
       <c r="CJ97" t="n">
-        <v>12.02545568849963</v>
+        <v>12.02545566535981</v>
       </c>
       <c r="CK97" t="n">
-        <v>15.02693336330284</v>
+        <v>15.02693334971656</v>
       </c>
       <c r="CL97" t="n">
-        <v>21.92822734758292</v>
+        <v>21.92822736995206</v>
       </c>
       <c r="CM97" t="n">
         <v>41.10111584317051</v>
       </c>
       <c r="CN97" t="n">
-        <v>26.68409630808468</v>
+        <v>26.68409629451</v>
       </c>
       <c r="CO97" t="n">
-        <v>15.73775952882787</v>
+        <v>15.73775953044531</v>
       </c>
       <c r="CP97" t="n">
-        <v>10.44627155121577</v>
+        <v>10.44627156748584</v>
       </c>
       <c r="CQ97" t="inlineStr"/>
       <c r="CR97" t="n">
-        <v>16.17959398205331</v>
+        <v>16.17959397886844</v>
       </c>
       <c r="CS97" t="n">
-        <v>15.38234644606536</v>
+        <v>15.38234644008094</v>
       </c>
       <c r="CT97" t="n">
-        <v>13.84411180145882</v>
+        <v>13.84411179607284</v>
       </c>
       <c r="CU97" t="n">
         <v>4</v>
@@ -47762,10 +47762,10 @@
         <v>1.8</v>
       </c>
       <c r="CX97" t="n">
-        <v>-31.36285697028837</v>
+        <v>-31.36285699699128</v>
       </c>
       <c r="CY97" t="n">
-        <v>-19.78386752179841</v>
+        <v>-19.78386753758858</v>
       </c>
       <c r="CZ97" t="inlineStr">
         <is>
@@ -48092,10 +48092,10 @@
         <v>15.77000045776367</v>
       </c>
       <c r="CJ98" t="n">
-        <v>7.940764279361635</v>
+        <v>7.940764281141179</v>
       </c>
       <c r="CK98" t="n">
-        <v>14.73011773821583</v>
+        <v>14.73011774151689</v>
       </c>
       <c r="CL98" t="n">
         <v>10.12366792952367</v>
@@ -48116,7 +48116,7 @@
         <v>9.605938210417623</v>
       </c>
       <c r="CR98" t="n">
-        <v>12.14173308353562</v>
+        <v>12.14173308417069</v>
       </c>
       <c r="CS98" t="n">
         <v>9.864803069970648</v>
@@ -48137,7 +48137,7 @@
         <v>-43.70118893304959</v>
       </c>
       <c r="CY98" t="n">
-        <v>-23.0074018320135</v>
+        <v>-23.00740182798639</v>
       </c>
       <c r="CZ98" t="inlineStr">
         <is>
@@ -48456,37 +48456,37 @@
         <v>23.01000022888184</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.039638088001113</v>
+        <v>5.039638075183882</v>
       </c>
       <c r="CK99" t="n">
-        <v>7.15740889659159</v>
+        <v>7.157408893733233</v>
       </c>
       <c r="CL99" t="n">
-        <v>10.59572234710865</v>
+        <v>10.59572236982511</v>
       </c>
       <c r="CM99" t="n">
         <v>14.53384923599866</v>
       </c>
       <c r="CN99" t="n">
-        <v>7.141105314573355</v>
+        <v>7.141105327279114</v>
       </c>
       <c r="CO99" t="n">
-        <v>8.435979170945961</v>
+        <v>8.435979172568844</v>
       </c>
       <c r="CP99" t="n">
-        <v>5.265851231511875</v>
+        <v>5.265851244618263</v>
       </c>
       <c r="CQ99" t="n">
         <v>10.72346608033207</v>
       </c>
       <c r="CR99" t="n">
-        <v>8.611627545632908</v>
+        <v>8.611627549942396</v>
       </c>
       <c r="CS99" t="n">
-        <v>7.796694033768775</v>
+        <v>7.796694033151039</v>
       </c>
       <c r="CT99" t="n">
-        <v>7.017024630391898</v>
+        <v>7.017024629835935</v>
       </c>
       <c r="CU99" t="n">
         <v>8</v>
@@ -48498,10 +48498,10 @@
         <v>2.9</v>
       </c>
       <c r="CX99" t="n">
-        <v>-69.50445649459741</v>
+        <v>-69.50445649701358</v>
       </c>
       <c r="CY99" t="n">
-        <v>-62.57441347252265</v>
+        <v>-62.57441345379389</v>
       </c>
       <c r="CZ99" t="inlineStr">
         <is>
@@ -48812,10 +48812,10 @@
         <v>7.199999809265137</v>
       </c>
       <c r="CJ100" t="n">
-        <v>3.230736917571415</v>
+        <v>3.230736921033268</v>
       </c>
       <c r="CK100" t="n">
-        <v>5.993016982094974</v>
+        <v>5.993016988516711</v>
       </c>
       <c r="CL100" t="inlineStr"/>
       <c r="CM100" t="inlineStr"/>
@@ -48826,13 +48826,13 @@
         <v>9.346171559984855</v>
       </c>
       <c r="CR100" t="n">
-        <v>6.189975153217081</v>
+        <v>6.189975156511611</v>
       </c>
       <c r="CS100" t="n">
-        <v>5.993016982094974</v>
+        <v>5.993016988516711</v>
       </c>
       <c r="CT100" t="n">
-        <v>5.393715283885477</v>
+        <v>5.39371528966504</v>
       </c>
       <c r="CU100" t="n">
         <v>3</v>
@@ -48844,10 +48844,10 @@
         <v>2.9</v>
       </c>
       <c r="CX100" t="n">
-        <v>-25.08728573930361</v>
+        <v>-25.0872856590319</v>
       </c>
       <c r="CY100" t="n">
-        <v>-14.02812059450794</v>
+        <v>-14.02812054875059</v>
       </c>
       <c r="CZ100" t="inlineStr">
         <is>
@@ -49158,10 +49158,10 @@
         <v>45.29999923706055</v>
       </c>
       <c r="CJ101" t="n">
-        <v>9.911113139221213</v>
+        <v>9.911113136263427</v>
       </c>
       <c r="CK101" t="n">
-        <v>18.38511487325535</v>
+        <v>18.38511486776866</v>
       </c>
       <c r="CL101" t="n">
         <v>85.6241069744725</v>
@@ -49170,13 +49170,13 @@
         <v>75.68006991304929</v>
       </c>
       <c r="CN101" t="n">
-        <v>103.2210458227874</v>
+        <v>103.2210458236879</v>
       </c>
       <c r="CO101" t="n">
-        <v>16.00956545058075</v>
+        <v>16.15577152790574</v>
       </c>
       <c r="CP101" t="n">
-        <v>69.70318634022945</v>
+        <v>69.70318634450852</v>
       </c>
       <c r="CQ101" t="n">
         <v>21.32072017314016</v>
@@ -49516,25 +49516,25 @@
         <v>47.36999893188477</v>
       </c>
       <c r="CJ102" t="n">
-        <v>18.2068996218922</v>
+        <v>18.2068995566113</v>
       </c>
       <c r="CK102" t="n">
-        <v>19.98880949651264</v>
+        <v>19.9888094666673</v>
       </c>
       <c r="CL102" t="n">
-        <v>23.30440146569601</v>
+        <v>23.30440151445818</v>
       </c>
       <c r="CM102" t="n">
         <v>50.5405114948287</v>
       </c>
       <c r="CN102" t="n">
-        <v>19.28041170702663</v>
+        <v>19.28041172079479</v>
       </c>
       <c r="CO102" t="n">
-        <v>23.25458367932727</v>
+        <v>23.25458368483036</v>
       </c>
       <c r="CP102" t="n">
-        <v>10.0064968524978</v>
+        <v>10.00649689719172</v>
       </c>
       <c r="CQ102" t="n">
         <v>117.9256251674622</v>
@@ -49870,37 +49870,37 @@
         <v>53.11999893188477</v>
       </c>
       <c r="CJ103" t="n">
-        <v>16.22648836998729</v>
+        <v>16.2264884211855</v>
       </c>
       <c r="CK103" t="n">
-        <v>24.67943851138124</v>
+        <v>24.67943854085114</v>
       </c>
       <c r="CL103" t="n">
-        <v>44.49393107876148</v>
+        <v>44.4939309915037</v>
       </c>
       <c r="CM103" t="n">
         <v>61.84069244222911</v>
       </c>
       <c r="CN103" t="n">
-        <v>35.49872157960584</v>
+        <v>35.49872156419589</v>
       </c>
       <c r="CO103" t="n">
-        <v>26.76189247376796</v>
+        <v>26.76189246934416</v>
       </c>
       <c r="CP103" t="n">
-        <v>22.24510782619203</v>
+        <v>22.24510778176836</v>
       </c>
       <c r="CQ103" t="n">
         <v>21.78028972750627</v>
       </c>
       <c r="CR103" t="n">
-        <v>31.69082025117891</v>
+        <v>31.69082024232302</v>
       </c>
       <c r="CS103" t="n">
-        <v>25.7206654925746</v>
+        <v>25.72066550509765</v>
       </c>
       <c r="CT103" t="n">
-        <v>23.14859894331714</v>
+        <v>23.14859895458789</v>
       </c>
       <c r="CU103" t="n">
         <v>8</v>
@@ -49912,10 +49912,10 @@
         <v>3.8</v>
       </c>
       <c r="CX103" t="n">
-        <v>-56.42206436600205</v>
+        <v>-56.42206434478454</v>
       </c>
       <c r="CY103" t="n">
-        <v>-40.3410751347798</v>
+        <v>-40.34107515145128</v>
       </c>
       <c r="CZ103" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>17.6</v>
       </c>
       <c r="BN104" t="n">
-        <v>8.199999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BO104" t="n">
         <v>4.98</v>
@@ -50242,10 +50242,10 @@
         <v>11.9399995803833</v>
       </c>
       <c r="CJ104" t="n">
-        <v>2.124475130446333</v>
+        <v>2.124475143344242</v>
       </c>
       <c r="CK104" t="n">
-        <v>3.940901366977947</v>
+        <v>3.940901390903568</v>
       </c>
       <c r="CL104" t="n">
         <v>12.07671713283044</v>
@@ -50254,25 +50254,25 @@
         <v>13.36902203749528</v>
       </c>
       <c r="CN104" t="n">
-        <v>8.686980475092447</v>
+        <v>8.68698047000683</v>
       </c>
       <c r="CO104" t="n">
-        <v>5.736769278310394</v>
+        <v>5.73676927720083</v>
       </c>
       <c r="CP104" t="n">
-        <v>6.468133900785195</v>
+        <v>6.468133888924277</v>
       </c>
       <c r="CQ104" t="n">
         <v>11.9399995803833</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.888360538839287</v>
+        <v>8.888360539677789</v>
       </c>
       <c r="CS104" t="n">
-        <v>8.686980475092447</v>
+        <v>8.68698047000683</v>
       </c>
       <c r="CT104" t="n">
-        <v>7.818282427583203</v>
+        <v>7.818282423006147</v>
       </c>
       <c r="CU104" t="n">
         <v>7</v>
@@ -50284,10 +50284,10 @@
         <v>6.3</v>
       </c>
       <c r="CX104" t="n">
-        <v>-34.52024537397666</v>
+        <v>-34.52024541231044</v>
       </c>
       <c r="CY104" t="n">
-        <v>-25.55811682403802</v>
+        <v>-25.5581168170154</v>
       </c>
       <c r="CZ104" t="inlineStr">
         <is>
@@ -50598,10 +50598,10 @@
         <v>2.990000009536743</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.6261540001197431</v>
+        <v>0.6261539976981418</v>
       </c>
       <c r="CK105" t="n">
-        <v>1.161515670222123</v>
+        <v>1.161515665730053</v>
       </c>
       <c r="CL105" t="n">
         <v>3.424157314292294</v>
@@ -50610,13 +50610,13 @@
         <v>3.957621711457321</v>
       </c>
       <c r="CN105" t="n">
-        <v>2.391887521715025</v>
+        <v>2.391887522029286</v>
       </c>
       <c r="CO105" t="n">
-        <v>2.635932104385423</v>
+        <v>2.635932104696672</v>
       </c>
       <c r="CP105" t="n">
-        <v>1.717596292461161</v>
+        <v>1.717596294500536</v>
       </c>
       <c r="CQ105" t="n">
         <v>9.031114164496099</v>
@@ -50942,10 +50942,10 @@
         <v>55.43999862670898</v>
       </c>
       <c r="CJ106" t="n">
-        <v>62.75021524304587</v>
+        <v>62.75021531380185</v>
       </c>
       <c r="CK106" t="n">
-        <v>91.3643133938748</v>
+        <v>91.36431349689549</v>
       </c>
       <c r="CL106" t="n">
         <v>24.25645711896397</v>
@@ -51560,7 +51560,7 @@
         <v>113.9</v>
       </c>
       <c r="BN108" t="n">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="BO108" t="n">
         <v>3.7</v>
@@ -51626,10 +51626,10 @@
         <v>93.48999786376953</v>
       </c>
       <c r="CJ108" t="n">
-        <v>4.770651220601801</v>
+        <v>4.770651220748134</v>
       </c>
       <c r="CK108" t="n">
-        <v>8.84955801421634</v>
+        <v>8.849558014487791</v>
       </c>
       <c r="CL108" t="n">
         <v>41.68043309875323</v>
@@ -51638,13 +51638,13 @@
         <v>41.35009616132553</v>
       </c>
       <c r="CN108" t="n">
-        <v>34.48348113247781</v>
+        <v>34.4834811322802</v>
       </c>
       <c r="CO108" t="n">
-        <v>17.71052555146585</v>
+        <v>17.71052555145224</v>
       </c>
       <c r="CP108" t="n">
-        <v>28.6662502672336</v>
+        <v>28.66625026706606</v>
       </c>
       <c r="CQ108" t="n">
         <v>43.17568011524377</v>
@@ -52644,10 +52644,10 @@
         <v>16.81999969482422</v>
       </c>
       <c r="CJ111" t="n">
-        <v>3.158272792015751</v>
+        <v>3.158272786284772</v>
       </c>
       <c r="CK111" t="n">
-        <v>5.858596029189219</v>
+        <v>5.858596018558251</v>
       </c>
       <c r="CL111" t="n">
         <v>14.7690520845872</v>
@@ -52656,23 +52656,23 @@
         <v>15.75245189589746</v>
       </c>
       <c r="CN111" t="n">
-        <v>10.52924634891141</v>
+        <v>10.52924635266081</v>
       </c>
       <c r="CO111" t="n">
-        <v>13.03158635033064</v>
+        <v>13.03158635132297</v>
       </c>
       <c r="CP111" t="n">
-        <v>7.75427653968915</v>
+        <v>7.754276545388036</v>
       </c>
       <c r="CQ111" t="inlineStr"/>
       <c r="CR111" t="n">
-        <v>11.28253487476751</v>
+        <v>11.28253487473579</v>
       </c>
       <c r="CS111" t="n">
-        <v>11.78041634962103</v>
+        <v>11.78041635199189</v>
       </c>
       <c r="CT111" t="n">
-        <v>10.60237471465893</v>
+        <v>10.6023747167927</v>
       </c>
       <c r="CU111" t="n">
         <v>6</v>
@@ -52684,10 +52684,10 @@
         <v>5</v>
       </c>
       <c r="CX111" t="n">
-        <v>-36.96566642672744</v>
+        <v>-36.9656664140415</v>
       </c>
       <c r="CY111" t="n">
-        <v>-32.92190796983589</v>
+        <v>-32.92190797002451</v>
       </c>
       <c r="CZ111" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
         <v>14.85999965667725</v>
       </c>
       <c r="CJ112" t="n">
-        <v>3.75207803704681</v>
+        <v>3.752078042790786</v>
       </c>
       <c r="CK112" t="n">
-        <v>4.765173621315222</v>
+        <v>4.765173627644832</v>
       </c>
       <c r="CL112" t="n">
-        <v>14.23467812397049</v>
+        <v>14.23467812108693</v>
       </c>
       <c r="CM112" t="n">
         <v>37.15722486020687</v>
       </c>
       <c r="CN112" t="n">
-        <v>9.753710215116421</v>
+        <v>9.753710220367291</v>
       </c>
       <c r="CO112" t="n">
-        <v>48.88725230463022</v>
+        <v>49.08124933659791</v>
       </c>
       <c r="CP112" t="n">
-        <v>6.83619827638033</v>
+        <v>6.836198274343285</v>
       </c>
       <c r="CQ112" t="n">
         <v>26.75481109869832</v>
@@ -53031,7 +53031,7 @@
         <v>0</v>
       </c>
       <c r="CW112" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="CX112" t="inlineStr"/>
       <c r="CY112" t="inlineStr"/>
@@ -53227,7 +53227,7 @@
         <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>27984250880</v>
+        <v>27986405376</v>
       </c>
       <c r="AX113" t="n">
         <v>22.84</v>
@@ -53344,25 +53344,25 @@
         <v>14.88000011444092</v>
       </c>
       <c r="CJ113" t="n">
-        <v>1.392564511919522</v>
+        <v>1.392564516324504</v>
       </c>
       <c r="CK113" t="n">
-        <v>2.563328940052346</v>
+        <v>2.563328945412863</v>
       </c>
       <c r="CL113" t="n">
-        <v>8.565797763982767</v>
+        <v>8.56579775480038</v>
       </c>
       <c r="CM113" t="n">
         <v>10.6034032697214</v>
       </c>
       <c r="CN113" t="n">
-        <v>4.724956874554761</v>
+        <v>4.724956872025244</v>
       </c>
       <c r="CO113" t="n">
-        <v>7.686442866696645</v>
+        <v>7.68644286611425</v>
       </c>
       <c r="CP113" t="n">
-        <v>4.173838468045146</v>
+        <v>4.173838464757972</v>
       </c>
       <c r="CQ113" t="n">
         <v>11.44599456161724</v>
@@ -53573,7 +53573,7 @@
         <v>1</v>
       </c>
       <c r="AW114" t="n">
-        <v>44453134336</v>
+        <v>44203687936</v>
       </c>
       <c r="AX114" t="n">
         <v>3259.92</v>
@@ -53690,10 +53690,10 @@
         <v>18.29999923706055</v>
       </c>
       <c r="CJ114" t="n">
-        <v>11.70299365104377</v>
+        <v>11.70299356891736</v>
       </c>
       <c r="CK114" t="n">
-        <v>14.60330077325896</v>
+        <v>14.60330067077949</v>
       </c>
       <c r="CL114" t="inlineStr"/>
       <c r="CM114" t="inlineStr"/>
@@ -54028,10 +54028,10 @@
         <v>11.22000026702881</v>
       </c>
       <c r="CJ115" t="n">
-        <v>2.438138899975475</v>
+        <v>2.438138895589552</v>
       </c>
       <c r="CK115" t="n">
-        <v>4.522747659454507</v>
+        <v>4.522747651318619</v>
       </c>
       <c r="CL115" t="n">
         <v>12.15576480279082</v>
@@ -54040,13 +54040,13 @@
         <v>12.68205556729091</v>
       </c>
       <c r="CN115" t="n">
-        <v>9.594467794723874</v>
+        <v>9.594467796954879</v>
       </c>
       <c r="CO115" t="n">
-        <v>0.7922280655318928</v>
+        <v>0.7922280655901908</v>
       </c>
       <c r="CP115" t="n">
-        <v>6.727276599984005</v>
+        <v>6.727276604542205</v>
       </c>
       <c r="CQ115" t="n">
         <v>7.245675643801825</v>
@@ -54374,25 +54374,25 @@
         <v>8.840000152587891</v>
       </c>
       <c r="CJ116" t="n">
-        <v>2.273351422843626</v>
+        <v>2.273351429613759</v>
       </c>
       <c r="CK116" t="n">
-        <v>2.459392453544285</v>
+        <v>2.459392458998841</v>
       </c>
       <c r="CL116" t="n">
-        <v>3.240521376497504</v>
+        <v>3.240521374034079</v>
       </c>
       <c r="CM116" t="n">
         <v>10.0855898347917</v>
       </c>
       <c r="CN116" t="n">
-        <v>1.903039101332723</v>
+        <v>1.903039102142002</v>
       </c>
       <c r="CO116" t="n">
-        <v>5.908796684426145</v>
+        <v>5.908796683911463</v>
       </c>
       <c r="CP116" t="n">
-        <v>1.367445364143663</v>
+        <v>1.367445361826111</v>
       </c>
       <c r="CQ116" t="n">
         <v>14.58705591648655</v>
@@ -54732,10 +54732,10 @@
         <v>4.829999923706055</v>
       </c>
       <c r="CJ117" t="n">
-        <v>1.485870067539157</v>
+        <v>1.485870067911941</v>
       </c>
       <c r="CK117" t="n">
-        <v>1.548606803724144</v>
+        <v>1.548606804112668</v>
       </c>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
@@ -55068,10 +55068,10 @@
         <v>3.359999895095825</v>
       </c>
       <c r="CJ118" t="n">
-        <v>1.655532335467828</v>
+        <v>1.655532338322624</v>
       </c>
       <c r="CK118" t="n">
-        <v>3.071012482292821</v>
+        <v>3.071012487588468</v>
       </c>
       <c r="CL118" t="n">
         <v>1.185934965637178</v>
@@ -55080,7 +55080,7 @@
         <v>4.749225176208076</v>
       </c>
       <c r="CN118" t="n">
-        <v>1.646708883594875</v>
+        <v>1.64670888465953</v>
       </c>
       <c r="CO118" t="n">
         <v>0.7445919647652398</v>
@@ -55414,10 +55414,10 @@
         <v>6.599999904632568</v>
       </c>
       <c r="CJ119" t="n">
-        <v>1.062191975559362</v>
+        <v>1.062191980375533</v>
       </c>
       <c r="CK119" t="n">
-        <v>1.970366114662617</v>
+        <v>1.970366123596613</v>
       </c>
       <c r="CL119" t="inlineStr"/>
       <c r="CM119" t="inlineStr"/>
@@ -55750,25 +55750,25 @@
         <v>3.650000095367432</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.251013900860789</v>
+        <v>1.25101390315633</v>
       </c>
       <c r="CK120" t="n">
-        <v>1.269554586873298</v>
+        <v>1.269554588372241</v>
       </c>
       <c r="CL120" t="n">
-        <v>1.32222996445492</v>
+        <v>1.322229963589837</v>
       </c>
       <c r="CM120" t="n">
         <v>4.079804341937684</v>
       </c>
       <c r="CN120" t="n">
-        <v>0.908045607212298</v>
+        <v>0.908045607368969</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.169845198517764</v>
+        <v>2.169845198345659</v>
       </c>
       <c r="CP120" t="n">
-        <v>0.5078925746537154</v>
+        <v>0.5078925737426611</v>
       </c>
       <c r="CQ120" t="n">
         <v>5.283509282575594</v>
@@ -56100,10 +56100,10 @@
         <v>5.5</v>
       </c>
       <c r="CJ121" t="n">
-        <v>5.453484854162689</v>
+        <v>5.453484852396258</v>
       </c>
       <c r="CK121" t="n">
-        <v>7.940273947660877</v>
+        <v>7.940273945088953</v>
       </c>
       <c r="CL121" t="inlineStr"/>
       <c r="CM121" t="inlineStr"/>
@@ -56112,13 +56112,13 @@
       <c r="CP121" t="inlineStr"/>
       <c r="CQ121" t="inlineStr"/>
       <c r="CR121" t="n">
-        <v>6.696879400911783</v>
+        <v>6.696879398742606</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.696879400911783</v>
+        <v>6.696879398742606</v>
       </c>
       <c r="CT121" t="n">
-        <v>6.027191460820605</v>
+        <v>6.027191458868345</v>
       </c>
       <c r="CU121" t="n">
         <v>2</v>
@@ -56130,10 +56130,10 @@
         <v>1.5</v>
       </c>
       <c r="CX121" t="n">
-        <v>9.585299287647352</v>
+        <v>9.585299252151724</v>
       </c>
       <c r="CY121" t="n">
-        <v>21.7614436529415</v>
+        <v>21.76144361350192</v>
       </c>
       <c r="CZ121" t="inlineStr">
         <is>
@@ -56444,10 +56444,10 @@
         <v>5.320000171661377</v>
       </c>
       <c r="CJ122" t="n">
-        <v>5.856172599717159</v>
+        <v>5.856172596181932</v>
       </c>
       <c r="CK122" t="n">
-        <v>10.44092073862826</v>
+        <v>10.44092073232533</v>
       </c>
       <c r="CL122" t="inlineStr"/>
       <c r="CM122" t="inlineStr"/>
@@ -56456,13 +56456,13 @@
       <c r="CP122" t="inlineStr"/>
       <c r="CQ122" t="inlineStr"/>
       <c r="CR122" t="n">
-        <v>8.148546669172708</v>
+        <v>8.14854666425363</v>
       </c>
       <c r="CS122" t="n">
-        <v>8.148546669172708</v>
+        <v>8.14854666425363</v>
       </c>
       <c r="CT122" t="n">
-        <v>7.333692002255438</v>
+        <v>7.333691997828267</v>
       </c>
       <c r="CU122" t="n">
         <v>2</v>
@@ -56474,10 +56474,10 @@
         <v>1.8</v>
       </c>
       <c r="CX122" t="n">
-        <v>37.85134897778033</v>
+        <v>37.85134889456285</v>
       </c>
       <c r="CY122" t="n">
-        <v>53.16816553086703</v>
+        <v>53.16816543840315</v>
       </c>
       <c r="CZ122" t="inlineStr">
         <is>
@@ -56782,10 +56782,10 @@
         <v>22</v>
       </c>
       <c r="CJ123" t="n">
-        <v>38.19068414881785</v>
+        <v>38.19068415585433</v>
       </c>
       <c r="CK123" t="n">
-        <v>70.84371909605711</v>
+        <v>70.84371910910978</v>
       </c>
       <c r="CL123" t="n">
         <v>19.69594594594594</v>
@@ -56804,7 +56804,7 @@
       </c>
       <c r="CQ123" t="inlineStr"/>
       <c r="CR123" t="n">
-        <v>25.80022402842386</v>
+        <v>25.80022402959661</v>
       </c>
       <c r="CS123" t="n">
         <v>22.95973920566808</v>
@@ -56825,7 +56825,7 @@
         <v>-6.073794158630585</v>
       </c>
       <c r="CY123" t="n">
-        <v>17.27374558374482</v>
+        <v>17.27374558907549</v>
       </c>
       <c r="CZ123" t="inlineStr">
         <is>
@@ -57136,25 +57136,25 @@
         <v>9.079999923706055</v>
       </c>
       <c r="CJ124" t="n">
-        <v>3.508565476730569</v>
+        <v>3.508565492363704</v>
       </c>
       <c r="CK124" t="n">
-        <v>3.620356124970978</v>
+        <v>3.620356138614594</v>
       </c>
       <c r="CL124" t="n">
-        <v>4.365533866123363</v>
+        <v>4.36553386312371</v>
       </c>
       <c r="CM124" t="n">
         <v>18.86542389459268</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.429630196331217</v>
+        <v>3.429630205727388</v>
       </c>
       <c r="CO124" t="n">
-        <v>7.741903460717436</v>
+        <v>7.741903460081911</v>
       </c>
       <c r="CP124" t="n">
-        <v>1.724012498458983</v>
+        <v>1.724012495391137</v>
       </c>
       <c r="CQ124" t="n">
         <v>21.8229114254654</v>
@@ -57482,10 +57482,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.7838805198029571</v>
+        <v>0.7838805201187189</v>
       </c>
       <c r="CK125" t="n">
-        <v>1.454098364234485</v>
+        <v>1.454098364820223</v>
       </c>
       <c r="CL125" t="n">
         <v>15.56199010537595</v>
@@ -57494,13 +57494,13 @@
         <v>16.26314871365512</v>
       </c>
       <c r="CN125" t="n">
-        <v>13.64124870085884</v>
+        <v>13.64124870079006</v>
       </c>
       <c r="CO125" t="n">
-        <v>1.677467519644437</v>
+        <v>1.677467519637728</v>
       </c>
       <c r="CP125" t="n">
-        <v>11.00817213179681</v>
+        <v>11.00817213147004</v>
       </c>
       <c r="CQ125" t="inlineStr"/>
       <c r="CR125" t="inlineStr"/>
@@ -58160,25 +58160,25 @@
         <v>18.60000038146973</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.6412328413633123</v>
+        <v>0.641232840839856</v>
       </c>
       <c r="CK127" t="n">
-        <v>0.854992154729054</v>
+        <v>0.8549921540839575</v>
       </c>
       <c r="CL127" t="n">
-        <v>4.50294802865909</v>
+        <v>4.502948028937472</v>
       </c>
       <c r="CM127" t="n">
         <v>11.33513440194061</v>
       </c>
       <c r="CN127" t="n">
-        <v>1.725838691967489</v>
+        <v>1.725838692067746</v>
       </c>
       <c r="CO127" t="n">
-        <v>0.6737065028655262</v>
+        <v>0.673706502869484</v>
       </c>
       <c r="CP127" t="n">
-        <v>2.204429654769076</v>
+        <v>2.204429654949188</v>
       </c>
       <c r="CQ127" t="n">
         <v>18.60000038146973</v>
@@ -58514,10 +58514,10 @@
         <v>5.199999809265137</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.285816878240072</v>
+        <v>1.285816874815919</v>
       </c>
       <c r="CK128" t="n">
-        <v>2.151989884399975</v>
+        <v>2.151989878669188</v>
       </c>
       <c r="CL128" t="inlineStr"/>
       <c r="CM128" t="inlineStr"/>
@@ -58528,13 +58528,13 @@
         <v>5.739109502577318</v>
       </c>
       <c r="CR128" t="n">
-        <v>1.718903381320024</v>
+        <v>1.718903376742553</v>
       </c>
       <c r="CS128" t="n">
-        <v>1.718903381320024</v>
+        <v>1.718903376742553</v>
       </c>
       <c r="CT128" t="n">
-        <v>1.547013043188021</v>
+        <v>1.547013039068298</v>
       </c>
       <c r="CU128" t="n">
         <v>2</v>
@@ -58546,10 +58546,10 @@
         <v>4.5</v>
       </c>
       <c r="CX128" t="n">
-        <v>-70.24974807822839</v>
+        <v>-70.24974815745384</v>
       </c>
       <c r="CY128" t="n">
-        <v>-66.94416453136488</v>
+        <v>-66.94416461939316</v>
       </c>
       <c r="CZ128" t="inlineStr">
         <is>
@@ -58790,7 +58790,7 @@
         <v>-17.3</v>
       </c>
       <c r="BN129" t="n">
-        <v>4.87</v>
+        <v>6.76</v>
       </c>
       <c r="BO129" t="n">
         <v>3.71</v>
@@ -59198,37 +59198,37 @@
         <v>17.65999984741211</v>
       </c>
       <c r="CJ130" t="n">
-        <v>2.127790690273236</v>
+        <v>2.127790691837735</v>
       </c>
       <c r="CK130" t="n">
-        <v>3.759843135366839</v>
+        <v>3.759843136869673</v>
       </c>
       <c r="CL130" t="n">
-        <v>9.74198510857371</v>
+        <v>9.741985105304664</v>
       </c>
       <c r="CM130" t="n">
         <v>12.08493439512116</v>
       </c>
       <c r="CN130" t="n">
-        <v>5.648205435279769</v>
+        <v>5.648205434228563</v>
       </c>
       <c r="CO130" t="n">
-        <v>5.613969606566635</v>
+        <v>5.613969606428337</v>
       </c>
       <c r="CP130" t="n">
-        <v>4.793870056232893</v>
+        <v>4.793870054970404</v>
       </c>
       <c r="CQ130" t="n">
         <v>16.0617953943026</v>
       </c>
       <c r="CR130" t="n">
-        <v>6.940467956190166</v>
+        <v>6.940467955487133</v>
       </c>
       <c r="CS130" t="n">
-        <v>5.631087520923202</v>
+        <v>5.63108752032845</v>
       </c>
       <c r="CT130" t="n">
-        <v>5.067978768830883</v>
+        <v>5.067978768295605</v>
       </c>
       <c r="CU130" t="n">
         <v>6</v>
@@ -59240,10 +59240,10 @@
         <v>7.5</v>
       </c>
       <c r="CX130" t="n">
-        <v>-71.30249822978598</v>
+        <v>-71.302498232817</v>
       </c>
       <c r="CY130" t="n">
-        <v>-60.69950160725952</v>
+        <v>-60.69950161124047</v>
       </c>
       <c r="CZ130" t="inlineStr">
         <is>
@@ -59546,10 +59546,10 @@
         <v>4.309999942779541</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.9059813517137003</v>
+        <v>0.905981351483423</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.680595407428914</v>
+        <v>1.68059540700175</v>
       </c>
       <c r="CL131" t="inlineStr"/>
       <c r="CM131" t="inlineStr"/>
@@ -59558,13 +59558,13 @@
       <c r="CP131" t="inlineStr"/>
       <c r="CQ131" t="inlineStr"/>
       <c r="CR131" t="n">
-        <v>1.293288379571307</v>
+        <v>1.293288379242586</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.293288379571307</v>
+        <v>1.293288379242586</v>
       </c>
       <c r="CT131" t="n">
-        <v>1.163959541614177</v>
+        <v>1.163959541318328</v>
       </c>
       <c r="CU131" t="n">
         <v>2</v>
@@ -59576,10 +59576,10 @@
         <v>1.9</v>
       </c>
       <c r="CX131" t="n">
-        <v>-72.99397779426575</v>
+        <v>-72.99397780113</v>
       </c>
       <c r="CY131" t="n">
-        <v>-69.99330866029527</v>
+        <v>-69.99330866792222</v>
       </c>
       <c r="CZ131" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>0</v>
       </c>
       <c r="AU132" t="n">
-        <v>5.85</v>
+        <v>4.22</v>
       </c>
       <c r="AV132" t="b">
         <v>0</v>
@@ -59892,10 +59892,10 @@
         <v>1.169999957084656</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.3441507059227179</v>
+        <v>0.3441507057735512</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.6383995594866416</v>
+        <v>0.6383995592099375</v>
       </c>
       <c r="CL132" t="inlineStr"/>
       <c r="CM132" t="inlineStr"/>
@@ -59904,13 +59904,13 @@
       <c r="CP132" t="inlineStr"/>
       <c r="CQ132" t="inlineStr"/>
       <c r="CR132" t="n">
-        <v>0.4912751327046798</v>
+        <v>0.4912751324917444</v>
       </c>
       <c r="CS132" t="n">
-        <v>0.4912751327046798</v>
+        <v>0.4912751324917444</v>
       </c>
       <c r="CT132" t="n">
-        <v>0.4421476194342118</v>
+        <v>0.44214761924257</v>
       </c>
       <c r="CU132" t="n">
         <v>2</v>
@@ -59922,10 +59922,10 @@
         <v>1.9</v>
       </c>
       <c r="CX132" t="n">
-        <v>-62.20960379041962</v>
+        <v>-62.20960380679927</v>
       </c>
       <c r="CY132" t="n">
-        <v>-58.01067087824403</v>
+        <v>-58.01067089644363</v>
       </c>
       <c r="CZ132" t="inlineStr">
         <is>
@@ -60576,10 +60576,10 @@
         <v>36.66999816894531</v>
       </c>
       <c r="CJ134" t="n">
-        <v>8.259335405507473</v>
+        <v>8.259335386625484</v>
       </c>
       <c r="CK134" t="n">
-        <v>12.02559235041888</v>
+        <v>12.02559232292671</v>
       </c>
       <c r="CL134" t="n">
         <v>7.913840650695814</v>
@@ -60918,10 +60918,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ135" t="n">
-        <v>0.9904024023179506</v>
+        <v>0.9904024027729145</v>
       </c>
       <c r="CK135" t="n">
-        <v>1.837196456299798</v>
+        <v>1.837196457143756</v>
       </c>
       <c r="CL135" t="inlineStr"/>
       <c r="CM135" t="inlineStr"/>
@@ -60932,13 +60932,13 @@
         <v>2.84152338750234</v>
       </c>
       <c r="CR135" t="n">
-        <v>1.889707415373363</v>
+        <v>1.889707415806337</v>
       </c>
       <c r="CS135" t="n">
-        <v>1.837196456299798</v>
+        <v>1.837196457143756</v>
       </c>
       <c r="CT135" t="n">
-        <v>1.653476810669818</v>
+        <v>1.653476811429381</v>
       </c>
       <c r="CU135" t="n">
         <v>3</v>
@@ -60950,10 +60950,10 @@
         <v>2.9</v>
       </c>
       <c r="CX135" t="n">
-        <v>-68.14110226512503</v>
+        <v>-68.14110225048992</v>
       </c>
       <c r="CY135" t="n">
-        <v>-63.58945289905431</v>
+        <v>-63.58945289071185</v>
       </c>
       <c r="CZ135" t="inlineStr">
         <is>
@@ -61272,25 +61272,25 @@
         <v>4.949999809265137</v>
       </c>
       <c r="CJ136" t="n">
-        <v>1.537094636329786</v>
+        <v>1.537094634273867</v>
       </c>
       <c r="CK136" t="n">
-        <v>1.688537257923824</v>
+        <v>1.688537256174416</v>
       </c>
       <c r="CL136" t="n">
-        <v>2.418475244715078</v>
+        <v>2.418475245444214</v>
       </c>
       <c r="CM136" t="n">
         <v>7.627771328933809</v>
       </c>
       <c r="CN136" t="n">
-        <v>1.683198691993163</v>
+        <v>1.683198691263043</v>
       </c>
       <c r="CO136" t="n">
-        <v>1.780877327092232</v>
+        <v>1.780877327152923</v>
       </c>
       <c r="CP136" t="n">
-        <v>1.039152456914678</v>
+        <v>1.039152457582277</v>
       </c>
       <c r="CQ136" t="n">
         <v>0.3242832207911349</v>
@@ -61616,10 +61616,10 @@
         <v>2.150000095367432</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.6036238994472205</v>
+        <v>0.6036238981680291</v>
       </c>
       <c r="CK137" t="n">
-        <v>0.8788763975951531</v>
+        <v>0.8788763957326503</v>
       </c>
       <c r="CL137" t="n">
         <v>0.3524590320274478</v>
@@ -61682,7 +61682,7 @@
         <v>-3.153150105435787</v>
       </c>
       <c r="DL137" t="n">
-        <v>-49.46447734414618</v>
+        <v>-49.46447165359152</v>
       </c>
       <c r="DM137" t="b">
         <v>0</v>
@@ -62274,10 +62274,10 @@
         <v>6.900000095367432</v>
       </c>
       <c r="CJ139" t="n">
-        <v>1.893532149097346</v>
+        <v>1.893532152103147</v>
       </c>
       <c r="CK139" t="n">
-        <v>2.756982809085736</v>
+        <v>2.756982813462183</v>
       </c>
       <c r="CL139" t="n">
         <v>1.700071096702708</v>
@@ -63274,10 +63274,10 @@
         <v>18.26000022888184</v>
       </c>
       <c r="CJ142" t="n">
-        <v>27.71516700009337</v>
+        <v>27.71516699324949</v>
       </c>
       <c r="CK142" t="n">
-        <v>37.07673452012492</v>
+        <v>37.07673451096932</v>
       </c>
       <c r="CL142" t="n">
         <v>2.525466010009227</v>
@@ -63286,10 +63286,10 @@
         <v>7.009520407943455</v>
       </c>
       <c r="CN142" t="n">
-        <v>6.461779399822392</v>
+        <v>6.461779398435588</v>
       </c>
       <c r="CO142" t="n">
-        <v>3.046690502845772</v>
+        <v>3.155500877947406</v>
       </c>
       <c r="CP142" t="n">
         <v>1.237646149955021</v>
@@ -63633,7 +63633,7 @@
         <v>0.2687596883120737</v>
       </c>
       <c r="CO143" t="n">
-        <v>0.4172981554868033</v>
+        <v>0.4552343514401491</v>
       </c>
       <c r="CP143" t="n">
         <v>0.3052495646871551</v>
@@ -63962,10 +63962,10 @@
         <v>3.900000095367432</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.7054953864038204</v>
+        <v>0.7054953878133331</v>
       </c>
       <c r="CK144" t="n">
-        <v>1.308693941779087</v>
+        <v>1.308693944393733</v>
       </c>
       <c r="CL144" t="inlineStr"/>
       <c r="CM144" t="inlineStr"/>
@@ -63976,13 +63976,13 @@
         <v>3.536464154706048</v>
       </c>
       <c r="CR144" t="n">
-        <v>1.007094664091454</v>
+        <v>1.007094666103533</v>
       </c>
       <c r="CS144" t="n">
-        <v>1.007094664091454</v>
+        <v>1.007094666103533</v>
       </c>
       <c r="CT144" t="n">
-        <v>0.9063851976823082</v>
+        <v>0.9063851994931796</v>
       </c>
       <c r="CU144" t="n">
         <v>2</v>
@@ -63994,10 +63994,10 @@
         <v>5</v>
       </c>
       <c r="CX144" t="n">
-        <v>-76.7593544738897</v>
+        <v>-76.75935442745711</v>
       </c>
       <c r="CY144" t="n">
-        <v>-74.17706052654411</v>
+        <v>-74.17706047495234</v>
       </c>
       <c r="CZ144" t="inlineStr">
         <is>
@@ -64306,10 +64306,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ145" t="n">
-        <v>9.566327462133877</v>
+        <v>9.566327443060169</v>
       </c>
       <c r="CK145" t="n">
-        <v>13.92857278486693</v>
+        <v>13.92857275709561</v>
       </c>
       <c r="CL145" t="n">
         <v>4.670347661304791</v>
@@ -65338,10 +65338,10 @@
         <v>11.1899995803833</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.978835440609752</v>
+        <v>5.978835445703428</v>
       </c>
       <c r="CK148" t="n">
-        <v>10.94348323981237</v>
+        <v>10.94348324913568</v>
       </c>
       <c r="CL148" t="inlineStr"/>
       <c r="CM148" t="inlineStr"/>
@@ -65352,13 +65352,13 @@
         <v>3.360116783680318</v>
       </c>
       <c r="CR148" t="n">
-        <v>6.760811821367479</v>
+        <v>6.760811826173142</v>
       </c>
       <c r="CS148" t="n">
-        <v>5.978835440609752</v>
+        <v>5.978835445703428</v>
       </c>
       <c r="CT148" t="n">
-        <v>5.380951896548777</v>
+        <v>5.380951901133085</v>
       </c>
       <c r="CU148" t="n">
         <v>3</v>
@@ -65370,10 +65370,10 @@
         <v>3.3</v>
       </c>
       <c r="CX148" t="n">
-        <v>-51.91284988087141</v>
+        <v>-51.91284983990351</v>
       </c>
       <c r="CY148" t="n">
-        <v>-39.58166152910709</v>
+        <v>-39.58166148616103</v>
       </c>
       <c r="CZ148" t="inlineStr">
         <is>
@@ -65559,13 +65559,13 @@
         <v>1</v>
       </c>
       <c r="AU149" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AV149" t="b">
         <v>1</v>
       </c>
       <c r="AW149" t="n">
-        <v>50139860992</v>
+        <v>50332286976</v>
       </c>
       <c r="AX149" t="n">
         <v>52.94</v>
@@ -66030,10 +66030,10 @@
         <v>15.25</v>
       </c>
       <c r="CJ150" t="n">
-        <v>3.902183818581833</v>
+        <v>3.902183816680577</v>
       </c>
       <c r="CK150" t="n">
-        <v>5.681579639855149</v>
+        <v>5.68157963708692</v>
       </c>
       <c r="CL150" t="inlineStr"/>
       <c r="CM150" t="inlineStr"/>
@@ -66044,7 +66044,7 @@
         <v>5.478426920725005</v>
       </c>
       <c r="CR150" t="n">
-        <v>5.02073012638733</v>
+        <v>5.020730124830834</v>
       </c>
       <c r="CS150" t="n">
         <v>5.478426920725005</v>
@@ -66065,7 +66065,7 @@
         <v>-67.66830013998357</v>
       </c>
       <c r="CY150" t="n">
-        <v>-67.07717949909947</v>
+        <v>-67.07717950930601</v>
       </c>
       <c r="CZ150" t="inlineStr">
         <is>

--- a/reports/screener_2026-09-01.xlsx
+++ b/reports/screener_2026-09-01.xlsx
@@ -1278,10 +1278,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.806389169061072</v>
+        <v>5.8063891607569</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085190860829</v>
+        <v>10.77085189320405</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -1290,7 +1290,7 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.98631684731713</v>
+        <v>66.98631681410043</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -1352,7 +1352,7 @@
         <v>-4.990758938380024</v>
       </c>
       <c r="DL2" t="n">
-        <v>-27.36880747332325</v>
+        <v>-27.36880243865982</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -1628,10 +1628,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958268167085</v>
+        <v>14.76958273885434</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.39757587449942</v>
+        <v>27.3975759805748</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -1640,13 +1640,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097375230589</v>
+        <v>74.51097364566313</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789232821682</v>
+        <v>48.47789228578153</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.35679571353672</v>
+        <v>26.35679553710962</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -1978,10 +1978,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247029995932</v>
+        <v>16.22247028405236</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268240642453</v>
+        <v>30.09268237691713</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -1990,19 +1990,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726798479</v>
+        <v>125.5537726851971</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311038452</v>
+        <v>25.70896311266156</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.8994465569868</v>
+        <v>61.89944659111422</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.17744912059148</v>
+        <v>47.177449121741</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -2023,7 +2023,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479610823401</v>
+        <v>92.95479611293551</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224629224546</v>
+        <v>3.770224611126729</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.993766687211532</v>
+        <v>6.993766653640082</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -2348,25 +2348,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502456886212</v>
+        <v>25.12502458100001</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762231827</v>
+        <v>11.21765762961229</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.59486131297011</v>
+        <v>10.59486135807276</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533149785834</v>
+        <v>9.312533152923372</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802518178071</v>
+        <v>9.655802540729397</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222266360264</v>
+        <v>8.690222286656457</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -2378,10 +2378,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029413652544</v>
+        <v>109.4029418543193</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.3983839947677</v>
+        <v>124.398384070371</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933225533877</v>
+        <v>3.224933208520007</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251133365341</v>
+        <v>5.982251101804613</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -2708,7 +2708,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385727115359</v>
+        <v>24.33385721914613</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -2720,7 +2720,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929366320583</v>
+        <v>11.46929365126752</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -2741,7 +2741,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862774939709</v>
+        <v>159.4862772238733</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418025063309</v>
+        <v>18.62418020062737</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785436492438</v>
+        <v>34.54785427216376</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -3058,23 +3058,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694233343052</v>
+        <v>100.3694234128933</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.8454123413184</v>
+        <v>47.8454123533156</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710154611024</v>
+        <v>59.21710164661773</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.05597282654397</v>
+        <v>44.05597279385169</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.19663335312139</v>
+        <v>41.19663331273968</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.07697001780925</v>
+        <v>37.07696998146571</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -3086,10 +3086,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.13142863070796</v>
+        <v>-24.13142870507576</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.850677737993419</v>
+        <v>-9.850677804889852</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.40168918913402</v>
+        <v>6.401689196500936</v>
       </c>
       <c r="CK8" t="n">
-        <v>11.87513344584361</v>
+        <v>11.87513345950924</v>
       </c>
       <c r="CL8" t="n">
         <v>25.33800212822936</v>
@@ -3416,19 +3416,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN8" t="n">
-        <v>35.10892157198074</v>
+        <v>35.10892155998621</v>
       </c>
       <c r="CO8" t="n">
-        <v>12.29620298488673</v>
+        <v>12.29620298348503</v>
       </c>
       <c r="CP8" t="n">
-        <v>20.31530581605768</v>
+        <v>20.31530580062193</v>
       </c>
       <c r="CQ8" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR8" t="n">
-        <v>20.27452914237111</v>
+        <v>20.27452914020449</v>
       </c>
       <c r="CS8" t="n">
         <v>18.56484347595736</v>
@@ -3449,7 +3449,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY8" t="n">
-        <v>29.13712986420787</v>
+        <v>29.13712985040775</v>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ9" t="n">
-        <v>127.5892443491088</v>
+        <v>127.5892447839196</v>
       </c>
       <c r="CK9" t="n">
-        <v>236.6780482675968</v>
+        <v>236.6780490741708</v>
       </c>
       <c r="CL9" t="n">
         <v>132.6522965266787</v>
@@ -3790,13 +3790,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR9" t="n">
-        <v>139.7795669440898</v>
+        <v>139.7795670992629</v>
       </c>
       <c r="CS9" t="n">
-        <v>124.3641613433398</v>
+        <v>124.3641615607452</v>
       </c>
       <c r="CT9" t="n">
-        <v>111.9277452090058</v>
+        <v>111.9277454046706</v>
       </c>
       <c r="CU9" t="n">
         <v>8</v>
@@ -3808,10 +3808,10 @@
         <v>5.6</v>
       </c>
       <c r="CX9" t="n">
-        <v>157.0097523991609</v>
+        <v>157.0097528484488</v>
       </c>
       <c r="CY9" t="n">
-        <v>220.9634199606116</v>
+        <v>220.9634203169218</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL9" t="n">
-        <v>-8.627323714303436</v>
+        <v>-8.627331177634668</v>
       </c>
       <c r="DM9" t="b">
         <v>1</v>
@@ -4130,10 +4130,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ10" t="n">
-        <v>45.30199113338053</v>
+        <v>45.30199092173366</v>
       </c>
       <c r="CK10" t="n">
-        <v>84.03519355242089</v>
+        <v>84.03519315981595</v>
       </c>
       <c r="CL10" t="n">
         <v>67.58333047231037</v>
@@ -4154,7 +4154,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR10" t="n">
-        <v>76.94607056901533</v>
+        <v>76.94607048269363</v>
       </c>
       <c r="CS10" t="n">
         <v>67.58333047231037</v>
@@ -4175,7 +4175,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY10" t="n">
-        <v>137.1950487866635</v>
+        <v>137.195048520567</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -4498,37 +4498,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ11" t="n">
-        <v>24.21612672531058</v>
+        <v>24.216126628887</v>
       </c>
       <c r="CK11" t="n">
-        <v>32.67790195654321</v>
+        <v>32.67790267207057</v>
       </c>
       <c r="CL11" t="n">
-        <v>34.37896779052954</v>
+        <v>34.37896868019397</v>
       </c>
       <c r="CM11" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN11" t="n">
-        <v>48.80739055469227</v>
+        <v>48.80739130308112</v>
       </c>
       <c r="CO11" t="n">
-        <v>50.94836381156785</v>
+        <v>50.94836393549667</v>
       </c>
       <c r="CP11" t="n">
-        <v>16.8919128436142</v>
+        <v>16.89191340686676</v>
       </c>
       <c r="CQ11" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR11" t="n">
-        <v>31.6120696777737</v>
+        <v>31.612070045816</v>
       </c>
       <c r="CS11" t="n">
-        <v>28.4470143409269</v>
+        <v>28.44701465047878</v>
       </c>
       <c r="CT11" t="n">
-        <v>25.60231290683421</v>
+        <v>25.60231318543091</v>
       </c>
       <c r="CU11" t="n">
         <v>8</v>
@@ -4540,10 +4540,10 @@
         <v>3</v>
       </c>
       <c r="CX11" t="n">
-        <v>-21.46529415589349</v>
+        <v>-21.46529330130236</v>
       </c>
       <c r="CY11" t="n">
-        <v>-3.030456572357343</v>
+        <v>-3.030455443393165</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ12" t="n">
-        <v>133.9252023858741</v>
+        <v>133.9252028900013</v>
       </c>
       <c r="CK12" t="n">
-        <v>248.4312504257963</v>
+        <v>248.4312513609524</v>
       </c>
       <c r="CL12" t="n">
         <v>131.5457818930041</v>
@@ -4884,7 +4884,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR12" t="n">
-        <v>141.1793354152908</v>
+        <v>141.1793355952013</v>
       </c>
       <c r="CS12" t="n">
         <v>125.8371913580247</v>
@@ -4905,7 +4905,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY12" t="n">
-        <v>192.5996588917945</v>
+        <v>192.5996592646658</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -5206,10 +5206,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ13" t="n">
-        <v>13.2653263333155</v>
+        <v>13.26532630965794</v>
       </c>
       <c r="CK13" t="n">
-        <v>24.60718034830025</v>
+        <v>24.60718030441548</v>
       </c>
       <c r="CL13" t="n">
         <v>19.93179967973907</v>
@@ -5218,7 +5218,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN13" t="n">
-        <v>33.72989547161279</v>
+        <v>33.72989544579784</v>
       </c>
       <c r="CO13" t="n">
         <v>22.8984489302328</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
-        <v>20.1756888228969</v>
+        <v>20.17568880601132</v>
       </c>
       <c r="CS13" t="n">
         <v>21.41512430498593</v>
@@ -5249,7 +5249,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY13" t="n">
-        <v>4.537251919444762</v>
+        <v>4.537251831954725</v>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ14" t="n">
-        <v>3.228277656794087</v>
+        <v>3.228277659127442</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.988455053353031</v>
+        <v>5.988455057681404</v>
       </c>
       <c r="CL14" t="n">
         <v>19.81956093381139</v>
@@ -5580,7 +5580,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN14" t="n">
-        <v>31.89244531916918</v>
+        <v>31.89244532600328</v>
       </c>
       <c r="CO14" t="n">
         <v>10.95072400487419</v>
@@ -5926,10 +5926,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ15" t="n">
-        <v>10.67756767844085</v>
+        <v>10.67756771487573</v>
       </c>
       <c r="CK15" t="n">
-        <v>19.80688804350778</v>
+        <v>19.80688811109448</v>
       </c>
       <c r="CL15" t="n">
         <v>38.98902044102951</v>
@@ -5938,25 +5938,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN15" t="n">
-        <v>44.33179747510008</v>
+        <v>44.331797494034</v>
       </c>
       <c r="CO15" t="n">
-        <v>34.59948398607202</v>
+        <v>34.59948397864836</v>
       </c>
       <c r="CP15" t="n">
-        <v>19.85450031530278</v>
+        <v>19.85450027304415</v>
       </c>
       <c r="CQ15" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR15" t="n">
-        <v>32.77627194416817</v>
+        <v>32.77627194943079</v>
       </c>
       <c r="CS15" t="n">
-        <v>34.59948398607202</v>
+        <v>34.59948397864836</v>
       </c>
       <c r="CT15" t="n">
-        <v>31.13953558746482</v>
+        <v>31.13953558078352</v>
       </c>
       <c r="CU15" t="n">
         <v>7</v>
@@ -5968,10 +5968,10 @@
         <v>4.2</v>
       </c>
       <c r="CX15" t="n">
-        <v>78.75737916810424</v>
+        <v>78.75737912975009</v>
       </c>
       <c r="CY15" t="n">
-        <v>88.15311022169192</v>
+        <v>88.15311025190215</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -6286,37 +6286,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ16" t="n">
-        <v>24.9923191544161</v>
+        <v>24.99231901649256</v>
       </c>
       <c r="CK16" t="n">
-        <v>31.99913671117761</v>
+        <v>31.99913693185174</v>
       </c>
       <c r="CL16" t="n">
-        <v>35.8797735080852</v>
+        <v>35.87977395352864</v>
       </c>
       <c r="CM16" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN16" t="n">
-        <v>50.33277069131262</v>
+        <v>50.33277096672724</v>
       </c>
       <c r="CO16" t="n">
-        <v>48.65905499129359</v>
+        <v>48.6590550508374</v>
       </c>
       <c r="CP16" t="n">
-        <v>17.29535377830975</v>
+        <v>17.29535408841702</v>
       </c>
       <c r="CQ16" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR16" t="n">
-        <v>34.65367014276948</v>
+        <v>34.65367028942694</v>
       </c>
       <c r="CS16" t="n">
-        <v>33.9394551096314</v>
+        <v>33.93945544269019</v>
       </c>
       <c r="CT16" t="n">
-        <v>30.54550959866826</v>
+        <v>30.54550989842117</v>
       </c>
       <c r="CU16" t="n">
         <v>8</v>
@@ -6328,10 +6328,10 @@
         <v>2.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>-12.12453661211524</v>
+        <v>-12.12453574976507</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0.305892358740012</v>
+        <v>-0.3058919368255419</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -6646,37 +6646,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.03288994712749</v>
+        <v>10.03288996891136</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.09423440962371</v>
+        <v>18.09423435037944</v>
       </c>
       <c r="CL17" t="n">
-        <v>23.57397883421233</v>
+        <v>23.57397870584134</v>
       </c>
       <c r="CM17" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN17" t="n">
-        <v>36.27022040828844</v>
+        <v>36.27022038810384</v>
       </c>
       <c r="CO17" t="n">
-        <v>24.18418238883785</v>
+        <v>24.18418237935125</v>
       </c>
       <c r="CP17" t="n">
-        <v>11.54642591600218</v>
+        <v>11.54642586826937</v>
       </c>
       <c r="CQ17" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR17" t="n">
-        <v>18.89005841231417</v>
+        <v>18.89005838190975</v>
       </c>
       <c r="CS17" t="n">
-        <v>17.75138478758163</v>
+        <v>17.75138475795949</v>
       </c>
       <c r="CT17" t="n">
-        <v>15.97624630882347</v>
+        <v>15.97624628216354</v>
       </c>
       <c r="CU17" t="n">
         <v>8</v>
@@ -6688,10 +6688,10 @@
         <v>3.6</v>
       </c>
       <c r="CX17" t="n">
-        <v>59.60285657863653</v>
+        <v>59.60285631230366</v>
       </c>
       <c r="CY17" t="n">
-        <v>88.71186793593391</v>
+        <v>88.71186763219339</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.337978094534551</v>
+        <v>3.337978108833978</v>
       </c>
       <c r="CK18" t="n">
-        <v>6.191949365361591</v>
+        <v>6.19194939188703</v>
       </c>
       <c r="CL18" t="n">
         <v>19.28911530241674</v>
@@ -7018,13 +7018,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.60183926079271</v>
+        <v>20.60183925918205</v>
       </c>
       <c r="CO18" t="n">
-        <v>15.92145423049115</v>
+        <v>15.92145422761735</v>
       </c>
       <c r="CP18" t="n">
-        <v>12.84225515070877</v>
+        <v>12.84225513257595</v>
       </c>
       <c r="CQ18" t="n">
         <v>29.10394270806049</v>
@@ -7080,7 +7080,7 @@
         <v>-13.64003621653164</v>
       </c>
       <c r="DL18" t="n">
-        <v>-35.1978807685883</v>
+        <v>-35.19786534004677</v>
       </c>
       <c r="DM18" t="b">
         <v>1</v>
@@ -7356,10 +7356,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ19" t="n">
-        <v>9.410499890742297</v>
+        <v>9.410499913334329</v>
       </c>
       <c r="CK19" t="n">
-        <v>17.45647729732696</v>
+        <v>17.45647733923518</v>
       </c>
       <c r="CL19" t="n">
         <v>21.3058429709553</v>
@@ -7368,25 +7368,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN19" t="n">
-        <v>30.17445903082277</v>
+        <v>30.17445896128012</v>
       </c>
       <c r="CO19" t="n">
-        <v>25.20917160528171</v>
+        <v>25.20917158818038</v>
       </c>
       <c r="CP19" t="n">
-        <v>11.01207341511035</v>
+        <v>11.01207334198808</v>
       </c>
       <c r="CQ19" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR19" t="n">
-        <v>17.05929122616115</v>
+        <v>17.05929121425289</v>
       </c>
       <c r="CS19" t="n">
-        <v>15.0119724891403</v>
+        <v>15.01197251009441</v>
       </c>
       <c r="CT19" t="n">
-        <v>13.51077524022627</v>
+        <v>13.51077525908497</v>
       </c>
       <c r="CU19" t="n">
         <v>8</v>
@@ -7398,10 +7398,10 @@
         <v>3.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>24.29416175225072</v>
+        <v>24.29416192574381</v>
       </c>
       <c r="CY19" t="n">
-        <v>56.93920336489246</v>
+        <v>56.93920325534094</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ20" t="n">
-        <v>7.255085112878843</v>
+        <v>7.255085131110492</v>
       </c>
       <c r="CK20" t="n">
-        <v>13.45818288439025</v>
+        <v>13.45818291820996</v>
       </c>
       <c r="CL20" t="n">
         <v>35.08558886655294</v>
@@ -7728,19 +7728,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN20" t="n">
-        <v>43.3170474218836</v>
+        <v>43.31704739419273</v>
       </c>
       <c r="CO20" t="n">
-        <v>26.42844995275339</v>
+        <v>26.42844994811291</v>
       </c>
       <c r="CP20" t="n">
-        <v>28.12717782341828</v>
+        <v>28.1271777904963</v>
       </c>
       <c r="CQ20" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR20" t="n">
-        <v>28.30913260631269</v>
+        <v>28.30913260182217</v>
       </c>
       <c r="CS20" t="n">
         <v>27.73936337556392</v>
@@ -7761,7 +7761,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY20" t="n">
-        <v>3.393475069485996</v>
+        <v>3.393475053085271</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>-2.318949375511759</v>
       </c>
       <c r="DL20" t="n">
-        <v>-22.38825953382606</v>
+        <v>-22.38825110400813</v>
       </c>
       <c r="DM20" t="b">
         <v>1</v>
@@ -8084,10 +8084,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ21" t="n">
-        <v>3.14037232458228</v>
+        <v>3.140372323820429</v>
       </c>
       <c r="CK21" t="n">
-        <v>5.825390662100129</v>
+        <v>5.825390660686896</v>
       </c>
       <c r="CL21" t="n">
         <v>32.87416582383663</v>
@@ -8096,7 +8096,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN21" t="n">
-        <v>42.11194018305507</v>
+        <v>42.11194018186733</v>
       </c>
       <c r="CO21" t="n">
         <v>10.85340539909456</v>
@@ -8414,10 +8414,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ22" t="n">
-        <v>36.63430055379242</v>
+        <v>36.63430058651684</v>
       </c>
       <c r="CK22" t="n">
-        <v>53.33954160632177</v>
+        <v>53.33954165396852</v>
       </c>
       <c r="CL22" t="n">
         <v>48.73630032327193</v>
@@ -8434,13 +8434,13 @@
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
-        <v>49.55357686680095</v>
+        <v>49.55357688689375</v>
       </c>
       <c r="CS22" t="n">
-        <v>51.03792096479685</v>
+        <v>51.03792098862023</v>
       </c>
       <c r="CT22" t="n">
-        <v>45.93412886831716</v>
+        <v>45.93412888975821</v>
       </c>
       <c r="CU22" t="n">
         <v>4</v>
@@ -8452,10 +8452,10 @@
         <v>1.6</v>
       </c>
       <c r="CX22" t="n">
-        <v>14.77793189131804</v>
+        <v>14.77793194489387</v>
       </c>
       <c r="CY22" t="n">
-        <v>23.82202973510415</v>
+        <v>23.82202978531105</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.414124724269988</v>
+        <v>3.414124725457547</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.333201363520827</v>
+        <v>6.333201365723748</v>
       </c>
       <c r="CL23" t="n">
         <v>31.64000679932063</v>
@@ -8790,7 +8790,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN23" t="n">
-        <v>39.13586008681204</v>
+        <v>39.1358600879658</v>
       </c>
       <c r="CO23" t="n">
         <v>10.59424454785779</v>
@@ -8852,7 +8852,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL23" t="n">
-        <v>-27.83708127316356</v>
+        <v>-27.83707532184228</v>
       </c>
       <c r="DM23" t="b">
         <v>1</v>
@@ -9108,35 +9108,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ24" t="n">
-        <v>8.694392932746011</v>
+        <v>8.694392951335713</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.60549913479195</v>
+        <v>13.60549911404338</v>
       </c>
       <c r="CL24" t="n">
-        <v>17.89239264267922</v>
+        <v>17.8923925771369</v>
       </c>
       <c r="CM24" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.47099642670662</v>
+        <v>22.47099640849115</v>
       </c>
       <c r="CO24" t="n">
-        <v>17.30064966763078</v>
+        <v>17.30064966242656</v>
       </c>
       <c r="CP24" t="n">
-        <v>8.943457188436387</v>
+        <v>8.943457156765485</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
-        <v>14.37323359446199</v>
+        <v>14.37323357623564</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.45307440121136</v>
+        <v>15.45307438823497</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.90776696109023</v>
+        <v>13.90776694941147</v>
       </c>
       <c r="CU24" t="n">
         <v>4</v>
@@ -9148,10 +9148,10 @@
         <v>2.1</v>
       </c>
       <c r="CX24" t="n">
-        <v>7.395885451209439</v>
+        <v>7.395885361026022</v>
       </c>
       <c r="CY24" t="n">
-        <v>10.99022244138255</v>
+        <v>10.99022230063853</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ25" t="n">
-        <v>7.02162015327599</v>
+        <v>7.02162031798788</v>
       </c>
       <c r="CK25" t="n">
-        <v>13.02510538432696</v>
+        <v>13.02510568986752</v>
       </c>
       <c r="CL25" t="n">
         <v>5.692307765667254</v>
@@ -9498,7 +9498,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR25" t="n">
-        <v>7.373583613138371</v>
+        <v>7.373583671919927</v>
       </c>
       <c r="CS25" t="n">
         <v>5.912820549500294</v>
@@ -9519,7 +9519,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY25" t="n">
-        <v>24.55377564377335</v>
+        <v>24.55377663670502</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ26" t="n">
-        <v>20.20396545957872</v>
+        <v>20.2039654163783</v>
       </c>
       <c r="CK26" t="n">
-        <v>37.47835592751852</v>
+        <v>37.47835584738174</v>
       </c>
       <c r="CL26" t="n">
         <v>55.97851442143241</v>
@@ -9828,23 +9828,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN26" t="n">
-        <v>61.597478452734</v>
+        <v>61.59747852382779</v>
       </c>
       <c r="CO26" t="n">
-        <v>45.15222535796428</v>
+        <v>45.15222537147327</v>
       </c>
       <c r="CP26" t="n">
-        <v>30.9891522987558</v>
+        <v>30.98915238410255</v>
       </c>
       <c r="CQ26" t="inlineStr"/>
       <c r="CR26" t="n">
-        <v>39.70326529162348</v>
+        <v>39.70326526416643</v>
       </c>
       <c r="CS26" t="n">
-        <v>41.3152906427414</v>
+        <v>41.31529060942751</v>
       </c>
       <c r="CT26" t="n">
-        <v>37.18376157846726</v>
+        <v>37.18376154848476</v>
       </c>
       <c r="CU26" t="n">
         <v>4</v>
@@ -9856,10 +9856,10 @@
         <v>2.8</v>
       </c>
       <c r="CX26" t="n">
-        <v>-5.868231020696224</v>
+        <v>-5.868231096597798</v>
       </c>
       <c r="CY26" t="n">
-        <v>0.5099655737725639</v>
+        <v>0.5099655042642537</v>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.4302802537439</v>
+        <v>9.430280392303015</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.49316987069493</v>
+        <v>17.49317012772209</v>
       </c>
       <c r="CL27" t="n">
         <v>30.9711095548374</v>
@@ -10166,23 +10166,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN27" t="n">
-        <v>34.71574758824536</v>
+        <v>34.71574761304258</v>
       </c>
       <c r="CO27" t="n">
-        <v>25.47771503272126</v>
+        <v>25.47771500457578</v>
       </c>
       <c r="CP27" t="n">
-        <v>15.278816331191</v>
+        <v>15.27881615890105</v>
       </c>
       <c r="CQ27" t="inlineStr"/>
       <c r="CR27" t="n">
-        <v>20.84306867799937</v>
+        <v>20.84306876985957</v>
       </c>
       <c r="CS27" t="n">
-        <v>21.4854424517081</v>
+        <v>21.48544256614893</v>
       </c>
       <c r="CT27" t="n">
-        <v>19.33689820653729</v>
+        <v>19.33689830953404</v>
       </c>
       <c r="CU27" t="n">
         <v>4</v>
@@ -10194,10 +10194,10 @@
         <v>3.3</v>
       </c>
       <c r="CX27" t="n">
-        <v>27.46801654111344</v>
+        <v>27.46801722006367</v>
       </c>
       <c r="CY27" t="n">
-        <v>37.39662869593978</v>
+        <v>37.39662930147831</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL27" t="n">
-        <v>-16.60346541872488</v>
+        <v>-16.60347445371087</v>
       </c>
       <c r="DM27" t="b">
         <v>1</v>
@@ -10512,37 +10512,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ28" t="n">
-        <v>17.07331078335307</v>
+        <v>17.07331076704757</v>
       </c>
       <c r="CK28" t="n">
-        <v>28.37657059421937</v>
+        <v>28.37657059222237</v>
       </c>
       <c r="CL28" t="n">
-        <v>47.66545634773779</v>
+        <v>47.6654563899052</v>
       </c>
       <c r="CM28" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN28" t="n">
-        <v>56.5946922453201</v>
+        <v>56.59469224000675</v>
       </c>
       <c r="CO28" t="n">
-        <v>42.9486530639905</v>
+        <v>42.94865306694228</v>
       </c>
       <c r="CP28" t="n">
-        <v>23.70643963717476</v>
+        <v>23.70643965541214</v>
       </c>
       <c r="CQ28" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR28" t="n">
-        <v>37.60349435172751</v>
+        <v>37.60349435669509</v>
       </c>
       <c r="CS28" t="n">
-        <v>37.07077016830048</v>
+        <v>37.07077016977637</v>
       </c>
       <c r="CT28" t="n">
-        <v>33.36369315147043</v>
+        <v>33.36369315279873</v>
       </c>
       <c r="CU28" t="n">
         <v>8</v>
@@ -10554,10 +10554,10 @@
         <v>3.3</v>
       </c>
       <c r="CX28" t="n">
-        <v>24.95764868209449</v>
+        <v>24.9576486870694</v>
       </c>
       <c r="CY28" t="n">
-        <v>40.83705347275676</v>
+        <v>40.83705349136197</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -10872,37 +10872,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ29" t="n">
-        <v>5.830932745051316</v>
+        <v>5.830932713942503</v>
       </c>
       <c r="CK29" t="n">
-        <v>8.573470604546189</v>
+        <v>8.573470631141689</v>
       </c>
       <c r="CL29" t="n">
-        <v>11.02317114120126</v>
+        <v>11.023171234206</v>
       </c>
       <c r="CM29" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN29" t="n">
-        <v>9.992439980409005</v>
+        <v>9.992440030131663</v>
       </c>
       <c r="CO29" t="n">
-        <v>14.93936637695643</v>
+        <v>14.93936638791466</v>
       </c>
       <c r="CP29" t="n">
-        <v>5.501588150409129</v>
+        <v>5.501588200780516</v>
       </c>
       <c r="CQ29" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.794723683220752</v>
+        <v>9.794723708163716</v>
       </c>
       <c r="CS29" t="n">
-        <v>10.44705004062795</v>
+        <v>10.44705006548928</v>
       </c>
       <c r="CT29" t="n">
-        <v>9.402345036565155</v>
+        <v>9.402345058940352</v>
       </c>
       <c r="CU29" t="n">
         <v>8</v>
@@ -10914,10 +10914,10 @@
         <v>2.7</v>
       </c>
       <c r="CX29" t="n">
-        <v>-37.4428130165611</v>
+        <v>-37.44281286769087</v>
       </c>
       <c r="CY29" t="n">
-        <v>-34.83217659855213</v>
+        <v>-34.83217643259762</v>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
@@ -11232,37 +11232,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ30" t="n">
-        <v>30.83210627958053</v>
+        <v>30.83210609800769</v>
       </c>
       <c r="CK30" t="n">
-        <v>35.07524614717919</v>
+        <v>35.07524628662182</v>
       </c>
       <c r="CL30" t="n">
-        <v>37.91415975715928</v>
+        <v>37.91416013116773</v>
       </c>
       <c r="CM30" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN30" t="n">
-        <v>59.10496008950702</v>
+        <v>59.1049602948329</v>
       </c>
       <c r="CO30" t="n">
-        <v>16.57964502823301</v>
+        <v>16.5796450461548</v>
       </c>
       <c r="CP30" t="n">
-        <v>16.88731316749069</v>
+        <v>16.88731348929585</v>
       </c>
       <c r="CQ30" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR30" t="n">
-        <v>34.28114189782255</v>
+        <v>34.28114200743894</v>
       </c>
       <c r="CS30" t="n">
-        <v>32.95367621337986</v>
+        <v>32.95367619231476</v>
       </c>
       <c r="CT30" t="n">
-        <v>29.65830859204187</v>
+        <v>29.65830857308329</v>
       </c>
       <c r="CU30" t="n">
         <v>8</v>
@@ -11274,10 +11274,10 @@
         <v>3.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>-23.32391841249989</v>
+        <v>-23.32391846151382</v>
       </c>
       <c r="CY30" t="n">
-        <v>-11.37243633052561</v>
+        <v>-11.37243604713268</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -11574,35 +11574,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ31" t="n">
-        <v>10.16567239950484</v>
+        <v>10.16567243419626</v>
       </c>
       <c r="CK31" t="n">
-        <v>17.61110253775026</v>
+        <v>17.61110253190278</v>
       </c>
       <c r="CL31" t="n">
-        <v>28.75563254934464</v>
+        <v>28.75563244166521</v>
       </c>
       <c r="CM31" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN31" t="n">
-        <v>32.08888080692324</v>
+        <v>32.08888080437558</v>
       </c>
       <c r="CO31" t="n">
-        <v>27.8717377425716</v>
+        <v>27.8717377347679</v>
       </c>
       <c r="CP31" t="n">
-        <v>14.20689959299714</v>
+        <v>14.20689954986044</v>
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>21.10103630729284</v>
+        <v>21.10103628563304</v>
       </c>
       <c r="CS31" t="n">
-        <v>22.74142014016093</v>
+        <v>22.74142013333534</v>
       </c>
       <c r="CT31" t="n">
-        <v>20.46727812614484</v>
+        <v>20.46727812000181</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -11614,10 +11614,10 @@
         <v>2.8</v>
       </c>
       <c r="CX31" t="n">
-        <v>19.83183968131894</v>
+        <v>19.83183964535273</v>
       </c>
       <c r="CY31" t="n">
-        <v>23.54236769056313</v>
+        <v>23.54236756374932</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -11940,37 +11940,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ32" t="n">
-        <v>32.50257839087045</v>
+        <v>32.50257843225724</v>
       </c>
       <c r="CK32" t="n">
-        <v>44.74764038431965</v>
+        <v>44.74764030437347</v>
       </c>
       <c r="CL32" t="n">
-        <v>51.52715699679499</v>
+        <v>51.52715683912498</v>
       </c>
       <c r="CM32" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN32" t="n">
-        <v>71.44157081911828</v>
+        <v>71.44157073374672</v>
       </c>
       <c r="CO32" t="n">
-        <v>59.88947341794151</v>
+        <v>59.88947340102621</v>
       </c>
       <c r="CP32" t="n">
-        <v>25.45084462941759</v>
+        <v>25.45084453315852</v>
       </c>
       <c r="CQ32" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR32" t="n">
-        <v>51.51519284560929</v>
+        <v>51.51519279626238</v>
       </c>
       <c r="CS32" t="n">
-        <v>49.93498894616923</v>
+        <v>49.93498886733423</v>
       </c>
       <c r="CT32" t="n">
-        <v>44.94149005155231</v>
+        <v>44.94148998060081</v>
       </c>
       <c r="CU32" t="n">
         <v>8</v>
@@ -11982,10 +11982,10 @@
         <v>3.1</v>
       </c>
       <c r="CX32" t="n">
-        <v>0.3158277162976342</v>
+        <v>0.3158275579237424</v>
       </c>
       <c r="CY32" t="n">
-        <v>14.98927170291921</v>
+        <v>14.98927159276986</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -12290,10 +12290,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ33" t="n">
-        <v>10.47626037274054</v>
+        <v>10.4762603651497</v>
       </c>
       <c r="CK33" t="n">
-        <v>19.43346299143371</v>
+        <v>19.43346297735269</v>
       </c>
       <c r="CL33" t="n">
         <v>60.73011328156327</v>
@@ -12302,7 +12302,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN33" t="n">
-        <v>81.29749124757811</v>
+        <v>81.29749123848728</v>
       </c>
       <c r="CO33" t="n">
         <v>11.76833333333333</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>13.89268556583586</v>
+        <v>13.8926855586119</v>
       </c>
       <c r="CS33" t="n">
         <v>11.76833333333333</v>
@@ -12333,7 +12333,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY33" t="n">
-        <v>-74.07113644818179</v>
+        <v>-74.07113646166437</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ34" t="n">
-        <v>15.6869427790179</v>
+        <v>15.68694277725812</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.0992788550782</v>
+        <v>29.0992788518138</v>
       </c>
       <c r="CL34" t="n">
         <v>55.61293748708871</v>
@@ -12642,23 +12642,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN34" t="n">
-        <v>62.11186603670111</v>
+        <v>62.11186603712093</v>
       </c>
       <c r="CO34" t="n">
-        <v>36.65076910251672</v>
+        <v>36.65076910283077</v>
       </c>
       <c r="CP34" t="n">
-        <v>30.94726542671738</v>
+        <v>30.94726542914714</v>
       </c>
       <c r="CQ34" t="inlineStr"/>
       <c r="CR34" t="n">
-        <v>34.26248205592537</v>
+        <v>34.26248205474785</v>
       </c>
       <c r="CS34" t="n">
-        <v>32.87502397879746</v>
+        <v>32.87502397732229</v>
       </c>
       <c r="CT34" t="n">
-        <v>29.58752158091771</v>
+        <v>29.58752157959006</v>
       </c>
       <c r="CU34" t="n">
         <v>4</v>
@@ -12670,10 +12670,10 @@
         <v>3.5</v>
       </c>
       <c r="CX34" t="n">
-        <v>-1.40779288484485</v>
+        <v>-1.4077928892689</v>
       </c>
       <c r="CY34" t="n">
-        <v>14.17021591006493</v>
+        <v>14.17021590614116</v>
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>0.2672900865030137</v>
       </c>
       <c r="DL34" t="n">
-        <v>-17.68854281697311</v>
+        <v>-17.68853399965281</v>
       </c>
       <c r="DM34" t="b">
         <v>1</v>
@@ -12990,10 +12990,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ35" t="n">
-        <v>13.32483359494353</v>
+        <v>13.32483351699633</v>
       </c>
       <c r="CK35" t="n">
-        <v>19.40095771423778</v>
+        <v>19.40095760074666</v>
       </c>
       <c r="CL35" t="n">
         <v>16.70870841086448</v>
@@ -13012,7 +13012,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR35" t="n">
-        <v>16.31393973381754</v>
+        <v>16.31393970191115</v>
       </c>
       <c r="CS35" t="n">
         <v>15.78776446356376</v>
@@ -13033,7 +13033,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY35" t="n">
-        <v>52.46672920210042</v>
+        <v>52.46672890390987</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -13348,10 +13348,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ36" t="n">
-        <v>8.850909473613465</v>
+        <v>8.850909515701334</v>
       </c>
       <c r="CK36" t="n">
-        <v>16.41843707355297</v>
+        <v>16.41843715162597</v>
       </c>
       <c r="CL36" t="n">
         <v>16.35235520731475</v>
@@ -13360,7 +13360,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN36" t="n">
-        <v>25.87578448106929</v>
+        <v>25.87578451960625</v>
       </c>
       <c r="CO36" t="n">
         <v>19.94489718117502</v>
@@ -13372,7 +13372,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR36" t="n">
-        <v>16.79289066362578</v>
+        <v>16.79289068346301</v>
       </c>
       <c r="CS36" t="n">
         <v>16.28957786959118</v>
@@ -13393,7 +13393,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY36" t="n">
-        <v>-11.0074726191268</v>
+        <v>-11.00747251400105</v>
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
@@ -14328,10 +14328,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.806389169061072</v>
+        <v>5.8063891607569</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085190860829</v>
+        <v>10.77085189320405</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -14340,7 +14340,7 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.98631684731713</v>
+        <v>66.98631681410043</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -14402,7 +14402,7 @@
         <v>-4.990758938380024</v>
       </c>
       <c r="DL2" t="n">
-        <v>-27.36880747332325</v>
+        <v>-27.36880243865982</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -14678,10 +14678,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958268167085</v>
+        <v>14.76958273885434</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.39757587449942</v>
+        <v>27.3975759805748</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -14690,13 +14690,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097375230589</v>
+        <v>74.51097364566313</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789232821682</v>
+        <v>48.47789228578153</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.35679571353672</v>
+        <v>26.35679553710962</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -15028,10 +15028,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247029995932</v>
+        <v>16.22247028405236</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268240642453</v>
+        <v>30.09268237691713</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -15040,19 +15040,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726798479</v>
+        <v>125.5537726851971</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311038452</v>
+        <v>25.70896311266156</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.8994465569868</v>
+        <v>61.89944659111422</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.17744912059148</v>
+        <v>47.177449121741</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -15073,7 +15073,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479610823401</v>
+        <v>92.95479611293551</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -15386,10 +15386,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224629224546</v>
+        <v>3.770224611126729</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.993766687211532</v>
+        <v>6.993766653640082</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -15398,25 +15398,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502456886212</v>
+        <v>25.12502458100001</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762231827</v>
+        <v>11.21765762961229</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.59486131297011</v>
+        <v>10.59486135807276</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533149785834</v>
+        <v>9.312533152923372</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802518178071</v>
+        <v>9.655802540729397</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222266360264</v>
+        <v>8.690222286656457</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -15428,10 +15428,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029413652544</v>
+        <v>109.4029418543193</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.3983839947677</v>
+        <v>124.398384070371</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -15746,10 +15746,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933225533877</v>
+        <v>3.224933208520007</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251133365341</v>
+        <v>5.982251101804613</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -15758,7 +15758,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385727115359</v>
+        <v>24.33385721914613</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -15770,7 +15770,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929366320583</v>
+        <v>11.46929365126752</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -15791,7 +15791,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862774939709</v>
+        <v>159.4862772238733</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -16096,10 +16096,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418025063309</v>
+        <v>18.62418020062737</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785436492438</v>
+        <v>34.54785427216376</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -16108,23 +16108,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694233343052</v>
+        <v>100.3694234128933</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.8454123413184</v>
+        <v>47.8454123533156</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710154611024</v>
+        <v>59.21710164661773</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.05597282654397</v>
+        <v>44.05597279385169</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.19663335312139</v>
+        <v>41.19663331273968</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.07697001780925</v>
+        <v>37.07696998146571</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -16136,10 +16136,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.13142863070796</v>
+        <v>-24.13142870507576</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.850677737993419</v>
+        <v>-9.850677804889852</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -16678,10 +16678,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.40168918913402</v>
+        <v>6.401689196500936</v>
       </c>
       <c r="CK9" t="n">
-        <v>11.87513344584361</v>
+        <v>11.87513345950924</v>
       </c>
       <c r="CL9" t="n">
         <v>25.33800212822936</v>
@@ -16690,19 +16690,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN9" t="n">
-        <v>35.10892157198074</v>
+        <v>35.10892155998621</v>
       </c>
       <c r="CO9" t="n">
-        <v>12.29620298488673</v>
+        <v>12.29620298348503</v>
       </c>
       <c r="CP9" t="n">
-        <v>20.31530581605768</v>
+        <v>20.31530580062193</v>
       </c>
       <c r="CQ9" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR9" t="n">
-        <v>20.27452914237111</v>
+        <v>20.27452914020449</v>
       </c>
       <c r="CS9" t="n">
         <v>18.56484347595736</v>
@@ -16723,7 +16723,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY9" t="n">
-        <v>29.13712986420787</v>
+        <v>29.13712985040775</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ10" t="n">
-        <v>127.5892443491088</v>
+        <v>127.5892447839196</v>
       </c>
       <c r="CK10" t="n">
-        <v>236.6780482675968</v>
+        <v>236.6780490741708</v>
       </c>
       <c r="CL10" t="n">
         <v>132.6522965266787</v>
@@ -17064,13 +17064,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR10" t="n">
-        <v>139.7795669440898</v>
+        <v>139.7795670992629</v>
       </c>
       <c r="CS10" t="n">
-        <v>124.3641613433398</v>
+        <v>124.3641615607452</v>
       </c>
       <c r="CT10" t="n">
-        <v>111.9277452090058</v>
+        <v>111.9277454046706</v>
       </c>
       <c r="CU10" t="n">
         <v>8</v>
@@ -17082,10 +17082,10 @@
         <v>5.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>157.0097523991609</v>
+        <v>157.0097528484488</v>
       </c>
       <c r="CY10" t="n">
-        <v>220.9634199606116</v>
+        <v>220.9634203169218</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL10" t="n">
-        <v>-8.627323714303436</v>
+        <v>-8.627331177634668</v>
       </c>
       <c r="DM10" t="b">
         <v>1</v>
@@ -17404,10 +17404,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ11" t="n">
-        <v>45.30199113338053</v>
+        <v>45.30199092173366</v>
       </c>
       <c r="CK11" t="n">
-        <v>84.03519355242089</v>
+        <v>84.03519315981595</v>
       </c>
       <c r="CL11" t="n">
         <v>67.58333047231037</v>
@@ -17428,7 +17428,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR11" t="n">
-        <v>76.94607056901533</v>
+        <v>76.94607048269363</v>
       </c>
       <c r="CS11" t="n">
         <v>67.58333047231037</v>
@@ -17449,7 +17449,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY11" t="n">
-        <v>137.1950487866635</v>
+        <v>137.195048520567</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -17772,37 +17772,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ12" t="n">
-        <v>24.21612672531058</v>
+        <v>24.216126628887</v>
       </c>
       <c r="CK12" t="n">
-        <v>32.67790195654321</v>
+        <v>32.67790267207057</v>
       </c>
       <c r="CL12" t="n">
-        <v>34.37896779052954</v>
+        <v>34.37896868019397</v>
       </c>
       <c r="CM12" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN12" t="n">
-        <v>48.80739055469227</v>
+        <v>48.80739130308112</v>
       </c>
       <c r="CO12" t="n">
-        <v>50.94836381156785</v>
+        <v>50.94836393549667</v>
       </c>
       <c r="CP12" t="n">
-        <v>16.8919128436142</v>
+        <v>16.89191340686676</v>
       </c>
       <c r="CQ12" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR12" t="n">
-        <v>31.6120696777737</v>
+        <v>31.612070045816</v>
       </c>
       <c r="CS12" t="n">
-        <v>28.4470143409269</v>
+        <v>28.44701465047878</v>
       </c>
       <c r="CT12" t="n">
-        <v>25.60231290683421</v>
+        <v>25.60231318543091</v>
       </c>
       <c r="CU12" t="n">
         <v>8</v>
@@ -17814,10 +17814,10 @@
         <v>3</v>
       </c>
       <c r="CX12" t="n">
-        <v>-21.46529415589349</v>
+        <v>-21.46529330130236</v>
       </c>
       <c r="CY12" t="n">
-        <v>-3.030456572357343</v>
+        <v>-3.030455443393165</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -18132,10 +18132,10 @@
         <v>6.929999828338623</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.512298822881542</v>
+        <v>6.512298811966652</v>
       </c>
       <c r="CK13" t="n">
-        <v>12.08031431644526</v>
+        <v>12.08031429619814</v>
       </c>
       <c r="CL13" t="n">
         <v>39.92282509803772</v>
@@ -18144,7 +18144,7 @@
         <v>26.88461902486203</v>
       </c>
       <c r="CN13" t="n">
-        <v>84.8357308458352</v>
+        <v>84.83573077939674</v>
       </c>
       <c r="CO13" t="n">
         <v>51.88018214566937</v>
@@ -18480,10 +18480,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ14" t="n">
-        <v>133.9252023858741</v>
+        <v>133.9252028900013</v>
       </c>
       <c r="CK14" t="n">
-        <v>248.4312504257963</v>
+        <v>248.4312513609524</v>
       </c>
       <c r="CL14" t="n">
         <v>131.5457818930041</v>
@@ -18504,7 +18504,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR14" t="n">
-        <v>141.1793354152908</v>
+        <v>141.1793355952013</v>
       </c>
       <c r="CS14" t="n">
         <v>125.8371913580247</v>
@@ -18525,7 +18525,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY14" t="n">
-        <v>192.5996588917945</v>
+        <v>192.5996592646658</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -19172,10 +19172,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ16" t="n">
-        <v>13.2653263333155</v>
+        <v>13.26532630965794</v>
       </c>
       <c r="CK16" t="n">
-        <v>24.60718034830025</v>
+        <v>24.60718030441548</v>
       </c>
       <c r="CL16" t="n">
         <v>19.93179967973907</v>
@@ -19184,7 +19184,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN16" t="n">
-        <v>33.72989547161279</v>
+        <v>33.72989544579784</v>
       </c>
       <c r="CO16" t="n">
         <v>22.8984489302328</v>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
-        <v>20.1756888228969</v>
+        <v>20.17568880601132</v>
       </c>
       <c r="CS16" t="n">
         <v>21.41512430498593</v>
@@ -19215,7 +19215,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY16" t="n">
-        <v>4.537251919444762</v>
+        <v>4.537251831954725</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -19524,10 +19524,10 @@
         <v>13.86999988555908</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.06948874831884</v>
+        <v>10.06948873190079</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.67890162813145</v>
+        <v>18.67890159767597</v>
       </c>
       <c r="CL17" t="n">
         <v>48.87699427756856</v>
@@ -19536,23 +19536,23 @@
         <v>47.98315406169494</v>
       </c>
       <c r="CN17" t="n">
-        <v>67.71366091713611</v>
+        <v>67.71366088648355</v>
       </c>
       <c r="CO17" t="n">
-        <v>33.90963923836745</v>
+        <v>33.90963924095704</v>
       </c>
       <c r="CP17" t="n">
-        <v>28.8504292240355</v>
+        <v>28.85042924319338</v>
       </c>
       <c r="CQ17" t="inlineStr"/>
       <c r="CR17" t="n">
-        <v>33.82184504802249</v>
+        <v>33.82184503873386</v>
       </c>
       <c r="CS17" t="n">
-        <v>33.90963923836745</v>
+        <v>33.90963924095704</v>
       </c>
       <c r="CT17" t="n">
-        <v>30.5186753145307</v>
+        <v>30.51867531686134</v>
       </c>
       <c r="CU17" t="n">
         <v>3</v>
@@ -19564,10 +19564,10 @@
         <v>4.9</v>
       </c>
       <c r="CX17" t="n">
-        <v>120.0337099231384</v>
+        <v>120.0337099399419</v>
       </c>
       <c r="CY17" t="n">
-        <v>143.848920887422</v>
+        <v>143.8489208204528</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -19878,10 +19878,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.228277656794087</v>
+        <v>3.228277659127442</v>
       </c>
       <c r="CK18" t="n">
-        <v>5.988455053353031</v>
+        <v>5.988455057681404</v>
       </c>
       <c r="CL18" t="n">
         <v>19.81956093381139</v>
@@ -19890,7 +19890,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN18" t="n">
-        <v>31.89244531916918</v>
+        <v>31.89244532600328</v>
       </c>
       <c r="CO18" t="n">
         <v>10.95072400487419</v>
@@ -20236,10 +20236,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ19" t="n">
-        <v>10.67756767844085</v>
+        <v>10.67756771487573</v>
       </c>
       <c r="CK19" t="n">
-        <v>19.80688804350778</v>
+        <v>19.80688811109448</v>
       </c>
       <c r="CL19" t="n">
         <v>38.98902044102951</v>
@@ -20248,25 +20248,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN19" t="n">
-        <v>44.33179747510008</v>
+        <v>44.331797494034</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.59948398607202</v>
+        <v>34.59948397864836</v>
       </c>
       <c r="CP19" t="n">
-        <v>19.85450031530278</v>
+        <v>19.85450027304415</v>
       </c>
       <c r="CQ19" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR19" t="n">
-        <v>32.77627194416817</v>
+        <v>32.77627194943079</v>
       </c>
       <c r="CS19" t="n">
-        <v>34.59948398607202</v>
+        <v>34.59948397864836</v>
       </c>
       <c r="CT19" t="n">
-        <v>31.13953558746482</v>
+        <v>31.13953558078352</v>
       </c>
       <c r="CU19" t="n">
         <v>7</v>
@@ -20278,10 +20278,10 @@
         <v>4.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>78.75737916810424</v>
+        <v>78.75737912975009</v>
       </c>
       <c r="CY19" t="n">
-        <v>88.15311022169192</v>
+        <v>88.15311025190215</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -20596,37 +20596,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ20" t="n">
-        <v>24.9923191544161</v>
+        <v>24.99231901649256</v>
       </c>
       <c r="CK20" t="n">
-        <v>31.99913671117761</v>
+        <v>31.99913693185174</v>
       </c>
       <c r="CL20" t="n">
-        <v>35.8797735080852</v>
+        <v>35.87977395352864</v>
       </c>
       <c r="CM20" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN20" t="n">
-        <v>50.33277069131262</v>
+        <v>50.33277096672724</v>
       </c>
       <c r="CO20" t="n">
-        <v>48.65905499129359</v>
+        <v>48.6590550508374</v>
       </c>
       <c r="CP20" t="n">
-        <v>17.29535377830975</v>
+        <v>17.29535408841702</v>
       </c>
       <c r="CQ20" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR20" t="n">
-        <v>34.65367014276948</v>
+        <v>34.65367028942694</v>
       </c>
       <c r="CS20" t="n">
-        <v>33.9394551096314</v>
+        <v>33.93945544269019</v>
       </c>
       <c r="CT20" t="n">
-        <v>30.54550959866826</v>
+        <v>30.54550989842117</v>
       </c>
       <c r="CU20" t="n">
         <v>8</v>
@@ -20638,10 +20638,10 @@
         <v>2.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>-12.12453661211524</v>
+        <v>-12.12453574976507</v>
       </c>
       <c r="CY20" t="n">
-        <v>-0.305892358740012</v>
+        <v>-0.3058919368255419</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -20956,37 +20956,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ21" t="n">
-        <v>10.03288994712749</v>
+        <v>10.03288996891136</v>
       </c>
       <c r="CK21" t="n">
-        <v>18.09423440962371</v>
+        <v>18.09423435037944</v>
       </c>
       <c r="CL21" t="n">
-        <v>23.57397883421233</v>
+        <v>23.57397870584134</v>
       </c>
       <c r="CM21" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN21" t="n">
-        <v>36.27022040828844</v>
+        <v>36.27022038810384</v>
       </c>
       <c r="CO21" t="n">
-        <v>24.18418238883785</v>
+        <v>24.18418237935125</v>
       </c>
       <c r="CP21" t="n">
-        <v>11.54642591600218</v>
+        <v>11.54642586826937</v>
       </c>
       <c r="CQ21" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR21" t="n">
-        <v>18.89005841231417</v>
+        <v>18.89005838190975</v>
       </c>
       <c r="CS21" t="n">
-        <v>17.75138478758163</v>
+        <v>17.75138475795949</v>
       </c>
       <c r="CT21" t="n">
-        <v>15.97624630882347</v>
+        <v>15.97624628216354</v>
       </c>
       <c r="CU21" t="n">
         <v>8</v>
@@ -20998,10 +20998,10 @@
         <v>3.6</v>
       </c>
       <c r="CX21" t="n">
-        <v>59.60285657863653</v>
+        <v>59.60285631230366</v>
       </c>
       <c r="CY21" t="n">
-        <v>88.71186793593391</v>
+        <v>88.71186763219339</v>
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
         <v>3.460000038146973</v>
       </c>
       <c r="CJ22" t="n">
-        <v>5.001737475679065</v>
+        <v>5.001737505921974</v>
       </c>
       <c r="CK22" t="n">
-        <v>9.278223017384667</v>
+        <v>9.278223073485261</v>
       </c>
       <c r="CL22" t="n">
         <v>8.458487178126823</v>
@@ -21664,10 +21664,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.337978094534551</v>
+        <v>3.337978108833978</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.191949365361591</v>
+        <v>6.19194939188703</v>
       </c>
       <c r="CL23" t="n">
         <v>19.28911530241674</v>
@@ -21676,13 +21676,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN23" t="n">
-        <v>20.60183926079271</v>
+        <v>20.60183925918205</v>
       </c>
       <c r="CO23" t="n">
-        <v>15.92145423049115</v>
+        <v>15.92145422761735</v>
       </c>
       <c r="CP23" t="n">
-        <v>12.84225515070877</v>
+        <v>12.84225513257595</v>
       </c>
       <c r="CQ23" t="n">
         <v>29.10394270806049</v>
@@ -21738,7 +21738,7 @@
         <v>-13.64003621653164</v>
       </c>
       <c r="DL23" t="n">
-        <v>-35.1978807685883</v>
+        <v>-35.19786534004677</v>
       </c>
       <c r="DM23" t="b">
         <v>1</v>
@@ -22014,10 +22014,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ24" t="n">
-        <v>9.410499890742297</v>
+        <v>9.410499913334329</v>
       </c>
       <c r="CK24" t="n">
-        <v>17.45647729732696</v>
+        <v>17.45647733923518</v>
       </c>
       <c r="CL24" t="n">
         <v>21.3058429709553</v>
@@ -22026,25 +22026,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN24" t="n">
-        <v>30.17445903082277</v>
+        <v>30.17445896128012</v>
       </c>
       <c r="CO24" t="n">
-        <v>25.20917160528171</v>
+        <v>25.20917158818038</v>
       </c>
       <c r="CP24" t="n">
-        <v>11.01207341511035</v>
+        <v>11.01207334198808</v>
       </c>
       <c r="CQ24" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR24" t="n">
-        <v>17.05929122616115</v>
+        <v>17.05929121425289</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.0119724891403</v>
+        <v>15.01197251009441</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.51077524022627</v>
+        <v>13.51077525908497</v>
       </c>
       <c r="CU24" t="n">
         <v>8</v>
@@ -22056,10 +22056,10 @@
         <v>3.2</v>
       </c>
       <c r="CX24" t="n">
-        <v>24.29416175225072</v>
+        <v>24.29416192574381</v>
       </c>
       <c r="CY24" t="n">
-        <v>56.93920336489246</v>
+        <v>56.93920325534094</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -22382,10 +22382,10 @@
         <v>14.68000030517578</v>
       </c>
       <c r="CJ25" t="n">
-        <v>4.507867427855095</v>
+        <v>4.507867421528296</v>
       </c>
       <c r="CK25" t="n">
-        <v>8.3620940786712</v>
+        <v>8.36209406693499</v>
       </c>
       <c r="CL25" t="n">
         <v>23.72073220043647</v>
@@ -22394,25 +22394,25 @@
         <v>19.98846940520332</v>
       </c>
       <c r="CN25" t="n">
-        <v>28.6420639937558</v>
+        <v>28.64206399895949</v>
       </c>
       <c r="CO25" t="n">
-        <v>16.68542399477433</v>
+        <v>16.68542399610983</v>
       </c>
       <c r="CP25" t="n">
-        <v>17.9483805060213</v>
+        <v>17.94838051608192</v>
       </c>
       <c r="CQ25" t="n">
         <v>14.42556031369228</v>
       </c>
       <c r="CR25" t="n">
-        <v>18.53896064179353</v>
+        <v>18.53896064248833</v>
       </c>
       <c r="CS25" t="n">
-        <v>17.9483805060213</v>
+        <v>17.94838051608192</v>
       </c>
       <c r="CT25" t="n">
-        <v>16.15354245541917</v>
+        <v>16.15354246447373</v>
       </c>
       <c r="CU25" t="n">
         <v>7</v>
@@ -22424,10 +22424,10 @@
         <v>6.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>10.03775285838282</v>
+        <v>10.03775292006239</v>
       </c>
       <c r="CY25" t="n">
-        <v>26.28719520705445</v>
+        <v>26.28719521178742</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -23446,10 +23446,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ28" t="n">
-        <v>7.255085112878843</v>
+        <v>7.255085131110492</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.45818288439025</v>
+        <v>13.45818291820996</v>
       </c>
       <c r="CL28" t="n">
         <v>35.08558886655294</v>
@@ -23458,19 +23458,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN28" t="n">
-        <v>43.3170474218836</v>
+        <v>43.31704739419273</v>
       </c>
       <c r="CO28" t="n">
-        <v>26.42844995275339</v>
+        <v>26.42844994811291</v>
       </c>
       <c r="CP28" t="n">
-        <v>28.12717782341828</v>
+        <v>28.1271777904963</v>
       </c>
       <c r="CQ28" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR28" t="n">
-        <v>28.30913260631269</v>
+        <v>28.30913260182217</v>
       </c>
       <c r="CS28" t="n">
         <v>27.73936337556392</v>
@@ -23491,7 +23491,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY28" t="n">
-        <v>3.393475069485996</v>
+        <v>3.393475053085271</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>-2.318949375511759</v>
       </c>
       <c r="DL28" t="n">
-        <v>-22.38825953382606</v>
+        <v>-22.38825110400813</v>
       </c>
       <c r="DM28" t="b">
         <v>1</v>
@@ -23814,10 +23814,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ29" t="n">
-        <v>3.14037232458228</v>
+        <v>3.140372323820429</v>
       </c>
       <c r="CK29" t="n">
-        <v>5.825390662100129</v>
+        <v>5.825390660686896</v>
       </c>
       <c r="CL29" t="n">
         <v>32.87416582383663</v>
@@ -23826,7 +23826,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN29" t="n">
-        <v>42.11194018305507</v>
+        <v>42.11194018186733</v>
       </c>
       <c r="CO29" t="n">
         <v>10.85340539909456</v>
@@ -24144,10 +24144,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ30" t="n">
-        <v>36.63430055379242</v>
+        <v>36.63430058651684</v>
       </c>
       <c r="CK30" t="n">
-        <v>53.33954160632177</v>
+        <v>53.33954165396852</v>
       </c>
       <c r="CL30" t="n">
         <v>48.73630032327193</v>
@@ -24164,13 +24164,13 @@
       </c>
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="n">
-        <v>49.55357686680095</v>
+        <v>49.55357688689375</v>
       </c>
       <c r="CS30" t="n">
-        <v>51.03792096479685</v>
+        <v>51.03792098862023</v>
       </c>
       <c r="CT30" t="n">
-        <v>45.93412886831716</v>
+        <v>45.93412888975821</v>
       </c>
       <c r="CU30" t="n">
         <v>4</v>
@@ -24182,10 +24182,10 @@
         <v>1.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>14.77793189131804</v>
+        <v>14.77793194489387</v>
       </c>
       <c r="CY30" t="n">
-        <v>23.82202973510415</v>
+        <v>23.82202978531105</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -24508,10 +24508,10 @@
         <v>23.02000045776367</v>
       </c>
       <c r="CJ31" t="n">
-        <v>11.94334398071796</v>
+        <v>11.94334398297249</v>
       </c>
       <c r="CK31" t="n">
-        <v>22.15490308423182</v>
+        <v>22.15490308841397</v>
       </c>
       <c r="CL31" t="n">
         <v>56.48426038247567</v>
@@ -24520,13 +24520,13 @@
         <v>47.22610297818421</v>
       </c>
       <c r="CN31" t="n">
-        <v>78.27396583451041</v>
+        <v>78.27396583459199</v>
       </c>
       <c r="CO31" t="n">
-        <v>33.63213434021188</v>
+        <v>33.6321343398026</v>
       </c>
       <c r="CP31" t="n">
-        <v>41.12575258137358</v>
+        <v>41.12575257775082</v>
       </c>
       <c r="CQ31" t="n">
         <v>5.143948645500518</v>
@@ -24840,35 +24840,35 @@
         <v>23.10000038146973</v>
       </c>
       <c r="CJ32" t="n">
-        <v>16.58090084571571</v>
+        <v>16.5809008518415</v>
       </c>
       <c r="CK32" t="n">
-        <v>29.63840536348659</v>
+        <v>29.63840536255767</v>
       </c>
       <c r="CL32" t="n">
-        <v>49.98948367587612</v>
+        <v>49.98948365584082</v>
       </c>
       <c r="CM32" t="n">
         <v>49.51516084050021</v>
       </c>
       <c r="CN32" t="n">
-        <v>61.73920146015001</v>
+        <v>61.73920146263635</v>
       </c>
       <c r="CO32" t="n">
-        <v>45.75571211411884</v>
+        <v>45.75571211278687</v>
       </c>
       <c r="CP32" t="n">
-        <v>24.53598510757604</v>
+        <v>24.53598510000211</v>
       </c>
       <c r="CQ32" t="inlineStr"/>
       <c r="CR32" t="n">
-        <v>35.49112549979932</v>
+        <v>35.49112549575672</v>
       </c>
       <c r="CS32" t="n">
-        <v>37.69705873880272</v>
+        <v>37.69705873767227</v>
       </c>
       <c r="CT32" t="n">
-        <v>33.92735286492245</v>
+        <v>33.92735286390504</v>
       </c>
       <c r="CU32" t="n">
         <v>4</v>
@@ -24880,10 +24880,10 @@
         <v>3</v>
       </c>
       <c r="CX32" t="n">
-        <v>46.87165499849155</v>
+        <v>46.87165499408719</v>
       </c>
       <c r="CY32" t="n">
-        <v>53.64123339266027</v>
+        <v>53.64123337515985</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -25540,10 +25540,10 @@
         <v>32.75</v>
       </c>
       <c r="CJ34" t="n">
-        <v>7.767166859025735</v>
+        <v>7.76716688307775</v>
       </c>
       <c r="CK34" t="n">
-        <v>14.40809452349274</v>
+        <v>14.40809456810923</v>
       </c>
       <c r="CL34" t="n">
         <v>61.90263908701854</v>
@@ -25552,7 +25552,7 @@
         <v>36.11117259360064</v>
       </c>
       <c r="CN34" t="n">
-        <v>85.59063281403144</v>
+        <v>85.59063286206684</v>
       </c>
       <c r="CO34" t="n">
         <v>22.51480113099953</v>
@@ -25886,10 +25886,10 @@
         <v>33.20000076293945</v>
       </c>
       <c r="CJ35" t="n">
-        <v>15.04507767185095</v>
+        <v>15.04507766193056</v>
       </c>
       <c r="CK35" t="n">
-        <v>27.9086190812835</v>
+        <v>27.90861906288119</v>
       </c>
       <c r="CL35" t="n">
         <v>19.77078697118866</v>
@@ -25898,7 +25898,7 @@
         <v>36.42710872951999</v>
       </c>
       <c r="CN35" t="n">
-        <v>26.62611668223447</v>
+        <v>26.62611667599243</v>
       </c>
       <c r="CO35" t="n">
         <v>15.03391666666667</v>
@@ -25910,7 +25910,7 @@
         <v>78.26206757492224</v>
       </c>
       <c r="CR35" t="n">
-        <v>22.22625156766716</v>
+        <v>22.22625156272934</v>
       </c>
       <c r="CS35" t="n">
         <v>19.77078697118866</v>
@@ -25931,7 +25931,7 @@
         <v>-46.40449438202248</v>
       </c>
       <c r="CY35" t="n">
-        <v>-33.05346067197109</v>
+        <v>-33.05346068684404</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -26250,10 +26250,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ36" t="n">
-        <v>3.414124724269988</v>
+        <v>3.414124725457547</v>
       </c>
       <c r="CK36" t="n">
-        <v>6.333201363520827</v>
+        <v>6.333201365723748</v>
       </c>
       <c r="CL36" t="n">
         <v>31.64000679932063</v>
@@ -26262,7 +26262,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN36" t="n">
-        <v>39.13586008681204</v>
+        <v>39.1358600879658</v>
       </c>
       <c r="CO36" t="n">
         <v>10.59424454785779</v>
@@ -26324,7 +26324,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL36" t="n">
-        <v>-27.83708127316356</v>
+        <v>-27.83707532184228</v>
       </c>
       <c r="DM36" t="b">
         <v>1</v>
@@ -26580,35 +26580,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ37" t="n">
-        <v>8.694392932746011</v>
+        <v>8.694392951335713</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.60549913479195</v>
+        <v>13.60549911404338</v>
       </c>
       <c r="CL37" t="n">
-        <v>17.89239264267922</v>
+        <v>17.8923925771369</v>
       </c>
       <c r="CM37" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN37" t="n">
-        <v>22.47099642670662</v>
+        <v>22.47099640849115</v>
       </c>
       <c r="CO37" t="n">
-        <v>17.30064966763078</v>
+        <v>17.30064966242656</v>
       </c>
       <c r="CP37" t="n">
-        <v>8.943457188436387</v>
+        <v>8.943457156765485</v>
       </c>
       <c r="CQ37" t="inlineStr"/>
       <c r="CR37" t="n">
-        <v>14.37323359446199</v>
+        <v>14.37323357623564</v>
       </c>
       <c r="CS37" t="n">
-        <v>15.45307440121136</v>
+        <v>15.45307438823497</v>
       </c>
       <c r="CT37" t="n">
-        <v>13.90776696109023</v>
+        <v>13.90776694941147</v>
       </c>
       <c r="CU37" t="n">
         <v>4</v>
@@ -26620,10 +26620,10 @@
         <v>2.1</v>
       </c>
       <c r="CX37" t="n">
-        <v>7.395885451209439</v>
+        <v>7.395885361026022</v>
       </c>
       <c r="CY37" t="n">
-        <v>10.99022244138255</v>
+        <v>10.99022230063853</v>
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
@@ -26946,10 +26946,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ38" t="n">
-        <v>7.02162015327599</v>
+        <v>7.02162031798788</v>
       </c>
       <c r="CK38" t="n">
-        <v>13.02510538432696</v>
+        <v>13.02510568986752</v>
       </c>
       <c r="CL38" t="n">
         <v>5.692307765667254</v>
@@ -26970,7 +26970,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR38" t="n">
-        <v>7.373583613138371</v>
+        <v>7.373583671919927</v>
       </c>
       <c r="CS38" t="n">
         <v>5.912820549500294</v>
@@ -26991,7 +26991,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY38" t="n">
-        <v>24.55377564377335</v>
+        <v>24.55377663670502</v>
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
@@ -27288,10 +27288,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ39" t="n">
-        <v>20.20396545957872</v>
+        <v>20.2039654163783</v>
       </c>
       <c r="CK39" t="n">
-        <v>37.47835592751852</v>
+        <v>37.47835584738174</v>
       </c>
       <c r="CL39" t="n">
         <v>55.97851442143241</v>
@@ -27300,23 +27300,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN39" t="n">
-        <v>61.597478452734</v>
+        <v>61.59747852382779</v>
       </c>
       <c r="CO39" t="n">
-        <v>45.15222535796428</v>
+        <v>45.15222537147327</v>
       </c>
       <c r="CP39" t="n">
-        <v>30.9891522987558</v>
+        <v>30.98915238410255</v>
       </c>
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="n">
-        <v>39.70326529162348</v>
+        <v>39.70326526416643</v>
       </c>
       <c r="CS39" t="n">
-        <v>41.3152906427414</v>
+        <v>41.31529060942751</v>
       </c>
       <c r="CT39" t="n">
-        <v>37.18376157846726</v>
+        <v>37.18376154848476</v>
       </c>
       <c r="CU39" t="n">
         <v>4</v>
@@ -27328,10 +27328,10 @@
         <v>2.8</v>
       </c>
       <c r="CX39" t="n">
-        <v>-5.868231020696224</v>
+        <v>-5.868231096597798</v>
       </c>
       <c r="CY39" t="n">
-        <v>0.5099655737725639</v>
+        <v>0.5099655042642537</v>
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
@@ -27626,10 +27626,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ40" t="n">
-        <v>9.4302802537439</v>
+        <v>9.430280392303015</v>
       </c>
       <c r="CK40" t="n">
-        <v>17.49316987069493</v>
+        <v>17.49317012772209</v>
       </c>
       <c r="CL40" t="n">
         <v>30.9711095548374</v>
@@ -27638,23 +27638,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN40" t="n">
-        <v>34.71574758824536</v>
+        <v>34.71574761304258</v>
       </c>
       <c r="CO40" t="n">
-        <v>25.47771503272126</v>
+        <v>25.47771500457578</v>
       </c>
       <c r="CP40" t="n">
-        <v>15.278816331191</v>
+        <v>15.27881615890105</v>
       </c>
       <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="n">
-        <v>20.84306867799937</v>
+        <v>20.84306876985957</v>
       </c>
       <c r="CS40" t="n">
-        <v>21.4854424517081</v>
+        <v>21.48544256614893</v>
       </c>
       <c r="CT40" t="n">
-        <v>19.33689820653729</v>
+        <v>19.33689830953404</v>
       </c>
       <c r="CU40" t="n">
         <v>4</v>
@@ -27666,10 +27666,10 @@
         <v>3.3</v>
       </c>
       <c r="CX40" t="n">
-        <v>27.46801654111344</v>
+        <v>27.46801722006367</v>
       </c>
       <c r="CY40" t="n">
-        <v>37.39662869593978</v>
+        <v>37.39662930147831</v>
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL40" t="n">
-        <v>-16.60346541872488</v>
+        <v>-16.60347445371087</v>
       </c>
       <c r="DM40" t="b">
         <v>1</v>
@@ -27984,10 +27984,10 @@
         <v>12.77999973297119</v>
       </c>
       <c r="CJ41" t="n">
-        <v>1.574362026260813</v>
+        <v>1.574362040737032</v>
       </c>
       <c r="CK41" t="n">
-        <v>2.920441558713808</v>
+        <v>2.920441585567194</v>
       </c>
       <c r="CL41" t="n">
         <v>12.71283757221233</v>
@@ -27996,7 +27996,7 @@
         <v>9.285279950653386</v>
       </c>
       <c r="CN41" t="n">
-        <v>16.04662645362006</v>
+        <v>16.04662646883531</v>
       </c>
       <c r="CO41" t="n">
         <v>6.104046666666666</v>
@@ -28054,7 +28054,7 @@
         <v>-11.43451515806805</v>
       </c>
       <c r="DL41" t="n">
-        <v>-29.69468656045111</v>
+        <v>-29.69469396946918</v>
       </c>
       <c r="DM41" t="b">
         <v>0</v>
@@ -28330,37 +28330,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ42" t="n">
-        <v>17.07331078335307</v>
+        <v>17.07331076704757</v>
       </c>
       <c r="CK42" t="n">
-        <v>28.37657059421937</v>
+        <v>28.37657059222237</v>
       </c>
       <c r="CL42" t="n">
-        <v>47.66545634773779</v>
+        <v>47.6654563899052</v>
       </c>
       <c r="CM42" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN42" t="n">
-        <v>56.5946922453201</v>
+        <v>56.59469224000675</v>
       </c>
       <c r="CO42" t="n">
-        <v>42.9486530639905</v>
+        <v>42.94865306694228</v>
       </c>
       <c r="CP42" t="n">
-        <v>23.70643963717476</v>
+        <v>23.70643965541214</v>
       </c>
       <c r="CQ42" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR42" t="n">
-        <v>37.60349435172751</v>
+        <v>37.60349435669509</v>
       </c>
       <c r="CS42" t="n">
-        <v>37.07077016830048</v>
+        <v>37.07077016977637</v>
       </c>
       <c r="CT42" t="n">
-        <v>33.36369315147043</v>
+        <v>33.36369315279873</v>
       </c>
       <c r="CU42" t="n">
         <v>8</v>
@@ -28372,10 +28372,10 @@
         <v>3.3</v>
       </c>
       <c r="CX42" t="n">
-        <v>24.95764868209449</v>
+        <v>24.9576486870694</v>
       </c>
       <c r="CY42" t="n">
-        <v>40.83705347275676</v>
+        <v>40.83705349136197</v>
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
@@ -28690,37 +28690,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ43" t="n">
-        <v>5.830932745051316</v>
+        <v>5.830932713942503</v>
       </c>
       <c r="CK43" t="n">
-        <v>8.573470604546189</v>
+        <v>8.573470631141689</v>
       </c>
       <c r="CL43" t="n">
-        <v>11.02317114120126</v>
+        <v>11.023171234206</v>
       </c>
       <c r="CM43" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN43" t="n">
-        <v>9.992439980409005</v>
+        <v>9.992440030131663</v>
       </c>
       <c r="CO43" t="n">
-        <v>14.93936637695643</v>
+        <v>14.93936638791466</v>
       </c>
       <c r="CP43" t="n">
-        <v>5.501588150409129</v>
+        <v>5.501588200780516</v>
       </c>
       <c r="CQ43" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR43" t="n">
-        <v>9.794723683220752</v>
+        <v>9.794723708163716</v>
       </c>
       <c r="CS43" t="n">
-        <v>10.44705004062795</v>
+        <v>10.44705006548928</v>
       </c>
       <c r="CT43" t="n">
-        <v>9.402345036565155</v>
+        <v>9.402345058940352</v>
       </c>
       <c r="CU43" t="n">
         <v>8</v>
@@ -28732,10 +28732,10 @@
         <v>2.7</v>
       </c>
       <c r="CX43" t="n">
-        <v>-37.4428130165611</v>
+        <v>-37.44281286769087</v>
       </c>
       <c r="CY43" t="n">
-        <v>-34.83217659855213</v>
+        <v>-34.83217643259762</v>
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
@@ -29050,10 +29050,10 @@
         <v>11.73999977111816</v>
       </c>
       <c r="CJ44" t="n">
-        <v>4.77225638200441</v>
+        <v>4.772256367513212</v>
       </c>
       <c r="CK44" t="n">
-        <v>8.852535588618181</v>
+        <v>8.852535561737009</v>
       </c>
       <c r="CL44" t="n">
         <v>25.04911384336806</v>
@@ -29062,25 +29062,25 @@
         <v>28.15420526956483</v>
       </c>
       <c r="CN44" t="n">
-        <v>23.1659001747162</v>
+        <v>23.16590016263882</v>
       </c>
       <c r="CO44" t="n">
-        <v>14.15725438048856</v>
+        <v>14.15725438193565</v>
       </c>
       <c r="CP44" t="n">
-        <v>12.84913869248639</v>
+        <v>12.84913870542993</v>
       </c>
       <c r="CQ44" t="n">
         <v>4.799038879412761</v>
       </c>
       <c r="CR44" t="n">
-        <v>18.7046913248737</v>
+        <v>18.70469132077905</v>
       </c>
       <c r="CS44" t="n">
-        <v>18.66157727760238</v>
+        <v>18.66157727228724</v>
       </c>
       <c r="CT44" t="n">
-        <v>16.79541954984214</v>
+        <v>16.79541954505851</v>
       </c>
       <c r="CU44" t="n">
         <v>6</v>
@@ -29092,10 +29092,10 @@
         <v>5.9</v>
       </c>
       <c r="CX44" t="n">
-        <v>43.0614981029295</v>
+        <v>43.06149806218311</v>
       </c>
       <c r="CY44" t="n">
-        <v>59.32446072860693</v>
+        <v>59.32446069372914</v>
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
@@ -29406,37 +29406,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ45" t="n">
-        <v>30.83210627958053</v>
+        <v>30.83210609800769</v>
       </c>
       <c r="CK45" t="n">
-        <v>35.07524614717919</v>
+        <v>35.07524628662182</v>
       </c>
       <c r="CL45" t="n">
-        <v>37.91415975715928</v>
+        <v>37.91416013116773</v>
       </c>
       <c r="CM45" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN45" t="n">
-        <v>59.10496008950702</v>
+        <v>59.1049602948329</v>
       </c>
       <c r="CO45" t="n">
-        <v>16.57964502823301</v>
+        <v>16.5796450461548</v>
       </c>
       <c r="CP45" t="n">
-        <v>16.88731316749069</v>
+        <v>16.88731348929585</v>
       </c>
       <c r="CQ45" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR45" t="n">
-        <v>34.28114189782255</v>
+        <v>34.28114200743894</v>
       </c>
       <c r="CS45" t="n">
-        <v>32.95367621337986</v>
+        <v>32.95367619231476</v>
       </c>
       <c r="CT45" t="n">
-        <v>29.65830859204187</v>
+        <v>29.65830857308329</v>
       </c>
       <c r="CU45" t="n">
         <v>8</v>
@@ -29448,10 +29448,10 @@
         <v>3.6</v>
       </c>
       <c r="CX45" t="n">
-        <v>-23.32391841249989</v>
+        <v>-23.32391846151382</v>
       </c>
       <c r="CY45" t="n">
-        <v>-11.37243633052561</v>
+        <v>-11.37243604713268</v>
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
@@ -29766,10 +29766,10 @@
         <v>9.279999732971191</v>
       </c>
       <c r="CJ46" t="n">
-        <v>2.530273360000627</v>
+        <v>2.530273381107185</v>
       </c>
       <c r="CK46" t="n">
-        <v>4.693657082801162</v>
+        <v>4.693657121953827</v>
       </c>
       <c r="CL46" t="n">
         <v>13.27861732849549</v>
@@ -29778,25 +29778,25 @@
         <v>15.00003440426151</v>
       </c>
       <c r="CN46" t="n">
-        <v>10.31764099326716</v>
+        <v>10.31764099556944</v>
       </c>
       <c r="CO46" t="n">
-        <v>7.30508943741188</v>
+        <v>7.305089435384939</v>
       </c>
       <c r="CP46" t="n">
-        <v>6.757993222156737</v>
+        <v>6.757993203545821</v>
       </c>
       <c r="CQ46" t="n">
         <v>10.43331654384748</v>
       </c>
       <c r="CR46" t="n">
-        <v>9.683764144605917</v>
+        <v>9.683764147579788</v>
       </c>
       <c r="CS46" t="n">
-        <v>10.31764099326716</v>
+        <v>10.31764099556944</v>
       </c>
       <c r="CT46" t="n">
-        <v>9.285876893940443</v>
+        <v>9.285876896012498</v>
       </c>
       <c r="CU46" t="n">
         <v>7</v>
@@ -29808,10 +29808,10 @@
         <v>5.9</v>
       </c>
       <c r="CX46" t="n">
-        <v>0.06333147778410098</v>
+        <v>0.06333150011228472</v>
       </c>
       <c r="CY46" t="n">
-        <v>4.350909733328745</v>
+        <v>4.350909765374777</v>
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>-0.2150586812202149</v>
       </c>
       <c r="DL46" t="n">
-        <v>-35.02794846614577</v>
+        <v>-35.02795298830792</v>
       </c>
       <c r="DM46" t="b">
         <v>0</v>
@@ -30122,10 +30122,10 @@
         <v>33.38000106811523</v>
       </c>
       <c r="CJ47" t="n">
-        <v>14.45460462227885</v>
+        <v>14.45460462730396</v>
       </c>
       <c r="CK47" t="n">
-        <v>26.81329157432727</v>
+        <v>26.81329158364885</v>
       </c>
       <c r="CL47" t="n">
         <v>54.20159487163318</v>
@@ -30134,25 +30134,25 @@
         <v>41.89994969714121</v>
       </c>
       <c r="CN47" t="n">
-        <v>69.22029413950256</v>
+        <v>69.22029413300554</v>
       </c>
       <c r="CO47" t="n">
-        <v>38.39264062574333</v>
+        <v>38.39264062446339</v>
       </c>
       <c r="CP47" t="n">
-        <v>38.8495766111008</v>
+        <v>38.84957660159772</v>
       </c>
       <c r="CQ47" t="n">
         <v>21.08922927558395</v>
       </c>
       <c r="CR47" t="n">
-        <v>41.49522525643318</v>
+        <v>41.49522525529625</v>
       </c>
       <c r="CS47" t="n">
-        <v>38.8495766111008</v>
+        <v>38.84957660159772</v>
       </c>
       <c r="CT47" t="n">
-        <v>34.96461894999072</v>
+        <v>34.96461894143795</v>
       </c>
       <c r="CU47" t="n">
         <v>7</v>
@@ -30164,10 +30164,10 @@
         <v>4.8</v>
       </c>
       <c r="CX47" t="n">
-        <v>4.747207403145115</v>
+        <v>4.747207377522678</v>
       </c>
       <c r="CY47" t="n">
-        <v>24.31163549623028</v>
+        <v>24.31163549282427</v>
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
@@ -30476,10 +30476,10 @@
         <v>6.550000190734863</v>
       </c>
       <c r="CJ48" t="n">
-        <v>7.793139942703395</v>
+        <v>7.793139984833482</v>
       </c>
       <c r="CK48" t="n">
-        <v>11.34681175657614</v>
+        <v>11.34681181791755</v>
       </c>
       <c r="CL48" t="n">
         <v>8.052009690737892</v>
@@ -30498,7 +30498,7 @@
         <v>5.354239830150741</v>
       </c>
       <c r="CR48" t="n">
-        <v>8.367187711840348</v>
+        <v>8.367187729085597</v>
       </c>
       <c r="CS48" t="n">
         <v>8.416227402183392</v>
@@ -30519,7 +30519,7 @@
         <v>15.64281589914329</v>
       </c>
       <c r="CY48" t="n">
-        <v>27.74332012502749</v>
+        <v>27.74332038831373</v>
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
@@ -30812,35 +30812,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ49" t="n">
-        <v>10.16567239950484</v>
+        <v>10.16567243419626</v>
       </c>
       <c r="CK49" t="n">
-        <v>17.61110253775026</v>
+        <v>17.61110253190278</v>
       </c>
       <c r="CL49" t="n">
-        <v>28.75563254934464</v>
+        <v>28.75563244166521</v>
       </c>
       <c r="CM49" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN49" t="n">
-        <v>32.08888080692324</v>
+        <v>32.08888080437558</v>
       </c>
       <c r="CO49" t="n">
-        <v>27.8717377425716</v>
+        <v>27.8717377347679</v>
       </c>
       <c r="CP49" t="n">
-        <v>14.20689959299714</v>
+        <v>14.20689954986044</v>
       </c>
       <c r="CQ49" t="inlineStr"/>
       <c r="CR49" t="n">
-        <v>21.10103630729284</v>
+        <v>21.10103628563304</v>
       </c>
       <c r="CS49" t="n">
-        <v>22.74142014016093</v>
+        <v>22.74142013333534</v>
       </c>
       <c r="CT49" t="n">
-        <v>20.46727812614484</v>
+        <v>20.46727812000181</v>
       </c>
       <c r="CU49" t="n">
         <v>4</v>
@@ -30852,10 +30852,10 @@
         <v>2.8</v>
       </c>
       <c r="CX49" t="n">
-        <v>19.83183968131894</v>
+        <v>19.83183964535273</v>
       </c>
       <c r="CY49" t="n">
-        <v>23.54236769056313</v>
+        <v>23.54236756374932</v>
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
@@ -31170,10 +31170,10 @@
         <v>32.70000076293945</v>
       </c>
       <c r="CJ50" t="n">
-        <v>11.11179111323442</v>
+        <v>11.11179107006598</v>
       </c>
       <c r="CK50" t="n">
-        <v>20.61237251504984</v>
+        <v>20.6123724349724</v>
       </c>
       <c r="CL50" t="n">
         <v>55.69087533534032</v>
@@ -31182,19 +31182,19 @@
         <v>52.54606660988762</v>
       </c>
       <c r="CN50" t="n">
-        <v>58.06561443885076</v>
+        <v>58.06561444807646</v>
       </c>
       <c r="CO50" t="n">
-        <v>28.27593786778185</v>
+        <v>28.27593776329305</v>
       </c>
       <c r="CP50" t="n">
-        <v>35.15802047672543</v>
+        <v>35.15802053135249</v>
       </c>
       <c r="CQ50" t="n">
         <v>54.68623962474753</v>
       </c>
       <c r="CR50" t="n">
-        <v>43.57644669548333</v>
+        <v>43.57644667823855</v>
       </c>
       <c r="CS50" t="n">
         <v>52.54606660988762</v>
@@ -31215,7 +31215,7 @@
         <v>44.62219830433958</v>
       </c>
       <c r="CY50" t="n">
-        <v>33.26130176997029</v>
+        <v>33.26130171723396</v>
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
@@ -31534,37 +31534,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ51" t="n">
-        <v>32.50257839087045</v>
+        <v>32.50257843225724</v>
       </c>
       <c r="CK51" t="n">
-        <v>44.74764038431965</v>
+        <v>44.74764030437347</v>
       </c>
       <c r="CL51" t="n">
-        <v>51.52715699679499</v>
+        <v>51.52715683912498</v>
       </c>
       <c r="CM51" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN51" t="n">
-        <v>71.44157081911828</v>
+        <v>71.44157073374672</v>
       </c>
       <c r="CO51" t="n">
-        <v>59.88947341794151</v>
+        <v>59.88947340102621</v>
       </c>
       <c r="CP51" t="n">
-        <v>25.45084462941759</v>
+        <v>25.45084453315852</v>
       </c>
       <c r="CQ51" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR51" t="n">
-        <v>51.51519284560929</v>
+        <v>51.51519279626238</v>
       </c>
       <c r="CS51" t="n">
-        <v>49.93498894616923</v>
+        <v>49.93498886733423</v>
       </c>
       <c r="CT51" t="n">
-        <v>44.94149005155231</v>
+        <v>44.94148998060081</v>
       </c>
       <c r="CU51" t="n">
         <v>8</v>
@@ -31576,10 +31576,10 @@
         <v>3.1</v>
       </c>
       <c r="CX51" t="n">
-        <v>0.3158277162976342</v>
+        <v>0.3158275579237424</v>
       </c>
       <c r="CY51" t="n">
-        <v>14.98927170291921</v>
+        <v>14.98927159276986</v>
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
@@ -31894,37 +31894,37 @@
         <v>10.89000034332275</v>
       </c>
       <c r="CJ52" t="n">
-        <v>8.332366149887951</v>
+        <v>8.332366134251071</v>
       </c>
       <c r="CK52" t="n">
-        <v>11.54775601885551</v>
+        <v>11.54775601479417</v>
       </c>
       <c r="CL52" t="n">
-        <v>16.84415144067704</v>
+        <v>16.84415146636343</v>
       </c>
       <c r="CM52" t="n">
         <v>24.06372840589797</v>
       </c>
       <c r="CN52" t="n">
-        <v>24.25150330823</v>
+        <v>24.2515032986743</v>
       </c>
       <c r="CO52" t="n">
-        <v>20.9951649930635</v>
+        <v>20.995164996001</v>
       </c>
       <c r="CP52" t="n">
-        <v>8.332401445240945</v>
+        <v>8.332401460735218</v>
       </c>
       <c r="CQ52" t="n">
         <v>9.730400983158669</v>
       </c>
       <c r="CR52" t="n">
-        <v>15.51218409312645</v>
+        <v>15.51218409498448</v>
       </c>
       <c r="CS52" t="n">
-        <v>14.19595372976627</v>
+        <v>14.1959537405788</v>
       </c>
       <c r="CT52" t="n">
-        <v>12.77635835678965</v>
+        <v>12.77635836652092</v>
       </c>
       <c r="CU52" t="n">
         <v>8</v>
@@ -31936,10 +31936,10 @@
         <v>2.9</v>
       </c>
       <c r="CX52" t="n">
-        <v>17.32192795222014</v>
+        <v>17.32192804157984</v>
       </c>
       <c r="CY52" t="n">
-        <v>42.44429388505762</v>
+        <v>42.44429390211941</v>
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
@@ -32244,10 +32244,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ53" t="n">
-        <v>10.47626037274054</v>
+        <v>10.4762603651497</v>
       </c>
       <c r="CK53" t="n">
-        <v>19.43346299143371</v>
+        <v>19.43346297735269</v>
       </c>
       <c r="CL53" t="n">
         <v>60.73011328156327</v>
@@ -32256,7 +32256,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN53" t="n">
-        <v>81.29749124757811</v>
+        <v>81.29749123848728</v>
       </c>
       <c r="CO53" t="n">
         <v>11.76833333333333</v>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="CQ53" t="inlineStr"/>
       <c r="CR53" t="n">
-        <v>13.89268556583586</v>
+        <v>13.8926855586119</v>
       </c>
       <c r="CS53" t="n">
         <v>11.76833333333333</v>
@@ -32287,7 +32287,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY53" t="n">
-        <v>-74.07113644818179</v>
+        <v>-74.07113646166437</v>
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
@@ -32584,10 +32584,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ54" t="n">
-        <v>15.6869427790179</v>
+        <v>15.68694277725812</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.0992788550782</v>
+        <v>29.0992788518138</v>
       </c>
       <c r="CL54" t="n">
         <v>55.61293748708871</v>
@@ -32596,23 +32596,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN54" t="n">
-        <v>62.11186603670111</v>
+        <v>62.11186603712093</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.65076910251672</v>
+        <v>36.65076910283077</v>
       </c>
       <c r="CP54" t="n">
-        <v>30.94726542671738</v>
+        <v>30.94726542914714</v>
       </c>
       <c r="CQ54" t="inlineStr"/>
       <c r="CR54" t="n">
-        <v>34.26248205592537</v>
+        <v>34.26248205474785</v>
       </c>
       <c r="CS54" t="n">
-        <v>32.87502397879746</v>
+        <v>32.87502397732229</v>
       </c>
       <c r="CT54" t="n">
-        <v>29.58752158091771</v>
+        <v>29.58752157959006</v>
       </c>
       <c r="CU54" t="n">
         <v>4</v>
@@ -32624,10 +32624,10 @@
         <v>3.5</v>
       </c>
       <c r="CX54" t="n">
-        <v>-1.40779288484485</v>
+        <v>-1.4077928892689</v>
       </c>
       <c r="CY54" t="n">
-        <v>14.17021591006493</v>
+        <v>14.17021590614116</v>
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>0.2672900865030137</v>
       </c>
       <c r="DL54" t="n">
-        <v>-17.68854281697311</v>
+        <v>-17.68853399965281</v>
       </c>
       <c r="DM54" t="b">
         <v>1</v>
@@ -32952,10 +32952,10 @@
         <v>4.78000020980835</v>
       </c>
       <c r="CJ55" t="n">
-        <v>1.10588409695656</v>
+        <v>1.105884093656507</v>
       </c>
       <c r="CK55" t="n">
-        <v>2.051414999854419</v>
+        <v>2.05141499373282</v>
       </c>
       <c r="CL55" t="n">
         <v>9.640030864529775</v>
@@ -32964,13 +32964,13 @@
         <v>9.075586225783375</v>
       </c>
       <c r="CN55" t="n">
-        <v>10.67250377023472</v>
+        <v>10.67250376991099</v>
       </c>
       <c r="CO55" t="n">
-        <v>4.221651665671916</v>
+        <v>4.221651666021244</v>
       </c>
       <c r="CP55" t="n">
-        <v>7.17078239923543</v>
+        <v>7.170782403452104</v>
       </c>
       <c r="CQ55" t="n">
         <v>6.969578707797512</v>
@@ -33022,7 +33022,7 @@
         <v>0.4201676463198689</v>
       </c>
       <c r="DL55" t="n">
-        <v>-33.99458340061891</v>
+        <v>-33.99457898883335</v>
       </c>
       <c r="DM55" t="b">
         <v>0</v>
@@ -33294,10 +33294,10 @@
         <v>24.1299991607666</v>
       </c>
       <c r="CJ56" t="n">
-        <v>4.231713749960219</v>
+        <v>4.231713747916599</v>
       </c>
       <c r="CK56" t="n">
-        <v>7.849829006176207</v>
+        <v>7.849829002385292</v>
       </c>
       <c r="CL56" t="n">
         <v>28.04583235790854</v>
@@ -33306,13 +33306,13 @@
         <v>27.96001968388332</v>
       </c>
       <c r="CN56" t="n">
-        <v>24.90509226527422</v>
+        <v>24.90509226646387</v>
       </c>
       <c r="CO56" t="n">
-        <v>2.969615091474098</v>
+        <v>2.969615091521579</v>
       </c>
       <c r="CP56" t="n">
-        <v>18.04256698414713</v>
+        <v>18.04256698647244</v>
       </c>
       <c r="CQ56" t="n">
         <v>17.75746799357721</v>
@@ -33638,10 +33638,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ57" t="n">
-        <v>13.32483359494353</v>
+        <v>13.32483351699633</v>
       </c>
       <c r="CK57" t="n">
-        <v>19.40095771423778</v>
+        <v>19.40095760074666</v>
       </c>
       <c r="CL57" t="n">
         <v>16.70870841086448</v>
@@ -33660,7 +33660,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR57" t="n">
-        <v>16.31393973381754</v>
+        <v>16.31393970191115</v>
       </c>
       <c r="CS57" t="n">
         <v>15.78776446356376</v>
@@ -33681,7 +33681,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY57" t="n">
-        <v>52.46672920210042</v>
+        <v>52.46672890390987</v>
       </c>
       <c r="CZ57" t="inlineStr">
         <is>
@@ -34004,10 +34004,10 @@
         <v>49.97999954223633</v>
       </c>
       <c r="CJ58" t="n">
-        <v>8.318203507580391</v>
+        <v>8.318203492324766</v>
       </c>
       <c r="CK58" t="n">
-        <v>15.43026750656162</v>
+        <v>15.43026747826244</v>
       </c>
       <c r="CL58" t="n">
         <v>19.67424224404727</v>
@@ -34016,25 +34016,25 @@
         <v>12.23202482325925</v>
       </c>
       <c r="CN58" t="n">
-        <v>14.08088736399888</v>
+        <v>14.08088742847641</v>
       </c>
       <c r="CO58" t="n">
-        <v>20.63682240359299</v>
+        <v>20.63682241277904</v>
       </c>
       <c r="CP58" t="n">
-        <v>10.64281638880638</v>
+        <v>10.6428164333235</v>
       </c>
       <c r="CQ58" t="n">
         <v>13.15686200775853</v>
       </c>
       <c r="CR58" t="n">
-        <v>14.27151578070066</v>
+        <v>14.2715157900289</v>
       </c>
       <c r="CS58" t="n">
-        <v>13.6188746858787</v>
+        <v>13.61887471811747</v>
       </c>
       <c r="CT58" t="n">
-        <v>12.25698721729083</v>
+        <v>12.25698724630572</v>
       </c>
       <c r="CU58" t="n">
         <v>8</v>
@@ -34046,10 +34046,10 @@
         <v>2.5</v>
       </c>
       <c r="CX58" t="n">
-        <v>-75.47621582722728</v>
+        <v>-75.47621576917427</v>
       </c>
       <c r="CY58" t="n">
-        <v>-71.44554639573313</v>
+        <v>-71.44554637706919</v>
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
@@ -34368,10 +34368,10 @@
         <v>34.81999969482422</v>
       </c>
       <c r="CJ59" t="n">
-        <v>12.29771090237208</v>
+        <v>12.29771088658043</v>
       </c>
       <c r="CK59" t="n">
-        <v>22.8122537239002</v>
+        <v>22.8122536946067</v>
       </c>
       <c r="CL59" t="n">
         <v>41.04670782530435</v>
@@ -34380,25 +34380,25 @@
         <v>33.52046162339458</v>
       </c>
       <c r="CN59" t="n">
-        <v>41.80899890089865</v>
+        <v>41.80899892378783</v>
       </c>
       <c r="CO59" t="n">
-        <v>23.77591432505459</v>
+        <v>23.7759143280636</v>
       </c>
       <c r="CP59" t="n">
-        <v>24.92756548487464</v>
+        <v>24.92756551162569</v>
       </c>
       <c r="CQ59" t="n">
         <v>27.30596254019629</v>
       </c>
       <c r="CR59" t="n">
-        <v>28.43694691574942</v>
+        <v>28.43694691669493</v>
       </c>
       <c r="CS59" t="n">
-        <v>26.11676401253547</v>
+        <v>26.11676402591099</v>
       </c>
       <c r="CT59" t="n">
-        <v>23.50508761128192</v>
+        <v>23.50508762331989</v>
       </c>
       <c r="CU59" t="n">
         <v>8</v>
@@ -34410,10 +34410,10 @@
         <v>3.4</v>
       </c>
       <c r="CX59" t="n">
-        <v>-32.4954399273708</v>
+        <v>-32.49543989279879</v>
       </c>
       <c r="CY59" t="n">
-        <v>-18.33157046243052</v>
+        <v>-18.33157045971511</v>
       </c>
       <c r="CZ59" t="inlineStr">
         <is>
@@ -34724,10 +34724,10 @@
         <v>4.25</v>
       </c>
       <c r="CJ60" t="n">
-        <v>2.760517245314274</v>
+        <v>2.760517251263386</v>
       </c>
       <c r="CK60" t="n">
-        <v>5.120759490057978</v>
+        <v>5.12075950109358</v>
       </c>
       <c r="CL60" t="n">
         <v>13.06554524361949</v>
@@ -34736,13 +34736,13 @@
         <v>14.63912825766184</v>
       </c>
       <c r="CN60" t="n">
-        <v>15.1308318947896</v>
+        <v>15.1308319055519</v>
       </c>
       <c r="CO60" t="n">
-        <v>9.474664849484594</v>
+        <v>9.474664848710324</v>
       </c>
       <c r="CP60" t="n">
-        <v>6.508725016288722</v>
+        <v>6.508725010906916</v>
       </c>
       <c r="CQ60" t="n">
         <v>1.476527849208126</v>
@@ -35070,37 +35070,37 @@
         <v>24.77000045776367</v>
       </c>
       <c r="CJ61" t="n">
-        <v>10.94213059726783</v>
+        <v>10.94213062594946</v>
       </c>
       <c r="CK61" t="n">
-        <v>13.84673160981596</v>
+        <v>13.84673159525765</v>
       </c>
       <c r="CL61" t="n">
-        <v>16.40252498822795</v>
+        <v>16.40252492798803</v>
       </c>
       <c r="CM61" t="n">
         <v>20.87886833295617</v>
       </c>
       <c r="CN61" t="n">
-        <v>16.02102943323814</v>
+        <v>16.02102939451337</v>
       </c>
       <c r="CO61" t="n">
-        <v>23.0689194877811</v>
+        <v>23.06891947934167</v>
       </c>
       <c r="CP61" t="n">
-        <v>7.863807342006963</v>
+        <v>7.863807299174953</v>
       </c>
       <c r="CQ61" t="n">
         <v>18.59237633123597</v>
       </c>
       <c r="CR61" t="n">
-        <v>15.95204851531626</v>
+        <v>15.95204849830216</v>
       </c>
       <c r="CS61" t="n">
-        <v>16.21177721073305</v>
+        <v>16.2117771612507</v>
       </c>
       <c r="CT61" t="n">
-        <v>14.59059948965974</v>
+        <v>14.59059944512563</v>
       </c>
       <c r="CU61" t="n">
         <v>8</v>
@@ -35112,10 +35112,10 @@
         <v>2.9</v>
       </c>
       <c r="CX61" t="n">
-        <v>-41.09568340727824</v>
+        <v>-41.09568358706876</v>
       </c>
       <c r="CY61" t="n">
-        <v>-35.59932086995016</v>
+        <v>-35.59932093863849</v>
       </c>
       <c r="CZ61" t="inlineStr">
         <is>
@@ -35426,37 +35426,37 @@
         <v>29.61000061035156</v>
       </c>
       <c r="CJ62" t="n">
-        <v>13.82349757249801</v>
+        <v>13.82349747817716</v>
       </c>
       <c r="CK62" t="n">
-        <v>14.35866820528189</v>
+        <v>14.35866818605365</v>
       </c>
       <c r="CL62" t="n">
-        <v>15.04713247051169</v>
+        <v>15.04713255303149</v>
       </c>
       <c r="CM62" t="n">
         <v>30.31758334384464</v>
       </c>
       <c r="CN62" t="n">
-        <v>14.1879739941943</v>
+        <v>14.18797403645908</v>
       </c>
       <c r="CO62" t="n">
-        <v>30.44468448567737</v>
+        <v>30.44468450550795</v>
       </c>
       <c r="CP62" t="n">
-        <v>6.004060766484719</v>
+        <v>6.004060849902078</v>
       </c>
       <c r="CQ62" t="n">
         <v>37.94236112090656</v>
       </c>
       <c r="CR62" t="n">
-        <v>17.74051440549894</v>
+        <v>17.74051442185372</v>
       </c>
       <c r="CS62" t="n">
-        <v>14.35866820528189</v>
+        <v>14.35866818605365</v>
       </c>
       <c r="CT62" t="n">
-        <v>12.9228013847537</v>
+        <v>12.92280136744829</v>
       </c>
       <c r="CU62" t="n">
         <v>7</v>
@@ -35468,10 +35468,10 @@
         <v>6.3</v>
       </c>
       <c r="CX62" t="n">
-        <v>-56.35663249450954</v>
+        <v>-56.35663255295403</v>
       </c>
       <c r="CY62" t="n">
-        <v>-40.08607213842166</v>
+        <v>-40.08607208318769</v>
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
@@ -35782,10 +35782,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ63" t="n">
-        <v>8.850909473613465</v>
+        <v>8.850909515701334</v>
       </c>
       <c r="CK63" t="n">
-        <v>16.41843707355297</v>
+        <v>16.41843715162597</v>
       </c>
       <c r="CL63" t="n">
         <v>16.35235520731475</v>
@@ -35794,7 +35794,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN63" t="n">
-        <v>25.87578448106929</v>
+        <v>25.87578451960625</v>
       </c>
       <c r="CO63" t="n">
         <v>19.94489718117502</v>
@@ -35806,7 +35806,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR63" t="n">
-        <v>16.79289066362578</v>
+        <v>16.79289068346301</v>
       </c>
       <c r="CS63" t="n">
         <v>16.28957786959118</v>
@@ -35827,7 +35827,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY63" t="n">
-        <v>-11.0074726191268</v>
+        <v>-11.00747251400105</v>
       </c>
       <c r="CZ63" t="inlineStr">
         <is>
@@ -36154,35 +36154,35 @@
         <v>3.410000085830688</v>
       </c>
       <c r="CJ64" t="n">
-        <v>2.617517221042489</v>
+        <v>2.617517203301139</v>
       </c>
       <c r="CK64" t="n">
-        <v>2.995865535931345</v>
+        <v>2.995865530362893</v>
       </c>
       <c r="CL64" t="n">
-        <v>3.583269942064618</v>
+        <v>3.583269959691505</v>
       </c>
       <c r="CM64" t="n">
         <v>6.696150695272573</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.400672783178041</v>
+        <v>5.400672775121945</v>
       </c>
       <c r="CO64" t="n">
-        <v>8.464613710247207</v>
+        <v>8.464613714785392</v>
       </c>
       <c r="CP64" t="n">
-        <v>1.604916847274464</v>
+        <v>1.604916862277968</v>
       </c>
       <c r="CQ64" t="inlineStr"/>
       <c r="CR64" t="n">
-        <v>4.480429533572962</v>
+        <v>4.480429534401916</v>
       </c>
       <c r="CS64" t="n">
-        <v>3.583269942064618</v>
+        <v>3.583269959691505</v>
       </c>
       <c r="CT64" t="n">
-        <v>3.224942947858156</v>
+        <v>3.224942963722355</v>
       </c>
       <c r="CU64" t="n">
         <v>7</v>
@@ -36194,10 +36194,10 @@
         <v>5.3</v>
       </c>
       <c r="CX64" t="n">
-        <v>-5.426895405119958</v>
+        <v>-5.426894939894201</v>
       </c>
       <c r="CY64" t="n">
-        <v>31.39089210554999</v>
+        <v>31.39089212985951</v>
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
@@ -36520,10 +36520,10 @@
         <v>35.18000030517578</v>
       </c>
       <c r="CJ65" t="n">
-        <v>10.0731230057133</v>
+        <v>10.07312303163065</v>
       </c>
       <c r="CK65" t="n">
-        <v>18.68564317559816</v>
+        <v>18.68564322367486</v>
       </c>
       <c r="CL65" t="n">
         <v>28.5272340295948</v>
@@ -36532,25 +36532,25 @@
         <v>21.17723585857856</v>
       </c>
       <c r="CN65" t="n">
-        <v>25.90721695523408</v>
+        <v>25.90721689304261</v>
       </c>
       <c r="CO65" t="n">
-        <v>22.6873645016019</v>
+        <v>22.68736449336911</v>
       </c>
       <c r="CP65" t="n">
-        <v>16.61118113978281</v>
+        <v>16.61118108673309</v>
       </c>
       <c r="CQ65" t="n">
         <v>27.23126452034872</v>
       </c>
       <c r="CR65" t="n">
-        <v>21.36253289830654</v>
+        <v>21.36253289212155</v>
       </c>
       <c r="CS65" t="n">
-        <v>21.93230018009023</v>
+        <v>21.93230017597384</v>
       </c>
       <c r="CT65" t="n">
-        <v>19.73907016208121</v>
+        <v>19.73907015837645</v>
       </c>
       <c r="CU65" t="n">
         <v>8</v>
@@ -36562,10 +36562,10 @@
         <v>2.8</v>
       </c>
       <c r="CX65" t="n">
-        <v>-43.89121662634795</v>
+        <v>-43.8912166368788</v>
       </c>
       <c r="CY65" t="n">
-        <v>-39.27648461343639</v>
+        <v>-39.27648463101738</v>
       </c>
       <c r="CZ65" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>-2.467422781198825</v>
       </c>
       <c r="DL65" t="n">
-        <v>-21.73873559212695</v>
+        <v>-21.73874227621538</v>
       </c>
       <c r="DM65" t="b">
         <v>0</v>
@@ -36854,10 +36854,10 @@
         <v>13.14999961853027</v>
       </c>
       <c r="CJ66" t="n">
-        <v>11.12140753099835</v>
+        <v>11.12140751604742</v>
       </c>
       <c r="CK66" t="n">
-        <v>16.19276936513359</v>
+        <v>16.19276934336504</v>
       </c>
       <c r="CL66" t="n">
         <v>15.50566848443479</v>
@@ -36874,13 +36874,13 @@
       </c>
       <c r="CQ66" t="inlineStr"/>
       <c r="CR66" t="n">
-        <v>12.53829467847502</v>
+        <v>12.53829466929515</v>
       </c>
       <c r="CS66" t="n">
-        <v>13.31353800771657</v>
+        <v>13.3135380002411</v>
       </c>
       <c r="CT66" t="n">
-        <v>11.98218420694491</v>
+        <v>11.98218420021699</v>
       </c>
       <c r="CU66" t="n">
         <v>4</v>
@@ -36892,10 +36892,10 @@
         <v>2.2</v>
       </c>
       <c r="CX66" t="n">
-        <v>-8.880725821008696</v>
+        <v>-8.880725872171569</v>
       </c>
       <c r="CY66" t="n">
-        <v>-4.651748728519156</v>
+        <v>-4.65174879832807</v>
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
@@ -37206,10 +37206,10 @@
         <v>8.340000152587891</v>
       </c>
       <c r="CJ67" t="n">
-        <v>1.607882485612103</v>
+        <v>1.607882484553667</v>
       </c>
       <c r="CK67" t="n">
-        <v>2.98262201081045</v>
+        <v>2.982622008847051</v>
       </c>
       <c r="CL67" t="n">
         <v>24.39404018141049</v>
@@ -37218,13 +37218,13 @@
         <v>24.19815257966773</v>
       </c>
       <c r="CN67" t="n">
-        <v>26.08971931941487</v>
+        <v>26.08971931808049</v>
       </c>
       <c r="CO67" t="n">
-        <v>6.710381499833533</v>
+        <v>6.710381499896859</v>
       </c>
       <c r="CP67" t="n">
-        <v>18.19403113258484</v>
+        <v>18.19403113380221</v>
       </c>
       <c r="CQ67" t="n">
         <v>15.56402401821373</v>
@@ -37552,10 +37552,10 @@
         <v>8.439999580383301</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.5022232223349544</v>
+        <v>0.5022232223091929</v>
       </c>
       <c r="CK68" t="n">
-        <v>0.9316240774313405</v>
+        <v>0.9316240773835527</v>
       </c>
       <c r="CL68" t="n">
         <v>9.437130332496094</v>
@@ -37564,13 +37564,13 @@
         <v>8.668386285715835</v>
       </c>
       <c r="CN68" t="n">
-        <v>10.35702314718015</v>
+        <v>10.35702314720457</v>
       </c>
       <c r="CO68" t="n">
-        <v>0.7357683740995217</v>
+        <v>0.7357683741000202</v>
       </c>
       <c r="CP68" t="n">
-        <v>8.039858089828902</v>
+        <v>8.039858089863383</v>
       </c>
       <c r="CQ68" t="inlineStr"/>
       <c r="CR68" t="inlineStr"/>
@@ -37902,25 +37902,25 @@
         <v>2.240000009536743</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.6430659547212066</v>
+        <v>0.6430659526810664</v>
       </c>
       <c r="CK69" t="n">
-        <v>0.9085084054675461</v>
+        <v>0.9085084030131898</v>
       </c>
       <c r="CL69" t="n">
-        <v>3.343849485350326</v>
+        <v>3.343849486925272</v>
       </c>
       <c r="CM69" t="n">
         <v>6.907675204991913</v>
       </c>
       <c r="CN69" t="n">
-        <v>2.56499845842287</v>
+        <v>2.564998455657244</v>
       </c>
       <c r="CO69" t="n">
-        <v>2.230430075302555</v>
+        <v>2.230430075397271</v>
       </c>
       <c r="CP69" t="n">
-        <v>1.66036457131954</v>
+        <v>1.66036457223695</v>
       </c>
       <c r="CQ69" t="n">
         <v>6.634722275472289</v>
@@ -38256,10 +38256,10 @@
         <v>21.36000061035156</v>
       </c>
       <c r="CJ70" t="n">
-        <v>5.90719807467577</v>
+        <v>5.907198071889892</v>
       </c>
       <c r="CK70" t="n">
-        <v>10.95785242852355</v>
+        <v>10.95785242335575</v>
       </c>
       <c r="CL70" t="n">
         <v>32.3451437813895</v>
@@ -38268,25 +38268,25 @@
         <v>33.26867930684288</v>
       </c>
       <c r="CN70" t="n">
-        <v>28.98255279643806</v>
+        <v>28.98255279669993</v>
       </c>
       <c r="CO70" t="n">
-        <v>25.1983497779687</v>
+        <v>25.19834977841975</v>
       </c>
       <c r="CP70" t="n">
-        <v>18.79799008451286</v>
+        <v>18.79799008747926</v>
       </c>
       <c r="CQ70" t="n">
         <v>13.70244046469206</v>
       </c>
       <c r="CR70" t="n">
-        <v>23.32185837719538</v>
+        <v>23.32185837698274</v>
       </c>
       <c r="CS70" t="n">
-        <v>25.1983497779687</v>
+        <v>25.19834977841975</v>
       </c>
       <c r="CT70" t="n">
-        <v>22.67851480017183</v>
+        <v>22.67851480057778</v>
       </c>
       <c r="CU70" t="n">
         <v>7</v>
@@ -38298,10 +38298,10 @@
         <v>5.6</v>
       </c>
       <c r="CX70" t="n">
-        <v>6.172819064346324</v>
+        <v>6.172819066246804</v>
       </c>
       <c r="CY70" t="n">
-        <v>9.184727110415203</v>
+        <v>9.184727109419688</v>
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
@@ -38612,25 +38612,25 @@
         <v>17.28000068664551</v>
       </c>
       <c r="CJ71" t="n">
-        <v>4.022695612443805</v>
+        <v>4.022695626089441</v>
       </c>
       <c r="CK71" t="n">
-        <v>6.903155493895718</v>
+        <v>6.903155510688491</v>
       </c>
       <c r="CL71" t="n">
-        <v>23.48224778224658</v>
+        <v>23.48224775971444</v>
       </c>
       <c r="CM71" t="n">
         <v>32.85543339401257</v>
       </c>
       <c r="CN71" t="n">
-        <v>16.59077768056397</v>
+        <v>16.59077768712898</v>
       </c>
       <c r="CO71" t="n">
-        <v>20.50985171834286</v>
+        <v>20.50985171685842</v>
       </c>
       <c r="CP71" t="n">
-        <v>11.62167798067715</v>
+        <v>11.62167797149091</v>
       </c>
       <c r="CQ71" t="n">
         <v>22.25954302628453</v>
@@ -38958,10 +38958,10 @@
         <v>3.819999933242798</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.9263872497989677</v>
+        <v>0.9263872494178996</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.718448348377085</v>
+        <v>1.718448347670204</v>
       </c>
       <c r="CL72" t="n">
         <v>6.076230386010452</v>
@@ -38970,7 +38970,7 @@
         <v>4.03575162850128</v>
       </c>
       <c r="CN72" t="n">
-        <v>8.43570474139586</v>
+        <v>8.435704740755408</v>
       </c>
       <c r="CO72" t="n">
         <v>3.760485277130923</v>
@@ -39312,10 +39312,10 @@
         <v>12.57999992370605</v>
       </c>
       <c r="CJ73" t="n">
-        <v>2.081714462794371</v>
+        <v>2.081714458963004</v>
       </c>
       <c r="CK73" t="n">
-        <v>3.861580328483558</v>
+        <v>3.861580321376372</v>
       </c>
       <c r="CL73" t="n">
         <v>16.32566101754214</v>
@@ -39324,7 +39324,7 @@
         <v>12.94873547769632</v>
       </c>
       <c r="CN73" t="n">
-        <v>21.33633705530969</v>
+        <v>21.33633705005611</v>
       </c>
       <c r="CO73" t="n">
         <v>9.294207014285712</v>
@@ -39658,35 +39658,35 @@
         <v>24.09000015258789</v>
       </c>
       <c r="CJ74" t="n">
-        <v>23.14624711752801</v>
+        <v>23.14624737485934</v>
       </c>
       <c r="CK74" t="n">
-        <v>28.51028672947743</v>
+        <v>28.5102867956948</v>
       </c>
       <c r="CL74" t="n">
-        <v>36.66924162669387</v>
+        <v>36.66924130418612</v>
       </c>
       <c r="CM74" t="n">
         <v>60.85541453379113</v>
       </c>
       <c r="CN74" t="n">
-        <v>65.92125698907222</v>
+        <v>65.92125722940563</v>
       </c>
       <c r="CO74" t="n">
-        <v>41.61752979774013</v>
+        <v>41.61752976038338</v>
       </c>
       <c r="CP74" t="n">
-        <v>17.33029135342939</v>
+        <v>17.33029111271137</v>
       </c>
       <c r="CQ74" t="inlineStr"/>
       <c r="CR74" t="n">
-        <v>39.15003830681889</v>
+        <v>39.15003830157598</v>
       </c>
       <c r="CS74" t="n">
-        <v>36.66924162669387</v>
+        <v>36.66924130418612</v>
       </c>
       <c r="CT74" t="n">
-        <v>33.00231746402449</v>
+        <v>33.00231717376751</v>
       </c>
       <c r="CU74" t="n">
         <v>7</v>
@@ -39698,10 +39698,10 @@
         <v>3.8</v>
       </c>
       <c r="CX74" t="n">
-        <v>36.99592052712867</v>
+        <v>36.99591932224295</v>
       </c>
       <c r="CY74" t="n">
-        <v>62.51572461120618</v>
+        <v>62.51572458944234</v>
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
@@ -40012,10 +40012,10 @@
         <v>25.28000068664551</v>
       </c>
       <c r="CJ75" t="n">
-        <v>4.637679044239077</v>
+        <v>4.637679039570942</v>
       </c>
       <c r="CK75" t="n">
-        <v>8.602894627063487</v>
+        <v>8.602894618404097</v>
       </c>
       <c r="CL75" t="n">
         <v>30.23104775253185</v>
@@ -40024,19 +40024,19 @@
         <v>25.66642298400775</v>
       </c>
       <c r="CN75" t="n">
-        <v>34.91506256197618</v>
+        <v>34.91506256771081</v>
       </c>
       <c r="CO75" t="n">
-        <v>11.77719501756868</v>
+        <v>11.77719501810132</v>
       </c>
       <c r="CP75" t="n">
-        <v>24.35835628850705</v>
+        <v>24.35835629581922</v>
       </c>
       <c r="CQ75" t="n">
         <v>25.28000068664551</v>
       </c>
       <c r="CR75" t="n">
-        <v>25.3713475485395</v>
+        <v>25.37134755080274</v>
       </c>
       <c r="CS75" t="n">
         <v>25.47321183532663</v>
@@ -40057,7 +40057,7 @@
         <v>-9.312143872271072</v>
       </c>
       <c r="CY75" t="n">
-        <v>0.3613404248926644</v>
+        <v>0.3613404338453474</v>
       </c>
       <c r="CZ75" t="inlineStr">
         <is>
@@ -40366,10 +40366,10 @@
         <v>54.72999954223633</v>
       </c>
       <c r="CJ76" t="n">
-        <v>39.80284439285852</v>
+        <v>39.80284410105673</v>
       </c>
       <c r="CK76" t="n">
-        <v>57.95294143600201</v>
+        <v>57.95294101113861</v>
       </c>
       <c r="CL76" t="n">
         <v>35.04876817975726</v>
@@ -40388,13 +40388,13 @@
         <v>48.01546263696088</v>
       </c>
       <c r="CR76" t="n">
-        <v>42.74450959294544</v>
+        <v>42.74450947350125</v>
       </c>
       <c r="CS76" t="n">
-        <v>40.82420864774879</v>
+        <v>40.8242085018479</v>
       </c>
       <c r="CT76" t="n">
-        <v>36.74178778297392</v>
+        <v>36.74178765166311</v>
       </c>
       <c r="CU76" t="n">
         <v>6</v>
@@ -40406,10 +40406,10 @@
         <v>6.4</v>
       </c>
       <c r="CX76" t="n">
-        <v>-32.86718784892465</v>
+        <v>-32.86718808884937</v>
       </c>
       <c r="CY76" t="n">
-        <v>-21.89930577295441</v>
+        <v>-21.89930599119706</v>
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
@@ -40720,10 +40720,10 @@
         <v>28.80999946594238</v>
       </c>
       <c r="CJ77" t="n">
-        <v>13.46031126486381</v>
+        <v>13.46031123347453</v>
       </c>
       <c r="CK77" t="n">
-        <v>24.96887739632236</v>
+        <v>24.96887733809526</v>
       </c>
       <c r="CL77" t="n">
         <v>36.32088419826228</v>
@@ -40732,25 +40732,25 @@
         <v>25.32755497782173</v>
       </c>
       <c r="CN77" t="n">
-        <v>40.52264091471584</v>
+        <v>40.52264098878622</v>
       </c>
       <c r="CO77" t="n">
-        <v>42.02971217213049</v>
+        <v>42.02971218854545</v>
       </c>
       <c r="CP77" t="n">
-        <v>21.52400193771418</v>
+        <v>21.52400201055486</v>
       </c>
       <c r="CQ77" t="n">
         <v>24.88607192490505</v>
       </c>
       <c r="CR77" t="n">
-        <v>28.63000684834197</v>
+        <v>28.63000685755567</v>
       </c>
       <c r="CS77" t="n">
-        <v>25.14821618707204</v>
+        <v>25.1482161579585</v>
       </c>
       <c r="CT77" t="n">
-        <v>22.63339456836484</v>
+        <v>22.63339454216265</v>
       </c>
       <c r="CU77" t="n">
         <v>8</v>
@@ -40762,10 +40762,10 @@
         <v>3.1</v>
       </c>
       <c r="CX77" t="n">
-        <v>-21.43910104850639</v>
+        <v>-21.43910113945466</v>
       </c>
       <c r="CY77" t="n">
-        <v>-0.624757448583757</v>
+        <v>-0.6247574166028391</v>
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
@@ -41084,10 +41084,10 @@
         <v>15.0600004196167</v>
       </c>
       <c r="CJ78" t="n">
-        <v>2.430224155283246</v>
+        <v>2.430224157038559</v>
       </c>
       <c r="CK78" t="n">
-        <v>4.508065808050421</v>
+        <v>4.508065811306527</v>
       </c>
       <c r="CL78" t="n">
         <v>24.78819944843742</v>
@@ -41096,7 +41096,7 @@
         <v>18.97850370269514</v>
       </c>
       <c r="CN78" t="n">
-        <v>32.28858937493365</v>
+        <v>32.28858937798637</v>
       </c>
       <c r="CO78" t="n">
         <v>10.38593205872702</v>
@@ -41430,10 +41430,10 @@
         <v>14.94999980926514</v>
       </c>
       <c r="CJ79" t="n">
-        <v>9.768327017563797</v>
+        <v>9.768326972321068</v>
       </c>
       <c r="CK79" t="n">
-        <v>18.12024661758084</v>
+        <v>18.12024653365558</v>
       </c>
       <c r="CL79" t="n">
         <v>13.9204144394071</v>
@@ -41454,7 +41454,7 @@
         <v>12.34226887232652</v>
       </c>
       <c r="CR79" t="n">
-        <v>15.11537394954413</v>
+        <v>15.11537393339812</v>
       </c>
       <c r="CS79" t="n">
         <v>13.26668799219724</v>
@@ -41475,7 +41475,7 @@
         <v>-20.13364986414387</v>
       </c>
       <c r="CY79" t="n">
-        <v>1.106181554440555</v>
+        <v>1.106181446440546</v>
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
@@ -41794,25 +41794,25 @@
         <v>26.40999984741211</v>
       </c>
       <c r="CJ80" t="n">
-        <v>12.0306244249184</v>
+        <v>12.03062437526879</v>
       </c>
       <c r="CK80" t="n">
-        <v>12.63784574728765</v>
+        <v>12.63784572456727</v>
       </c>
       <c r="CL80" t="n">
-        <v>13.76140422928458</v>
+        <v>13.76140426133667</v>
       </c>
       <c r="CM80" t="n">
         <v>32.21690097207528</v>
       </c>
       <c r="CN80" t="n">
-        <v>12.78505274084192</v>
+        <v>12.78505274310483</v>
       </c>
       <c r="CO80" t="n">
-        <v>24.65491712204005</v>
+        <v>24.65491712879319</v>
       </c>
       <c r="CP80" t="n">
-        <v>5.58374478404144</v>
+        <v>5.583744815805273</v>
       </c>
       <c r="CQ80" t="n">
         <v>60.10895866204905</v>
@@ -42140,10 +42140,10 @@
         <v>10.42000007629395</v>
       </c>
       <c r="CJ81" t="n">
-        <v>6.386823413548832</v>
+        <v>6.386823451454461</v>
       </c>
       <c r="CK81" t="n">
-        <v>11.84755743213308</v>
+        <v>11.84755750244802</v>
       </c>
       <c r="CL81" t="n">
         <v>7.980635896583511</v>
@@ -42164,7 +42164,7 @@
         <v>39.24041441528669</v>
       </c>
       <c r="CR81" t="n">
-        <v>10.25521141598726</v>
+        <v>10.25521143144734</v>
       </c>
       <c r="CS81" t="n">
         <v>7.980635896583511</v>
@@ -42185,7 +42185,7 @@
         <v>-31.06936416184972</v>
       </c>
       <c r="CY81" t="n">
-        <v>-1.581465058542453</v>
+        <v>-1.581464910173147</v>
       </c>
       <c r="CZ81" t="inlineStr">
         <is>
@@ -42496,10 +42496,10 @@
         <v>6.909999847412109</v>
       </c>
       <c r="CJ82" t="n">
-        <v>1.245705646893949</v>
+        <v>1.245705649383535</v>
       </c>
       <c r="CK82" t="n">
-        <v>2.310783974988275</v>
+        <v>2.310783979606457</v>
       </c>
       <c r="CL82" t="n">
         <v>9.844892255721552</v>
@@ -42508,13 +42508,13 @@
         <v>9.691148910902541</v>
       </c>
       <c r="CN82" t="n">
-        <v>9.426422451633274</v>
+        <v>9.426422450752398</v>
       </c>
       <c r="CO82" t="n">
-        <v>1.870915582792464</v>
+        <v>1.870915582686666</v>
       </c>
       <c r="CP82" t="n">
-        <v>6.731347711501887</v>
+        <v>6.731347708592457</v>
       </c>
       <c r="CQ82" t="n">
         <v>10.56671555133091</v>
@@ -43194,10 +43194,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ84" t="n">
-        <v>3.069412991811349</v>
+        <v>3.06941298712796</v>
       </c>
       <c r="CK84" t="n">
-        <v>4.469065316077325</v>
+        <v>4.46906530925831</v>
       </c>
       <c r="CL84" t="n">
         <v>4.457142906283466</v>
@@ -43894,10 +43894,10 @@
         <v>18.57999992370605</v>
       </c>
       <c r="CJ86" t="n">
-        <v>4.512852214528588</v>
+        <v>4.512852222608041</v>
       </c>
       <c r="CK86" t="n">
-        <v>8.371340857950532</v>
+        <v>8.371340872937916</v>
       </c>
       <c r="CL86" t="n">
         <v>30.43077861422808</v>
@@ -43906,13 +43906,13 @@
         <v>32.84488176258051</v>
       </c>
       <c r="CN86" t="n">
-        <v>26.12312849990618</v>
+        <v>26.12312850144557</v>
       </c>
       <c r="CO86" t="n">
-        <v>11.11283324357972</v>
+        <v>11.11283324302213</v>
       </c>
       <c r="CP86" t="n">
-        <v>17.64670994598274</v>
+        <v>17.64670993816183</v>
       </c>
       <c r="CQ86" t="n">
         <v>40.63403637942744</v>
@@ -44248,25 +44248,25 @@
         <v>1.539999961853027</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.1373663637954049</v>
+        <v>0.1373663640494014</v>
       </c>
       <c r="CK87" t="n">
-        <v>0.1568558708386782</v>
+        <v>0.1568558711179774</v>
       </c>
       <c r="CL87" t="n">
-        <v>0.7489968440166799</v>
+        <v>0.7489968439654238</v>
       </c>
       <c r="CM87" t="n">
         <v>3.105192066391262</v>
       </c>
       <c r="CN87" t="n">
-        <v>0.2569714889974152</v>
+        <v>0.2569714891397609</v>
       </c>
       <c r="CO87" t="n">
-        <v>0.5416066536824292</v>
+        <v>0.5416066536783812</v>
       </c>
       <c r="CP87" t="n">
-        <v>0.3347614235198564</v>
+        <v>0.3347614234760471</v>
       </c>
       <c r="CQ87" t="inlineStr"/>
       <c r="CR87" t="inlineStr"/>
@@ -44592,10 +44592,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CJ88" t="n">
-        <v>11.99325227643426</v>
+        <v>11.9932523424147</v>
       </c>
       <c r="CK88" t="n">
-        <v>22.24748297278554</v>
+        <v>22.24748309517928</v>
       </c>
       <c r="CL88" t="n">
         <v>15.02382038547176</v>
@@ -44616,13 +44616,13 @@
         <v>22.65224107444971</v>
       </c>
       <c r="CR88" t="n">
-        <v>19.72597609750072</v>
+        <v>19.72597612104749</v>
       </c>
       <c r="CS88" t="n">
-        <v>18.63565167912865</v>
+        <v>18.63565174032552</v>
       </c>
       <c r="CT88" t="n">
-        <v>16.77208651121579</v>
+        <v>16.77208656629297</v>
       </c>
       <c r="CU88" t="n">
         <v>8</v>
@@ -44634,10 +44634,10 @@
         <v>2.9</v>
       </c>
       <c r="CX88" t="n">
-        <v>-29.52904601316598</v>
+        <v>-29.52904578174925</v>
       </c>
       <c r="CY88" t="n">
-        <v>-17.11774483259604</v>
+        <v>-17.11774473366</v>
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
@@ -44946,10 +44946,10 @@
         <v>14.02999973297119</v>
       </c>
       <c r="CJ89" t="n">
-        <v>6.056552957448704</v>
+        <v>6.056552938226275</v>
       </c>
       <c r="CK89" t="n">
-        <v>8.818341106045313</v>
+        <v>8.818341078057458</v>
       </c>
       <c r="CL89" t="n">
         <v>3.791891819721943</v>
@@ -45274,10 +45274,10 @@
         <v>56.88999938964844</v>
       </c>
       <c r="CJ90" t="n">
-        <v>11.93657435517729</v>
+        <v>11.93657439088583</v>
       </c>
       <c r="CK90" t="n">
-        <v>17.37965226113814</v>
+        <v>17.37965231312977</v>
       </c>
       <c r="CL90" t="inlineStr"/>
       <c r="CM90" t="inlineStr"/>
@@ -45288,13 +45288,13 @@
       <c r="CP90" t="inlineStr"/>
       <c r="CQ90" t="inlineStr"/>
       <c r="CR90" t="n">
-        <v>18.54797553877181</v>
+        <v>18.5479755680052</v>
       </c>
       <c r="CS90" t="n">
-        <v>17.37965226113814</v>
+        <v>17.37965231312977</v>
       </c>
       <c r="CT90" t="n">
-        <v>15.64168703502433</v>
+        <v>15.64168708181679</v>
       </c>
       <c r="CU90" t="n">
         <v>3</v>
@@ -45306,10 +45306,10 @@
         <v>2.2</v>
       </c>
       <c r="CX90" t="n">
-        <v>-72.50538371798532</v>
+        <v>-72.50538363573456</v>
       </c>
       <c r="CY90" t="n">
-        <v>-67.39677318023183</v>
+        <v>-67.39677312884601</v>
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
@@ -45628,10 +45628,10 @@
         <v>6.980000019073486</v>
       </c>
       <c r="CJ91" t="n">
-        <v>2.904946337862583</v>
+        <v>2.904946331496027</v>
       </c>
       <c r="CK91" t="n">
-        <v>5.388675456735091</v>
+        <v>5.38867544492513</v>
       </c>
       <c r="CL91" t="n">
         <v>13.62076586932602</v>
@@ -45640,23 +45640,23 @@
         <v>14.67172452167963</v>
       </c>
       <c r="CN91" t="n">
-        <v>12.87347153252058</v>
+        <v>12.87347152926946</v>
       </c>
       <c r="CO91" t="n">
-        <v>14.97590881306693</v>
+        <v>14.97590881441537</v>
       </c>
       <c r="CP91" t="n">
-        <v>7.073198852302207</v>
+        <v>7.073198858509854</v>
       </c>
       <c r="CQ91" t="inlineStr"/>
       <c r="CR91" t="n">
-        <v>11.43395750760508</v>
+        <v>11.43395750635424</v>
       </c>
       <c r="CS91" t="n">
-        <v>13.2471187009233</v>
+        <v>13.24711869929774</v>
       </c>
       <c r="CT91" t="n">
-        <v>11.92240683083097</v>
+        <v>11.92240682936797</v>
       </c>
       <c r="CU91" t="n">
         <v>6</v>
@@ -45668,10 +45668,10 @@
         <v>5.2</v>
       </c>
       <c r="CX91" t="n">
-        <v>70.8081203187952</v>
+        <v>70.8081202978353</v>
       </c>
       <c r="CY91" t="n">
-        <v>63.81027903095624</v>
+        <v>63.81027901303597</v>
       </c>
       <c r="CZ91" t="inlineStr">
         <is>
@@ -45980,10 +45980,10 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CJ92" t="n">
-        <v>4.969684097335415</v>
+        <v>4.969684062719159</v>
       </c>
       <c r="CK92" t="n">
-        <v>7.235860045720364</v>
+        <v>7.235859995319097</v>
       </c>
       <c r="CL92" t="n">
         <v>5.964932973104989</v>
@@ -46002,13 +46002,13 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CR92" t="n">
-        <v>6.64016223278468</v>
+        <v>6.640162218615093</v>
       </c>
       <c r="CS92" t="n">
-        <v>6.600396509412676</v>
+        <v>6.600396484212043</v>
       </c>
       <c r="CT92" t="n">
-        <v>5.940356858471409</v>
+        <v>5.940356835790839</v>
       </c>
       <c r="CU92" t="n">
         <v>6</v>
@@ -46020,10 +46020,10 @@
         <v>5.9</v>
       </c>
       <c r="CX92" t="n">
-        <v>-23.05237020836838</v>
+        <v>-23.05237050215816</v>
       </c>
       <c r="CY92" t="n">
-        <v>-13.98753350717595</v>
+        <v>-13.98753369071983</v>
       </c>
       <c r="CZ92" t="inlineStr">
         <is>
@@ -46336,10 +46336,10 @@
         <v>3.670000076293945</v>
       </c>
       <c r="CJ93" t="n">
-        <v>33.45871388966976</v>
+        <v>33.4587140558825</v>
       </c>
       <c r="CK93" t="n">
-        <v>62.0659142653374</v>
+        <v>62.06591457366204</v>
       </c>
       <c r="CL93" t="n">
         <v>4.702853095831215</v>
@@ -46680,10 +46680,10 @@
         <v>78.58000183105469</v>
       </c>
       <c r="CJ94" t="n">
-        <v>58.74948816122167</v>
+        <v>58.74948806819323</v>
       </c>
       <c r="CK94" t="n">
-        <v>85.53925476273876</v>
+        <v>85.53925462728935</v>
       </c>
       <c r="CL94" t="n">
         <v>24.51941251254032</v>
@@ -47028,10 +47028,10 @@
         <v>34.81000137329102</v>
       </c>
       <c r="CJ95" t="n">
-        <v>8.619676376756265</v>
+        <v>8.61967638205285</v>
       </c>
       <c r="CK95" t="n">
-        <v>15.98949967888287</v>
+        <v>15.98949968870804</v>
       </c>
       <c r="CL95" t="n">
         <v>40.07232999097358</v>
@@ -47040,19 +47040,19 @@
         <v>40.41788990153368</v>
       </c>
       <c r="CN95" t="n">
-        <v>33.44033780657554</v>
+        <v>33.44033780365254</v>
       </c>
       <c r="CO95" t="n">
-        <v>50.0492526579016</v>
+        <v>50.04925265646109</v>
       </c>
       <c r="CP95" t="n">
-        <v>22.50871824188368</v>
+        <v>22.50871823599684</v>
       </c>
       <c r="CQ95" t="n">
         <v>53.2004618761326</v>
       </c>
       <c r="CR95" t="n">
-        <v>36.52549859341194</v>
+        <v>36.52549859335119</v>
       </c>
       <c r="CS95" t="n">
         <v>40.07232999097358</v>
@@ -47073,7 +47073,7 @@
         <v>3.605560382276285</v>
       </c>
       <c r="CY95" t="n">
-        <v>4.928173376738765</v>
+        <v>4.92817337656426</v>
       </c>
       <c r="CZ95" t="inlineStr">
         <is>
@@ -47384,10 +47384,10 @@
         <v>19.60000038146973</v>
       </c>
       <c r="CJ96" t="n">
-        <v>2.023112504224832</v>
+        <v>2.0231125049518</v>
       </c>
       <c r="CK96" t="n">
-        <v>3.752873695337063</v>
+        <v>3.752873696685589</v>
       </c>
       <c r="CL96" t="n">
         <v>10.14849570357459</v>
@@ -47396,19 +47396,19 @@
         <v>8.468407387765433</v>
       </c>
       <c r="CN96" t="n">
-        <v>9.993116431142193</v>
+        <v>9.99311642966622</v>
       </c>
       <c r="CO96" t="n">
-        <v>7.537047558136668</v>
+        <v>7.537047557971457</v>
       </c>
       <c r="CP96" t="n">
-        <v>7.631782585575396</v>
+        <v>7.631782584397649</v>
       </c>
       <c r="CQ96" t="n">
         <v>13.57810210946071</v>
       </c>
       <c r="CR96" t="n">
-        <v>8.729975067284579</v>
+        <v>8.729975067074522</v>
       </c>
       <c r="CS96" t="n">
         <v>8.468407387765433</v>
@@ -47429,7 +47429,7 @@
         <v>-61.11445662932493</v>
       </c>
       <c r="CY96" t="n">
-        <v>-55.45931174808501</v>
+        <v>-55.45931174915674</v>
       </c>
       <c r="CZ96" t="inlineStr">
         <is>
@@ -47722,35 +47722,35 @@
         <v>20.17000007629395</v>
       </c>
       <c r="CJ97" t="n">
-        <v>12.02545566535981</v>
+        <v>12.02545559589612</v>
       </c>
       <c r="CK97" t="n">
-        <v>15.02693334971656</v>
+        <v>15.02693330893174</v>
       </c>
       <c r="CL97" t="n">
-        <v>21.92822736995206</v>
+        <v>21.92822743710228</v>
       </c>
       <c r="CM97" t="n">
         <v>41.10111584317051</v>
       </c>
       <c r="CN97" t="n">
-        <v>26.68409629451</v>
+        <v>26.68409625375999</v>
       </c>
       <c r="CO97" t="n">
-        <v>15.73775953044531</v>
+        <v>15.73775953530073</v>
       </c>
       <c r="CP97" t="n">
-        <v>10.44627156748584</v>
+        <v>10.44627161632715</v>
       </c>
       <c r="CQ97" t="inlineStr"/>
       <c r="CR97" t="n">
-        <v>16.17959397886844</v>
+        <v>16.17959396930772</v>
       </c>
       <c r="CS97" t="n">
-        <v>15.38234644008094</v>
+        <v>15.38234642211624</v>
       </c>
       <c r="CT97" t="n">
-        <v>13.84411179607284</v>
+        <v>13.84411177990461</v>
       </c>
       <c r="CU97" t="n">
         <v>4</v>
@@ -47762,10 +47762,10 @@
         <v>1.8</v>
       </c>
       <c r="CX97" t="n">
-        <v>-31.36285699699128</v>
+        <v>-31.36285707715107</v>
       </c>
       <c r="CY97" t="n">
-        <v>-19.78386753758858</v>
+        <v>-19.78386758498925</v>
       </c>
       <c r="CZ97" t="inlineStr">
         <is>
@@ -48092,10 +48092,10 @@
         <v>15.77000045776367</v>
       </c>
       <c r="CJ98" t="n">
-        <v>7.940764281141179</v>
+        <v>7.940764299585794</v>
       </c>
       <c r="CK98" t="n">
-        <v>14.73011774151689</v>
+        <v>14.73011777573165</v>
       </c>
       <c r="CL98" t="n">
         <v>10.12366792952367</v>
@@ -48116,7 +48116,7 @@
         <v>9.605938210417623</v>
       </c>
       <c r="CR98" t="n">
-        <v>12.14173308417069</v>
+        <v>12.14173309075311</v>
       </c>
       <c r="CS98" t="n">
         <v>9.864803069970648</v>
@@ -48137,7 +48137,7 @@
         <v>-43.70118893304959</v>
       </c>
       <c r="CY98" t="n">
-        <v>-23.00740182798639</v>
+        <v>-23.00740178624623</v>
       </c>
       <c r="CZ98" t="inlineStr">
         <is>
@@ -48456,37 +48456,37 @@
         <v>23.01000022888184</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.039638075183882</v>
+        <v>5.039638103109806</v>
       </c>
       <c r="CK99" t="n">
-        <v>7.157408893733233</v>
+        <v>7.157408899960964</v>
       </c>
       <c r="CL99" t="n">
-        <v>10.59572236982511</v>
+        <v>10.59572232033094</v>
       </c>
       <c r="CM99" t="n">
         <v>14.53384923599866</v>
       </c>
       <c r="CN99" t="n">
-        <v>7.141105327279114</v>
+        <v>7.141105299596063</v>
       </c>
       <c r="CO99" t="n">
-        <v>8.435979172568844</v>
+        <v>8.43597916903294</v>
       </c>
       <c r="CP99" t="n">
-        <v>5.265851244618263</v>
+        <v>5.26585121606233</v>
       </c>
       <c r="CQ99" t="n">
         <v>10.72346608033207</v>
       </c>
       <c r="CR99" t="n">
-        <v>8.611627549942396</v>
+        <v>8.611627540552972</v>
       </c>
       <c r="CS99" t="n">
-        <v>7.796694033151039</v>
+        <v>7.796694034496952</v>
       </c>
       <c r="CT99" t="n">
-        <v>7.017024629835935</v>
+        <v>7.017024631047256</v>
       </c>
       <c r="CU99" t="n">
         <v>8</v>
@@ -48498,10 +48498,10 @@
         <v>2.9</v>
       </c>
       <c r="CX99" t="n">
-        <v>-69.50445649701358</v>
+        <v>-69.50445649174925</v>
       </c>
       <c r="CY99" t="n">
-        <v>-62.57441345379389</v>
+        <v>-62.57441349459973</v>
       </c>
       <c r="CZ99" t="inlineStr">
         <is>
@@ -48812,10 +48812,10 @@
         <v>7.199999809265137</v>
       </c>
       <c r="CJ100" t="n">
-        <v>3.230736921033268</v>
+        <v>3.230736911355043</v>
       </c>
       <c r="CK100" t="n">
-        <v>5.993016988516711</v>
+        <v>5.993016970563604</v>
       </c>
       <c r="CL100" t="inlineStr"/>
       <c r="CM100" t="inlineStr"/>
@@ -48826,13 +48826,13 @@
         <v>9.346171559984855</v>
       </c>
       <c r="CR100" t="n">
-        <v>6.189975156511611</v>
+        <v>6.189975147301166</v>
       </c>
       <c r="CS100" t="n">
-        <v>5.993016988516711</v>
+        <v>5.993016970563604</v>
       </c>
       <c r="CT100" t="n">
-        <v>5.39371528966504</v>
+        <v>5.393715273507244</v>
       </c>
       <c r="CU100" t="n">
         <v>3</v>
@@ -48844,10 +48844,10 @@
         <v>2.9</v>
       </c>
       <c r="CX100" t="n">
-        <v>-25.0872856590319</v>
+        <v>-25.08728588344574</v>
       </c>
       <c r="CY100" t="n">
-        <v>-14.02812054875059</v>
+        <v>-14.02812067667343</v>
       </c>
       <c r="CZ100" t="inlineStr">
         <is>
@@ -49158,10 +49158,10 @@
         <v>45.29999923706055</v>
       </c>
       <c r="CJ101" t="n">
-        <v>9.911113136263427</v>
+        <v>9.911113136628117</v>
       </c>
       <c r="CK101" t="n">
-        <v>18.38511486776866</v>
+        <v>18.38511486844516</v>
       </c>
       <c r="CL101" t="n">
         <v>85.6241069744725</v>
@@ -49170,13 +49170,13 @@
         <v>75.68006991304929</v>
       </c>
       <c r="CN101" t="n">
-        <v>103.2210458236879</v>
+        <v>103.2210458235768</v>
       </c>
       <c r="CO101" t="n">
-        <v>16.15577152790574</v>
+        <v>16.15577152788715</v>
       </c>
       <c r="CP101" t="n">
-        <v>69.70318634450852</v>
+        <v>69.70318634398092</v>
       </c>
       <c r="CQ101" t="n">
         <v>21.32072017314016</v>
@@ -49516,25 +49516,25 @@
         <v>47.36999893188477</v>
       </c>
       <c r="CJ102" t="n">
-        <v>18.2068995566113</v>
+        <v>18.20689963591309</v>
       </c>
       <c r="CK102" t="n">
-        <v>19.9888094666673</v>
+        <v>19.98880950292275</v>
       </c>
       <c r="CL102" t="n">
-        <v>23.30440151445818</v>
+        <v>23.30440145522299</v>
       </c>
       <c r="CM102" t="n">
         <v>50.5405114948287</v>
       </c>
       <c r="CN102" t="n">
-        <v>19.28041172079479</v>
+        <v>19.28041170406953</v>
       </c>
       <c r="CO102" t="n">
-        <v>23.25458368483036</v>
+        <v>23.25458367814533</v>
       </c>
       <c r="CP102" t="n">
-        <v>10.00649689719172</v>
+        <v>10.00649684289855</v>
       </c>
       <c r="CQ102" t="n">
         <v>117.9256251674622</v>
@@ -49870,37 +49870,37 @@
         <v>53.11999893188477</v>
       </c>
       <c r="CJ103" t="n">
-        <v>16.2264884211855</v>
+        <v>16.22648837543075</v>
       </c>
       <c r="CK103" t="n">
-        <v>24.67943854085114</v>
+        <v>24.67943851451451</v>
       </c>
       <c r="CL103" t="n">
-        <v>44.4939309915037</v>
+        <v>44.49393106948413</v>
       </c>
       <c r="CM103" t="n">
         <v>61.84069244222911</v>
       </c>
       <c r="CN103" t="n">
-        <v>35.49872156419589</v>
+        <v>35.49872157796744</v>
       </c>
       <c r="CO103" t="n">
-        <v>26.76189246934416</v>
+        <v>26.76189247329762</v>
       </c>
       <c r="CP103" t="n">
-        <v>22.24510778176836</v>
+        <v>22.24510782146885</v>
       </c>
       <c r="CQ103" t="n">
         <v>21.78028972750627</v>
       </c>
       <c r="CR103" t="n">
-        <v>31.69082024232302</v>
+        <v>31.69082025023733</v>
       </c>
       <c r="CS103" t="n">
-        <v>25.72066550509765</v>
+        <v>25.72066549390606</v>
       </c>
       <c r="CT103" t="n">
-        <v>23.14859895458789</v>
+        <v>23.14859894451546</v>
       </c>
       <c r="CU103" t="n">
         <v>8</v>
@@ -49912,10 +49912,10 @@
         <v>3.8</v>
       </c>
       <c r="CX103" t="n">
-        <v>-56.42206434478454</v>
+        <v>-56.42206436374618</v>
       </c>
       <c r="CY103" t="n">
-        <v>-40.34107515145128</v>
+        <v>-40.34107513655234</v>
       </c>
       <c r="CZ103" t="inlineStr">
         <is>
@@ -50242,10 +50242,10 @@
         <v>11.9399995803833</v>
       </c>
       <c r="CJ104" t="n">
-        <v>2.124475143344242</v>
+        <v>2.124475142251035</v>
       </c>
       <c r="CK104" t="n">
-        <v>3.940901390903568</v>
+        <v>3.94090138887567</v>
       </c>
       <c r="CL104" t="n">
         <v>12.07671713283044</v>
@@ -50254,25 +50254,25 @@
         <v>13.36902203749528</v>
       </c>
       <c r="CN104" t="n">
-        <v>8.68698047000683</v>
+        <v>8.686980470437879</v>
       </c>
       <c r="CO104" t="n">
-        <v>5.73676927720083</v>
+        <v>5.736769277294875</v>
       </c>
       <c r="CP104" t="n">
-        <v>6.468133888924277</v>
+        <v>6.468133889929589</v>
       </c>
       <c r="CQ104" t="n">
         <v>11.9399995803833</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.888360539677789</v>
+        <v>8.888360539606719</v>
       </c>
       <c r="CS104" t="n">
-        <v>8.68698047000683</v>
+        <v>8.686980470437879</v>
       </c>
       <c r="CT104" t="n">
-        <v>7.818282423006147</v>
+        <v>7.818282423394091</v>
       </c>
       <c r="CU104" t="n">
         <v>7</v>
@@ -50284,10 +50284,10 @@
         <v>6.3</v>
       </c>
       <c r="CX104" t="n">
-        <v>-34.52024541231044</v>
+        <v>-34.52024540906133</v>
       </c>
       <c r="CY104" t="n">
-        <v>-25.5581168170154</v>
+        <v>-25.55811681761062</v>
       </c>
       <c r="CZ104" t="inlineStr">
         <is>
@@ -50598,10 +50598,10 @@
         <v>2.990000009536743</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.6261539976981418</v>
+        <v>0.6261539968435469</v>
       </c>
       <c r="CK105" t="n">
-        <v>1.161515665730053</v>
+        <v>1.161515664144779</v>
       </c>
       <c r="CL105" t="n">
         <v>3.424157314292294</v>
@@ -50610,13 +50610,13 @@
         <v>3.957621711457321</v>
       </c>
       <c r="CN105" t="n">
-        <v>2.391887522029286</v>
+        <v>2.39188752214019</v>
       </c>
       <c r="CO105" t="n">
-        <v>2.635932104696672</v>
+        <v>2.635932104806514</v>
       </c>
       <c r="CP105" t="n">
-        <v>1.717596294500536</v>
+        <v>1.717596295220242</v>
       </c>
       <c r="CQ105" t="n">
         <v>9.031114164496099</v>
@@ -50942,10 +50942,10 @@
         <v>55.43999862670898</v>
       </c>
       <c r="CJ106" t="n">
-        <v>62.75021531380185</v>
+        <v>62.75021551388411</v>
       </c>
       <c r="CK106" t="n">
-        <v>91.36431349689549</v>
+        <v>91.36431378821527</v>
       </c>
       <c r="CL106" t="n">
         <v>24.25645711896397</v>
@@ -51284,10 +51284,10 @@
         <v>6.489999771118164</v>
       </c>
       <c r="CJ107" t="n">
-        <v>0.06255174980550408</v>
+        <v>0.06255174950368395</v>
       </c>
       <c r="CK107" t="n">
-        <v>0.1160334958892101</v>
+        <v>0.1160334953293337</v>
       </c>
       <c r="CL107" t="inlineStr"/>
       <c r="CM107" t="inlineStr"/>
@@ -51626,10 +51626,10 @@
         <v>93.48999786376953</v>
       </c>
       <c r="CJ108" t="n">
-        <v>4.770651220748134</v>
+        <v>4.770651246602801</v>
       </c>
       <c r="CK108" t="n">
-        <v>8.849558014487791</v>
+        <v>8.849558062448196</v>
       </c>
       <c r="CL108" t="n">
         <v>41.68043309875323</v>
@@ -51638,13 +51638,13 @@
         <v>41.35009616132553</v>
       </c>
       <c r="CN108" t="n">
-        <v>34.4834811322802</v>
+        <v>34.4834810973677</v>
       </c>
       <c r="CO108" t="n">
-        <v>17.71052555145224</v>
+        <v>17.71052554904738</v>
       </c>
       <c r="CP108" t="n">
-        <v>28.66625026706606</v>
+        <v>28.66625023746557</v>
       </c>
       <c r="CQ108" t="n">
         <v>43.17568011524377</v>
@@ -52644,10 +52644,10 @@
         <v>16.81999969482422</v>
       </c>
       <c r="CJ111" t="n">
-        <v>3.158272786284772</v>
+        <v>3.158272795064714</v>
       </c>
       <c r="CK111" t="n">
-        <v>5.858596018558251</v>
+        <v>5.858596034845045</v>
       </c>
       <c r="CL111" t="n">
         <v>14.7690520845872</v>
@@ -52656,23 +52656,23 @@
         <v>15.75245189589746</v>
       </c>
       <c r="CN111" t="n">
-        <v>10.52924635266081</v>
+        <v>10.52924634691668</v>
       </c>
       <c r="CO111" t="n">
-        <v>13.03158635132297</v>
+        <v>13.03158634980271</v>
       </c>
       <c r="CP111" t="n">
-        <v>7.754276545388036</v>
+        <v>7.754276536657259</v>
       </c>
       <c r="CQ111" t="inlineStr"/>
       <c r="CR111" t="n">
-        <v>11.28253487473579</v>
+        <v>11.28253487478439</v>
       </c>
       <c r="CS111" t="n">
-        <v>11.78041635199189</v>
+        <v>11.7804163483597</v>
       </c>
       <c r="CT111" t="n">
-        <v>10.6023747167927</v>
+        <v>10.60237471352373</v>
       </c>
       <c r="CU111" t="n">
         <v>6</v>
@@ -52684,10 +52684,10 @@
         <v>5</v>
       </c>
       <c r="CX111" t="n">
-        <v>-36.9656664140415</v>
+        <v>-36.96566643347654</v>
       </c>
       <c r="CY111" t="n">
-        <v>-32.92190797002451</v>
+        <v>-32.92190796973552</v>
       </c>
       <c r="CZ111" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
         <v>14.85999965667725</v>
       </c>
       <c r="CJ112" t="n">
-        <v>3.752078042790786</v>
+        <v>3.752078040089657</v>
       </c>
       <c r="CK112" t="n">
-        <v>4.765173627644832</v>
+        <v>4.765173624668306</v>
       </c>
       <c r="CL112" t="n">
-        <v>14.23467812108693</v>
+        <v>14.23467812244294</v>
       </c>
       <c r="CM112" t="n">
         <v>37.15722486020687</v>
       </c>
       <c r="CN112" t="n">
-        <v>9.753710220367291</v>
+        <v>9.753710217898046</v>
       </c>
       <c r="CO112" t="n">
-        <v>49.08124933659791</v>
+        <v>49.08124933706215</v>
       </c>
       <c r="CP112" t="n">
-        <v>6.836198274343285</v>
+        <v>6.836198275301213</v>
       </c>
       <c r="CQ112" t="n">
         <v>26.75481109869832</v>
@@ -53690,10 +53690,10 @@
         <v>18.29999923706055</v>
       </c>
       <c r="CJ114" t="n">
-        <v>11.70299356891736</v>
+        <v>11.70299357599525</v>
       </c>
       <c r="CK114" t="n">
-        <v>14.60330067077949</v>
+        <v>14.60330067961146</v>
       </c>
       <c r="CL114" t="inlineStr"/>
       <c r="CM114" t="inlineStr"/>
@@ -54028,10 +54028,10 @@
         <v>11.22000026702881</v>
       </c>
       <c r="CJ115" t="n">
-        <v>2.438138895589552</v>
+        <v>2.438138897667095</v>
       </c>
       <c r="CK115" t="n">
-        <v>4.522747651318619</v>
+        <v>4.52274765517246</v>
       </c>
       <c r="CL115" t="n">
         <v>12.15576480279082</v>
@@ -54040,13 +54040,13 @@
         <v>12.68205556729091</v>
       </c>
       <c r="CN115" t="n">
-        <v>9.594467796954879</v>
+        <v>9.594467795898089</v>
       </c>
       <c r="CO115" t="n">
-        <v>0.7922280655901908</v>
+        <v>0.7922280655625757</v>
       </c>
       <c r="CP115" t="n">
-        <v>6.727276604542205</v>
+        <v>6.727276602383058</v>
       </c>
       <c r="CQ115" t="n">
         <v>7.245675643801825</v>
@@ -54374,25 +54374,25 @@
         <v>8.840000152587891</v>
       </c>
       <c r="CJ116" t="n">
-        <v>2.273351429613759</v>
+        <v>2.273351428656042</v>
       </c>
       <c r="CK116" t="n">
-        <v>2.459392458998841</v>
+        <v>2.459392458227228</v>
       </c>
       <c r="CL116" t="n">
-        <v>3.240521374034079</v>
+        <v>3.24052137438256</v>
       </c>
       <c r="CM116" t="n">
         <v>10.0855898347917</v>
       </c>
       <c r="CN116" t="n">
-        <v>1.903039102142002</v>
+        <v>1.903039102027519</v>
       </c>
       <c r="CO116" t="n">
-        <v>5.908796683911463</v>
+        <v>5.908796683984271</v>
       </c>
       <c r="CP116" t="n">
-        <v>1.367445361826111</v>
+        <v>1.367445362153957</v>
       </c>
       <c r="CQ116" t="n">
         <v>14.58705591648655</v>
@@ -54732,10 +54732,10 @@
         <v>4.829999923706055</v>
       </c>
       <c r="CJ117" t="n">
-        <v>1.485870067911941</v>
+        <v>1.485870076719454</v>
       </c>
       <c r="CK117" t="n">
-        <v>1.548606804112668</v>
+        <v>1.548606813292053</v>
       </c>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
@@ -55068,10 +55068,10 @@
         <v>3.359999895095825</v>
       </c>
       <c r="CJ118" t="n">
-        <v>1.655532338322624</v>
+        <v>1.655532339525894</v>
       </c>
       <c r="CK118" t="n">
-        <v>3.071012487588468</v>
+        <v>3.071012489820533</v>
       </c>
       <c r="CL118" t="n">
         <v>1.185934965637178</v>
@@ -55080,7 +55080,7 @@
         <v>4.749225176208076</v>
       </c>
       <c r="CN118" t="n">
-        <v>1.64670888465953</v>
+        <v>1.646708885108271</v>
       </c>
       <c r="CO118" t="n">
         <v>0.7445919647652398</v>
@@ -55414,10 +55414,10 @@
         <v>6.599999904632568</v>
       </c>
       <c r="CJ119" t="n">
-        <v>1.062191980375533</v>
+        <v>1.062191983107449</v>
       </c>
       <c r="CK119" t="n">
-        <v>1.970366123596613</v>
+        <v>1.970366128664318</v>
       </c>
       <c r="CL119" t="inlineStr"/>
       <c r="CM119" t="inlineStr"/>
@@ -55750,25 +55750,25 @@
         <v>3.650000095367432</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.25101390315633</v>
+        <v>1.251013902380214</v>
       </c>
       <c r="CK120" t="n">
-        <v>1.269554588372241</v>
+        <v>1.269554587865452</v>
       </c>
       <c r="CL120" t="n">
-        <v>1.322229963589837</v>
+        <v>1.322229963882319</v>
       </c>
       <c r="CM120" t="n">
         <v>4.079804341937684</v>
       </c>
       <c r="CN120" t="n">
-        <v>0.908045607368969</v>
+        <v>0.9080456073159989</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.169845198345659</v>
+        <v>2.169845198403848</v>
       </c>
       <c r="CP120" t="n">
-        <v>0.5078925737426611</v>
+        <v>0.5078925740506862</v>
       </c>
       <c r="CQ120" t="n">
         <v>5.283509282575594</v>
@@ -56100,10 +56100,10 @@
         <v>5.5</v>
       </c>
       <c r="CJ121" t="n">
-        <v>5.453484852396258</v>
+        <v>5.453484861815507</v>
       </c>
       <c r="CK121" t="n">
-        <v>7.940273945088953</v>
+        <v>7.940273958803379</v>
       </c>
       <c r="CL121" t="inlineStr"/>
       <c r="CM121" t="inlineStr"/>
@@ -56112,13 +56112,13 @@
       <c r="CP121" t="inlineStr"/>
       <c r="CQ121" t="inlineStr"/>
       <c r="CR121" t="n">
-        <v>6.696879398742606</v>
+        <v>6.696879410309443</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.696879398742606</v>
+        <v>6.696879410309443</v>
       </c>
       <c r="CT121" t="n">
-        <v>6.027191458868345</v>
+        <v>6.027191469278499</v>
       </c>
       <c r="CU121" t="n">
         <v>2</v>
@@ -56130,10 +56130,10 @@
         <v>1.5</v>
       </c>
       <c r="CX121" t="n">
-        <v>9.585299252151724</v>
+        <v>9.585299441427253</v>
       </c>
       <c r="CY121" t="n">
-        <v>21.76144361350192</v>
+        <v>21.76144382380807</v>
       </c>
       <c r="CZ121" t="inlineStr">
         <is>
@@ -56444,10 +56444,10 @@
         <v>5.320000171661377</v>
       </c>
       <c r="CJ122" t="n">
-        <v>5.856172596181932</v>
+        <v>5.856172610805581</v>
       </c>
       <c r="CK122" t="n">
-        <v>10.44092073232533</v>
+        <v>10.44092075839771</v>
       </c>
       <c r="CL122" t="inlineStr"/>
       <c r="CM122" t="inlineStr"/>
@@ -56456,13 +56456,13 @@
       <c r="CP122" t="inlineStr"/>
       <c r="CQ122" t="inlineStr"/>
       <c r="CR122" t="n">
-        <v>8.14854666425363</v>
+        <v>8.148546684601644</v>
       </c>
       <c r="CS122" t="n">
-        <v>8.14854666425363</v>
+        <v>8.148546684601644</v>
       </c>
       <c r="CT122" t="n">
-        <v>7.333691997828267</v>
+        <v>7.33369201614148</v>
       </c>
       <c r="CU122" t="n">
         <v>2</v>
@@ -56474,10 +56474,10 @@
         <v>1.8</v>
       </c>
       <c r="CX122" t="n">
-        <v>37.85134889456285</v>
+        <v>37.85134923879616</v>
       </c>
       <c r="CY122" t="n">
-        <v>53.16816543840315</v>
+        <v>53.16816582088462</v>
       </c>
       <c r="CZ122" t="inlineStr">
         <is>
@@ -56782,10 +56782,10 @@
         <v>22</v>
       </c>
       <c r="CJ123" t="n">
-        <v>38.19068415585433</v>
+        <v>38.19068408430406</v>
       </c>
       <c r="CK123" t="n">
-        <v>70.84371910910978</v>
+        <v>70.84371897638403</v>
       </c>
       <c r="CL123" t="n">
         <v>19.69594594594594</v>
@@ -56804,7 +56804,7 @@
       </c>
       <c r="CQ123" t="inlineStr"/>
       <c r="CR123" t="n">
-        <v>25.80022402959661</v>
+        <v>25.80022401767156</v>
       </c>
       <c r="CS123" t="n">
         <v>22.95973920566808</v>
@@ -56825,7 +56825,7 @@
         <v>-6.073794158630585</v>
       </c>
       <c r="CY123" t="n">
-        <v>17.27374558907549</v>
+        <v>17.27374553487076</v>
       </c>
       <c r="CZ123" t="inlineStr">
         <is>
@@ -57136,25 +57136,25 @@
         <v>9.079999923706055</v>
       </c>
       <c r="CJ124" t="n">
-        <v>3.508565492363704</v>
+        <v>3.508565476378518</v>
       </c>
       <c r="CK124" t="n">
-        <v>3.620356138614594</v>
+        <v>3.62035612466373</v>
       </c>
       <c r="CL124" t="n">
-        <v>4.36553386312371</v>
+        <v>4.365533866190914</v>
       </c>
       <c r="CM124" t="n">
         <v>18.86542389459268</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.429630205727388</v>
+        <v>3.429630196119621</v>
       </c>
       <c r="CO124" t="n">
-        <v>7.741903460081911</v>
+        <v>7.741903460731747</v>
       </c>
       <c r="CP124" t="n">
-        <v>1.724012495391137</v>
+        <v>1.724012498528069</v>
       </c>
       <c r="CQ124" t="n">
         <v>21.8229114254654</v>
@@ -57482,10 +57482,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.7838805201187189</v>
+        <v>0.7838805198043993</v>
       </c>
       <c r="CK125" t="n">
-        <v>1.454098364820223</v>
+        <v>1.454098364237161</v>
       </c>
       <c r="CL125" t="n">
         <v>15.56199010537595</v>
@@ -57494,13 +57494,13 @@
         <v>16.26314871365512</v>
       </c>
       <c r="CN125" t="n">
-        <v>13.64124870079006</v>
+        <v>13.64124870085852</v>
       </c>
       <c r="CO125" t="n">
-        <v>1.677467519637728</v>
+        <v>1.677467519644407</v>
       </c>
       <c r="CP125" t="n">
-        <v>11.00817213147004</v>
+        <v>11.00817213179532</v>
       </c>
       <c r="CQ125" t="inlineStr"/>
       <c r="CR125" t="inlineStr"/>
@@ -58160,25 +58160,25 @@
         <v>18.60000038146973</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.641232840839856</v>
+        <v>0.6412328433588004</v>
       </c>
       <c r="CK127" t="n">
-        <v>0.8549921540839575</v>
+        <v>0.8549921571882522</v>
       </c>
       <c r="CL127" t="n">
-        <v>4.502948028937472</v>
+        <v>4.502948027597863</v>
       </c>
       <c r="CM127" t="n">
         <v>11.33513440194061</v>
       </c>
       <c r="CN127" t="n">
-        <v>1.725838692067746</v>
+        <v>1.725838691585297</v>
       </c>
       <c r="CO127" t="n">
-        <v>0.673706502869484</v>
+        <v>0.6737065028504394</v>
       </c>
       <c r="CP127" t="n">
-        <v>2.204429654949188</v>
+        <v>2.204429654082469</v>
       </c>
       <c r="CQ127" t="n">
         <v>18.60000038146973</v>
@@ -58514,10 +58514,10 @@
         <v>5.199999809265137</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.285816874815919</v>
+        <v>1.285816877554555</v>
       </c>
       <c r="CK128" t="n">
-        <v>2.151989878669188</v>
+        <v>2.151989883252669</v>
       </c>
       <c r="CL128" t="inlineStr"/>
       <c r="CM128" t="inlineStr"/>
@@ -58528,13 +58528,13 @@
         <v>5.739109502577318</v>
       </c>
       <c r="CR128" t="n">
-        <v>1.718903376742553</v>
+        <v>1.718903380403612</v>
       </c>
       <c r="CS128" t="n">
-        <v>1.718903376742553</v>
+        <v>1.718903380403612</v>
       </c>
       <c r="CT128" t="n">
-        <v>1.547013039068298</v>
+        <v>1.547013042363251</v>
       </c>
       <c r="CU128" t="n">
         <v>2</v>
@@ -58546,10 +58546,10 @@
         <v>4.5</v>
       </c>
       <c r="CX128" t="n">
-        <v>-70.24974815745384</v>
+        <v>-70.24974809408936</v>
       </c>
       <c r="CY128" t="n">
-        <v>-66.94416461939316</v>
+        <v>-66.94416454898817</v>
       </c>
       <c r="CZ128" t="inlineStr">
         <is>
@@ -58856,10 +58856,10 @@
         <v>17.1299991607666</v>
       </c>
       <c r="CJ129" t="n">
-        <v>1.320220912501634</v>
+        <v>1.320220912227982</v>
       </c>
       <c r="CK129" t="n">
-        <v>1.922241648602379</v>
+        <v>1.922241648203942</v>
       </c>
       <c r="CL129" t="n">
         <v>1.219133588393709</v>
@@ -59198,37 +59198,37 @@
         <v>17.65999984741211</v>
       </c>
       <c r="CJ130" t="n">
-        <v>2.127790691837735</v>
+        <v>2.127790684215423</v>
       </c>
       <c r="CK130" t="n">
-        <v>3.759843136869673</v>
+        <v>3.759843129547795</v>
       </c>
       <c r="CL130" t="n">
-        <v>9.741985105304664</v>
+        <v>9.741985121231609</v>
       </c>
       <c r="CM130" t="n">
         <v>12.08493439512116</v>
       </c>
       <c r="CN130" t="n">
-        <v>5.648205434228563</v>
+        <v>5.648205439350086</v>
       </c>
       <c r="CO130" t="n">
-        <v>5.613969606428337</v>
+        <v>5.613969607102133</v>
       </c>
       <c r="CP130" t="n">
-        <v>4.793870054970404</v>
+        <v>4.793870061121305</v>
       </c>
       <c r="CQ130" t="n">
         <v>16.0617953943026</v>
       </c>
       <c r="CR130" t="n">
-        <v>6.940467955487133</v>
+        <v>6.940467958912347</v>
       </c>
       <c r="CS130" t="n">
-        <v>5.63108752032845</v>
+        <v>5.63108752322611</v>
       </c>
       <c r="CT130" t="n">
-        <v>5.067978768295605</v>
+        <v>5.067978770903498</v>
       </c>
       <c r="CU130" t="n">
         <v>6</v>
@@ -59240,10 +59240,10 @@
         <v>7.5</v>
       </c>
       <c r="CX130" t="n">
-        <v>-71.302498232817</v>
+        <v>-71.30249821804978</v>
       </c>
       <c r="CY130" t="n">
-        <v>-60.69950161124047</v>
+        <v>-60.69950159184514</v>
       </c>
       <c r="CZ130" t="inlineStr">
         <is>
@@ -59546,10 +59546,10 @@
         <v>4.309999942779541</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.905981351483423</v>
+        <v>0.9059813508621624</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.68059540700175</v>
+        <v>1.680595405849311</v>
       </c>
       <c r="CL131" t="inlineStr"/>
       <c r="CM131" t="inlineStr"/>
@@ -59558,13 +59558,13 @@
       <c r="CP131" t="inlineStr"/>
       <c r="CQ131" t="inlineStr"/>
       <c r="CR131" t="n">
-        <v>1.293288379242586</v>
+        <v>1.293288378355737</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.293288379242586</v>
+        <v>1.293288378355737</v>
       </c>
       <c r="CT131" t="n">
-        <v>1.163959541318328</v>
+        <v>1.163959540520163</v>
       </c>
       <c r="CU131" t="n">
         <v>2</v>
@@ -59576,10 +59576,10 @@
         <v>1.9</v>
       </c>
       <c r="CX131" t="n">
-        <v>-72.99397780113</v>
+        <v>-72.99397781964889</v>
       </c>
       <c r="CY131" t="n">
-        <v>-69.99330866792222</v>
+        <v>-69.99330868849877</v>
       </c>
       <c r="CZ131" t="inlineStr">
         <is>
@@ -59892,10 +59892,10 @@
         <v>1.169999957084656</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.3441507057735512</v>
+        <v>0.3441507059227179</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.6383995592099375</v>
+        <v>0.6383995594866416</v>
       </c>
       <c r="CL132" t="inlineStr"/>
       <c r="CM132" t="inlineStr"/>
@@ -59904,13 +59904,13 @@
       <c r="CP132" t="inlineStr"/>
       <c r="CQ132" t="inlineStr"/>
       <c r="CR132" t="n">
-        <v>0.4912751324917444</v>
+        <v>0.4912751327046798</v>
       </c>
       <c r="CS132" t="n">
-        <v>0.4912751324917444</v>
+        <v>0.4912751327046798</v>
       </c>
       <c r="CT132" t="n">
-        <v>0.44214761924257</v>
+        <v>0.4421476194342118</v>
       </c>
       <c r="CU132" t="n">
         <v>2</v>
@@ -59922,10 +59922,10 @@
         <v>1.9</v>
       </c>
       <c r="CX132" t="n">
-        <v>-62.20960380679927</v>
+        <v>-62.20960379041962</v>
       </c>
       <c r="CY132" t="n">
-        <v>-58.01067089644363</v>
+        <v>-58.01067087824403</v>
       </c>
       <c r="CZ132" t="inlineStr">
         <is>
@@ -60576,10 +60576,10 @@
         <v>36.66999816894531</v>
       </c>
       <c r="CJ134" t="n">
-        <v>8.259335386625484</v>
+        <v>8.259335362740455</v>
       </c>
       <c r="CK134" t="n">
-        <v>12.02559232292671</v>
+        <v>12.0255922881501</v>
       </c>
       <c r="CL134" t="n">
         <v>7.913840650695814</v>
@@ -60918,10 +60918,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ135" t="n">
-        <v>0.9904024027729145</v>
+        <v>0.9904024025802123</v>
       </c>
       <c r="CK135" t="n">
-        <v>1.837196457143756</v>
+        <v>1.837196456786294</v>
       </c>
       <c r="CL135" t="inlineStr"/>
       <c r="CM135" t="inlineStr"/>
@@ -60932,13 +60932,13 @@
         <v>2.84152338750234</v>
       </c>
       <c r="CR135" t="n">
-        <v>1.889707415806337</v>
+        <v>1.889707415622949</v>
       </c>
       <c r="CS135" t="n">
-        <v>1.837196457143756</v>
+        <v>1.837196456786294</v>
       </c>
       <c r="CT135" t="n">
-        <v>1.653476811429381</v>
+        <v>1.653476811107664</v>
       </c>
       <c r="CU135" t="n">
         <v>3</v>
@@ -60950,10 +60950,10 @@
         <v>2.9</v>
       </c>
       <c r="CX135" t="n">
-        <v>-68.14110225048992</v>
+        <v>-68.1411022566887</v>
       </c>
       <c r="CY135" t="n">
-        <v>-63.58945289071185</v>
+        <v>-63.58945289424535</v>
       </c>
       <c r="CZ135" t="inlineStr">
         <is>
@@ -61272,25 +61272,25 @@
         <v>4.949999809265137</v>
       </c>
       <c r="CJ136" t="n">
-        <v>1.537094634273867</v>
+        <v>1.53709464273051</v>
       </c>
       <c r="CK136" t="n">
-        <v>1.688537256174416</v>
+        <v>1.688537263370283</v>
       </c>
       <c r="CL136" t="n">
-        <v>2.418475245444214</v>
+        <v>2.418475242445044</v>
       </c>
       <c r="CM136" t="n">
         <v>7.627771328933809</v>
       </c>
       <c r="CN136" t="n">
-        <v>1.683198691263043</v>
+        <v>1.683198694266259</v>
       </c>
       <c r="CO136" t="n">
-        <v>1.780877327152923</v>
+        <v>1.780877326903282</v>
       </c>
       <c r="CP136" t="n">
-        <v>1.039152457582277</v>
+        <v>1.039152454836235</v>
       </c>
       <c r="CQ136" t="n">
         <v>0.3242832207911349</v>
@@ -61616,10 +61616,10 @@
         <v>2.150000095367432</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.6036238981680291</v>
+        <v>0.6036239000816457</v>
       </c>
       <c r="CK137" t="n">
-        <v>0.8788763957326503</v>
+        <v>0.8788763985188763</v>
       </c>
       <c r="CL137" t="n">
         <v>0.3524590320274478</v>
@@ -61682,7 +61682,7 @@
         <v>-3.153150105435787</v>
       </c>
       <c r="DL137" t="n">
-        <v>-49.46447165359152</v>
+        <v>-49.46447734414618</v>
       </c>
       <c r="DM137" t="b">
         <v>0</v>
@@ -62274,10 +62274,10 @@
         <v>6.900000095367432</v>
       </c>
       <c r="CJ139" t="n">
-        <v>1.893532152103147</v>
+        <v>1.893532161321219</v>
       </c>
       <c r="CK139" t="n">
-        <v>2.756982813462183</v>
+        <v>2.756982826883696</v>
       </c>
       <c r="CL139" t="n">
         <v>1.700071096702708</v>
@@ -63274,10 +63274,10 @@
         <v>18.26000022888184</v>
       </c>
       <c r="CJ142" t="n">
-        <v>27.71516699324949</v>
+        <v>27.71516713193429</v>
       </c>
       <c r="CK142" t="n">
-        <v>37.07673451096932</v>
+        <v>37.07673469649876</v>
       </c>
       <c r="CL142" t="n">
         <v>2.525466010009227</v>
@@ -63286,7 +63286,7 @@
         <v>7.009520407943455</v>
       </c>
       <c r="CN142" t="n">
-        <v>6.461779398435588</v>
+        <v>6.461779426537877</v>
       </c>
       <c r="CO142" t="n">
         <v>3.155500877947406</v>
@@ -64306,10 +64306,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ145" t="n">
-        <v>9.566327443060169</v>
+        <v>9.566327508601873</v>
       </c>
       <c r="CK145" t="n">
-        <v>13.92857275709561</v>
+        <v>13.92857285252433</v>
       </c>
       <c r="CL145" t="n">
         <v>4.670347661304791</v>
@@ -65338,10 +65338,10 @@
         <v>11.1899995803833</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.978835445703428</v>
+        <v>5.978835451916871</v>
       </c>
       <c r="CK148" t="n">
-        <v>10.94348324913568</v>
+        <v>10.94348326050858</v>
       </c>
       <c r="CL148" t="inlineStr"/>
       <c r="CM148" t="inlineStr"/>
@@ -65352,13 +65352,13 @@
         <v>3.360116783680318</v>
       </c>
       <c r="CR148" t="n">
-        <v>6.760811826173142</v>
+        <v>6.760811832035258</v>
       </c>
       <c r="CS148" t="n">
-        <v>5.978835445703428</v>
+        <v>5.978835451916871</v>
       </c>
       <c r="CT148" t="n">
-        <v>5.380951901133085</v>
+        <v>5.380951906725184</v>
       </c>
       <c r="CU148" t="n">
         <v>3</v>
@@ -65370,10 +65370,10 @@
         <v>3.3</v>
       </c>
       <c r="CX148" t="n">
-        <v>-51.91284983990351</v>
+        <v>-51.91284978992942</v>
       </c>
       <c r="CY148" t="n">
-        <v>-39.58166148616103</v>
+        <v>-39.58166143377394</v>
       </c>
       <c r="CZ148" t="inlineStr">
         <is>
@@ -66030,10 +66030,10 @@
         <v>15.25</v>
       </c>
       <c r="CJ150" t="n">
-        <v>3.902183816680577</v>
+        <v>3.902183831070954</v>
       </c>
       <c r="CK150" t="n">
-        <v>5.68157963708692</v>
+        <v>5.681579658039309</v>
       </c>
       <c r="CL150" t="inlineStr"/>
       <c r="CM150" t="inlineStr"/>
@@ -66044,7 +66044,7 @@
         <v>5.478426920725005</v>
       </c>
       <c r="CR150" t="n">
-        <v>5.020730124830834</v>
+        <v>5.020730136611757</v>
       </c>
       <c r="CS150" t="n">
         <v>5.478426920725005</v>
@@ -66065,7 +66065,7 @@
         <v>-67.66830013998357</v>
       </c>
       <c r="CY150" t="n">
-        <v>-67.07717950930601</v>
+        <v>-67.07717943205405</v>
       </c>
       <c r="CZ150" t="inlineStr">
         <is>

--- a/reports/screener_2026-09-01.xlsx
+++ b/reports/screener_2026-09-01.xlsx
@@ -1278,10 +1278,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.8063891607569</v>
+        <v>5.806389198829497</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085189320405</v>
+        <v>10.77085196382872</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -1290,7 +1290,7 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.98631681410043</v>
+        <v>66.98631696639082</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -1352,7 +1352,7 @@
         <v>-4.990758938380024</v>
       </c>
       <c r="DL2" t="n">
-        <v>-27.36880243865982</v>
+        <v>-27.36880747332325</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -1628,10 +1628,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958273885434</v>
+        <v>14.76958263089643</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.3975759805748</v>
+        <v>27.39757578031287</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -1640,13 +1640,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097364566313</v>
+        <v>74.51097384699619</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789228578153</v>
+        <v>48.477892365896</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.35679553710962</v>
+        <v>26.35679587019002</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -1978,10 +1978,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247028405236</v>
+        <v>16.22247028274917</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268237691713</v>
+        <v>30.09268237449971</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -1990,19 +1990,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726851971</v>
+        <v>125.5537726856353</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311266156</v>
+        <v>25.70896311284811</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944659111422</v>
+        <v>61.89944659391013</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.177449121741</v>
+        <v>47.17744912183517</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -2023,7 +2023,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479611293551</v>
+        <v>92.9547961133207</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224611126729</v>
+        <v>3.770224622535882</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.993766653640082</v>
+        <v>6.99376667480406</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -2348,25 +2348,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502458100001</v>
+        <v>25.12502457334809</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762961229</v>
+        <v>11.21765762501402</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.59486135807276</v>
+        <v>10.59486132963933</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533152923372</v>
+        <v>9.312533150945416</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802540729397</v>
+        <v>9.65580252651268</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222286656457</v>
+        <v>8.690222273861412</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -2378,10 +2378,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029418543193</v>
+        <v>109.4029415460049</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.398384070371</v>
+        <v>124.3983840227094</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>0.7281604524675522</v>
       </c>
       <c r="DL5" t="n">
-        <v>-36.46408229840906</v>
+        <v>-36.46407744847748</v>
       </c>
       <c r="DM5" t="b">
         <v>1</v>
@@ -2696,10 +2696,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933208520007</v>
+        <v>3.224933215410524</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251101804613</v>
+        <v>5.982251114586521</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -2708,7 +2708,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385721914613</v>
+        <v>24.33385724020884</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -2720,7 +2720,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929365126752</v>
+        <v>11.46929365610247</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -2741,7 +2741,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862772238733</v>
+        <v>159.4862773332613</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418020062737</v>
+        <v>18.62418025977003</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785427216376</v>
+        <v>34.54785438187341</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -3058,23 +3058,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694234128933</v>
+        <v>100.3694233199457</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.8454123533156</v>
+        <v>48.35621745306714</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710164661773</v>
+        <v>59.21710152774573</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.05597279385169</v>
+        <v>44.18367411100265</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.19663331273968</v>
+        <v>41.45203591747027</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.07696998146571</v>
+        <v>37.30683232572324</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -3086,10 +3086,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.13142870507576</v>
+        <v>-23.66107398995101</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.850677804889852</v>
+        <v>-9.589369599565456</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="AW8" t="n">
-        <v>3586087168</v>
+        <v>3586845440</v>
       </c>
       <c r="AX8" t="n">
         <v>8.210000000000001</v>
@@ -3404,10 +3404,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.401689196500936</v>
+        <v>6.401689197981169</v>
       </c>
       <c r="CK8" t="n">
-        <v>11.87513345950924</v>
+        <v>11.87513346225507</v>
       </c>
       <c r="CL8" t="n">
         <v>25.33800212822936</v>
@@ -3416,19 +3416,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN8" t="n">
-        <v>35.10892155998621</v>
+        <v>35.10892155757615</v>
       </c>
       <c r="CO8" t="n">
-        <v>12.29620298348503</v>
+        <v>12.29620298320339</v>
       </c>
       <c r="CP8" t="n">
-        <v>20.31530580062193</v>
+        <v>20.31530579752043</v>
       </c>
       <c r="CQ8" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR8" t="n">
-        <v>20.27452914020449</v>
+        <v>20.27452913976915</v>
       </c>
       <c r="CS8" t="n">
         <v>18.56484347595736</v>
@@ -3449,7 +3449,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY8" t="n">
-        <v>29.13712985040775</v>
+        <v>29.1371298476349</v>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ9" t="n">
-        <v>127.5892447839196</v>
+        <v>127.5892442340015</v>
       </c>
       <c r="CK9" t="n">
-        <v>236.6780490741708</v>
+        <v>236.6780480540727</v>
       </c>
       <c r="CL9" t="n">
         <v>132.6522965266787</v>
@@ -3790,13 +3790,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR9" t="n">
-        <v>139.7795670992629</v>
+        <v>139.7795669030108</v>
       </c>
       <c r="CS9" t="n">
-        <v>124.3641615607452</v>
+        <v>124.3641612857861</v>
       </c>
       <c r="CT9" t="n">
-        <v>111.9277454046706</v>
+        <v>111.9277451572075</v>
       </c>
       <c r="CU9" t="n">
         <v>8</v>
@@ -3808,10 +3808,10 @@
         <v>5.6</v>
       </c>
       <c r="CX9" t="n">
-        <v>157.0097528484488</v>
+        <v>157.0097522802211</v>
       </c>
       <c r="CY9" t="n">
-        <v>220.9634203169218</v>
+        <v>220.9634198662857</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL9" t="n">
-        <v>-8.627331177634668</v>
+        <v>-8.627323714303436</v>
       </c>
       <c r="DM9" t="b">
         <v>1</v>
@@ -4130,10 +4130,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ10" t="n">
-        <v>45.30199092173366</v>
+        <v>45.30199127084784</v>
       </c>
       <c r="CK10" t="n">
-        <v>84.03519315981595</v>
+        <v>84.03519380742274</v>
       </c>
       <c r="CL10" t="n">
         <v>67.58333047231037</v>
@@ -4154,7 +4154,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR10" t="n">
-        <v>76.94607048269363</v>
+        <v>76.94607062508236</v>
       </c>
       <c r="CS10" t="n">
         <v>67.58333047231037</v>
@@ -4175,7 +4175,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY10" t="n">
-        <v>137.195048520567</v>
+        <v>137.1950489594965</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -4498,37 +4498,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ11" t="n">
-        <v>24.216126628887</v>
+        <v>24.21612665383458</v>
       </c>
       <c r="CK11" t="n">
-        <v>32.67790267207057</v>
+        <v>32.67790248694287</v>
       </c>
       <c r="CL11" t="n">
-        <v>34.37896868019397</v>
+        <v>34.37896845001195</v>
       </c>
       <c r="CM11" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN11" t="n">
-        <v>48.80739130308112</v>
+        <v>48.8073911094512</v>
       </c>
       <c r="CO11" t="n">
-        <v>50.94836393549667</v>
+        <v>50.66919478615361</v>
       </c>
       <c r="CP11" t="n">
-        <v>16.89191340686676</v>
+        <v>16.89191326113697</v>
       </c>
       <c r="CQ11" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR11" t="n">
-        <v>31.612070045816</v>
+        <v>31.57717381093289</v>
       </c>
       <c r="CS11" t="n">
-        <v>28.44701465047878</v>
+        <v>28.44701457038872</v>
       </c>
       <c r="CT11" t="n">
-        <v>25.60231318543091</v>
+        <v>25.60231311334985</v>
       </c>
       <c r="CU11" t="n">
         <v>8</v>
@@ -4540,10 +4540,10 @@
         <v>3</v>
       </c>
       <c r="CX11" t="n">
-        <v>-21.46529330130236</v>
+        <v>-21.4652935224099</v>
       </c>
       <c r="CY11" t="n">
-        <v>-3.030455443393165</v>
+        <v>-3.137499113689091</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ12" t="n">
-        <v>133.9252028900013</v>
+        <v>133.9252023413278</v>
       </c>
       <c r="CK12" t="n">
-        <v>248.4312513609524</v>
+        <v>248.4312503431632</v>
       </c>
       <c r="CL12" t="n">
         <v>131.5457818930041</v>
@@ -4884,7 +4884,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR12" t="n">
-        <v>141.1793355952013</v>
+        <v>141.1793353993934</v>
       </c>
       <c r="CS12" t="n">
         <v>125.8371913580247</v>
@@ -4905,7 +4905,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY12" t="n">
-        <v>192.5996592646658</v>
+        <v>192.5996588588464</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>0.3954558219285254</v>
       </c>
       <c r="DL12" t="n">
-        <v>-9.168920601679343</v>
+        <v>-9.168913901075104</v>
       </c>
       <c r="DM12" t="b">
         <v>1</v>
@@ -5206,10 +5206,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ13" t="n">
-        <v>13.26532630965794</v>
+        <v>13.26532638438173</v>
       </c>
       <c r="CK13" t="n">
-        <v>24.60718030441548</v>
+        <v>24.60718044302811</v>
       </c>
       <c r="CL13" t="n">
         <v>19.93179967973907</v>
@@ -5218,7 +5218,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN13" t="n">
-        <v>33.72989544579784</v>
+        <v>33.72989552733588</v>
       </c>
       <c r="CO13" t="n">
         <v>22.8984489302328</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
-        <v>20.17568880601132</v>
+        <v>20.17568885934543</v>
       </c>
       <c r="CS13" t="n">
         <v>21.41512430498593</v>
@@ -5249,7 +5249,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY13" t="n">
-        <v>4.537251831954725</v>
+        <v>4.537252108297229</v>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ14" t="n">
-        <v>3.228277659127442</v>
+        <v>3.228277652643014</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.988455057681404</v>
+        <v>5.98845504565279</v>
       </c>
       <c r="CL14" t="n">
         <v>19.81956093381139</v>
@@ -5580,7 +5580,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN14" t="n">
-        <v>31.89244532600328</v>
+        <v>31.89244530701123</v>
       </c>
       <c r="CO14" t="n">
         <v>10.95072400487419</v>
@@ -5926,10 +5926,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ15" t="n">
-        <v>10.67756771487573</v>
+        <v>10.67756763384111</v>
       </c>
       <c r="CK15" t="n">
-        <v>19.80688811109448</v>
+        <v>19.80688796077525</v>
       </c>
       <c r="CL15" t="n">
         <v>38.98902044102951</v>
@@ -5938,25 +5938,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN15" t="n">
-        <v>44.331797494034</v>
+        <v>44.33179745192316</v>
       </c>
       <c r="CO15" t="n">
-        <v>34.59948397864836</v>
+        <v>34.59948399515928</v>
       </c>
       <c r="CP15" t="n">
-        <v>19.85450027304415</v>
+        <v>19.85450036703135</v>
       </c>
       <c r="CQ15" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR15" t="n">
-        <v>32.77627194943079</v>
+        <v>32.77627193772622</v>
       </c>
       <c r="CS15" t="n">
-        <v>34.59948397864836</v>
+        <v>34.59948399515928</v>
       </c>
       <c r="CT15" t="n">
-        <v>31.13953558078352</v>
+        <v>31.13953559564336</v>
       </c>
       <c r="CU15" t="n">
         <v>7</v>
@@ -5968,10 +5968,10 @@
         <v>4.2</v>
       </c>
       <c r="CX15" t="n">
-        <v>78.75737912975009</v>
+        <v>78.75737921505336</v>
       </c>
       <c r="CY15" t="n">
-        <v>88.15311025190215</v>
+        <v>88.15311018471176</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>-0.6274991787955986</v>
       </c>
       <c r="DL15" t="n">
-        <v>-23.70303109613396</v>
+        <v>-23.70303752784818</v>
       </c>
       <c r="DM15" t="b">
         <v>1</v>
@@ -6286,37 +6286,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ16" t="n">
-        <v>24.99231901649256</v>
+        <v>24.99231906719641</v>
       </c>
       <c r="CK16" t="n">
-        <v>31.99913693185174</v>
+        <v>31.99913685072687</v>
       </c>
       <c r="CL16" t="n">
-        <v>35.87977395352864</v>
+        <v>35.87977378977343</v>
       </c>
       <c r="CM16" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN16" t="n">
-        <v>50.33277096672724</v>
+        <v>50.33277086547852</v>
       </c>
       <c r="CO16" t="n">
-        <v>48.6590550508374</v>
+        <v>48.65905502894773</v>
       </c>
       <c r="CP16" t="n">
-        <v>17.29535408841702</v>
+        <v>17.29535397441449</v>
       </c>
       <c r="CQ16" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR16" t="n">
-        <v>34.65367028942694</v>
+        <v>34.6536702355123</v>
       </c>
       <c r="CS16" t="n">
-        <v>33.93945544269019</v>
+        <v>33.93945532025015</v>
       </c>
       <c r="CT16" t="n">
-        <v>30.54550989842117</v>
+        <v>30.54550978822514</v>
       </c>
       <c r="CU16" t="n">
         <v>8</v>
@@ -6328,10 +6328,10 @@
         <v>2.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>-12.12453574976507</v>
+        <v>-12.12453606678474</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0.3058919368255419</v>
+        <v>-0.3058920919309482</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -6646,37 +6646,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.03288996891136</v>
+        <v>10.03288996127143</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.09423435037944</v>
+        <v>18.09423437115729</v>
       </c>
       <c r="CL17" t="n">
-        <v>23.57397870584134</v>
+        <v>23.57397875086296</v>
       </c>
       <c r="CM17" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN17" t="n">
-        <v>36.27022038810384</v>
+        <v>36.27022039518288</v>
       </c>
       <c r="CO17" t="n">
-        <v>24.18418237935125</v>
+        <v>24.18418238267834</v>
       </c>
       <c r="CP17" t="n">
-        <v>11.54642586826937</v>
+        <v>11.54642588500997</v>
       </c>
       <c r="CQ17" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR17" t="n">
-        <v>18.89005838190975</v>
+        <v>18.89005839257303</v>
       </c>
       <c r="CS17" t="n">
-        <v>17.75138475795949</v>
+        <v>17.75138476834842</v>
       </c>
       <c r="CT17" t="n">
-        <v>15.97624628216354</v>
+        <v>15.97624629151357</v>
       </c>
       <c r="CU17" t="n">
         <v>8</v>
@@ -6688,10 +6688,10 @@
         <v>3.6</v>
       </c>
       <c r="CX17" t="n">
-        <v>59.60285631230366</v>
+        <v>59.60285640571055</v>
       </c>
       <c r="CY17" t="n">
-        <v>88.71186763219339</v>
+        <v>88.71186773871973</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.337978108833978</v>
+        <v>3.337978101471955</v>
       </c>
       <c r="CK18" t="n">
-        <v>6.19194939188703</v>
+        <v>6.191949378230475</v>
       </c>
       <c r="CL18" t="n">
         <v>19.28911530241674</v>
@@ -7018,13 +7018,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.60183925918205</v>
+        <v>20.6018392600113</v>
       </c>
       <c r="CO18" t="n">
-        <v>15.92145422761735</v>
+        <v>15.92145422909692</v>
       </c>
       <c r="CP18" t="n">
-        <v>12.84225513257595</v>
+        <v>12.84225514191158</v>
       </c>
       <c r="CQ18" t="n">
         <v>29.10394270806049</v>
@@ -7080,7 +7080,7 @@
         <v>-13.64003621653164</v>
       </c>
       <c r="DL18" t="n">
-        <v>-35.19786534004677</v>
+        <v>-35.19787305431846</v>
       </c>
       <c r="DM18" t="b">
         <v>1</v>
@@ -7356,10 +7356,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ19" t="n">
-        <v>9.410499913334329</v>
+        <v>9.410499909206081</v>
       </c>
       <c r="CK19" t="n">
-        <v>17.45647733923518</v>
+        <v>17.45647733157728</v>
       </c>
       <c r="CL19" t="n">
         <v>21.3058429709553</v>
@@ -7368,25 +7368,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN19" t="n">
-        <v>30.17445896128012</v>
+        <v>30.17445897398767</v>
       </c>
       <c r="CO19" t="n">
-        <v>25.20917158818038</v>
+        <v>25.20917159130531</v>
       </c>
       <c r="CP19" t="n">
-        <v>11.01207334198808</v>
+        <v>11.01207335534973</v>
       </c>
       <c r="CQ19" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR19" t="n">
-        <v>17.05929121425289</v>
+        <v>17.05929121642889</v>
       </c>
       <c r="CS19" t="n">
-        <v>15.01197251009441</v>
+        <v>15.01197250626546</v>
       </c>
       <c r="CT19" t="n">
-        <v>13.51077525908497</v>
+        <v>13.51077525563892</v>
       </c>
       <c r="CU19" t="n">
         <v>8</v>
@@ -7398,10 +7398,10 @@
         <v>3.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>24.29416192574381</v>
+        <v>24.29416189404137</v>
       </c>
       <c r="CY19" t="n">
-        <v>56.93920325534094</v>
+        <v>56.9392032753593</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ20" t="n">
-        <v>7.255085131110492</v>
+        <v>7.255085089269031</v>
       </c>
       <c r="CK20" t="n">
-        <v>13.45818291820996</v>
+        <v>13.45818284059405</v>
       </c>
       <c r="CL20" t="n">
         <v>35.08558886655294</v>
@@ -7728,19 +7728,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN20" t="n">
-        <v>43.31704739419273</v>
+        <v>43.31704745774301</v>
       </c>
       <c r="CO20" t="n">
-        <v>26.42844994811291</v>
+        <v>26.42844995876278</v>
       </c>
       <c r="CP20" t="n">
-        <v>28.1271777904963</v>
+        <v>28.12717786605194</v>
       </c>
       <c r="CQ20" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR20" t="n">
-        <v>28.30913260182217</v>
+        <v>28.30913261212787</v>
       </c>
       <c r="CS20" t="n">
         <v>27.73936337556392</v>
@@ -7761,7 +7761,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY20" t="n">
-        <v>3.393475053085271</v>
+        <v>3.393475090724785</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -8084,10 +8084,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ21" t="n">
-        <v>3.140372323820429</v>
+        <v>3.140372325447475</v>
       </c>
       <c r="CK21" t="n">
-        <v>5.825390660686896</v>
+        <v>5.825390663705067</v>
       </c>
       <c r="CL21" t="n">
         <v>32.87416582383663</v>
@@ -8096,7 +8096,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN21" t="n">
-        <v>42.11194018186733</v>
+        <v>42.11194018440393</v>
       </c>
       <c r="CO21" t="n">
         <v>10.85340539909456</v>
@@ -8414,10 +8414,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ22" t="n">
-        <v>36.63430058651684</v>
+        <v>36.63430051030803</v>
       </c>
       <c r="CK22" t="n">
-        <v>53.33954165396852</v>
+        <v>53.33954154300849</v>
       </c>
       <c r="CL22" t="n">
         <v>48.73630032327193</v>
@@ -8434,13 +8434,13 @@
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
-        <v>49.55357688689375</v>
+        <v>49.55357684010154</v>
       </c>
       <c r="CS22" t="n">
-        <v>51.03792098862023</v>
+        <v>51.03792093314021</v>
       </c>
       <c r="CT22" t="n">
-        <v>45.93412888975821</v>
+        <v>45.93412883982619</v>
       </c>
       <c r="CU22" t="n">
         <v>4</v>
@@ -8452,10 +8452,10 @@
         <v>1.6</v>
       </c>
       <c r="CX22" t="n">
-        <v>14.77793194489387</v>
+        <v>14.77793182012623</v>
       </c>
       <c r="CY22" t="n">
-        <v>23.82202978531105</v>
+        <v>23.82202966838898</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.414124725457547</v>
+        <v>3.41412471707062</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.333201365723748</v>
+        <v>6.333201350166</v>
       </c>
       <c r="CL23" t="n">
         <v>31.64000679932063</v>
@@ -8790,7 +8790,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN23" t="n">
-        <v>39.1358600879658</v>
+        <v>39.13586007981751</v>
       </c>
       <c r="CO23" t="n">
         <v>10.59424454785779</v>
@@ -8852,7 +8852,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL23" t="n">
-        <v>-27.83707532184228</v>
+        <v>-27.83708127316356</v>
       </c>
       <c r="DM23" t="b">
         <v>1</v>
@@ -9108,35 +9108,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ24" t="n">
-        <v>8.694392951335713</v>
+        <v>8.694392891896392</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.60549911404338</v>
+        <v>13.60549918038555</v>
       </c>
       <c r="CL24" t="n">
-        <v>17.8923925771369</v>
+        <v>17.89239278670407</v>
       </c>
       <c r="CM24" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.47099640849115</v>
+        <v>22.47099646673388</v>
       </c>
       <c r="CO24" t="n">
-        <v>17.30064966242656</v>
+        <v>17.30064967906669</v>
       </c>
       <c r="CP24" t="n">
-        <v>8.943457156765485</v>
+        <v>8.943457258031069</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
-        <v>14.37323357623564</v>
+        <v>14.37323363451318</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.45307438823497</v>
+        <v>15.45307442972612</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.90776694941147</v>
+        <v>13.90776698675351</v>
       </c>
       <c r="CU24" t="n">
         <v>4</v>
@@ -9148,10 +9148,10 @@
         <v>2.1</v>
       </c>
       <c r="CX24" t="n">
-        <v>7.395885361026022</v>
+        <v>7.395885649381517</v>
       </c>
       <c r="CY24" t="n">
-        <v>10.99022230063853</v>
+        <v>10.99022275065813</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ25" t="n">
-        <v>7.02162031798788</v>
+        <v>7.021620245364706</v>
       </c>
       <c r="CK25" t="n">
-        <v>13.02510568986752</v>
+        <v>13.02510555515153</v>
       </c>
       <c r="CL25" t="n">
         <v>5.692307765667254</v>
@@ -9498,7 +9498,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR25" t="n">
-        <v>7.373583671919927</v>
+        <v>7.373583646002531</v>
       </c>
       <c r="CS25" t="n">
         <v>5.912820549500294</v>
@@ -9519,7 +9519,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY25" t="n">
-        <v>24.55377663670502</v>
+        <v>24.55377619891117</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ26" t="n">
-        <v>20.2039654163783</v>
+        <v>20.20396550318609</v>
       </c>
       <c r="CK26" t="n">
-        <v>37.47835584738174</v>
+        <v>37.47835600841019</v>
       </c>
       <c r="CL26" t="n">
         <v>55.97851442143241</v>
@@ -9828,23 +9828,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN26" t="n">
-        <v>61.59747852382779</v>
+        <v>61.59747838097049</v>
       </c>
       <c r="CO26" t="n">
-        <v>45.15222537147327</v>
+        <v>45.58224653808353</v>
       </c>
       <c r="CP26" t="n">
-        <v>30.98915238410255</v>
+        <v>30.98915221260507</v>
       </c>
       <c r="CQ26" t="inlineStr"/>
       <c r="CR26" t="n">
-        <v>39.70326526416643</v>
+        <v>39.81077061777805</v>
       </c>
       <c r="CS26" t="n">
-        <v>41.31529060942751</v>
+        <v>41.53030127324686</v>
       </c>
       <c r="CT26" t="n">
-        <v>37.18376154848476</v>
+        <v>37.37727114592218</v>
       </c>
       <c r="CU26" t="n">
         <v>4</v>
@@ -9856,10 +9856,10 @@
         <v>2.8</v>
       </c>
       <c r="CX26" t="n">
-        <v>-5.868231096597798</v>
+        <v>-5.378355948199531</v>
       </c>
       <c r="CY26" t="n">
-        <v>0.5099655042642537</v>
+        <v>0.7821184194246156</v>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>-2.226610650473015</v>
       </c>
       <c r="DL26" t="n">
-        <v>-18.84844460254175</v>
+        <v>-18.8484510008869</v>
       </c>
       <c r="DM26" t="b">
         <v>1</v>
@@ -10154,10 +10154,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.430280392303015</v>
+        <v>9.430280365724084</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.49317012772209</v>
+        <v>17.49317007841817</v>
       </c>
       <c r="CL27" t="n">
         <v>30.9711095548374</v>
@@ -10166,23 +10166,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN27" t="n">
-        <v>34.71574761304258</v>
+        <v>34.71574760828589</v>
       </c>
       <c r="CO27" t="n">
-        <v>25.47771500457578</v>
+        <v>25.47771500997475</v>
       </c>
       <c r="CP27" t="n">
-        <v>15.27881615890105</v>
+        <v>15.27881619195036</v>
       </c>
       <c r="CQ27" t="inlineStr"/>
       <c r="CR27" t="n">
-        <v>20.84306876985957</v>
+        <v>20.8430687522386</v>
       </c>
       <c r="CS27" t="n">
-        <v>21.48544256614893</v>
+        <v>21.48544254419646</v>
       </c>
       <c r="CT27" t="n">
-        <v>19.33689830953404</v>
+        <v>19.33689828977682</v>
       </c>
       <c r="CU27" t="n">
         <v>4</v>
@@ -10194,10 +10194,10 @@
         <v>3.3</v>
       </c>
       <c r="CX27" t="n">
-        <v>27.46801722006367</v>
+        <v>27.46801708982489</v>
       </c>
       <c r="CY27" t="n">
-        <v>37.39662930147831</v>
+        <v>37.39662918532163</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL27" t="n">
-        <v>-16.60347445371087</v>
+        <v>-16.60345638373696</v>
       </c>
       <c r="DM27" t="b">
         <v>1</v>
@@ -10512,37 +10512,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ28" t="n">
-        <v>17.07331076704757</v>
+        <v>17.07331075788889</v>
       </c>
       <c r="CK28" t="n">
-        <v>28.37657059222237</v>
+        <v>28.37657059110066</v>
       </c>
       <c r="CL28" t="n">
-        <v>47.6654563899052</v>
+        <v>47.66545641359029</v>
       </c>
       <c r="CM28" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN28" t="n">
-        <v>56.59469224000675</v>
+        <v>56.59469223702227</v>
       </c>
       <c r="CO28" t="n">
-        <v>42.94865306694228</v>
+        <v>42.94865306860028</v>
       </c>
       <c r="CP28" t="n">
-        <v>23.70643965541214</v>
+        <v>23.70643966565593</v>
       </c>
       <c r="CQ28" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR28" t="n">
-        <v>37.60349435669509</v>
+        <v>37.60349435948535</v>
       </c>
       <c r="CS28" t="n">
-        <v>37.07077016977637</v>
+        <v>37.07077017060537</v>
       </c>
       <c r="CT28" t="n">
-        <v>33.36369315279873</v>
+        <v>33.36369315354484</v>
       </c>
       <c r="CU28" t="n">
         <v>8</v>
@@ -10554,10 +10554,10 @@
         <v>3.3</v>
       </c>
       <c r="CX28" t="n">
-        <v>24.9576486870694</v>
+        <v>24.95764868986381</v>
       </c>
       <c r="CY28" t="n">
-        <v>40.83705349136197</v>
+        <v>40.83705350181237</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -10872,37 +10872,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ29" t="n">
-        <v>5.830932713942503</v>
+        <v>5.830932729568524</v>
       </c>
       <c r="CK29" t="n">
-        <v>8.573470631141689</v>
+        <v>8.573470617782714</v>
       </c>
       <c r="CL29" t="n">
-        <v>11.023171234206</v>
+        <v>11.02317118748953</v>
       </c>
       <c r="CM29" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN29" t="n">
-        <v>9.992440030131663</v>
+        <v>9.992440005155867</v>
       </c>
       <c r="CO29" t="n">
-        <v>14.93936638791466</v>
+        <v>14.93936638241032</v>
       </c>
       <c r="CP29" t="n">
-        <v>5.501588200780516</v>
+        <v>5.501588175478861</v>
       </c>
       <c r="CQ29" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.794723708163716</v>
+        <v>9.794723695634811</v>
       </c>
       <c r="CS29" t="n">
-        <v>10.44705006548928</v>
+        <v>10.44705005300138</v>
       </c>
       <c r="CT29" t="n">
-        <v>9.402345058940352</v>
+        <v>9.402345047701242</v>
       </c>
       <c r="CU29" t="n">
         <v>8</v>
@@ -10914,10 +10914,10 @@
         <v>2.7</v>
       </c>
       <c r="CX29" t="n">
-        <v>-37.44281286769087</v>
+        <v>-37.44281294246871</v>
       </c>
       <c r="CY29" t="n">
-        <v>-34.83217643259762</v>
+        <v>-34.83217651595692</v>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
@@ -11232,37 +11232,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ30" t="n">
-        <v>30.83210609800769</v>
+        <v>30.83210615527411</v>
       </c>
       <c r="CK30" t="n">
-        <v>35.07524628662182</v>
+        <v>35.07524624264288</v>
       </c>
       <c r="CL30" t="n">
-        <v>37.91416013116773</v>
+        <v>37.91416001320885</v>
       </c>
       <c r="CM30" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN30" t="n">
-        <v>59.1049602948329</v>
+        <v>59.10496023007499</v>
       </c>
       <c r="CO30" t="n">
-        <v>16.5796450461548</v>
+        <v>16.57964504050243</v>
       </c>
       <c r="CP30" t="n">
-        <v>16.88731348929585</v>
+        <v>16.88731338780143</v>
       </c>
       <c r="CQ30" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR30" t="n">
-        <v>34.28114200743894</v>
+        <v>34.28114197286692</v>
       </c>
       <c r="CS30" t="n">
-        <v>32.95367619231476</v>
+        <v>32.9536761989585</v>
       </c>
       <c r="CT30" t="n">
-        <v>29.65830857308329</v>
+        <v>29.65830857906265</v>
       </c>
       <c r="CU30" t="n">
         <v>8</v>
@@ -11274,10 +11274,10 @@
         <v>3.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>-23.32391846151382</v>
+        <v>-23.32391844605528</v>
       </c>
       <c r="CY30" t="n">
-        <v>-11.37243604713268</v>
+        <v>-11.37243613651225</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>-0.667689601187782</v>
       </c>
       <c r="DL30" t="n">
-        <v>-11.71364092295562</v>
+        <v>-11.71364879963919</v>
       </c>
       <c r="DM30" t="b">
         <v>1</v>
@@ -11574,35 +11574,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ31" t="n">
-        <v>10.16567243419626</v>
+        <v>10.16567237210966</v>
       </c>
       <c r="CK31" t="n">
-        <v>17.61110253190278</v>
+        <v>17.61110254236791</v>
       </c>
       <c r="CL31" t="n">
-        <v>28.75563244166521</v>
+        <v>28.75563263437715</v>
       </c>
       <c r="CM31" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN31" t="n">
-        <v>32.08888080437558</v>
+        <v>32.08888080893509</v>
       </c>
       <c r="CO31" t="n">
-        <v>27.8717377347679</v>
+        <v>27.87173774873406</v>
       </c>
       <c r="CP31" t="n">
-        <v>14.20689954986044</v>
+        <v>14.20689962706141</v>
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>21.10103628563304</v>
+        <v>21.10103632439719</v>
       </c>
       <c r="CS31" t="n">
-        <v>22.74142013333534</v>
+        <v>22.74142014555098</v>
       </c>
       <c r="CT31" t="n">
-        <v>20.46727812000181</v>
+        <v>20.46727813099589</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -11614,10 +11614,10 @@
         <v>2.8</v>
       </c>
       <c r="CX31" t="n">
-        <v>19.83183964535273</v>
+        <v>19.83183970972087</v>
       </c>
       <c r="CY31" t="n">
-        <v>23.54236756374932</v>
+        <v>23.54236779070573</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>-1.328709123815142</v>
       </c>
       <c r="DL31" t="n">
-        <v>-19.58181543685118</v>
+        <v>-19.58182280530835</v>
       </c>
       <c r="DM31" t="b">
         <v>1</v>
@@ -11940,37 +11940,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ32" t="n">
-        <v>32.50257843225724</v>
+        <v>32.5025784223838</v>
       </c>
       <c r="CK32" t="n">
-        <v>44.74764030437347</v>
+        <v>44.74764032344584</v>
       </c>
       <c r="CL32" t="n">
-        <v>51.52715683912498</v>
+        <v>51.52715687673953</v>
       </c>
       <c r="CM32" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN32" t="n">
-        <v>71.44157073374672</v>
+        <v>71.44157075411339</v>
       </c>
       <c r="CO32" t="n">
-        <v>59.88947340102621</v>
+        <v>59.8894734050616</v>
       </c>
       <c r="CP32" t="n">
-        <v>25.45084453315852</v>
+        <v>25.45084455612257</v>
       </c>
       <c r="CQ32" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR32" t="n">
-        <v>51.51519279626238</v>
+        <v>51.51519280803483</v>
       </c>
       <c r="CS32" t="n">
-        <v>49.93498886733423</v>
+        <v>49.9349888861415</v>
       </c>
       <c r="CT32" t="n">
-        <v>44.94148998060081</v>
+        <v>44.94148999752736</v>
       </c>
       <c r="CU32" t="n">
         <v>8</v>
@@ -11982,10 +11982,10 @@
         <v>3.1</v>
       </c>
       <c r="CX32" t="n">
-        <v>0.3158275579237424</v>
+        <v>0.3158275957062084</v>
       </c>
       <c r="CY32" t="n">
-        <v>14.98927159276986</v>
+        <v>14.98927161904764</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -12290,10 +12290,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ33" t="n">
-        <v>10.4762603651497</v>
+        <v>10.47626032182234</v>
       </c>
       <c r="CK33" t="n">
-        <v>19.43346297735269</v>
+        <v>19.43346289698045</v>
       </c>
       <c r="CL33" t="n">
         <v>60.73011328156327</v>
@@ -12302,7 +12302,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN33" t="n">
-        <v>81.29749123848728</v>
+        <v>81.29749118659824</v>
       </c>
       <c r="CO33" t="n">
         <v>11.76833333333333</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>13.8926855586119</v>
+        <v>13.89268551737871</v>
       </c>
       <c r="CS33" t="n">
         <v>11.76833333333333</v>
@@ -12333,7 +12333,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY33" t="n">
-        <v>-74.07113646166437</v>
+        <v>-74.07113653862068</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ34" t="n">
-        <v>15.68694277725812</v>
+        <v>15.68694279428464</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.0992788518138</v>
+        <v>29.099278883398</v>
       </c>
       <c r="CL34" t="n">
         <v>55.61293748708871</v>
@@ -12642,23 +12642,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN34" t="n">
-        <v>62.11186603712093</v>
+        <v>62.1118660330591</v>
       </c>
       <c r="CO34" t="n">
-        <v>36.65076910283077</v>
+        <v>36.65076909979219</v>
       </c>
       <c r="CP34" t="n">
-        <v>30.94726542914714</v>
+        <v>30.94726540563828</v>
       </c>
       <c r="CQ34" t="inlineStr"/>
       <c r="CR34" t="n">
-        <v>34.26248205474785</v>
+        <v>34.26248206614089</v>
       </c>
       <c r="CS34" t="n">
-        <v>32.87502397732229</v>
+        <v>32.87502399159509</v>
       </c>
       <c r="CT34" t="n">
-        <v>29.58752157959006</v>
+        <v>29.58752159243559</v>
       </c>
       <c r="CU34" t="n">
         <v>4</v>
@@ -12670,10 +12670,10 @@
         <v>3.5</v>
       </c>
       <c r="CX34" t="n">
-        <v>-1.4077928892689</v>
+        <v>-1.407792846464739</v>
       </c>
       <c r="CY34" t="n">
-        <v>14.17021590614116</v>
+        <v>14.1702159441053</v>
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>0.2672900865030137</v>
       </c>
       <c r="DL34" t="n">
-        <v>-17.68853399965281</v>
+        <v>-17.68854281697311</v>
       </c>
       <c r="DM34" t="b">
         <v>1</v>
@@ -12990,10 +12990,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ35" t="n">
-        <v>13.32483351699633</v>
+        <v>13.32483352100944</v>
       </c>
       <c r="CK35" t="n">
-        <v>19.40095760074666</v>
+        <v>19.40095760658975</v>
       </c>
       <c r="CL35" t="n">
         <v>16.70870841086448</v>
@@ -13012,7 +13012,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR35" t="n">
-        <v>16.31393970191115</v>
+        <v>16.31393970355385</v>
       </c>
       <c r="CS35" t="n">
         <v>15.78776446356376</v>
@@ -13033,7 +13033,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY35" t="n">
-        <v>52.46672890390987</v>
+        <v>52.46672891926218</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -13348,10 +13348,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ36" t="n">
-        <v>8.850909515701334</v>
+        <v>8.850909482615476</v>
       </c>
       <c r="CK36" t="n">
-        <v>16.41843715162597</v>
+        <v>16.41843709025171</v>
       </c>
       <c r="CL36" t="n">
         <v>16.35235520731475</v>
@@ -13360,7 +13360,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN36" t="n">
-        <v>25.87578451960625</v>
+        <v>25.87578448931181</v>
       </c>
       <c r="CO36" t="n">
         <v>19.94489718117502</v>
@@ -13372,7 +13372,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR36" t="n">
-        <v>16.79289068346301</v>
+        <v>16.79289066786869</v>
       </c>
       <c r="CS36" t="n">
         <v>16.28957786959118</v>
@@ -13393,7 +13393,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY36" t="n">
-        <v>-11.00747251400105</v>
+        <v>-11.00747259664185</v>
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
@@ -14328,10 +14328,10 @@
         <v>10.21084403991699</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.8063891607569</v>
+        <v>5.806389198829497</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.77085189320405</v>
+        <v>10.77085196382872</v>
       </c>
       <c r="CL2" t="n">
         <v>38.65533815111432</v>
@@ -14340,7 +14340,7 @@
         <v>26.01963993575657</v>
       </c>
       <c r="CN2" t="n">
-        <v>66.98631681410043</v>
+        <v>66.98631696639082</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -14402,7 +14402,7 @@
         <v>-4.990758938380024</v>
       </c>
       <c r="DL2" t="n">
-        <v>-27.36880243865982</v>
+        <v>-27.36880747332325</v>
       </c>
       <c r="DM2" t="b">
         <v>1</v>
@@ -14678,10 +14678,10 @@
         <v>13.39000034332275</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.76958273885434</v>
+        <v>14.76958263089643</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.3975759805748</v>
+        <v>27.39757578031287</v>
       </c>
       <c r="CL3" t="n">
         <v>38.56902272804923</v>
@@ -14690,13 +14690,13 @@
         <v>23.3388790497667</v>
       </c>
       <c r="CN3" t="n">
-        <v>74.51097364566313</v>
+        <v>74.51097384699619</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.47789228578153</v>
+        <v>48.477892365896</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.35679553710962</v>
+        <v>26.35679587019002</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.837022794615942</v>
@@ -15028,10 +15028,10 @@
         <v>24.45000076293945</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.22247028405236</v>
+        <v>16.22247028274917</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.09268237691713</v>
+        <v>30.09268237449971</v>
       </c>
       <c r="CL4" t="n">
         <v>71.2005516722962</v>
@@ -15040,19 +15040,19 @@
         <v>51.60632681095359</v>
       </c>
       <c r="CN4" t="n">
-        <v>125.5537726851971</v>
+        <v>125.5537726856353</v>
       </c>
       <c r="CO4" t="n">
-        <v>25.70896311266156</v>
+        <v>25.70896311284811</v>
       </c>
       <c r="CP4" t="n">
-        <v>61.89944659111422</v>
+        <v>61.89944659391013</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.55672416650329</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.177449121741</v>
+        <v>47.17744912183517</v>
       </c>
       <c r="CS4" t="n">
         <v>47.08152548872845</v>
@@ -15073,7 +15073,7 @@
         <v>73.30622338500632</v>
       </c>
       <c r="CY4" t="n">
-        <v>92.95479611293551</v>
+        <v>92.9547961133207</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -15386,10 +15386,10 @@
         <v>4.150000095367432</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.770224611126729</v>
+        <v>3.770224622535882</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.993766653640082</v>
+        <v>6.99376667480406</v>
       </c>
       <c r="CL5" t="n">
         <v>12.93823559143964</v>
@@ -15398,25 +15398,25 @@
         <v>8.716743723386035</v>
       </c>
       <c r="CN5" t="n">
-        <v>25.12502458100001</v>
+        <v>25.12502457334809</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.21765762961229</v>
+        <v>11.21765762501402</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.59486135807276</v>
+        <v>10.59486132963933</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.413933961389416</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.312533152923372</v>
+        <v>9.312533150945416</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.655802540729397</v>
+        <v>9.65580252651268</v>
       </c>
       <c r="CT5" t="n">
-        <v>8.690222286656457</v>
+        <v>8.690222273861412</v>
       </c>
       <c r="CU5" t="n">
         <v>6</v>
@@ -15428,10 +15428,10 @@
         <v>6.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>109.4029418543193</v>
+        <v>109.4029415460049</v>
       </c>
       <c r="CY5" t="n">
-        <v>124.398384070371</v>
+        <v>124.3983840227094</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>0.7281604524675522</v>
       </c>
       <c r="DL5" t="n">
-        <v>-36.46408229840906</v>
+        <v>-36.46407744847748</v>
       </c>
       <c r="DM5" t="b">
         <v>1</v>
@@ -15746,10 +15746,10 @@
         <v>4.420000076293945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.224933208520007</v>
+        <v>3.224933215410524</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.982251101804613</v>
+        <v>5.982251114586521</v>
       </c>
       <c r="CL6" t="n">
         <v>12.78711812464951</v>
@@ -15758,7 +15758,7 @@
         <v>8.592293841909434</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.33385721914613</v>
+        <v>24.33385724020884</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -15770,7 +15770,7 @@
         <v>5.337104731202623</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.46929365126752</v>
+        <v>11.46929365610247</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -15791,7 +15791,7 @@
         <v>135.6928462927893</v>
       </c>
       <c r="CY6" t="n">
-        <v>159.4862772238733</v>
+        <v>159.4862773332613</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -16096,10 +16096,10 @@
         <v>48.86999893188477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.62418020062737</v>
+        <v>18.62418025977003</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.54785427216376</v>
+        <v>34.54785438187341</v>
       </c>
       <c r="CL7" t="n">
         <v>75.20644434930001</v>
@@ -16108,23 +16108,23 @@
         <v>56.28580733697414</v>
       </c>
       <c r="CN7" t="n">
-        <v>100.3694234128933</v>
+        <v>100.3694233199457</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.8454123533156</v>
+        <v>48.35621745306714</v>
       </c>
       <c r="CP7" t="n">
-        <v>59.21710164661773</v>
+        <v>59.21710152774573</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>44.05597279385169</v>
+        <v>44.18367411100265</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.19663331273968</v>
+        <v>41.45203591747027</v>
       </c>
       <c r="CT7" t="n">
-        <v>37.07696998146571</v>
+        <v>37.30683232572324</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -16136,10 +16136,10 @@
         <v>4</v>
       </c>
       <c r="CX7" t="n">
-        <v>-24.13142870507576</v>
+        <v>-23.66107398995101</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.850677804889852</v>
+        <v>-9.589369599565456</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>3586087168</v>
+        <v>3586845440</v>
       </c>
       <c r="AX9" t="n">
         <v>8.210000000000001</v>
@@ -16678,10 +16678,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.401689196500936</v>
+        <v>6.401689197981169</v>
       </c>
       <c r="CK9" t="n">
-        <v>11.87513345950924</v>
+        <v>11.87513346225507</v>
       </c>
       <c r="CL9" t="n">
         <v>25.33800212822936</v>
@@ -16690,19 +16690,19 @@
         <v>18.56484347595736</v>
       </c>
       <c r="CN9" t="n">
-        <v>35.10892155998621</v>
+        <v>35.10892155757615</v>
       </c>
       <c r="CO9" t="n">
-        <v>12.29620298348503</v>
+        <v>12.29620298320339</v>
       </c>
       <c r="CP9" t="n">
-        <v>20.31530580062193</v>
+        <v>20.31530579752043</v>
       </c>
       <c r="CQ9" t="n">
         <v>18.4232945736423</v>
       </c>
       <c r="CR9" t="n">
-        <v>20.27452914020449</v>
+        <v>20.27452913976915</v>
       </c>
       <c r="CS9" t="n">
         <v>18.56484347595736</v>
@@ -16723,7 +16723,7 @@
         <v>6.422670900297867</v>
       </c>
       <c r="CY9" t="n">
-        <v>29.13712985040775</v>
+        <v>29.1371298476349</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>43.54999923706055</v>
       </c>
       <c r="CJ10" t="n">
-        <v>127.5892447839196</v>
+        <v>127.5892442340015</v>
       </c>
       <c r="CK10" t="n">
-        <v>236.6780490741708</v>
+        <v>236.6780480540727</v>
       </c>
       <c r="CL10" t="n">
         <v>132.6522965266787</v>
@@ -17064,13 +17064,13 @@
         <v>53.533981815297</v>
       </c>
       <c r="CR10" t="n">
-        <v>139.7795670992629</v>
+        <v>139.7795669030108</v>
       </c>
       <c r="CS10" t="n">
-        <v>124.3641615607452</v>
+        <v>124.3641612857861</v>
       </c>
       <c r="CT10" t="n">
-        <v>111.9277454046706</v>
+        <v>111.9277451572075</v>
       </c>
       <c r="CU10" t="n">
         <v>8</v>
@@ -17082,10 +17082,10 @@
         <v>5.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>157.0097528484488</v>
+        <v>157.0097522802211</v>
       </c>
       <c r="CY10" t="n">
-        <v>220.9634203169218</v>
+        <v>220.9634198662857</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>1.346832193262903</v>
       </c>
       <c r="DL10" t="n">
-        <v>-8.627331177634668</v>
+        <v>-8.627323714303436</v>
       </c>
       <c r="DM10" t="b">
         <v>1</v>
@@ -17404,10 +17404,10 @@
         <v>32.43999862670898</v>
       </c>
       <c r="CJ11" t="n">
-        <v>45.30199092173366</v>
+        <v>45.30199127084784</v>
       </c>
       <c r="CK11" t="n">
-        <v>84.03519315981595</v>
+        <v>84.03519380742274</v>
       </c>
       <c r="CL11" t="n">
         <v>67.58333047231037</v>
@@ -17428,7 +17428,7 @@
         <v>25.42519513879396</v>
       </c>
       <c r="CR11" t="n">
-        <v>76.94607048269363</v>
+        <v>76.94607062508236</v>
       </c>
       <c r="CS11" t="n">
         <v>67.58333047231037</v>
@@ -17449,7 +17449,7 @@
         <v>87.49999999999996</v>
       </c>
       <c r="CY11" t="n">
-        <v>137.195048520567</v>
+        <v>137.1950489594965</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -17772,37 +17772,37 @@
         <v>32.59999847412109</v>
       </c>
       <c r="CJ12" t="n">
-        <v>24.216126628887</v>
+        <v>24.21612665383458</v>
       </c>
       <c r="CK12" t="n">
-        <v>32.67790267207057</v>
+        <v>32.67790248694287</v>
       </c>
       <c r="CL12" t="n">
-        <v>34.37896868019397</v>
+        <v>34.37896845001195</v>
       </c>
       <c r="CM12" t="n">
         <v>20.76067144334462</v>
       </c>
       <c r="CN12" t="n">
-        <v>48.80739130308112</v>
+        <v>48.8073911094512</v>
       </c>
       <c r="CO12" t="n">
-        <v>50.94836393549667</v>
+        <v>50.66919478615361</v>
       </c>
       <c r="CP12" t="n">
-        <v>16.89191340686676</v>
+        <v>16.89191326113697</v>
       </c>
       <c r="CQ12" t="n">
         <v>24.21522229658729</v>
       </c>
       <c r="CR12" t="n">
-        <v>31.612070045816</v>
+        <v>31.57717381093289</v>
       </c>
       <c r="CS12" t="n">
-        <v>28.44701465047878</v>
+        <v>28.44701457038872</v>
       </c>
       <c r="CT12" t="n">
-        <v>25.60231318543091</v>
+        <v>25.60231311334985</v>
       </c>
       <c r="CU12" t="n">
         <v>8</v>
@@ -17814,10 +17814,10 @@
         <v>3</v>
       </c>
       <c r="CX12" t="n">
-        <v>-21.46529330130236</v>
+        <v>-21.4652935224099</v>
       </c>
       <c r="CY12" t="n">
-        <v>-3.030455443393165</v>
+        <v>-3.137499113689091</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -18132,10 +18132,10 @@
         <v>6.929999828338623</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.512298811966652</v>
+        <v>6.512298812709455</v>
       </c>
       <c r="CK13" t="n">
-        <v>12.08031429619814</v>
+        <v>12.08031429757604</v>
       </c>
       <c r="CL13" t="n">
         <v>39.92282509803772</v>
@@ -18144,7 +18144,7 @@
         <v>26.88461902486203</v>
       </c>
       <c r="CN13" t="n">
-        <v>84.83573077939674</v>
+        <v>84.83573078391815</v>
       </c>
       <c r="CO13" t="n">
         <v>51.88018214566937</v>
@@ -18480,10 +18480,10 @@
         <v>48.25</v>
       </c>
       <c r="CJ14" t="n">
-        <v>133.9252028900013</v>
+        <v>133.9252023413278</v>
       </c>
       <c r="CK14" t="n">
-        <v>248.4312513609524</v>
+        <v>248.4312503431632</v>
       </c>
       <c r="CL14" t="n">
         <v>131.5457818930041</v>
@@ -18504,7 +18504,7 @@
         <v>51.95479643658221</v>
       </c>
       <c r="CR14" t="n">
-        <v>141.1793355952013</v>
+        <v>141.1793353993934</v>
       </c>
       <c r="CS14" t="n">
         <v>125.8371913580247</v>
@@ -18525,7 +18525,7 @@
         <v>134.7222222222221</v>
       </c>
       <c r="CY14" t="n">
-        <v>192.5996592646658</v>
+        <v>192.5996588588464</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>0.3954558219285254</v>
       </c>
       <c r="DL14" t="n">
-        <v>-9.168920601679343</v>
+        <v>-9.168913901075104</v>
       </c>
       <c r="DM14" t="b">
         <v>1</v>
@@ -18842,10 +18842,10 @@
         <v>13.67000007629395</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.2013630585133979</v>
+        <v>0.201363058490232</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.2931846131955074</v>
+        <v>0.2931846131617778</v>
       </c>
       <c r="CL15" t="n">
         <v>73.66217657692074</v>
@@ -19172,10 +19172,10 @@
         <v>19.29999923706055</v>
       </c>
       <c r="CJ16" t="n">
-        <v>13.26532630965794</v>
+        <v>13.26532638438173</v>
       </c>
       <c r="CK16" t="n">
-        <v>24.60718030441548</v>
+        <v>24.60718044302811</v>
       </c>
       <c r="CL16" t="n">
         <v>19.93179967973907</v>
@@ -19184,7 +19184,7 @@
         <v>12.45644672118639</v>
       </c>
       <c r="CN16" t="n">
-        <v>33.72989544579784</v>
+        <v>33.72989552733588</v>
       </c>
       <c r="CO16" t="n">
         <v>22.8984489302328</v>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
-        <v>20.17568880601132</v>
+        <v>20.17568885934543</v>
       </c>
       <c r="CS16" t="n">
         <v>21.41512430498593</v>
@@ -19215,7 +19215,7 @@
         <v>-0.1367220912762535</v>
       </c>
       <c r="CY16" t="n">
-        <v>4.537251831954725</v>
+        <v>4.537252108297229</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -19524,10 +19524,10 @@
         <v>13.86999988555908</v>
       </c>
       <c r="CJ17" t="n">
-        <v>10.06948873190079</v>
+        <v>10.06948871652759</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.67890159767597</v>
+        <v>18.67890156915868</v>
       </c>
       <c r="CL17" t="n">
         <v>48.87699427756856</v>
@@ -19536,23 +19536,23 @@
         <v>47.98315406169494</v>
       </c>
       <c r="CN17" t="n">
-        <v>67.71366088648355</v>
+        <v>67.71366085778172</v>
       </c>
       <c r="CO17" t="n">
-        <v>33.90963924095704</v>
+        <v>33.90963924338182</v>
       </c>
       <c r="CP17" t="n">
-        <v>28.85042924319338</v>
+        <v>28.85042926113207</v>
       </c>
       <c r="CQ17" t="inlineStr"/>
       <c r="CR17" t="n">
-        <v>33.82184503873386</v>
+        <v>33.82184503003636</v>
       </c>
       <c r="CS17" t="n">
-        <v>33.90963924095704</v>
+        <v>33.90963924338182</v>
       </c>
       <c r="CT17" t="n">
-        <v>30.51867531686134</v>
+        <v>30.51867531904364</v>
       </c>
       <c r="CU17" t="n">
         <v>3</v>
@@ -19564,10 +19564,10 @@
         <v>4.9</v>
       </c>
       <c r="CX17" t="n">
-        <v>120.0337099399419</v>
+        <v>120.0337099556758</v>
       </c>
       <c r="CY17" t="n">
-        <v>143.8489208204528</v>
+        <v>143.8489207577455</v>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
@@ -19878,10 +19878,10 @@
         <v>7.150000095367432</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.228277659127442</v>
+        <v>3.228277652643014</v>
       </c>
       <c r="CK18" t="n">
-        <v>5.988455057681404</v>
+        <v>5.98845504565279</v>
       </c>
       <c r="CL18" t="n">
         <v>19.81956093381139</v>
@@ -19890,7 +19890,7 @@
         <v>13.60541151568668</v>
       </c>
       <c r="CN18" t="n">
-        <v>31.89244532600328</v>
+        <v>31.89244530701123</v>
       </c>
       <c r="CO18" t="n">
         <v>10.95072400487419</v>
@@ -20236,10 +20236,10 @@
         <v>17.42000007629395</v>
       </c>
       <c r="CJ19" t="n">
-        <v>10.67756771487573</v>
+        <v>10.67756763384111</v>
       </c>
       <c r="CK19" t="n">
-        <v>19.80688811109448</v>
+        <v>19.80688796077525</v>
       </c>
       <c r="CL19" t="n">
         <v>38.98902044102951</v>
@@ -20248,25 +20248,25 @@
         <v>38.45309110662797</v>
       </c>
       <c r="CN19" t="n">
-        <v>44.331797494034</v>
+        <v>44.33179745192316</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.59948397864836</v>
+        <v>34.59948399515928</v>
       </c>
       <c r="CP19" t="n">
-        <v>19.85450027304415</v>
+        <v>19.85450036703135</v>
       </c>
       <c r="CQ19" t="n">
         <v>33.39912224153704</v>
       </c>
       <c r="CR19" t="n">
-        <v>32.77627194943079</v>
+        <v>32.77627193772622</v>
       </c>
       <c r="CS19" t="n">
-        <v>34.59948397864836</v>
+        <v>34.59948399515928</v>
       </c>
       <c r="CT19" t="n">
-        <v>31.13953558078352</v>
+        <v>31.13953559564336</v>
       </c>
       <c r="CU19" t="n">
         <v>7</v>
@@ -20278,10 +20278,10 @@
         <v>4.2</v>
       </c>
       <c r="CX19" t="n">
-        <v>78.75737912975009</v>
+        <v>78.75737921505336</v>
       </c>
       <c r="CY19" t="n">
-        <v>88.15311025190215</v>
+        <v>88.15311018471176</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>-0.6274991787955986</v>
       </c>
       <c r="DL19" t="n">
-        <v>-23.70303109613396</v>
+        <v>-23.70303752784818</v>
       </c>
       <c r="DM19" t="b">
         <v>1</v>
@@ -20596,37 +20596,37 @@
         <v>34.7599983215332</v>
       </c>
       <c r="CJ20" t="n">
-        <v>24.99231901649256</v>
+        <v>24.99231906719641</v>
       </c>
       <c r="CK20" t="n">
-        <v>31.99913693185174</v>
+        <v>31.99913685072687</v>
       </c>
       <c r="CL20" t="n">
-        <v>35.87977395352864</v>
+        <v>35.87977378977343</v>
       </c>
       <c r="CM20" t="n">
         <v>36.8468125807678</v>
       </c>
       <c r="CN20" t="n">
-        <v>50.33277096672724</v>
+        <v>50.33277086547852</v>
       </c>
       <c r="CO20" t="n">
-        <v>48.6590550508374</v>
+        <v>48.65905502894773</v>
       </c>
       <c r="CP20" t="n">
-        <v>17.29535408841702</v>
+        <v>17.29535397441449</v>
       </c>
       <c r="CQ20" t="n">
         <v>31.22413972679316</v>
       </c>
       <c r="CR20" t="n">
-        <v>34.65367028942694</v>
+        <v>34.6536702355123</v>
       </c>
       <c r="CS20" t="n">
-        <v>33.93945544269019</v>
+        <v>33.93945532025015</v>
       </c>
       <c r="CT20" t="n">
-        <v>30.54550989842117</v>
+        <v>30.54550978822514</v>
       </c>
       <c r="CU20" t="n">
         <v>8</v>
@@ -20638,10 +20638,10 @@
         <v>2.9</v>
       </c>
       <c r="CX20" t="n">
-        <v>-12.12453574976507</v>
+        <v>-12.12453606678474</v>
       </c>
       <c r="CY20" t="n">
-        <v>-0.3058919368255419</v>
+        <v>-0.3058920919309482</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -20956,37 +20956,37 @@
         <v>10.01000022888184</v>
       </c>
       <c r="CJ21" t="n">
-        <v>10.03288996891136</v>
+        <v>10.03288996127143</v>
       </c>
       <c r="CK21" t="n">
-        <v>18.09423435037944</v>
+        <v>18.09423437115729</v>
       </c>
       <c r="CL21" t="n">
-        <v>23.57397870584134</v>
+        <v>23.57397875086296</v>
       </c>
       <c r="CM21" t="n">
         <v>17.40853516553954</v>
       </c>
       <c r="CN21" t="n">
-        <v>36.27022038810384</v>
+        <v>36.27022039518288</v>
       </c>
       <c r="CO21" t="n">
-        <v>24.18418237935125</v>
+        <v>24.18418238267834</v>
       </c>
       <c r="CP21" t="n">
-        <v>11.54642586826937</v>
+        <v>11.54642588500997</v>
       </c>
       <c r="CQ21" t="n">
         <v>10.01000022888184</v>
       </c>
       <c r="CR21" t="n">
-        <v>18.89005838190975</v>
+        <v>18.89005839257303</v>
       </c>
       <c r="CS21" t="n">
-        <v>17.75138475795949</v>
+        <v>17.75138476834842</v>
       </c>
       <c r="CT21" t="n">
-        <v>15.97624628216354</v>
+        <v>15.97624629151357</v>
       </c>
       <c r="CU21" t="n">
         <v>8</v>
@@ -20998,10 +20998,10 @@
         <v>3.6</v>
       </c>
       <c r="CX21" t="n">
-        <v>59.60285631230366</v>
+        <v>59.60285640571055</v>
       </c>
       <c r="CY21" t="n">
-        <v>88.71186763219339</v>
+        <v>88.71186773871973</v>
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
         <v>3.460000038146973</v>
       </c>
       <c r="CJ22" t="n">
-        <v>5.001737505921974</v>
+        <v>5.001737507642476</v>
       </c>
       <c r="CK22" t="n">
-        <v>9.278223073485261</v>
+        <v>9.278223076676792</v>
       </c>
       <c r="CL22" t="n">
         <v>8.458487178126823</v>
@@ -21664,10 +21664,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.337978108833978</v>
+        <v>3.337978101471955</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.19194939188703</v>
+        <v>6.191949378230475</v>
       </c>
       <c r="CL23" t="n">
         <v>19.28911530241674</v>
@@ -21676,13 +21676,13 @@
         <v>18.18353960554619</v>
       </c>
       <c r="CN23" t="n">
-        <v>20.60183925918205</v>
+        <v>20.6018392600113</v>
       </c>
       <c r="CO23" t="n">
-        <v>15.92145422761735</v>
+        <v>15.92145422909692</v>
       </c>
       <c r="CP23" t="n">
-        <v>12.84225513257595</v>
+        <v>12.84225514191158</v>
       </c>
       <c r="CQ23" t="n">
         <v>29.10394270806049</v>
@@ -21738,7 +21738,7 @@
         <v>-13.64003621653164</v>
       </c>
       <c r="DL23" t="n">
-        <v>-35.19786534004677</v>
+        <v>-35.19787305431846</v>
       </c>
       <c r="DM23" t="b">
         <v>1</v>
@@ -22014,10 +22014,10 @@
         <v>10.86999988555908</v>
       </c>
       <c r="CJ24" t="n">
-        <v>9.410499913334329</v>
+        <v>9.410499909206081</v>
       </c>
       <c r="CK24" t="n">
-        <v>17.45647733923518</v>
+        <v>17.45647733157728</v>
       </c>
       <c r="CL24" t="n">
         <v>21.3058429709553</v>
@@ -22026,25 +22026,25 @@
         <v>12.56746768095365</v>
       </c>
       <c r="CN24" t="n">
-        <v>30.17445896128012</v>
+        <v>30.17445897398767</v>
       </c>
       <c r="CO24" t="n">
-        <v>25.20917158818038</v>
+        <v>25.20917159130531</v>
       </c>
       <c r="CP24" t="n">
-        <v>11.01207334198808</v>
+        <v>11.01207335534973</v>
       </c>
       <c r="CQ24" t="n">
         <v>9.338337918096139</v>
       </c>
       <c r="CR24" t="n">
-        <v>17.05929121425289</v>
+        <v>17.05929121642889</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.01197251009441</v>
+        <v>15.01197250626546</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.51077525908497</v>
+        <v>13.51077525563892</v>
       </c>
       <c r="CU24" t="n">
         <v>8</v>
@@ -22056,10 +22056,10 @@
         <v>3.2</v>
       </c>
       <c r="CX24" t="n">
-        <v>24.29416192574381</v>
+        <v>24.29416189404137</v>
       </c>
       <c r="CY24" t="n">
-        <v>56.93920325534094</v>
+        <v>56.9392032753593</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -22382,10 +22382,10 @@
         <v>14.68000030517578</v>
       </c>
       <c r="CJ25" t="n">
-        <v>4.507867421528296</v>
+        <v>4.507867423275931</v>
       </c>
       <c r="CK25" t="n">
-        <v>8.36209406693499</v>
+        <v>8.36209407017685</v>
       </c>
       <c r="CL25" t="n">
         <v>23.72073220043647</v>
@@ -22394,25 +22394,25 @@
         <v>19.98846940520332</v>
       </c>
       <c r="CN25" t="n">
-        <v>28.64206399895949</v>
+        <v>28.64206399752209</v>
       </c>
       <c r="CO25" t="n">
-        <v>16.68542399610983</v>
+        <v>16.68542399574093</v>
       </c>
       <c r="CP25" t="n">
-        <v>17.94838051608192</v>
+        <v>17.9483805133029</v>
       </c>
       <c r="CQ25" t="n">
         <v>14.42556031369228</v>
       </c>
       <c r="CR25" t="n">
-        <v>18.53896064248833</v>
+        <v>18.53896064229641</v>
       </c>
       <c r="CS25" t="n">
-        <v>17.94838051608192</v>
+        <v>17.9483805133029</v>
       </c>
       <c r="CT25" t="n">
-        <v>16.15354246447373</v>
+        <v>16.15354246197261</v>
       </c>
       <c r="CU25" t="n">
         <v>7</v>
@@ -22424,10 +22424,10 @@
         <v>6.4</v>
       </c>
       <c r="CX25" t="n">
-        <v>10.03775292006239</v>
+        <v>10.0377529030248</v>
       </c>
       <c r="CY25" t="n">
-        <v>26.28719521178742</v>
+        <v>26.28719521048004</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>1</v>
       </c>
       <c r="AW27" t="n">
-        <v>10181245952</v>
+        <v>10181462016</v>
       </c>
       <c r="AX27" t="n">
         <v>14.61</v>
@@ -23090,10 +23090,10 @@
         <v>14.39999961853027</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.032620984984016</v>
+        <v>9.032620997008863</v>
       </c>
       <c r="CK27" t="n">
-        <v>16.75551192714535</v>
+        <v>16.75551194945144</v>
       </c>
       <c r="CL27" t="n">
         <v>13.05954790866024</v>
@@ -23114,7 +23114,7 @@
         <v>5.995386443060455</v>
       </c>
       <c r="CR27" t="n">
-        <v>11.10312102025261</v>
+        <v>11.10312102515703</v>
       </c>
       <c r="CS27" t="n">
         <v>10.62271216510394</v>
@@ -23135,7 +23135,7 @@
         <v>-33.60804720931423</v>
       </c>
       <c r="CY27" t="n">
-        <v>-22.89499087232724</v>
+        <v>-22.89499083826878</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -23446,10 +23446,10 @@
         <v>27.3799991607666</v>
       </c>
       <c r="CJ28" t="n">
-        <v>7.255085131110492</v>
+        <v>7.255085089269031</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.45818291820996</v>
+        <v>13.45818284059405</v>
       </c>
       <c r="CL28" t="n">
         <v>35.08558886655294</v>
@@ -23458,19 +23458,19 @@
         <v>27.73936337556392</v>
       </c>
       <c r="CN28" t="n">
-        <v>43.31704739419273</v>
+        <v>43.31704745774301</v>
       </c>
       <c r="CO28" t="n">
-        <v>26.42844994811291</v>
+        <v>26.42844995876278</v>
       </c>
       <c r="CP28" t="n">
-        <v>28.1271777904963</v>
+        <v>28.12717786605194</v>
       </c>
       <c r="CQ28" t="n">
         <v>24.00811791962647</v>
       </c>
       <c r="CR28" t="n">
-        <v>28.30913260182217</v>
+        <v>28.30913261212787</v>
       </c>
       <c r="CS28" t="n">
         <v>27.73936337556392</v>
@@ -23491,7 +23491,7 @@
         <v>-8.818744327132677</v>
       </c>
       <c r="CY28" t="n">
-        <v>3.393475053085271</v>
+        <v>3.393475090724785</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -23814,10 +23814,10 @@
         <v>22.28000068664551</v>
       </c>
       <c r="CJ29" t="n">
-        <v>3.140372323820429</v>
+        <v>3.140372325447475</v>
       </c>
       <c r="CK29" t="n">
-        <v>5.825390660686896</v>
+        <v>5.825390663705067</v>
       </c>
       <c r="CL29" t="n">
         <v>32.87416582383663</v>
@@ -23826,7 +23826,7 @@
         <v>27.45530789964172</v>
       </c>
       <c r="CN29" t="n">
-        <v>42.11194018186733</v>
+        <v>42.11194018440393</v>
       </c>
       <c r="CO29" t="n">
         <v>10.85340539909456</v>
@@ -24144,10 +24144,10 @@
         <v>40.02000045776367</v>
       </c>
       <c r="CJ30" t="n">
-        <v>36.63430058651684</v>
+        <v>36.63430051030803</v>
       </c>
       <c r="CK30" t="n">
-        <v>53.33954165396852</v>
+        <v>53.33954154300849</v>
       </c>
       <c r="CL30" t="n">
         <v>48.73630032327193</v>
@@ -24164,13 +24164,13 @@
       </c>
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="n">
-        <v>49.55357688689375</v>
+        <v>49.55357684010154</v>
       </c>
       <c r="CS30" t="n">
-        <v>51.03792098862023</v>
+        <v>51.03792093314021</v>
       </c>
       <c r="CT30" t="n">
-        <v>45.93412888975821</v>
+        <v>45.93412883982619</v>
       </c>
       <c r="CU30" t="n">
         <v>4</v>
@@ -24182,10 +24182,10 @@
         <v>1.6</v>
       </c>
       <c r="CX30" t="n">
-        <v>14.77793194489387</v>
+        <v>14.77793182012623</v>
       </c>
       <c r="CY30" t="n">
-        <v>23.82202978531105</v>
+        <v>23.82202966838898</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -24508,10 +24508,10 @@
         <v>23.02000045776367</v>
       </c>
       <c r="CJ31" t="n">
-        <v>11.94334398297249</v>
+        <v>11.94334397385358</v>
       </c>
       <c r="CK31" t="n">
-        <v>22.15490308841397</v>
+        <v>22.15490307149839</v>
       </c>
       <c r="CL31" t="n">
         <v>56.48426038247567</v>
@@ -24520,13 +24520,13 @@
         <v>47.22610297818421</v>
       </c>
       <c r="CN31" t="n">
-        <v>78.27396583459199</v>
+        <v>78.27396583426196</v>
       </c>
       <c r="CO31" t="n">
-        <v>33.6321343398026</v>
+        <v>33.63213434145803</v>
       </c>
       <c r="CP31" t="n">
-        <v>41.12575257775082</v>
+        <v>41.12575259240383</v>
       </c>
       <c r="CQ31" t="n">
         <v>5.143948645500518</v>
@@ -24840,35 +24840,35 @@
         <v>23.10000038146973</v>
       </c>
       <c r="CJ32" t="n">
-        <v>16.5809008518415</v>
+        <v>16.58090079746223</v>
       </c>
       <c r="CK32" t="n">
-        <v>29.63840536255767</v>
+        <v>29.63840537080371</v>
       </c>
       <c r="CL32" t="n">
-        <v>49.98948365584082</v>
+        <v>49.98948383369611</v>
       </c>
       <c r="CM32" t="n">
         <v>49.51516084050021</v>
       </c>
       <c r="CN32" t="n">
-        <v>61.73920146263635</v>
+        <v>61.73920144056483</v>
       </c>
       <c r="CO32" t="n">
-        <v>45.75571211278687</v>
+        <v>45.75571212461092</v>
       </c>
       <c r="CP32" t="n">
-        <v>24.53598510000211</v>
+        <v>24.53598516723664</v>
       </c>
       <c r="CQ32" t="inlineStr"/>
       <c r="CR32" t="n">
-        <v>35.49112549575672</v>
+        <v>35.49112553164325</v>
       </c>
       <c r="CS32" t="n">
-        <v>37.69705873767227</v>
+        <v>37.69705874770732</v>
       </c>
       <c r="CT32" t="n">
-        <v>33.92735286390504</v>
+        <v>33.92735287293659</v>
       </c>
       <c r="CU32" t="n">
         <v>4</v>
@@ -24880,10 +24880,10 @@
         <v>3</v>
       </c>
       <c r="CX32" t="n">
-        <v>46.87165499408719</v>
+        <v>46.8716550331848</v>
       </c>
       <c r="CY32" t="n">
-        <v>53.64123337515985</v>
+        <v>53.6412335305128</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -25194,10 +25194,10 @@
         <v>12.17000007629395</v>
       </c>
       <c r="CJ33" t="n">
-        <v>2.107067437494403</v>
+        <v>2.107067441758303</v>
       </c>
       <c r="CK33" t="n">
-        <v>3.908610096552117</v>
+        <v>3.908610104461651</v>
       </c>
       <c r="CL33" t="n">
         <v>27.14688569206982</v>
@@ -25206,7 +25206,7 @@
         <v>23.00571232673531</v>
       </c>
       <c r="CN33" t="n">
-        <v>35.69847563456747</v>
+        <v>35.69847564461707</v>
       </c>
       <c r="CO33" t="n">
         <v>9.158754146</v>
@@ -25540,10 +25540,10 @@
         <v>32.75</v>
       </c>
       <c r="CJ34" t="n">
-        <v>7.76716688307775</v>
+        <v>7.767166837618775</v>
       </c>
       <c r="CK34" t="n">
-        <v>14.40809456810923</v>
+        <v>14.40809448378283</v>
       </c>
       <c r="CL34" t="n">
         <v>61.90263908701854</v>
@@ -25552,7 +25552,7 @@
         <v>36.11117259360064</v>
       </c>
       <c r="CN34" t="n">
-        <v>85.59063286206684</v>
+        <v>85.59063277127859</v>
       </c>
       <c r="CO34" t="n">
         <v>22.51480113099953</v>
@@ -25886,10 +25886,10 @@
         <v>33.20000076293945</v>
       </c>
       <c r="CJ35" t="n">
-        <v>15.04507766193056</v>
+        <v>15.04507768481396</v>
       </c>
       <c r="CK35" t="n">
-        <v>27.90861906288119</v>
+        <v>27.9086191053299</v>
       </c>
       <c r="CL35" t="n">
         <v>19.77078697118866</v>
@@ -25898,7 +25898,7 @@
         <v>36.42710872951999</v>
       </c>
       <c r="CN35" t="n">
-        <v>26.62611667599243</v>
+        <v>26.62611669039097</v>
       </c>
       <c r="CO35" t="n">
         <v>15.03391666666667</v>
@@ -25910,7 +25910,7 @@
         <v>78.26206757492224</v>
       </c>
       <c r="CR35" t="n">
-        <v>22.22625156272934</v>
+        <v>22.22625157411943</v>
       </c>
       <c r="CS35" t="n">
         <v>19.77078697118866</v>
@@ -25931,7 +25931,7 @@
         <v>-46.40449438202248</v>
       </c>
       <c r="CY35" t="n">
-        <v>-33.05346068684404</v>
+        <v>-33.05346065253653</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -26250,10 +26250,10 @@
         <v>34.40999984741211</v>
       </c>
       <c r="CJ36" t="n">
-        <v>3.414124725457547</v>
+        <v>3.41412471707062</v>
       </c>
       <c r="CK36" t="n">
-        <v>6.333201365723748</v>
+        <v>6.333201350166</v>
       </c>
       <c r="CL36" t="n">
         <v>31.64000679932063</v>
@@ -26262,7 +26262,7 @@
         <v>22.17430500376899</v>
       </c>
       <c r="CN36" t="n">
-        <v>39.1358600879658</v>
+        <v>39.13586007981751</v>
       </c>
       <c r="CO36" t="n">
         <v>10.59424454785779</v>
@@ -26324,7 +26324,7 @@
         <v>-0.8071455473661948</v>
       </c>
       <c r="DL36" t="n">
-        <v>-27.83707532184228</v>
+        <v>-27.83708127316356</v>
       </c>
       <c r="DM36" t="b">
         <v>1</v>
@@ -26580,35 +26580,35 @@
         <v>12.94999980926514</v>
       </c>
       <c r="CJ37" t="n">
-        <v>8.694392951335713</v>
+        <v>8.694392891896392</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.60549911404338</v>
+        <v>13.60549918038555</v>
       </c>
       <c r="CL37" t="n">
-        <v>17.8923925771369</v>
+        <v>17.89239278670407</v>
       </c>
       <c r="CM37" t="n">
         <v>17.23601780571541</v>
       </c>
       <c r="CN37" t="n">
-        <v>22.47099640849115</v>
+        <v>22.47099646673388</v>
       </c>
       <c r="CO37" t="n">
-        <v>17.30064966242656</v>
+        <v>17.30064967906669</v>
       </c>
       <c r="CP37" t="n">
-        <v>8.943457156765485</v>
+        <v>8.943457258031069</v>
       </c>
       <c r="CQ37" t="inlineStr"/>
       <c r="CR37" t="n">
-        <v>14.37323357623564</v>
+        <v>14.37323363451318</v>
       </c>
       <c r="CS37" t="n">
-        <v>15.45307438823497</v>
+        <v>15.45307442972612</v>
       </c>
       <c r="CT37" t="n">
-        <v>13.90776694941147</v>
+        <v>13.90776698675351</v>
       </c>
       <c r="CU37" t="n">
         <v>4</v>
@@ -26620,10 +26620,10 @@
         <v>2.1</v>
       </c>
       <c r="CX37" t="n">
-        <v>7.395885361026022</v>
+        <v>7.395885649381517</v>
       </c>
       <c r="CY37" t="n">
-        <v>10.99022230063853</v>
+        <v>10.99022275065813</v>
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
@@ -26946,10 +26946,10 @@
         <v>5.920000076293945</v>
       </c>
       <c r="CJ38" t="n">
-        <v>7.02162031798788</v>
+        <v>7.021620245364706</v>
       </c>
       <c r="CK38" t="n">
-        <v>13.02510568986752</v>
+        <v>13.02510555515153</v>
       </c>
       <c r="CL38" t="n">
         <v>5.692307765667254</v>
@@ -26970,7 +26970,7 @@
         <v>5.41527423888321</v>
       </c>
       <c r="CR38" t="n">
-        <v>7.373583671919927</v>
+        <v>7.373583646002531</v>
       </c>
       <c r="CS38" t="n">
         <v>5.912820549500294</v>
@@ -26991,7 +26991,7 @@
         <v>-10.10914820998331</v>
       </c>
       <c r="CY38" t="n">
-        <v>24.55377663670502</v>
+        <v>24.55377619891117</v>
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
@@ -27288,10 +27288,10 @@
         <v>39.5018196105957</v>
       </c>
       <c r="CJ39" t="n">
-        <v>20.2039654163783</v>
+        <v>20.20396550318609</v>
       </c>
       <c r="CK39" t="n">
-        <v>37.47835584738174</v>
+        <v>37.47835600841019</v>
       </c>
       <c r="CL39" t="n">
         <v>55.97851442143241</v>
@@ -27300,23 +27300,23 @@
         <v>42.28563995842689</v>
       </c>
       <c r="CN39" t="n">
-        <v>61.59747852382779</v>
+        <v>61.59747838097049</v>
       </c>
       <c r="CO39" t="n">
-        <v>45.15222537147327</v>
+        <v>45.58224653808353</v>
       </c>
       <c r="CP39" t="n">
-        <v>30.98915238410255</v>
+        <v>30.98915221260507</v>
       </c>
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="n">
-        <v>39.70326526416643</v>
+        <v>39.81077061777805</v>
       </c>
       <c r="CS39" t="n">
-        <v>41.31529060942751</v>
+        <v>41.53030127324686</v>
       </c>
       <c r="CT39" t="n">
-        <v>37.18376154848476</v>
+        <v>37.37727114592218</v>
       </c>
       <c r="CU39" t="n">
         <v>4</v>
@@ -27328,10 +27328,10 @@
         <v>2.8</v>
       </c>
       <c r="CX39" t="n">
-        <v>-5.868231096597798</v>
+        <v>-5.378355948199531</v>
       </c>
       <c r="CY39" t="n">
-        <v>0.5099655042642537</v>
+        <v>0.7821184194246156</v>
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>-2.226610650473015</v>
       </c>
       <c r="DL39" t="n">
-        <v>-18.84844460254175</v>
+        <v>-18.8484510008869</v>
       </c>
       <c r="DM39" t="b">
         <v>1</v>
@@ -27626,10 +27626,10 @@
         <v>15.17000007629395</v>
       </c>
       <c r="CJ40" t="n">
-        <v>9.430280392303015</v>
+        <v>9.430280365724084</v>
       </c>
       <c r="CK40" t="n">
-        <v>17.49317012772209</v>
+        <v>17.49317007841817</v>
       </c>
       <c r="CL40" t="n">
         <v>30.9711095548374</v>
@@ -27638,23 +27638,23 @@
         <v>29.4483238128629</v>
       </c>
       <c r="CN40" t="n">
-        <v>34.71574761304258</v>
+        <v>34.71574760828589</v>
       </c>
       <c r="CO40" t="n">
-        <v>25.47771500457578</v>
+        <v>25.47771500997475</v>
       </c>
       <c r="CP40" t="n">
-        <v>15.27881615890105</v>
+        <v>15.27881619195036</v>
       </c>
       <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="n">
-        <v>20.84306876985957</v>
+        <v>20.8430687522386</v>
       </c>
       <c r="CS40" t="n">
-        <v>21.48544256614893</v>
+        <v>21.48544254419646</v>
       </c>
       <c r="CT40" t="n">
-        <v>19.33689830953404</v>
+        <v>19.33689828977682</v>
       </c>
       <c r="CU40" t="n">
         <v>4</v>
@@ -27666,10 +27666,10 @@
         <v>3.3</v>
       </c>
       <c r="CX40" t="n">
-        <v>27.46801722006367</v>
+        <v>27.46801708982489</v>
       </c>
       <c r="CY40" t="n">
-        <v>37.39662930147831</v>
+        <v>37.39662918532163</v>
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>0.6635725513920887</v>
       </c>
       <c r="DL40" t="n">
-        <v>-16.60347445371087</v>
+        <v>-16.60345638373696</v>
       </c>
       <c r="DM40" t="b">
         <v>1</v>
@@ -27984,10 +27984,10 @@
         <v>12.77999973297119</v>
       </c>
       <c r="CJ41" t="n">
-        <v>1.574362040737032</v>
+        <v>1.574362030108104</v>
       </c>
       <c r="CK41" t="n">
-        <v>2.920441585567194</v>
+        <v>2.920441565850533</v>
       </c>
       <c r="CL41" t="n">
         <v>12.71283757221233</v>
@@ -27996,7 +27996,7 @@
         <v>9.285279950653386</v>
       </c>
       <c r="CN41" t="n">
-        <v>16.04662646883531</v>
+        <v>16.04662645766376</v>
       </c>
       <c r="CO41" t="n">
         <v>6.104046666666666</v>
@@ -28330,37 +28330,37 @@
         <v>26.70000076293945</v>
       </c>
       <c r="CJ42" t="n">
-        <v>17.07331076704757</v>
+        <v>17.07331075788889</v>
       </c>
       <c r="CK42" t="n">
-        <v>28.37657059222237</v>
+        <v>28.37657059110066</v>
       </c>
       <c r="CL42" t="n">
-        <v>47.6654563899052</v>
+        <v>47.66545641359029</v>
       </c>
       <c r="CM42" t="n">
         <v>53.26994486941398</v>
       </c>
       <c r="CN42" t="n">
-        <v>56.59469224000675</v>
+        <v>56.59469223702227</v>
       </c>
       <c r="CO42" t="n">
-        <v>42.94865306694228</v>
+        <v>42.94865306860028</v>
       </c>
       <c r="CP42" t="n">
-        <v>23.70643965541214</v>
+        <v>23.70643966565593</v>
       </c>
       <c r="CQ42" t="n">
         <v>31.19288727261046</v>
       </c>
       <c r="CR42" t="n">
-        <v>37.60349435669509</v>
+        <v>37.60349435948535</v>
       </c>
       <c r="CS42" t="n">
-        <v>37.07077016977637</v>
+        <v>37.07077017060537</v>
       </c>
       <c r="CT42" t="n">
-        <v>33.36369315279873</v>
+        <v>33.36369315354484</v>
       </c>
       <c r="CU42" t="n">
         <v>8</v>
@@ -28372,10 +28372,10 @@
         <v>3.3</v>
       </c>
       <c r="CX42" t="n">
-        <v>24.9576486870694</v>
+        <v>24.95764868986381</v>
       </c>
       <c r="CY42" t="n">
-        <v>40.83705349136197</v>
+        <v>40.83705350181237</v>
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
@@ -28690,37 +28690,37 @@
         <v>15.02999973297119</v>
       </c>
       <c r="CJ43" t="n">
-        <v>5.830932713942503</v>
+        <v>5.830932729568524</v>
       </c>
       <c r="CK43" t="n">
-        <v>8.573470631141689</v>
+        <v>8.573470617782714</v>
       </c>
       <c r="CL43" t="n">
-        <v>11.023171234206</v>
+        <v>11.02317118748953</v>
       </c>
       <c r="CM43" t="n">
         <v>11.59516036634579</v>
       </c>
       <c r="CN43" t="n">
-        <v>9.992440030131663</v>
+        <v>9.992440005155867</v>
       </c>
       <c r="CO43" t="n">
-        <v>14.93936638791466</v>
+        <v>14.93936638241032</v>
       </c>
       <c r="CP43" t="n">
-        <v>5.501588200780516</v>
+        <v>5.501588175478861</v>
       </c>
       <c r="CQ43" t="n">
         <v>10.90166010084689</v>
       </c>
       <c r="CR43" t="n">
-        <v>9.794723708163716</v>
+        <v>9.794723695634811</v>
       </c>
       <c r="CS43" t="n">
-        <v>10.44705006548928</v>
+        <v>10.44705005300138</v>
       </c>
       <c r="CT43" t="n">
-        <v>9.402345058940352</v>
+        <v>9.402345047701242</v>
       </c>
       <c r="CU43" t="n">
         <v>8</v>
@@ -28732,10 +28732,10 @@
         <v>2.7</v>
       </c>
       <c r="CX43" t="n">
-        <v>-37.44281286769087</v>
+        <v>-37.44281294246871</v>
       </c>
       <c r="CY43" t="n">
-        <v>-34.83217643259762</v>
+        <v>-34.83217651595692</v>
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
@@ -29050,10 +29050,10 @@
         <v>11.73999977111816</v>
       </c>
       <c r="CJ44" t="n">
-        <v>4.772256367513212</v>
+        <v>4.772256365009031</v>
       </c>
       <c r="CK44" t="n">
-        <v>8.852535561737009</v>
+        <v>8.852535557091754</v>
       </c>
       <c r="CL44" t="n">
         <v>25.04911384336806</v>
@@ -29062,25 +29062,25 @@
         <v>28.15420526956483</v>
       </c>
       <c r="CN44" t="n">
-        <v>23.16590016263882</v>
+        <v>23.16590016055177</v>
       </c>
       <c r="CO44" t="n">
-        <v>14.15725438193565</v>
+        <v>14.15725438218572</v>
       </c>
       <c r="CP44" t="n">
-        <v>12.84913870542993</v>
+        <v>12.84913870766666</v>
       </c>
       <c r="CQ44" t="n">
         <v>4.799038879412761</v>
       </c>
       <c r="CR44" t="n">
-        <v>18.70469132077905</v>
+        <v>18.70469132007146</v>
       </c>
       <c r="CS44" t="n">
-        <v>18.66157727228724</v>
+        <v>18.66157727136874</v>
       </c>
       <c r="CT44" t="n">
-        <v>16.79541954505851</v>
+        <v>16.79541954423187</v>
       </c>
       <c r="CU44" t="n">
         <v>6</v>
@@ -29092,10 +29092,10 @@
         <v>5.9</v>
       </c>
       <c r="CX44" t="n">
-        <v>43.06149806218311</v>
+        <v>43.06149805514183</v>
       </c>
       <c r="CY44" t="n">
-        <v>59.32446069372914</v>
+        <v>59.32446068770201</v>
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
@@ -29406,37 +29406,37 @@
         <v>38.68000030517578</v>
       </c>
       <c r="CJ45" t="n">
-        <v>30.83210609800769</v>
+        <v>30.83210615527411</v>
       </c>
       <c r="CK45" t="n">
-        <v>35.07524628662182</v>
+        <v>35.07524624264288</v>
       </c>
       <c r="CL45" t="n">
-        <v>37.91416013116773</v>
+        <v>37.91416001320885</v>
       </c>
       <c r="CM45" t="n">
         <v>49.31082028143746</v>
       </c>
       <c r="CN45" t="n">
-        <v>59.1049602948329</v>
+        <v>59.10496023007499</v>
       </c>
       <c r="CO45" t="n">
-        <v>16.5796450461548</v>
+        <v>16.57964504050243</v>
       </c>
       <c r="CP45" t="n">
-        <v>16.88731348929585</v>
+        <v>16.88731338780143</v>
       </c>
       <c r="CQ45" t="n">
         <v>28.54488443199322</v>
       </c>
       <c r="CR45" t="n">
-        <v>34.28114200743894</v>
+        <v>34.28114197286692</v>
       </c>
       <c r="CS45" t="n">
-        <v>32.95367619231476</v>
+        <v>32.9536761989585</v>
       </c>
       <c r="CT45" t="n">
-        <v>29.65830857308329</v>
+        <v>29.65830857906265</v>
       </c>
       <c r="CU45" t="n">
         <v>8</v>
@@ -29448,10 +29448,10 @@
         <v>3.6</v>
       </c>
       <c r="CX45" t="n">
-        <v>-23.32391846151382</v>
+        <v>-23.32391844605528</v>
       </c>
       <c r="CY45" t="n">
-        <v>-11.37243604713268</v>
+        <v>-11.37243613651225</v>
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>-0.667689601187782</v>
       </c>
       <c r="DL45" t="n">
-        <v>-11.71364092295562</v>
+        <v>-11.71364879963919</v>
       </c>
       <c r="DM45" t="b">
         <v>1</v>
@@ -29766,10 +29766,10 @@
         <v>9.279999732971191</v>
       </c>
       <c r="CJ46" t="n">
-        <v>2.530273381107185</v>
+        <v>2.530273383083899</v>
       </c>
       <c r="CK46" t="n">
-        <v>4.693657121953827</v>
+        <v>4.693657125620631</v>
       </c>
       <c r="CL46" t="n">
         <v>13.27861732849549</v>
@@ -29778,25 +29778,25 @@
         <v>15.00003440426151</v>
       </c>
       <c r="CN46" t="n">
-        <v>10.31764099556944</v>
+        <v>10.31764099578506</v>
       </c>
       <c r="CO46" t="n">
-        <v>7.305089435384939</v>
+        <v>7.305089435195109</v>
       </c>
       <c r="CP46" t="n">
-        <v>6.757993203545821</v>
+        <v>6.757993201802833</v>
       </c>
       <c r="CQ46" t="n">
         <v>10.43331654384748</v>
       </c>
       <c r="CR46" t="n">
-        <v>9.683764147579788</v>
+        <v>9.683764147858302</v>
       </c>
       <c r="CS46" t="n">
-        <v>10.31764099556944</v>
+        <v>10.31764099578506</v>
       </c>
       <c r="CT46" t="n">
-        <v>9.285876896012498</v>
+        <v>9.285876896206554</v>
       </c>
       <c r="CU46" t="n">
         <v>7</v>
@@ -29808,10 +29808,10 @@
         <v>5.9</v>
       </c>
       <c r="CX46" t="n">
-        <v>0.06333150011228472</v>
+        <v>0.06333150220341199</v>
       </c>
       <c r="CY46" t="n">
-        <v>4.350909765374777</v>
+        <v>4.350909768375999</v>
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
@@ -30122,10 +30122,10 @@
         <v>33.38000106811523</v>
       </c>
       <c r="CJ47" t="n">
-        <v>14.45460462730396</v>
+        <v>14.45460463669485</v>
       </c>
       <c r="CK47" t="n">
-        <v>26.81329158364885</v>
+        <v>26.81329160106896</v>
       </c>
       <c r="CL47" t="n">
         <v>54.20159487163318</v>
@@ -30134,25 +30134,25 @@
         <v>41.89994969714121</v>
       </c>
       <c r="CN47" t="n">
-        <v>69.22029413300554</v>
+        <v>69.22029412086393</v>
       </c>
       <c r="CO47" t="n">
-        <v>38.39264062446339</v>
+        <v>38.39264062207143</v>
       </c>
       <c r="CP47" t="n">
-        <v>38.84957660159772</v>
+        <v>38.84957658383841</v>
       </c>
       <c r="CQ47" t="n">
         <v>21.08922927558395</v>
       </c>
       <c r="CR47" t="n">
-        <v>41.49522525529625</v>
+        <v>41.49522525317158</v>
       </c>
       <c r="CS47" t="n">
-        <v>38.84957660159772</v>
+        <v>38.84957658383841</v>
       </c>
       <c r="CT47" t="n">
-        <v>34.96461894143795</v>
+        <v>34.96461892545457</v>
       </c>
       <c r="CU47" t="n">
         <v>7</v>
@@ -30164,10 +30164,10 @@
         <v>4.8</v>
       </c>
       <c r="CX47" t="n">
-        <v>4.747207377522678</v>
+        <v>4.74720732963958</v>
       </c>
       <c r="CY47" t="n">
-        <v>24.31163549282427</v>
+        <v>24.31163548645914</v>
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
@@ -30476,10 +30476,10 @@
         <v>6.550000190734863</v>
       </c>
       <c r="CJ48" t="n">
-        <v>7.793139984833482</v>
+        <v>7.793140005521171</v>
       </c>
       <c r="CK48" t="n">
-        <v>11.34681181791755</v>
+        <v>11.34681184803883</v>
       </c>
       <c r="CL48" t="n">
         <v>8.052009690737892</v>
@@ -30498,7 +30498,7 @@
         <v>5.354239830150741</v>
       </c>
       <c r="CR48" t="n">
-        <v>8.367187729085597</v>
+        <v>8.367187737553758</v>
       </c>
       <c r="CS48" t="n">
         <v>8.416227402183392</v>
@@ -30519,7 +30519,7 @@
         <v>15.64281589914329</v>
       </c>
       <c r="CY48" t="n">
-        <v>27.74332038831373</v>
+        <v>27.74332051759863</v>
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
@@ -30812,35 +30812,35 @@
         <v>17.07999992370605</v>
       </c>
       <c r="CJ49" t="n">
-        <v>10.16567243419626</v>
+        <v>10.16567237210966</v>
       </c>
       <c r="CK49" t="n">
-        <v>17.61110253190278</v>
+        <v>17.61110254236791</v>
       </c>
       <c r="CL49" t="n">
-        <v>28.75563244166521</v>
+        <v>28.75563263437715</v>
       </c>
       <c r="CM49" t="n">
         <v>29.30345201543657</v>
       </c>
       <c r="CN49" t="n">
-        <v>32.08888080437558</v>
+        <v>32.08888080893509</v>
       </c>
       <c r="CO49" t="n">
-        <v>27.8717377347679</v>
+        <v>27.87173774873406</v>
       </c>
       <c r="CP49" t="n">
-        <v>14.20689954986044</v>
+        <v>14.20689962706141</v>
       </c>
       <c r="CQ49" t="inlineStr"/>
       <c r="CR49" t="n">
-        <v>21.10103628563304</v>
+        <v>21.10103632439719</v>
       </c>
       <c r="CS49" t="n">
-        <v>22.74142013333534</v>
+        <v>22.74142014555098</v>
       </c>
       <c r="CT49" t="n">
-        <v>20.46727812000181</v>
+        <v>20.46727813099589</v>
       </c>
       <c r="CU49" t="n">
         <v>4</v>
@@ -30852,10 +30852,10 @@
         <v>2.8</v>
       </c>
       <c r="CX49" t="n">
-        <v>19.83183964535273</v>
+        <v>19.83183970972087</v>
       </c>
       <c r="CY49" t="n">
-        <v>23.54236756374932</v>
+        <v>23.54236779070573</v>
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>-1.328709123815142</v>
       </c>
       <c r="DL49" t="n">
-        <v>-19.58181543685118</v>
+        <v>-19.58182280530835</v>
       </c>
       <c r="DM49" t="b">
         <v>1</v>
@@ -31170,10 +31170,10 @@
         <v>32.70000076293945</v>
       </c>
       <c r="CJ50" t="n">
-        <v>11.11179107006598</v>
+        <v>11.1117911199577</v>
       </c>
       <c r="CK50" t="n">
-        <v>20.6123724349724</v>
+        <v>20.61237252752154</v>
       </c>
       <c r="CL50" t="n">
         <v>55.69087533534032</v>
@@ -31182,19 +31182,19 @@
         <v>52.54606660988762</v>
       </c>
       <c r="CN50" t="n">
-        <v>58.06561444807646</v>
+        <v>58.06561443741389</v>
       </c>
       <c r="CO50" t="n">
-        <v>28.27593776329305</v>
+        <v>28.2759378840555</v>
       </c>
       <c r="CP50" t="n">
-        <v>35.15802053135249</v>
+        <v>35.15802046821751</v>
       </c>
       <c r="CQ50" t="n">
         <v>54.68623962474753</v>
       </c>
       <c r="CR50" t="n">
-        <v>43.57644667823855</v>
+        <v>43.57644669816914</v>
       </c>
       <c r="CS50" t="n">
         <v>52.54606660988762</v>
@@ -31215,7 +31215,7 @@
         <v>44.62219830433958</v>
       </c>
       <c r="CY50" t="n">
-        <v>33.26130171723396</v>
+        <v>33.26130177818376</v>
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
@@ -31534,37 +31534,37 @@
         <v>44.79999923706055</v>
       </c>
       <c r="CJ51" t="n">
-        <v>32.50257843225724</v>
+        <v>32.5025784223838</v>
       </c>
       <c r="CK51" t="n">
-        <v>44.74764030437347</v>
+        <v>44.74764032344584</v>
       </c>
       <c r="CL51" t="n">
-        <v>51.52715683912498</v>
+        <v>51.52715687673953</v>
       </c>
       <c r="CM51" t="n">
         <v>48.34282089554348</v>
       </c>
       <c r="CN51" t="n">
-        <v>71.44157073374672</v>
+        <v>71.44157075411339</v>
       </c>
       <c r="CO51" t="n">
-        <v>59.88947340102621</v>
+        <v>59.8894734050616</v>
       </c>
       <c r="CP51" t="n">
-        <v>25.45084453315852</v>
+        <v>25.45084455612257</v>
       </c>
       <c r="CQ51" t="n">
         <v>78.21945723086839</v>
       </c>
       <c r="CR51" t="n">
-        <v>51.51519279626238</v>
+        <v>51.51519280803483</v>
       </c>
       <c r="CS51" t="n">
-        <v>49.93498886733423</v>
+        <v>49.9349888861415</v>
       </c>
       <c r="CT51" t="n">
-        <v>44.94148998060081</v>
+        <v>44.94148999752736</v>
       </c>
       <c r="CU51" t="n">
         <v>8</v>
@@ -31576,10 +31576,10 @@
         <v>3.1</v>
       </c>
       <c r="CX51" t="n">
-        <v>0.3158275579237424</v>
+        <v>0.3158275957062084</v>
       </c>
       <c r="CY51" t="n">
-        <v>14.98927159276986</v>
+        <v>14.98927161904764</v>
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
@@ -31894,37 +31894,37 @@
         <v>10.89000034332275</v>
       </c>
       <c r="CJ52" t="n">
-        <v>8.332366134251071</v>
+        <v>8.332366134717367</v>
       </c>
       <c r="CK52" t="n">
-        <v>11.54775601479417</v>
+        <v>11.54775601491527</v>
       </c>
       <c r="CL52" t="n">
-        <v>16.84415146636343</v>
+        <v>16.84415146559745</v>
       </c>
       <c r="CM52" t="n">
         <v>24.06372840589797</v>
       </c>
       <c r="CN52" t="n">
-        <v>24.2515032986743</v>
+        <v>24.25150329895925</v>
       </c>
       <c r="CO52" t="n">
-        <v>20.995164996001</v>
+        <v>20.9951649959134</v>
       </c>
       <c r="CP52" t="n">
-        <v>8.332401460735218</v>
+        <v>8.332401460273175</v>
       </c>
       <c r="CQ52" t="n">
         <v>9.730400983158669</v>
       </c>
       <c r="CR52" t="n">
-        <v>15.51218409498448</v>
+        <v>15.51218409492907</v>
       </c>
       <c r="CS52" t="n">
-        <v>14.1959537405788</v>
+        <v>14.19595374025636</v>
       </c>
       <c r="CT52" t="n">
-        <v>12.77635836652092</v>
+        <v>12.77635836623072</v>
       </c>
       <c r="CU52" t="n">
         <v>8</v>
@@ -31936,10 +31936,10 @@
         <v>2.9</v>
       </c>
       <c r="CX52" t="n">
-        <v>17.32192804157984</v>
+        <v>17.32192803891506</v>
       </c>
       <c r="CY52" t="n">
-        <v>42.44429390211941</v>
+        <v>42.44429390161062</v>
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
@@ -32244,10 +32244,10 @@
         <v>53.58000183105469</v>
       </c>
       <c r="CJ53" t="n">
-        <v>10.4762603651497</v>
+        <v>10.47626032182234</v>
       </c>
       <c r="CK53" t="n">
-        <v>19.43346297735269</v>
+        <v>19.43346289698045</v>
       </c>
       <c r="CL53" t="n">
         <v>60.73011328156327</v>
@@ -32256,7 +32256,7 @@
         <v>45.40663627814871</v>
       </c>
       <c r="CN53" t="n">
-        <v>81.29749123848728</v>
+        <v>81.29749118659824</v>
       </c>
       <c r="CO53" t="n">
         <v>11.76833333333333</v>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="CQ53" t="inlineStr"/>
       <c r="CR53" t="n">
-        <v>13.8926855586119</v>
+        <v>13.89268551737871</v>
       </c>
       <c r="CS53" t="n">
         <v>11.76833333333333</v>
@@ -32287,7 +32287,7 @@
         <v>-80.23236349749205</v>
       </c>
       <c r="CY53" t="n">
-        <v>-74.07113646166437</v>
+        <v>-74.07113653862068</v>
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
@@ -32584,10 +32584,10 @@
         <v>30.01000022888184</v>
       </c>
       <c r="CJ54" t="n">
-        <v>15.68694277725812</v>
+        <v>15.68694279428464</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.0992788518138</v>
+        <v>29.099278883398</v>
       </c>
       <c r="CL54" t="n">
         <v>55.61293748708871</v>
@@ -32596,23 +32596,23 @@
         <v>50.30315509462811</v>
       </c>
       <c r="CN54" t="n">
-        <v>62.11186603712093</v>
+        <v>62.1118660330591</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.65076910283077</v>
+        <v>36.65076909979219</v>
       </c>
       <c r="CP54" t="n">
-        <v>30.94726542914714</v>
+        <v>30.94726540563828</v>
       </c>
       <c r="CQ54" t="inlineStr"/>
       <c r="CR54" t="n">
-        <v>34.26248205474785</v>
+        <v>34.26248206614089</v>
       </c>
       <c r="CS54" t="n">
-        <v>32.87502397732229</v>
+        <v>32.87502399159509</v>
       </c>
       <c r="CT54" t="n">
-        <v>29.58752157959006</v>
+        <v>29.58752159243559</v>
       </c>
       <c r="CU54" t="n">
         <v>4</v>
@@ -32624,10 +32624,10 @@
         <v>3.5</v>
       </c>
       <c r="CX54" t="n">
-        <v>-1.4077928892689</v>
+        <v>-1.407792846464739</v>
       </c>
       <c r="CY54" t="n">
-        <v>14.17021590614116</v>
+        <v>14.1702159441053</v>
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>0.2672900865030137</v>
       </c>
       <c r="DL54" t="n">
-        <v>-17.68853399965281</v>
+        <v>-17.68854281697311</v>
       </c>
       <c r="DM54" t="b">
         <v>1</v>
@@ -32952,10 +32952,10 @@
         <v>4.78000020980835</v>
       </c>
       <c r="CJ55" t="n">
-        <v>1.105884093656507</v>
+        <v>1.105884094081563</v>
       </c>
       <c r="CK55" t="n">
-        <v>2.05141499373282</v>
+        <v>2.051414994521299</v>
       </c>
       <c r="CL55" t="n">
         <v>9.640030864529775</v>
@@ -32964,13 +32964,13 @@
         <v>9.075586225783375</v>
       </c>
       <c r="CN55" t="n">
-        <v>10.67250376991099</v>
+        <v>10.67250376995269</v>
       </c>
       <c r="CO55" t="n">
-        <v>4.221651666021244</v>
+        <v>4.221651665976251</v>
       </c>
       <c r="CP55" t="n">
-        <v>7.170782403452104</v>
+        <v>7.170782402908984</v>
       </c>
       <c r="CQ55" t="n">
         <v>6.969578707797512</v>
@@ -33294,10 +33294,10 @@
         <v>24.1299991607666</v>
       </c>
       <c r="CJ56" t="n">
-        <v>4.231713747916599</v>
+        <v>4.23171375625393</v>
       </c>
       <c r="CK56" t="n">
-        <v>7.849829002385292</v>
+        <v>7.849829017851039</v>
       </c>
       <c r="CL56" t="n">
         <v>28.04583235790854</v>
@@ -33306,13 +33306,13 @@
         <v>27.96001968388332</v>
       </c>
       <c r="CN56" t="n">
-        <v>24.90509226646387</v>
+        <v>24.90509226161047</v>
       </c>
       <c r="CO56" t="n">
-        <v>2.969615091521579</v>
+        <v>2.969615091327875</v>
       </c>
       <c r="CP56" t="n">
-        <v>18.04256698647244</v>
+        <v>18.0425669769859</v>
       </c>
       <c r="CQ56" t="n">
         <v>17.75746799357721</v>
@@ -33638,10 +33638,10 @@
         <v>10.69999980926514</v>
       </c>
       <c r="CJ57" t="n">
-        <v>13.32483351699633</v>
+        <v>13.32483352100944</v>
       </c>
       <c r="CK57" t="n">
-        <v>19.40095760074666</v>
+        <v>19.40095760658975</v>
       </c>
       <c r="CL57" t="n">
         <v>16.70870841086448</v>
@@ -33660,7 +33660,7 @@
         <v>14.86682051626305</v>
       </c>
       <c r="CR57" t="n">
-        <v>16.31393970191115</v>
+        <v>16.31393970355385</v>
       </c>
       <c r="CS57" t="n">
         <v>15.78776446356376</v>
@@ -33681,7 +33681,7 @@
         <v>32.79428290179798</v>
       </c>
       <c r="CY57" t="n">
-        <v>52.46672890390987</v>
+        <v>52.46672891926218</v>
       </c>
       <c r="CZ57" t="inlineStr">
         <is>
@@ -34004,10 +34004,10 @@
         <v>49.97999954223633</v>
       </c>
       <c r="CJ58" t="n">
-        <v>8.318203492324766</v>
+        <v>8.318203537609337</v>
       </c>
       <c r="CK58" t="n">
-        <v>15.43026747826244</v>
+        <v>15.43026756226532</v>
       </c>
       <c r="CL58" t="n">
         <v>19.67424224404727</v>
@@ -34016,25 +34016,25 @@
         <v>12.23202482325925</v>
       </c>
       <c r="CN58" t="n">
-        <v>14.08088742847641</v>
+        <v>14.08088723708225</v>
       </c>
       <c r="CO58" t="n">
-        <v>20.63682241277904</v>
+        <v>20.6368223855113</v>
       </c>
       <c r="CP58" t="n">
-        <v>10.6428164333235</v>
+        <v>10.6428163011795</v>
       </c>
       <c r="CQ58" t="n">
         <v>13.15686200775853</v>
       </c>
       <c r="CR58" t="n">
-        <v>14.2715157900289</v>
+        <v>14.27151576233909</v>
       </c>
       <c r="CS58" t="n">
-        <v>13.61887471811747</v>
+        <v>13.61887462242039</v>
       </c>
       <c r="CT58" t="n">
-        <v>12.25698724630572</v>
+        <v>12.25698716017835</v>
       </c>
       <c r="CU58" t="n">
         <v>8</v>
@@ -34046,10 +34046,10 @@
         <v>2.5</v>
       </c>
       <c r="CX58" t="n">
-        <v>-75.47621576917427</v>
+        <v>-75.47621594149795</v>
       </c>
       <c r="CY58" t="n">
-        <v>-71.44554637706919</v>
+        <v>-71.44554643247096</v>
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
@@ -34368,10 +34368,10 @@
         <v>34.81999969482422</v>
       </c>
       <c r="CJ59" t="n">
-        <v>12.29771088658043</v>
+        <v>12.29771088241347</v>
       </c>
       <c r="CK59" t="n">
-        <v>22.8122536946067</v>
+        <v>22.81225368687698</v>
       </c>
       <c r="CL59" t="n">
         <v>41.04670782530435</v>
@@ -34380,25 +34380,25 @@
         <v>33.52046162339458</v>
       </c>
       <c r="CN59" t="n">
-        <v>41.80899892378783</v>
+        <v>41.80899892982762</v>
       </c>
       <c r="CO59" t="n">
-        <v>23.7759143280636</v>
+        <v>24.57327730939855</v>
       </c>
       <c r="CP59" t="n">
-        <v>24.92756551162569</v>
+        <v>24.92756551868452</v>
       </c>
       <c r="CQ59" t="n">
         <v>27.30596254019629</v>
       </c>
       <c r="CR59" t="n">
-        <v>28.43694691669493</v>
+        <v>28.53661728951204</v>
       </c>
       <c r="CS59" t="n">
-        <v>26.11676402591099</v>
+        <v>26.11676402944041</v>
       </c>
       <c r="CT59" t="n">
-        <v>23.50508762331989</v>
+        <v>23.50508762649637</v>
       </c>
       <c r="CU59" t="n">
         <v>8</v>
@@ -34410,10 +34410,10 @@
         <v>3.4</v>
       </c>
       <c r="CX59" t="n">
-        <v>-32.49543989279879</v>
+        <v>-32.49543988367623</v>
       </c>
       <c r="CY59" t="n">
-        <v>-18.33157045971511</v>
+        <v>-18.04532584831171</v>
       </c>
       <c r="CZ59" t="inlineStr">
         <is>
@@ -34724,10 +34724,10 @@
         <v>4.25</v>
       </c>
       <c r="CJ60" t="n">
-        <v>2.760517251263386</v>
+        <v>2.760517252138171</v>
       </c>
       <c r="CK60" t="n">
-        <v>5.12075950109358</v>
+        <v>5.120759502716307</v>
       </c>
       <c r="CL60" t="n">
         <v>13.06554524361949</v>
@@ -34736,13 +34736,13 @@
         <v>14.63912825766184</v>
       </c>
       <c r="CN60" t="n">
-        <v>15.1308319055519</v>
+        <v>15.13083190713444</v>
       </c>
       <c r="CO60" t="n">
-        <v>9.474664848710324</v>
+        <v>9.474664848596472</v>
       </c>
       <c r="CP60" t="n">
-        <v>6.508725010906916</v>
+        <v>6.508725010115549</v>
       </c>
       <c r="CQ60" t="n">
         <v>1.476527849208126</v>
@@ -35070,37 +35070,37 @@
         <v>24.77000045776367</v>
       </c>
       <c r="CJ61" t="n">
-        <v>10.94213062594946</v>
+        <v>10.94213061298856</v>
       </c>
       <c r="CK61" t="n">
-        <v>13.84673159525765</v>
+        <v>13.84673160183639</v>
       </c>
       <c r="CL61" t="n">
-        <v>16.40252492798803</v>
+        <v>16.40252495520976</v>
       </c>
       <c r="CM61" t="n">
         <v>20.87886833295617</v>
       </c>
       <c r="CN61" t="n">
-        <v>16.02102939451337</v>
+        <v>16.02102941201264</v>
       </c>
       <c r="CO61" t="n">
-        <v>23.06891947934167</v>
+        <v>23.06891948315536</v>
       </c>
       <c r="CP61" t="n">
-        <v>7.863807299174953</v>
+        <v>7.863807318530241</v>
       </c>
       <c r="CQ61" t="n">
         <v>18.59237633123597</v>
       </c>
       <c r="CR61" t="n">
-        <v>15.95204849830216</v>
+        <v>15.95204850599064</v>
       </c>
       <c r="CS61" t="n">
-        <v>16.2117771612507</v>
+        <v>16.2117771836112</v>
       </c>
       <c r="CT61" t="n">
-        <v>14.59059944512563</v>
+        <v>14.59059946525008</v>
       </c>
       <c r="CU61" t="n">
         <v>8</v>
@@ -35112,10 +35112,10 @@
         <v>2.9</v>
       </c>
       <c r="CX61" t="n">
-        <v>-41.09568358706876</v>
+        <v>-41.0956835058235</v>
       </c>
       <c r="CY61" t="n">
-        <v>-35.59932093863849</v>
+        <v>-35.59932090759902</v>
       </c>
       <c r="CZ61" t="inlineStr">
         <is>
@@ -35426,37 +35426,37 @@
         <v>29.61000061035156</v>
       </c>
       <c r="CJ62" t="n">
-        <v>13.82349747817716</v>
+        <v>13.82349752151663</v>
       </c>
       <c r="CK62" t="n">
-        <v>14.35866818605365</v>
+        <v>14.35866819488883</v>
       </c>
       <c r="CL62" t="n">
-        <v>15.04713255303149</v>
+        <v>15.04713251511448</v>
       </c>
       <c r="CM62" t="n">
         <v>30.31758334384464</v>
       </c>
       <c r="CN62" t="n">
-        <v>14.18797403645908</v>
+        <v>14.18797401703884</v>
       </c>
       <c r="CO62" t="n">
-        <v>30.44468450550795</v>
+        <v>30.44468449639601</v>
       </c>
       <c r="CP62" t="n">
-        <v>6.004060849902078</v>
+        <v>6.00406081157265</v>
       </c>
       <c r="CQ62" t="n">
         <v>37.94236112090656</v>
       </c>
       <c r="CR62" t="n">
-        <v>17.74051442185372</v>
+        <v>17.74051441433887</v>
       </c>
       <c r="CS62" t="n">
-        <v>14.35866818605365</v>
+        <v>14.35866819488883</v>
       </c>
       <c r="CT62" t="n">
-        <v>12.92280136744829</v>
+        <v>12.92280137539995</v>
       </c>
       <c r="CU62" t="n">
         <v>7</v>
@@ -35468,10 +35468,10 @@
         <v>6.3</v>
       </c>
       <c r="CX62" t="n">
-        <v>-56.35663255295403</v>
+        <v>-56.35663252609938</v>
       </c>
       <c r="CY62" t="n">
-        <v>-40.08607208318769</v>
+        <v>-40.08607210856713</v>
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>-2.817918093619187</v>
       </c>
       <c r="DL62" t="n">
-        <v>-27.91533777463357</v>
+        <v>-27.91534451392703</v>
       </c>
       <c r="DM62" t="b">
         <v>0</v>
@@ -35782,10 +35782,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ63" t="n">
-        <v>8.850909515701334</v>
+        <v>8.850909482615476</v>
       </c>
       <c r="CK63" t="n">
-        <v>16.41843715162597</v>
+        <v>16.41843709025171</v>
       </c>
       <c r="CL63" t="n">
         <v>16.35235520731475</v>
@@ -35794,7 +35794,7 @@
         <v>16.22680053186761</v>
       </c>
       <c r="CN63" t="n">
-        <v>25.87578451960625</v>
+        <v>25.87578448931181</v>
       </c>
       <c r="CO63" t="n">
         <v>19.94489718117502</v>
@@ -35806,7 +35806,7 @@
         <v>16.20629426270699</v>
       </c>
       <c r="CR63" t="n">
-        <v>16.79289068346301</v>
+        <v>16.79289066786869</v>
       </c>
       <c r="CS63" t="n">
         <v>16.28957786959118</v>
@@ -35827,7 +35827,7 @@
         <v>-22.30726321881999</v>
       </c>
       <c r="CY63" t="n">
-        <v>-11.00747251400105</v>
+        <v>-11.00747259664185</v>
       </c>
       <c r="CZ63" t="inlineStr">
         <is>
@@ -36154,35 +36154,35 @@
         <v>3.410000085830688</v>
       </c>
       <c r="CJ64" t="n">
-        <v>2.617517203301139</v>
+        <v>2.617517202568415</v>
       </c>
       <c r="CK64" t="n">
-        <v>2.995865530362893</v>
+        <v>2.995865530132914</v>
       </c>
       <c r="CL64" t="n">
-        <v>3.583269959691505</v>
+        <v>3.583269960419502</v>
       </c>
       <c r="CM64" t="n">
         <v>6.696150695272573</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.400672775121945</v>
+        <v>5.400672774789226</v>
       </c>
       <c r="CO64" t="n">
-        <v>8.464613714785392</v>
+        <v>8.464613714972819</v>
       </c>
       <c r="CP64" t="n">
-        <v>1.604916862277968</v>
+        <v>1.604916862897619</v>
       </c>
       <c r="CQ64" t="inlineStr"/>
       <c r="CR64" t="n">
-        <v>4.480429534401916</v>
+        <v>4.480429534436152</v>
       </c>
       <c r="CS64" t="n">
-        <v>3.583269959691505</v>
+        <v>3.583269960419502</v>
       </c>
       <c r="CT64" t="n">
-        <v>3.224942963722355</v>
+        <v>3.224942964377552</v>
       </c>
       <c r="CU64" t="n">
         <v>7</v>
@@ -36194,10 +36194,10 @@
         <v>5.3</v>
       </c>
       <c r="CX64" t="n">
-        <v>-5.426894939894201</v>
+        <v>-5.426894920680225</v>
       </c>
       <c r="CY64" t="n">
-        <v>31.39089212985951</v>
+        <v>31.39089213086348</v>
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
@@ -36520,10 +36520,10 @@
         <v>35.18000030517578</v>
       </c>
       <c r="CJ65" t="n">
-        <v>10.07312303163065</v>
+        <v>10.07312298285732</v>
       </c>
       <c r="CK65" t="n">
-        <v>18.68564322367486</v>
+        <v>18.68564313320032</v>
       </c>
       <c r="CL65" t="n">
         <v>28.5272340295948</v>
@@ -36532,25 +36532,25 @@
         <v>21.17723585857856</v>
       </c>
       <c r="CN65" t="n">
-        <v>25.90721689304261</v>
+        <v>25.90721701007944</v>
       </c>
       <c r="CO65" t="n">
-        <v>22.68736449336911</v>
+        <v>22.68736450886221</v>
       </c>
       <c r="CP65" t="n">
-        <v>16.61118108673309</v>
+        <v>16.61118118656625</v>
       </c>
       <c r="CQ65" t="n">
         <v>27.23126452034872</v>
       </c>
       <c r="CR65" t="n">
-        <v>21.36253289212155</v>
+        <v>21.36253290376095</v>
       </c>
       <c r="CS65" t="n">
-        <v>21.93230017597384</v>
+        <v>21.93230018372039</v>
       </c>
       <c r="CT65" t="n">
-        <v>19.73907015837645</v>
+        <v>19.73907016534835</v>
       </c>
       <c r="CU65" t="n">
         <v>8</v>
@@ -36562,10 +36562,10 @@
         <v>2.8</v>
       </c>
       <c r="CX65" t="n">
-        <v>-43.8912166368788</v>
+        <v>-43.89121661706103</v>
       </c>
       <c r="CY65" t="n">
-        <v>-39.27648463101738</v>
+        <v>-39.2764845979321</v>
       </c>
       <c r="CZ65" t="inlineStr">
         <is>
@@ -36854,10 +36854,10 @@
         <v>13.14999961853027</v>
       </c>
       <c r="CJ66" t="n">
-        <v>11.12140751604742</v>
+        <v>11.12140754745396</v>
       </c>
       <c r="CK66" t="n">
-        <v>16.19276934336504</v>
+        <v>16.19276938909296</v>
       </c>
       <c r="CL66" t="n">
         <v>15.50566848443479</v>
@@ -36874,13 +36874,13 @@
       </c>
       <c r="CQ66" t="inlineStr"/>
       <c r="CR66" t="n">
-        <v>12.53829466929515</v>
+        <v>12.53829468857876</v>
       </c>
       <c r="CS66" t="n">
-        <v>13.3135380002411</v>
+        <v>13.31353801594437</v>
       </c>
       <c r="CT66" t="n">
-        <v>11.98218420021699</v>
+        <v>11.98218421434994</v>
       </c>
       <c r="CU66" t="n">
         <v>4</v>
@@ -36892,10 +36892,10 @@
         <v>2.2</v>
       </c>
       <c r="CX66" t="n">
-        <v>-8.880725872171569</v>
+        <v>-8.880725764696706</v>
       </c>
       <c r="CY66" t="n">
-        <v>-4.65174879832807</v>
+        <v>-4.651748651684606</v>
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
@@ -37206,10 +37206,10 @@
         <v>8.340000152587891</v>
       </c>
       <c r="CJ67" t="n">
-        <v>1.607882484553667</v>
+        <v>1.607882486513447</v>
       </c>
       <c r="CK67" t="n">
-        <v>2.982622008847051</v>
+        <v>2.982622012482444</v>
       </c>
       <c r="CL67" t="n">
         <v>24.39404018141049</v>
@@ -37218,13 +37218,13 @@
         <v>24.19815257966773</v>
       </c>
       <c r="CN67" t="n">
-        <v>26.08971931808049</v>
+        <v>26.0897193205512</v>
       </c>
       <c r="CO67" t="n">
-        <v>6.710381499896859</v>
+        <v>6.710381499779605</v>
       </c>
       <c r="CP67" t="n">
-        <v>18.19403113380221</v>
+        <v>18.19403113154815</v>
       </c>
       <c r="CQ67" t="n">
         <v>15.56402401821373</v>
@@ -37552,10 +37552,10 @@
         <v>8.439999580383301</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.5022232223091929</v>
+        <v>0.5022232239151386</v>
       </c>
       <c r="CK68" t="n">
-        <v>0.9316240773835527</v>
+        <v>0.931624080362582</v>
       </c>
       <c r="CL68" t="n">
         <v>9.437130332496094</v>
@@ -37564,13 +37564,13 @@
         <v>8.668386285715835</v>
       </c>
       <c r="CN68" t="n">
-        <v>10.35702314720457</v>
+        <v>10.35702314568219</v>
       </c>
       <c r="CO68" t="n">
-        <v>0.7357683741000202</v>
+        <v>0.7357683740689523</v>
       </c>
       <c r="CP68" t="n">
-        <v>8.039858089863383</v>
+        <v>8.039858087713858</v>
       </c>
       <c r="CQ68" t="inlineStr"/>
       <c r="CR68" t="inlineStr"/>
@@ -37902,25 +37902,25 @@
         <v>2.240000009536743</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.6430659526810664</v>
+        <v>0.6430659525574216</v>
       </c>
       <c r="CK69" t="n">
-        <v>0.9085084030131898</v>
+        <v>0.908508402864441</v>
       </c>
       <c r="CL69" t="n">
-        <v>3.343849486925272</v>
+        <v>3.343849487020723</v>
       </c>
       <c r="CM69" t="n">
         <v>6.907675204991913</v>
       </c>
       <c r="CN69" t="n">
-        <v>2.564998455657244</v>
+        <v>2.564998455489631</v>
       </c>
       <c r="CO69" t="n">
-        <v>2.230430075397271</v>
+        <v>2.230430075403012</v>
       </c>
       <c r="CP69" t="n">
-        <v>1.66036457223695</v>
+        <v>1.660364572292551</v>
       </c>
       <c r="CQ69" t="n">
         <v>6.634722275472289</v>
@@ -38256,10 +38256,10 @@
         <v>21.36000061035156</v>
       </c>
       <c r="CJ70" t="n">
-        <v>5.907198071889892</v>
+        <v>5.907198054017572</v>
       </c>
       <c r="CK70" t="n">
-        <v>10.95785242335575</v>
+        <v>10.95785239020259</v>
       </c>
       <c r="CL70" t="n">
         <v>32.3451437813895</v>
@@ -38268,25 +38268,25 @@
         <v>33.26867930684288</v>
       </c>
       <c r="CN70" t="n">
-        <v>28.98255279669993</v>
+        <v>28.98255279837994</v>
       </c>
       <c r="CO70" t="n">
-        <v>25.19834977841975</v>
+        <v>25.19834978131341</v>
       </c>
       <c r="CP70" t="n">
-        <v>18.79799008747926</v>
+        <v>18.7979901065097</v>
       </c>
       <c r="CQ70" t="n">
         <v>13.70244046469206</v>
       </c>
       <c r="CR70" t="n">
-        <v>23.32185837698274</v>
+        <v>23.32185837561858</v>
       </c>
       <c r="CS70" t="n">
-        <v>25.19834977841975</v>
+        <v>25.19834978131341</v>
       </c>
       <c r="CT70" t="n">
-        <v>22.67851480057778</v>
+        <v>22.67851480318207</v>
       </c>
       <c r="CU70" t="n">
         <v>7</v>
@@ -38298,10 +38298,10 @@
         <v>5.6</v>
       </c>
       <c r="CX70" t="n">
-        <v>6.172819066246804</v>
+        <v>6.172819078439185</v>
       </c>
       <c r="CY70" t="n">
-        <v>9.184727109419688</v>
+        <v>9.184727103033218</v>
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
@@ -38612,25 +38612,25 @@
         <v>17.28000068664551</v>
       </c>
       <c r="CJ71" t="n">
-        <v>4.022695626089441</v>
+        <v>4.022695603747645</v>
       </c>
       <c r="CK71" t="n">
-        <v>6.903155510688491</v>
+        <v>6.903155483193939</v>
       </c>
       <c r="CL71" t="n">
-        <v>23.48224775971444</v>
+        <v>23.48224779660599</v>
       </c>
       <c r="CM71" t="n">
         <v>32.85543339401257</v>
       </c>
       <c r="CN71" t="n">
-        <v>16.59077768712898</v>
+        <v>16.59077767638019</v>
       </c>
       <c r="CO71" t="n">
-        <v>20.50985171685842</v>
+        <v>20.50985171928888</v>
       </c>
       <c r="CP71" t="n">
-        <v>11.62167797149091</v>
+        <v>11.62167798653141</v>
       </c>
       <c r="CQ71" t="n">
         <v>22.25954302628453</v>
@@ -38682,7 +38682,7 @@
         <v>-0.4034564454475809</v>
       </c>
       <c r="DL71" t="n">
-        <v>-40.148197006589</v>
+        <v>-40.14819299276235</v>
       </c>
       <c r="DM71" t="b">
         <v>0</v>
@@ -38958,10 +38958,10 @@
         <v>3.819999933242798</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.9263872494178996</v>
+        <v>0.9263872481365849</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.718448347670204</v>
+        <v>1.718448345293365</v>
       </c>
       <c r="CL72" t="n">
         <v>6.076230386010452</v>
@@ -38970,7 +38970,7 @@
         <v>4.03575162850128</v>
       </c>
       <c r="CN72" t="n">
-        <v>8.435704740755408</v>
+        <v>8.43570473860194</v>
       </c>
       <c r="CO72" t="n">
         <v>3.760485277130923</v>
@@ -39028,7 +39028,7 @@
         <v>-6.829267753723601</v>
       </c>
       <c r="DL72" t="n">
-        <v>-47.77722489151894</v>
+        <v>-47.77722836921714</v>
       </c>
       <c r="DM72" t="b">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>12.57999992370605</v>
       </c>
       <c r="CJ73" t="n">
-        <v>2.081714458963004</v>
+        <v>2.081714463018078</v>
       </c>
       <c r="CK73" t="n">
-        <v>3.861580321376372</v>
+        <v>3.861580328898535</v>
       </c>
       <c r="CL73" t="n">
         <v>16.32566101754214</v>
@@ -39324,7 +39324,7 @@
         <v>12.94873547769632</v>
       </c>
       <c r="CN73" t="n">
-        <v>21.33633705005611</v>
+        <v>21.33633705561644</v>
       </c>
       <c r="CO73" t="n">
         <v>9.294207014285712</v>
@@ -39658,35 +39658,35 @@
         <v>24.09000015258789</v>
       </c>
       <c r="CJ74" t="n">
-        <v>23.14624737485934</v>
+        <v>23.14624718237044</v>
       </c>
       <c r="CK74" t="n">
-        <v>28.5102867956948</v>
+        <v>28.51028674616291</v>
       </c>
       <c r="CL74" t="n">
-        <v>36.66924130418612</v>
+        <v>36.66924154542826</v>
       </c>
       <c r="CM74" t="n">
         <v>60.85541453379113</v>
       </c>
       <c r="CN74" t="n">
-        <v>65.92125722940563</v>
+        <v>65.92125704963151</v>
       </c>
       <c r="CO74" t="n">
-        <v>41.61752976038338</v>
+        <v>41.61752978832697</v>
       </c>
       <c r="CP74" t="n">
-        <v>17.33029111271137</v>
+        <v>17.33029129277319</v>
       </c>
       <c r="CQ74" t="inlineStr"/>
       <c r="CR74" t="n">
-        <v>39.15003830157598</v>
+        <v>39.15003830549778</v>
       </c>
       <c r="CS74" t="n">
-        <v>36.66924130418612</v>
+        <v>36.66924154542826</v>
       </c>
       <c r="CT74" t="n">
-        <v>33.00231717376751</v>
+        <v>33.00231739088544</v>
       </c>
       <c r="CU74" t="n">
         <v>7</v>
@@ -39698,10 +39698,10 @@
         <v>3.8</v>
       </c>
       <c r="CX74" t="n">
-        <v>36.99591932224295</v>
+        <v>36.99592022352118</v>
       </c>
       <c r="CY74" t="n">
-        <v>62.51572458944234</v>
+        <v>62.51572460572214</v>
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
@@ -40012,10 +40012,10 @@
         <v>25.28000068664551</v>
       </c>
       <c r="CJ75" t="n">
-        <v>4.637679039570942</v>
+        <v>4.637679036445928</v>
       </c>
       <c r="CK75" t="n">
-        <v>8.602894618404097</v>
+        <v>8.602894612607196</v>
       </c>
       <c r="CL75" t="n">
         <v>30.23104775253185</v>
@@ -40024,19 +40024,19 @@
         <v>25.66642298400775</v>
       </c>
       <c r="CN75" t="n">
-        <v>34.91506256771081</v>
+        <v>34.91506257154977</v>
       </c>
       <c r="CO75" t="n">
-        <v>11.77719501810132</v>
+        <v>11.77719501845789</v>
       </c>
       <c r="CP75" t="n">
-        <v>24.35835629581922</v>
+        <v>24.35835630071423</v>
       </c>
       <c r="CQ75" t="n">
         <v>25.28000068664551</v>
       </c>
       <c r="CR75" t="n">
-        <v>25.37134755080274</v>
+        <v>25.37134755231783</v>
       </c>
       <c r="CS75" t="n">
         <v>25.47321183532663</v>
@@ -40057,7 +40057,7 @@
         <v>-9.312143872271072</v>
       </c>
       <c r="CY75" t="n">
-        <v>0.3613404338453474</v>
+        <v>0.3613404398385978</v>
       </c>
       <c r="CZ75" t="inlineStr">
         <is>
@@ -40366,10 +40366,10 @@
         <v>54.72999954223633</v>
       </c>
       <c r="CJ76" t="n">
-        <v>39.80284410105673</v>
+        <v>39.80284445624363</v>
       </c>
       <c r="CK76" t="n">
-        <v>57.95294101113861</v>
+        <v>57.95294152829074</v>
       </c>
       <c r="CL76" t="n">
         <v>35.04876817975726</v>
@@ -40388,13 +40388,13 @@
         <v>48.01546263696088</v>
       </c>
       <c r="CR76" t="n">
-        <v>42.74450947350125</v>
+        <v>42.74450961889108</v>
       </c>
       <c r="CS76" t="n">
-        <v>40.8242085018479</v>
+        <v>40.82420867944135</v>
       </c>
       <c r="CT76" t="n">
-        <v>36.74178765166311</v>
+        <v>36.74178781149721</v>
       </c>
       <c r="CU76" t="n">
         <v>6</v>
@@ -40406,10 +40406,10 @@
         <v>6.4</v>
       </c>
       <c r="CX76" t="n">
-        <v>-32.86718808884937</v>
+        <v>-32.86718779680826</v>
       </c>
       <c r="CY76" t="n">
-        <v>-21.89930599119706</v>
+        <v>-21.8993057255478</v>
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
@@ -40720,10 +40720,10 @@
         <v>28.80999946594238</v>
       </c>
       <c r="CJ77" t="n">
-        <v>13.46031123347453</v>
+        <v>13.46031126176645</v>
       </c>
       <c r="CK77" t="n">
-        <v>24.96887733809526</v>
+        <v>24.96887739057677</v>
       </c>
       <c r="CL77" t="n">
         <v>36.32088419826228</v>
@@ -40732,25 +40732,25 @@
         <v>25.32755497782173</v>
       </c>
       <c r="CN77" t="n">
-        <v>40.52264098878622</v>
+        <v>40.52264092202478</v>
       </c>
       <c r="CO77" t="n">
-        <v>42.02971218854545</v>
+        <v>42.02971217375025</v>
       </c>
       <c r="CP77" t="n">
-        <v>21.52400201055486</v>
+        <v>21.52400194490178</v>
       </c>
       <c r="CQ77" t="n">
         <v>24.88607192490505</v>
       </c>
       <c r="CR77" t="n">
-        <v>28.63000685755567</v>
+        <v>28.63000684925114</v>
       </c>
       <c r="CS77" t="n">
-        <v>25.1482161579585</v>
+        <v>25.14821618419925</v>
       </c>
       <c r="CT77" t="n">
-        <v>22.63339454216265</v>
+        <v>22.63339456577933</v>
       </c>
       <c r="CU77" t="n">
         <v>8</v>
@@ -40762,10 +40762,10 @@
         <v>3.1</v>
       </c>
       <c r="CX77" t="n">
-        <v>-21.43910113945466</v>
+        <v>-21.43910105748077</v>
       </c>
       <c r="CY77" t="n">
-        <v>-0.6247574166028391</v>
+        <v>-0.6247574454280036</v>
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>-1.161058781434998</v>
       </c>
       <c r="DL77" t="n">
-        <v>-24.30004332779303</v>
+        <v>-24.30003536590277</v>
       </c>
       <c r="DM77" t="b">
         <v>0</v>
@@ -41084,10 +41084,10 @@
         <v>15.0600004196167</v>
       </c>
       <c r="CJ78" t="n">
-        <v>2.430224157038559</v>
+        <v>2.43022414423353</v>
       </c>
       <c r="CK78" t="n">
-        <v>4.508065811306527</v>
+        <v>4.508065787553199</v>
       </c>
       <c r="CL78" t="n">
         <v>24.78819944843742</v>
@@ -41096,7 +41096,7 @@
         <v>18.97850370269514</v>
       </c>
       <c r="CN78" t="n">
-        <v>32.28858937798637</v>
+        <v>32.28858935571676</v>
       </c>
       <c r="CO78" t="n">
         <v>10.38593205872702</v>
@@ -41430,10 +41430,10 @@
         <v>14.94999980926514</v>
       </c>
       <c r="CJ79" t="n">
-        <v>9.768326972321068</v>
+        <v>9.768326992373042</v>
       </c>
       <c r="CK79" t="n">
-        <v>18.12024653365558</v>
+        <v>18.12024657085199</v>
       </c>
       <c r="CL79" t="n">
         <v>13.9204144394071</v>
@@ -41454,7 +41454,7 @@
         <v>12.34226887232652</v>
       </c>
       <c r="CR79" t="n">
-        <v>15.11537393339812</v>
+        <v>15.11537394055417</v>
       </c>
       <c r="CS79" t="n">
         <v>13.26668799219724</v>
@@ -41475,7 +41475,7 @@
         <v>-20.13364986414387</v>
       </c>
       <c r="CY79" t="n">
-        <v>1.106181446440546</v>
+        <v>1.106181494307101</v>
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
@@ -41794,25 +41794,25 @@
         <v>26.40999984741211</v>
       </c>
       <c r="CJ80" t="n">
-        <v>12.03062437526879</v>
+        <v>12.03062438578403</v>
       </c>
       <c r="CK80" t="n">
-        <v>12.63784572456727</v>
+        <v>12.6378457293792</v>
       </c>
       <c r="CL80" t="n">
-        <v>13.76140426133667</v>
+        <v>13.76140425454839</v>
       </c>
       <c r="CM80" t="n">
         <v>32.21690097207528</v>
       </c>
       <c r="CN80" t="n">
-        <v>12.78505274310483</v>
+        <v>12.78505274262557</v>
       </c>
       <c r="CO80" t="n">
-        <v>24.65491712879319</v>
+        <v>24.65491712736295</v>
       </c>
       <c r="CP80" t="n">
-        <v>5.583744815805273</v>
+        <v>5.583744809078041</v>
       </c>
       <c r="CQ80" t="n">
         <v>60.10895866204905</v>
@@ -42140,10 +42140,10 @@
         <v>10.42000007629395</v>
       </c>
       <c r="CJ81" t="n">
-        <v>6.386823451454461</v>
+        <v>6.386823428839545</v>
       </c>
       <c r="CK81" t="n">
-        <v>11.84755750244802</v>
+        <v>11.84755746049736</v>
       </c>
       <c r="CL81" t="n">
         <v>7.980635896583511</v>
@@ -42164,7 +42164,7 @@
         <v>39.24041441528669</v>
       </c>
       <c r="CR81" t="n">
-        <v>10.25521143144734</v>
+        <v>10.25521142222368</v>
       </c>
       <c r="CS81" t="n">
         <v>7.980635896583511</v>
@@ -42185,7 +42185,7 @@
         <v>-31.06936416184972</v>
       </c>
       <c r="CY81" t="n">
-        <v>-1.581464910173147</v>
+        <v>-1.581464998691928</v>
       </c>
       <c r="CZ81" t="inlineStr">
         <is>
@@ -42496,10 +42496,10 @@
         <v>6.909999847412109</v>
       </c>
       <c r="CJ82" t="n">
-        <v>1.245705649383535</v>
+        <v>1.245705646938801</v>
       </c>
       <c r="CK82" t="n">
-        <v>2.310783979606457</v>
+        <v>2.310783975071475</v>
       </c>
       <c r="CL82" t="n">
         <v>9.844892255721552</v>
@@ -42508,13 +42508,13 @@
         <v>9.691148910902541</v>
       </c>
       <c r="CN82" t="n">
-        <v>9.426422450752398</v>
+        <v>9.426422451617405</v>
       </c>
       <c r="CO82" t="n">
-        <v>1.870915582686666</v>
+        <v>1.870915582790559</v>
       </c>
       <c r="CP82" t="n">
-        <v>6.731347708592457</v>
+        <v>6.73134771144947</v>
       </c>
       <c r="CQ82" t="n">
         <v>10.56671555133091</v>
@@ -42842,35 +42842,35 @@
         <v>2.75</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.264836872829382</v>
+        <v>1.264836876263687</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.716202948150942</v>
+        <v>1.716202951353635</v>
       </c>
       <c r="CL83" t="n">
-        <v>3.611456783521727</v>
+        <v>3.611456780455363</v>
       </c>
       <c r="CM83" t="n">
         <v>7.004011379358229</v>
       </c>
       <c r="CN83" t="n">
-        <v>3.643127489572467</v>
+        <v>3.643127493029504</v>
       </c>
       <c r="CO83" t="n">
-        <v>1.339548791388968</v>
+        <v>1.339548791282592</v>
       </c>
       <c r="CP83" t="n">
-        <v>1.777210307299792</v>
+        <v>1.77721030537768</v>
       </c>
       <c r="CQ83" t="inlineStr"/>
       <c r="CR83" t="n">
-        <v>2.22539719879388</v>
+        <v>2.225397199627077</v>
       </c>
       <c r="CS83" t="n">
-        <v>1.746706627725367</v>
+        <v>1.746706628365657</v>
       </c>
       <c r="CT83" t="n">
-        <v>1.57203596495283</v>
+        <v>1.572035965529092</v>
       </c>
       <c r="CU83" t="n">
         <v>6</v>
@@ -42882,10 +42882,10 @@
         <v>5.5</v>
       </c>
       <c r="CX83" t="n">
-        <v>-42.83505581989707</v>
+        <v>-42.83505579894212</v>
       </c>
       <c r="CY83" t="n">
-        <v>-19.07646549840437</v>
+        <v>-19.0764654681063</v>
       </c>
       <c r="CZ83" t="inlineStr">
         <is>
@@ -43194,10 +43194,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ84" t="n">
-        <v>3.06941298712796</v>
+        <v>3.069412973111825</v>
       </c>
       <c r="CK84" t="n">
-        <v>4.46906530925831</v>
+        <v>4.469065288850818</v>
       </c>
       <c r="CL84" t="n">
         <v>4.457142906283466</v>
@@ -43894,10 +43894,10 @@
         <v>18.57999992370605</v>
       </c>
       <c r="CJ86" t="n">
-        <v>4.512852222608041</v>
+        <v>4.512852222220707</v>
       </c>
       <c r="CK86" t="n">
-        <v>8.371340872937916</v>
+        <v>8.371340872219411</v>
       </c>
       <c r="CL86" t="n">
         <v>30.43077861422808</v>
@@ -43906,13 +43906,13 @@
         <v>32.84488176258051</v>
       </c>
       <c r="CN86" t="n">
-        <v>26.12312850144557</v>
+        <v>26.12312850137177</v>
       </c>
       <c r="CO86" t="n">
-        <v>11.11283324302213</v>
+        <v>11.11283324304886</v>
       </c>
       <c r="CP86" t="n">
-        <v>17.64670993816183</v>
+        <v>17.64670993853677</v>
       </c>
       <c r="CQ86" t="n">
         <v>40.63403637942744</v>
@@ -44248,25 +44248,25 @@
         <v>1.539999961853027</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.1373663640494014</v>
+        <v>0.1373663638608602</v>
       </c>
       <c r="CK87" t="n">
-        <v>0.1568558711179774</v>
+        <v>0.1568558709106539</v>
       </c>
       <c r="CL87" t="n">
-        <v>0.7489968439654238</v>
+        <v>0.748996844003471</v>
       </c>
       <c r="CM87" t="n">
         <v>3.105192066391262</v>
       </c>
       <c r="CN87" t="n">
-        <v>0.2569714891397609</v>
+        <v>0.2569714890340979</v>
       </c>
       <c r="CO87" t="n">
-        <v>0.5416066536783812</v>
+        <v>0.5416066536813859</v>
       </c>
       <c r="CP87" t="n">
-        <v>0.3347614234760471</v>
+        <v>0.3347614235085667</v>
       </c>
       <c r="CQ87" t="inlineStr"/>
       <c r="CR87" t="inlineStr"/>
@@ -44592,10 +44592,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CJ88" t="n">
-        <v>11.9932523424147</v>
+        <v>11.99325221182622</v>
       </c>
       <c r="CK88" t="n">
-        <v>22.24748309517928</v>
+        <v>22.24748285293763</v>
       </c>
       <c r="CL88" t="n">
         <v>15.02382038547176</v>
@@ -44616,13 +44616,13 @@
         <v>22.65224107444971</v>
       </c>
       <c r="CR88" t="n">
-        <v>19.72597612104749</v>
+        <v>19.72597607444373</v>
       </c>
       <c r="CS88" t="n">
-        <v>18.63565174032552</v>
+        <v>18.63565161920469</v>
       </c>
       <c r="CT88" t="n">
-        <v>16.77208656629297</v>
+        <v>16.77208645728422</v>
       </c>
       <c r="CU88" t="n">
         <v>8</v>
@@ -44634,10 +44634,10 @@
         <v>2.9</v>
       </c>
       <c r="CX88" t="n">
-        <v>-29.52904578174925</v>
+        <v>-29.52904623976919</v>
       </c>
       <c r="CY88" t="n">
-        <v>-17.11774473366</v>
+        <v>-17.11774492947416</v>
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
@@ -44946,10 +44946,10 @@
         <v>14.02999973297119</v>
       </c>
       <c r="CJ89" t="n">
-        <v>6.056552938226275</v>
+        <v>6.05655295157942</v>
       </c>
       <c r="CK89" t="n">
-        <v>8.818341078057458</v>
+        <v>8.818341097499635</v>
       </c>
       <c r="CL89" t="n">
         <v>3.791891819721943</v>
@@ -45274,10 +45274,10 @@
         <v>56.88999938964844</v>
       </c>
       <c r="CJ90" t="n">
-        <v>11.93657439088583</v>
+        <v>11.93657439598704</v>
       </c>
       <c r="CK90" t="n">
-        <v>17.37965231312977</v>
+        <v>17.37965232055714</v>
       </c>
       <c r="CL90" t="inlineStr"/>
       <c r="CM90" t="inlineStr"/>
@@ -45288,13 +45288,13 @@
       <c r="CP90" t="inlineStr"/>
       <c r="CQ90" t="inlineStr"/>
       <c r="CR90" t="n">
-        <v>18.5479755680052</v>
+        <v>18.5479755721814</v>
       </c>
       <c r="CS90" t="n">
-        <v>17.37965231312977</v>
+        <v>17.37965232055714</v>
       </c>
       <c r="CT90" t="n">
-        <v>15.64168708181679</v>
+        <v>15.64168708850142</v>
       </c>
       <c r="CU90" t="n">
         <v>3</v>
@@ -45306,10 +45306,10 @@
         <v>2.2</v>
       </c>
       <c r="CX90" t="n">
-        <v>-72.50538363573456</v>
+        <v>-72.50538362398446</v>
       </c>
       <c r="CY90" t="n">
-        <v>-67.39677312884601</v>
+        <v>-67.39677312150518</v>
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>1.353996627598364</v>
       </c>
       <c r="DL90" t="n">
-        <v>-12.10365102226845</v>
+        <v>-12.10365646225029</v>
       </c>
       <c r="DM90" t="b">
         <v>0</v>
@@ -45628,10 +45628,10 @@
         <v>6.980000019073486</v>
       </c>
       <c r="CJ91" t="n">
-        <v>2.904946331496027</v>
+        <v>2.904946340061302</v>
       </c>
       <c r="CK91" t="n">
-        <v>5.38867544492513</v>
+        <v>5.388675460813715</v>
       </c>
       <c r="CL91" t="n">
         <v>13.62076586932602</v>
@@ -45640,23 +45640,23 @@
         <v>14.67172452167963</v>
       </c>
       <c r="CN91" t="n">
-        <v>12.87347152926946</v>
+        <v>12.87347153364337</v>
       </c>
       <c r="CO91" t="n">
-        <v>14.97590881441537</v>
+        <v>14.97590881260124</v>
       </c>
       <c r="CP91" t="n">
-        <v>7.073198858509854</v>
+        <v>7.073198850158368</v>
       </c>
       <c r="CQ91" t="inlineStr"/>
       <c r="CR91" t="n">
-        <v>11.43395750635424</v>
+        <v>11.43395750803706</v>
       </c>
       <c r="CS91" t="n">
-        <v>13.24711869929774</v>
+        <v>13.24711870148469</v>
       </c>
       <c r="CT91" t="n">
-        <v>11.92240682936797</v>
+        <v>11.92240683133622</v>
       </c>
       <c r="CU91" t="n">
         <v>6</v>
@@ -45668,10 +45668,10 @@
         <v>5.2</v>
       </c>
       <c r="CX91" t="n">
-        <v>70.8081202978353</v>
+        <v>70.80812032603379</v>
       </c>
       <c r="CY91" t="n">
-        <v>63.81027901303597</v>
+        <v>63.81027903714504</v>
       </c>
       <c r="CZ91" t="inlineStr">
         <is>
@@ -45980,10 +45980,10 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CJ92" t="n">
-        <v>4.969684062719159</v>
+        <v>4.969684098895033</v>
       </c>
       <c r="CK92" t="n">
-        <v>7.235859995319097</v>
+        <v>7.235860047991168</v>
       </c>
       <c r="CL92" t="n">
         <v>5.964932973104989</v>
@@ -46002,13 +46002,13 @@
         <v>7.71999979019165</v>
       </c>
       <c r="CR92" t="n">
-        <v>6.640162218615093</v>
+        <v>6.640162233423084</v>
       </c>
       <c r="CS92" t="n">
-        <v>6.600396484212043</v>
+        <v>6.600396510548078</v>
       </c>
       <c r="CT92" t="n">
-        <v>5.940356835790839</v>
+        <v>5.940356859493271</v>
       </c>
       <c r="CU92" t="n">
         <v>6</v>
@@ -46020,10 +46020,10 @@
         <v>5.9</v>
       </c>
       <c r="CX92" t="n">
-        <v>-23.05237050215816</v>
+        <v>-23.05237019513183</v>
       </c>
       <c r="CY92" t="n">
-        <v>-13.98753369071983</v>
+        <v>-13.98753349890648</v>
       </c>
       <c r="CZ92" t="inlineStr">
         <is>
@@ -46336,10 +46336,10 @@
         <v>3.670000076293945</v>
       </c>
       <c r="CJ93" t="n">
-        <v>33.4587140558825</v>
+        <v>33.4587137930077</v>
       </c>
       <c r="CK93" t="n">
-        <v>62.06591457366204</v>
+        <v>62.06591408602928</v>
       </c>
       <c r="CL93" t="n">
         <v>4.702853095831215</v>
@@ -46680,10 +46680,10 @@
         <v>78.58000183105469</v>
       </c>
       <c r="CJ94" t="n">
-        <v>58.74948806819323</v>
+        <v>58.74948828814306</v>
       </c>
       <c r="CK94" t="n">
-        <v>85.53925462728935</v>
+        <v>85.53925494753629</v>
       </c>
       <c r="CL94" t="n">
         <v>24.51941251254032</v>
@@ -47028,10 +47028,10 @@
         <v>34.81000137329102</v>
       </c>
       <c r="CJ95" t="n">
-        <v>8.61967638205285</v>
+        <v>8.619676368796281</v>
       </c>
       <c r="CK95" t="n">
-        <v>15.98949968870804</v>
+        <v>15.9894996641171</v>
       </c>
       <c r="CL95" t="n">
         <v>40.07232999097358</v>
@@ -47040,19 +47040,19 @@
         <v>40.41788990153368</v>
       </c>
       <c r="CN95" t="n">
-        <v>33.44033780365254</v>
+        <v>33.44033781096839</v>
       </c>
       <c r="CO95" t="n">
-        <v>50.04925265646109</v>
+        <v>50.04925266006651</v>
       </c>
       <c r="CP95" t="n">
-        <v>22.50871823599684</v>
+        <v>22.50871825073073</v>
       </c>
       <c r="CQ95" t="n">
         <v>53.2004618761326</v>
       </c>
       <c r="CR95" t="n">
-        <v>36.52549859335119</v>
+        <v>36.52549859350323</v>
       </c>
       <c r="CS95" t="n">
         <v>40.07232999097358</v>
@@ -47073,7 +47073,7 @@
         <v>3.605560382276285</v>
       </c>
       <c r="CY95" t="n">
-        <v>4.92817337656426</v>
+        <v>4.928173377000999</v>
       </c>
       <c r="CZ95" t="inlineStr">
         <is>
@@ -47384,10 +47384,10 @@
         <v>19.60000038146973</v>
       </c>
       <c r="CJ96" t="n">
-        <v>2.0231125049518</v>
+        <v>2.023112506994297</v>
       </c>
       <c r="CK96" t="n">
-        <v>3.752873696685589</v>
+        <v>3.752873700474421</v>
       </c>
       <c r="CL96" t="n">
         <v>10.14849570357459</v>
@@ -47396,19 +47396,19 @@
         <v>8.468407387765433</v>
       </c>
       <c r="CN96" t="n">
-        <v>9.99311642966622</v>
+        <v>9.993116425519316</v>
       </c>
       <c r="CO96" t="n">
-        <v>7.537047557971457</v>
+        <v>7.537047557507277</v>
       </c>
       <c r="CP96" t="n">
-        <v>7.631782584397649</v>
+        <v>7.631782581088641</v>
       </c>
       <c r="CQ96" t="n">
         <v>13.57810210946071</v>
       </c>
       <c r="CR96" t="n">
-        <v>8.729975067074522</v>
+        <v>8.729975066484341</v>
       </c>
       <c r="CS96" t="n">
         <v>8.468407387765433</v>
@@ -47429,7 +47429,7 @@
         <v>-61.11445662932493</v>
       </c>
       <c r="CY96" t="n">
-        <v>-55.45931174915674</v>
+        <v>-55.45931175216786</v>
       </c>
       <c r="CZ96" t="inlineStr">
         <is>
@@ -47722,35 +47722,35 @@
         <v>20.17000007629395</v>
       </c>
       <c r="CJ97" t="n">
-        <v>12.02545559589612</v>
+        <v>12.02545562360225</v>
       </c>
       <c r="CK97" t="n">
-        <v>15.02693330893174</v>
+        <v>15.02693332519908</v>
       </c>
       <c r="CL97" t="n">
-        <v>21.92822743710228</v>
+        <v>21.9282274103189</v>
       </c>
       <c r="CM97" t="n">
         <v>41.10111584317051</v>
       </c>
       <c r="CN97" t="n">
-        <v>26.68409625375999</v>
+        <v>26.68409627001344</v>
       </c>
       <c r="CO97" t="n">
-        <v>15.73775953530073</v>
+        <v>15.73775953336411</v>
       </c>
       <c r="CP97" t="n">
-        <v>10.44627161632715</v>
+        <v>10.44627159684642</v>
       </c>
       <c r="CQ97" t="inlineStr"/>
       <c r="CR97" t="n">
-        <v>16.17959396930772</v>
+        <v>16.17959397312109</v>
       </c>
       <c r="CS97" t="n">
-        <v>15.38234642211624</v>
+        <v>15.3823464292816</v>
       </c>
       <c r="CT97" t="n">
-        <v>13.84411177990461</v>
+        <v>13.84411178635344</v>
       </c>
       <c r="CU97" t="n">
         <v>4</v>
@@ -47762,10 +47762,10 @@
         <v>1.8</v>
       </c>
       <c r="CX97" t="n">
-        <v>-31.36285707715107</v>
+        <v>-31.36285704517871</v>
       </c>
       <c r="CY97" t="n">
-        <v>-19.78386758498925</v>
+        <v>-19.78386756608312</v>
       </c>
       <c r="CZ97" t="inlineStr">
         <is>
@@ -48092,10 +48092,10 @@
         <v>15.77000045776367</v>
       </c>
       <c r="CJ98" t="n">
-        <v>7.940764299585794</v>
+        <v>7.940764288300745</v>
       </c>
       <c r="CK98" t="n">
-        <v>14.73011777573165</v>
+        <v>14.73011775479788</v>
       </c>
       <c r="CL98" t="n">
         <v>10.12366792952367</v>
@@ -48116,7 +48116,7 @@
         <v>9.605938210417623</v>
       </c>
       <c r="CR98" t="n">
-        <v>12.14173309075311</v>
+        <v>12.14173308672576</v>
       </c>
       <c r="CS98" t="n">
         <v>9.864803069970648</v>
@@ -48137,7 +48137,7 @@
         <v>-43.70118893304959</v>
       </c>
       <c r="CY98" t="n">
-        <v>-23.00740178624623</v>
+        <v>-23.0074018117843</v>
       </c>
       <c r="CZ98" t="inlineStr">
         <is>
@@ -48456,37 +48456,37 @@
         <v>23.01000022888184</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.039638103109806</v>
+        <v>5.039638089952313</v>
       </c>
       <c r="CK99" t="n">
-        <v>7.157408899960964</v>
+        <v>7.157408897026726</v>
       </c>
       <c r="CL99" t="n">
-        <v>10.59572232033094</v>
+        <v>10.59572234365046</v>
       </c>
       <c r="CM99" t="n">
         <v>14.53384923599866</v>
       </c>
       <c r="CN99" t="n">
-        <v>7.141105299596063</v>
+        <v>7.141105312639126</v>
       </c>
       <c r="CO99" t="n">
-        <v>8.43597916903294</v>
+        <v>8.435979170698905</v>
       </c>
       <c r="CP99" t="n">
-        <v>5.26585121606233</v>
+        <v>5.265851229516655</v>
       </c>
       <c r="CQ99" t="n">
         <v>10.72346608033207</v>
       </c>
       <c r="CR99" t="n">
-        <v>8.611627540552972</v>
+        <v>8.611627544976864</v>
       </c>
       <c r="CS99" t="n">
-        <v>7.796694034496952</v>
+        <v>7.796694033862815</v>
       </c>
       <c r="CT99" t="n">
-        <v>7.017024631047256</v>
+        <v>7.017024630476534</v>
       </c>
       <c r="CU99" t="n">
         <v>8</v>
@@ -48498,10 +48498,10 @@
         <v>2.9</v>
       </c>
       <c r="CX99" t="n">
-        <v>-69.50445649174925</v>
+        <v>-69.50445649422959</v>
       </c>
       <c r="CY99" t="n">
-        <v>-62.57441349459973</v>
+        <v>-62.57441347537378</v>
       </c>
       <c r="CZ99" t="inlineStr">
         <is>
@@ -48812,10 +48812,10 @@
         <v>7.199999809265137</v>
       </c>
       <c r="CJ100" t="n">
-        <v>3.230736911355043</v>
+        <v>3.230736916150203</v>
       </c>
       <c r="CK100" t="n">
-        <v>5.993016970563604</v>
+        <v>5.993016979458626</v>
       </c>
       <c r="CL100" t="inlineStr"/>
       <c r="CM100" t="inlineStr"/>
@@ -48826,13 +48826,13 @@
         <v>9.346171559984855</v>
       </c>
       <c r="CR100" t="n">
-        <v>6.189975147301166</v>
+        <v>6.189975151864561</v>
       </c>
       <c r="CS100" t="n">
-        <v>5.993016970563604</v>
+        <v>5.993016979458626</v>
       </c>
       <c r="CT100" t="n">
-        <v>5.393715273507244</v>
+        <v>5.393715281512764</v>
       </c>
       <c r="CU100" t="n">
         <v>3</v>
@@ -48844,10 +48844,10 @@
         <v>2.9</v>
       </c>
       <c r="CX100" t="n">
-        <v>-25.08728588344574</v>
+        <v>-25.08728577225796</v>
       </c>
       <c r="CY100" t="n">
-        <v>-14.02812067667343</v>
+        <v>-14.02812061329295</v>
       </c>
       <c r="CZ100" t="inlineStr">
         <is>
@@ -49158,10 +49158,10 @@
         <v>45.29999923706055</v>
       </c>
       <c r="CJ101" t="n">
-        <v>9.911113136628117</v>
+        <v>9.911113133292559</v>
       </c>
       <c r="CK101" t="n">
-        <v>18.38511486844516</v>
+        <v>18.3851148622577</v>
       </c>
       <c r="CL101" t="n">
         <v>85.6241069744725</v>
@@ -49170,13 +49170,13 @@
         <v>75.68006991304929</v>
       </c>
       <c r="CN101" t="n">
-        <v>103.2210458235768</v>
+        <v>103.2210458245924</v>
       </c>
       <c r="CO101" t="n">
-        <v>16.15577152788715</v>
+        <v>16.15577152805714</v>
       </c>
       <c r="CP101" t="n">
-        <v>69.70318634398092</v>
+        <v>69.70318634880654</v>
       </c>
       <c r="CQ101" t="n">
         <v>21.32072017314016</v>
@@ -49516,25 +49516,25 @@
         <v>47.36999893188477</v>
       </c>
       <c r="CJ102" t="n">
-        <v>18.20689963591309</v>
+        <v>18.20689960577618</v>
       </c>
       <c r="CK102" t="n">
-        <v>19.98880950292275</v>
+        <v>19.98880948914466</v>
       </c>
       <c r="CL102" t="n">
-        <v>23.30440145522299</v>
+        <v>23.30440147773403</v>
       </c>
       <c r="CM102" t="n">
         <v>50.5405114948287</v>
       </c>
       <c r="CN102" t="n">
-        <v>19.28041170406953</v>
+        <v>19.2804117104256</v>
       </c>
       <c r="CO102" t="n">
-        <v>23.25458367814533</v>
+        <v>23.25458368068583</v>
       </c>
       <c r="CP102" t="n">
-        <v>10.00649684289855</v>
+        <v>10.00649686353148</v>
       </c>
       <c r="CQ102" t="n">
         <v>117.9256251674622</v>
@@ -49870,37 +49870,37 @@
         <v>53.11999893188477</v>
       </c>
       <c r="CJ103" t="n">
-        <v>16.22648837543075</v>
+        <v>16.22648837655992</v>
       </c>
       <c r="CK103" t="n">
-        <v>24.67943851451451</v>
+        <v>24.67943851516446</v>
       </c>
       <c r="CL103" t="n">
-        <v>44.49393106948413</v>
+        <v>44.49393106755965</v>
       </c>
       <c r="CM103" t="n">
         <v>61.84069244222911</v>
       </c>
       <c r="CN103" t="n">
-        <v>35.49872157796744</v>
+        <v>35.49872157762757</v>
       </c>
       <c r="CO103" t="n">
-        <v>26.76189247329762</v>
+        <v>26.76189247320005</v>
       </c>
       <c r="CP103" t="n">
-        <v>22.24510782146885</v>
+        <v>22.24510782048908</v>
       </c>
       <c r="CQ103" t="n">
         <v>21.78028972750627</v>
       </c>
       <c r="CR103" t="n">
-        <v>31.69082025023733</v>
+        <v>31.69082025004202</v>
       </c>
       <c r="CS103" t="n">
-        <v>25.72066549390606</v>
+        <v>25.72066549418226</v>
       </c>
       <c r="CT103" t="n">
-        <v>23.14859894451546</v>
+        <v>23.14859894476403</v>
       </c>
       <c r="CU103" t="n">
         <v>8</v>
@@ -49912,10 +49912,10 @@
         <v>3.8</v>
       </c>
       <c r="CX103" t="n">
-        <v>-56.42206436374618</v>
+        <v>-56.42206436327824</v>
       </c>
       <c r="CY103" t="n">
-        <v>-40.34107513655234</v>
+        <v>-40.34107513692003</v>
       </c>
       <c r="CZ103" t="inlineStr">
         <is>
@@ -50242,10 +50242,10 @@
         <v>11.9399995803833</v>
       </c>
       <c r="CJ104" t="n">
-        <v>2.124475142251035</v>
+        <v>2.124475140187192</v>
       </c>
       <c r="CK104" t="n">
-        <v>3.94090138887567</v>
+        <v>3.940901385047242</v>
       </c>
       <c r="CL104" t="n">
         <v>12.07671713283044</v>
@@ -50254,25 +50254,25 @@
         <v>13.36902203749528</v>
       </c>
       <c r="CN104" t="n">
-        <v>8.686980470437879</v>
+        <v>8.686980471251648</v>
       </c>
       <c r="CO104" t="n">
-        <v>5.736769277294875</v>
+        <v>5.736769277472419</v>
       </c>
       <c r="CP104" t="n">
-        <v>6.468133889929589</v>
+        <v>6.4681338918275</v>
       </c>
       <c r="CQ104" t="n">
         <v>11.9399995803833</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.888360539606719</v>
+        <v>8.888360539472547</v>
       </c>
       <c r="CS104" t="n">
-        <v>8.686980470437879</v>
+        <v>8.686980471251648</v>
       </c>
       <c r="CT104" t="n">
-        <v>7.818282423394091</v>
+        <v>7.818282424126483</v>
       </c>
       <c r="CU104" t="n">
         <v>7</v>
@@ -50284,10 +50284,10 @@
         <v>6.3</v>
       </c>
       <c r="CX104" t="n">
-        <v>-34.52024540906133</v>
+        <v>-34.52024540292741</v>
       </c>
       <c r="CY104" t="n">
-        <v>-25.55811681761062</v>
+        <v>-25.55811681873433</v>
       </c>
       <c r="CZ104" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>0</v>
       </c>
       <c r="AW105" t="n">
-        <v>3653004288</v>
+        <v>3653262080</v>
       </c>
       <c r="AX105" t="n">
         <v>11.57</v>
@@ -50598,10 +50598,10 @@
         <v>2.990000009536743</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.6261539968435469</v>
+        <v>0.6261540003308381</v>
       </c>
       <c r="CK105" t="n">
-        <v>1.161515664144779</v>
+        <v>1.161515670613705</v>
       </c>
       <c r="CL105" t="n">
         <v>3.424157314292294</v>
@@ -50610,13 +50610,13 @@
         <v>3.957621711457321</v>
       </c>
       <c r="CN105" t="n">
-        <v>2.39188752214019</v>
+        <v>2.39188752168763</v>
       </c>
       <c r="CO105" t="n">
-        <v>2.635932104806514</v>
+        <v>2.635932104358291</v>
       </c>
       <c r="CP105" t="n">
-        <v>1.717596295220242</v>
+        <v>1.717596292283385</v>
       </c>
       <c r="CQ105" t="n">
         <v>9.031114164496099</v>
@@ -50942,10 +50942,10 @@
         <v>55.43999862670898</v>
       </c>
       <c r="CJ106" t="n">
-        <v>62.75021551388411</v>
+        <v>62.75021537704892</v>
       </c>
       <c r="CK106" t="n">
-        <v>91.36431378821527</v>
+        <v>91.36431358898324</v>
       </c>
       <c r="CL106" t="n">
         <v>24.25645711896397</v>
@@ -51284,10 +51284,10 @@
         <v>6.489999771118164</v>
       </c>
       <c r="CJ107" t="n">
-        <v>0.06255174950368395</v>
+        <v>0.06255174980550408</v>
       </c>
       <c r="CK107" t="n">
-        <v>0.1160334953293337</v>
+        <v>0.1160334958892101</v>
       </c>
       <c r="CL107" t="inlineStr"/>
       <c r="CM107" t="inlineStr"/>
@@ -51626,10 +51626,10 @@
         <v>93.48999786376953</v>
       </c>
       <c r="CJ108" t="n">
-        <v>4.770651246602801</v>
+        <v>4.770651230689694</v>
       </c>
       <c r="CK108" t="n">
-        <v>8.849558062448196</v>
+        <v>8.849558032929384</v>
       </c>
       <c r="CL108" t="n">
         <v>41.68043309875323</v>
@@ -51638,13 +51638,13 @@
         <v>41.35009616132553</v>
       </c>
       <c r="CN108" t="n">
-        <v>34.4834810973677</v>
+        <v>34.48348111885575</v>
       </c>
       <c r="CO108" t="n">
-        <v>17.71052554904738</v>
+        <v>17.37636469108361</v>
       </c>
       <c r="CP108" t="n">
-        <v>28.66625023746557</v>
+        <v>28.66625025568417</v>
       </c>
       <c r="CQ108" t="n">
         <v>43.17568011524377</v>
@@ -52644,10 +52644,10 @@
         <v>16.81999969482422</v>
       </c>
       <c r="CJ111" t="n">
-        <v>3.158272795064714</v>
+        <v>3.158272787191747</v>
       </c>
       <c r="CK111" t="n">
-        <v>5.858596034845045</v>
+        <v>5.858596020240689</v>
       </c>
       <c r="CL111" t="n">
         <v>14.7690520845872</v>
@@ -52656,23 +52656,23 @@
         <v>15.75245189589746</v>
       </c>
       <c r="CN111" t="n">
-        <v>10.52924634691668</v>
+        <v>10.52924635206744</v>
       </c>
       <c r="CO111" t="n">
-        <v>13.03158634980271</v>
+        <v>13.03158635116592</v>
       </c>
       <c r="CP111" t="n">
-        <v>7.754276536657259</v>
+        <v>7.75427654448614</v>
       </c>
       <c r="CQ111" t="inlineStr"/>
       <c r="CR111" t="n">
-        <v>11.28253487478439</v>
+        <v>11.28253487474081</v>
       </c>
       <c r="CS111" t="n">
-        <v>11.7804163483597</v>
+        <v>11.78041635161668</v>
       </c>
       <c r="CT111" t="n">
-        <v>10.60237471352373</v>
+        <v>10.60237471645501</v>
       </c>
       <c r="CU111" t="n">
         <v>6</v>
@@ -52684,10 +52684,10 @@
         <v>5</v>
       </c>
       <c r="CX111" t="n">
-        <v>-36.96566643347654</v>
+        <v>-36.96566641604916</v>
       </c>
       <c r="CY111" t="n">
-        <v>-32.92190796973552</v>
+        <v>-32.92190796999465</v>
       </c>
       <c r="CZ111" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
         <v>14.85999965667725</v>
       </c>
       <c r="CJ112" t="n">
-        <v>3.752078040089657</v>
+        <v>3.752078049773426</v>
       </c>
       <c r="CK112" t="n">
-        <v>4.765173624668306</v>
+        <v>4.765173635339393</v>
       </c>
       <c r="CL112" t="n">
-        <v>14.23467812244294</v>
+        <v>14.23467811758155</v>
       </c>
       <c r="CM112" t="n">
         <v>37.15722486020687</v>
       </c>
       <c r="CN112" t="n">
-        <v>9.753710217898046</v>
+        <v>9.75371022675049</v>
       </c>
       <c r="CO112" t="n">
-        <v>49.08124933706215</v>
+        <v>49.08124933539783</v>
       </c>
       <c r="CP112" t="n">
-        <v>6.836198275301213</v>
+        <v>6.836198271866961</v>
       </c>
       <c r="CQ112" t="n">
         <v>26.75481109869832</v>
@@ -53344,25 +53344,25 @@
         <v>14.88000011444092</v>
       </c>
       <c r="CJ113" t="n">
-        <v>1.392564516324504</v>
+        <v>1.392564516895222</v>
       </c>
       <c r="CK113" t="n">
-        <v>2.563328945412863</v>
+        <v>2.563328946107382</v>
       </c>
       <c r="CL113" t="n">
-        <v>8.56579775480038</v>
+        <v>8.56579775361069</v>
       </c>
       <c r="CM113" t="n">
         <v>10.6034032697214</v>
       </c>
       <c r="CN113" t="n">
-        <v>4.724956872025244</v>
+        <v>4.724956871697514</v>
       </c>
       <c r="CO113" t="n">
-        <v>7.68644286611425</v>
+        <v>7.686442866038795</v>
       </c>
       <c r="CP113" t="n">
-        <v>4.173838464757972</v>
+        <v>4.173838464332079</v>
       </c>
       <c r="CQ113" t="n">
         <v>11.44599456161724</v>
@@ -53690,10 +53690,10 @@
         <v>18.29999923706055</v>
       </c>
       <c r="CJ114" t="n">
-        <v>11.70299357599525</v>
+        <v>11.7029935372901</v>
       </c>
       <c r="CK114" t="n">
-        <v>14.60330067961146</v>
+        <v>14.60330063131417</v>
       </c>
       <c r="CL114" t="inlineStr"/>
       <c r="CM114" t="inlineStr"/>
@@ -54028,10 +54028,10 @@
         <v>11.22000026702881</v>
       </c>
       <c r="CJ115" t="n">
-        <v>2.438138897667095</v>
+        <v>2.438138891292839</v>
       </c>
       <c r="CK115" t="n">
-        <v>4.52274765517246</v>
+        <v>4.522747643348215</v>
       </c>
       <c r="CL115" t="n">
         <v>12.15576480279082</v>
@@ -54040,13 +54040,13 @@
         <v>12.68205556729091</v>
       </c>
       <c r="CN115" t="n">
-        <v>9.594467795898089</v>
+        <v>9.594467799140505</v>
       </c>
       <c r="CO115" t="n">
-        <v>0.7922280655625757</v>
+        <v>0.7922280656473032</v>
       </c>
       <c r="CP115" t="n">
-        <v>6.727276602383058</v>
+        <v>6.727276609007695</v>
       </c>
       <c r="CQ115" t="n">
         <v>7.245675643801825</v>
@@ -54374,25 +54374,25 @@
         <v>8.840000152587891</v>
       </c>
       <c r="CJ116" t="n">
-        <v>2.273351428656042</v>
+        <v>2.273351422253348</v>
       </c>
       <c r="CK116" t="n">
-        <v>2.459392458227228</v>
+        <v>2.459392453068711</v>
       </c>
       <c r="CL116" t="n">
-        <v>3.24052137438256</v>
+        <v>3.240521376712287</v>
       </c>
       <c r="CM116" t="n">
         <v>10.0855898347917</v>
       </c>
       <c r="CN116" t="n">
-        <v>1.903039102027519</v>
+        <v>1.903039101262163</v>
       </c>
       <c r="CO116" t="n">
-        <v>5.908796683984271</v>
+        <v>5.90879668447102</v>
       </c>
       <c r="CP116" t="n">
-        <v>1.367445362153957</v>
+        <v>1.367445364345727</v>
       </c>
       <c r="CQ116" t="n">
         <v>14.58705591648655</v>
@@ -54732,10 +54732,10 @@
         <v>4.829999923706055</v>
       </c>
       <c r="CJ117" t="n">
-        <v>1.485870076719454</v>
+        <v>1.485870069110295</v>
       </c>
       <c r="CK117" t="n">
-        <v>1.548606813292053</v>
+        <v>1.548606805361619</v>
       </c>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
@@ -55068,10 +55068,10 @@
         <v>3.359999895095825</v>
       </c>
       <c r="CJ118" t="n">
-        <v>1.655532339525894</v>
+        <v>1.655532339686884</v>
       </c>
       <c r="CK118" t="n">
-        <v>3.071012489820533</v>
+        <v>3.071012490119169</v>
       </c>
       <c r="CL118" t="n">
         <v>1.185934965637178</v>
@@ -55080,7 +55080,7 @@
         <v>4.749225176208076</v>
       </c>
       <c r="CN118" t="n">
-        <v>1.646708885108271</v>
+        <v>1.64670888516831</v>
       </c>
       <c r="CO118" t="n">
         <v>0.7445919647652398</v>
@@ -55414,10 +55414,10 @@
         <v>6.599999904632568</v>
       </c>
       <c r="CJ119" t="n">
-        <v>1.062191983107449</v>
+        <v>1.062191978574661</v>
       </c>
       <c r="CK119" t="n">
-        <v>1.970366128664318</v>
+        <v>1.970366120255997</v>
       </c>
       <c r="CL119" t="inlineStr"/>
       <c r="CM119" t="inlineStr"/>
@@ -55750,25 +55750,25 @@
         <v>3.650000095367432</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.251013902380214</v>
+        <v>1.251013902426838</v>
       </c>
       <c r="CK120" t="n">
-        <v>1.269554587865452</v>
+        <v>1.269554587895897</v>
       </c>
       <c r="CL120" t="n">
-        <v>1.322229963882319</v>
+        <v>1.322229963864749</v>
       </c>
       <c r="CM120" t="n">
         <v>4.079804341937684</v>
       </c>
       <c r="CN120" t="n">
-        <v>0.9080456073159989</v>
+        <v>0.9080456073191808</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.169845198403848</v>
+        <v>2.169845198400352</v>
       </c>
       <c r="CP120" t="n">
-        <v>0.5078925740506862</v>
+        <v>0.5078925740321819</v>
       </c>
       <c r="CQ120" t="n">
         <v>5.283509282575594</v>
@@ -56100,10 +56100,10 @@
         <v>5.5</v>
       </c>
       <c r="CJ121" t="n">
-        <v>5.453484861815507</v>
+        <v>5.453484861028437</v>
       </c>
       <c r="CK121" t="n">
-        <v>7.940273958803379</v>
+        <v>7.940273957657405</v>
       </c>
       <c r="CL121" t="inlineStr"/>
       <c r="CM121" t="inlineStr"/>
@@ -56112,13 +56112,13 @@
       <c r="CP121" t="inlineStr"/>
       <c r="CQ121" t="inlineStr"/>
       <c r="CR121" t="n">
-        <v>6.696879410309443</v>
+        <v>6.696879409342921</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.696879410309443</v>
+        <v>6.696879409342921</v>
       </c>
       <c r="CT121" t="n">
-        <v>6.027191469278499</v>
+        <v>6.027191468408629</v>
       </c>
       <c r="CU121" t="n">
         <v>2</v>
@@ -56130,10 +56130,10 @@
         <v>1.5</v>
       </c>
       <c r="CX121" t="n">
-        <v>9.585299441427253</v>
+        <v>9.585299425611439</v>
       </c>
       <c r="CY121" t="n">
-        <v>21.76144382380807</v>
+        <v>21.76144380623493</v>
       </c>
       <c r="CZ121" t="inlineStr">
         <is>
@@ -56444,10 +56444,10 @@
         <v>5.320000171661377</v>
       </c>
       <c r="CJ122" t="n">
-        <v>5.856172610805581</v>
+        <v>5.85617259566696</v>
       </c>
       <c r="CK122" t="n">
-        <v>10.44092075839771</v>
+        <v>10.44092073140719</v>
       </c>
       <c r="CL122" t="inlineStr"/>
       <c r="CM122" t="inlineStr"/>
@@ -56456,13 +56456,13 @@
       <c r="CP122" t="inlineStr"/>
       <c r="CQ122" t="inlineStr"/>
       <c r="CR122" t="n">
-        <v>8.148546684601644</v>
+        <v>8.148546663537076</v>
       </c>
       <c r="CS122" t="n">
-        <v>8.148546684601644</v>
+        <v>8.148546663537076</v>
       </c>
       <c r="CT122" t="n">
-        <v>7.33369201614148</v>
+        <v>7.333691997183368</v>
       </c>
       <c r="CU122" t="n">
         <v>2</v>
@@ -56474,10 +56474,10 @@
         <v>1.8</v>
       </c>
       <c r="CX122" t="n">
-        <v>37.85134923879616</v>
+        <v>37.85134888244068</v>
       </c>
       <c r="CY122" t="n">
-        <v>53.16816582088462</v>
+        <v>53.1681654249341</v>
       </c>
       <c r="CZ122" t="inlineStr">
         <is>
@@ -56782,10 +56782,10 @@
         <v>22</v>
       </c>
       <c r="CJ123" t="n">
-        <v>38.19068408430406</v>
+        <v>38.19068430219833</v>
       </c>
       <c r="CK123" t="n">
-        <v>70.84371897638403</v>
+        <v>70.84371938057789</v>
       </c>
       <c r="CL123" t="n">
         <v>19.69594594594594</v>
@@ -56804,7 +56804,7 @@
       </c>
       <c r="CQ123" t="inlineStr"/>
       <c r="CR123" t="n">
-        <v>25.80022401767156</v>
+        <v>25.80022405398728</v>
       </c>
       <c r="CS123" t="n">
         <v>22.95973920566808</v>
@@ -56825,7 +56825,7 @@
         <v>-6.073794158630585</v>
       </c>
       <c r="CY123" t="n">
-        <v>17.27374553487076</v>
+        <v>17.27374569994215</v>
       </c>
       <c r="CZ123" t="inlineStr">
         <is>
@@ -57136,25 +57136,25 @@
         <v>9.079999923706055</v>
       </c>
       <c r="CJ124" t="n">
-        <v>3.508565476378518</v>
+        <v>3.508565461571328</v>
       </c>
       <c r="CK124" t="n">
-        <v>3.62035612466373</v>
+        <v>3.620356111740948</v>
       </c>
       <c r="CL124" t="n">
-        <v>4.365533866190914</v>
+        <v>4.365533869032086</v>
       </c>
       <c r="CM124" t="n">
         <v>18.86542389459268</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.429630196119621</v>
+        <v>3.429630187219877</v>
       </c>
       <c r="CO124" t="n">
-        <v>7.741903460731747</v>
+        <v>7.741903461333696</v>
       </c>
       <c r="CP124" t="n">
-        <v>1.724012498528069</v>
+        <v>1.724012501433833</v>
       </c>
       <c r="CQ124" t="n">
         <v>21.8229114254654</v>
@@ -57482,10 +57482,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.7838805198043993</v>
+        <v>0.7838805191185597</v>
       </c>
       <c r="CK125" t="n">
-        <v>1.454098364237161</v>
+        <v>1.454098362964928</v>
       </c>
       <c r="CL125" t="n">
         <v>15.56199010537595</v>
@@ -57494,13 +57494,13 @@
         <v>16.26314871365512</v>
       </c>
       <c r="CN125" t="n">
-        <v>13.64124870085852</v>
+        <v>13.64124870100792</v>
       </c>
       <c r="CO125" t="n">
-        <v>1.677467519644407</v>
+        <v>1.677467519658981</v>
       </c>
       <c r="CP125" t="n">
-        <v>11.00817213179532</v>
+        <v>11.00817213250508</v>
       </c>
       <c r="CQ125" t="inlineStr"/>
       <c r="CR125" t="inlineStr"/>
@@ -58160,25 +58160,25 @@
         <v>18.60000038146973</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.6412328433588004</v>
+        <v>0.6412328412330476</v>
       </c>
       <c r="CK127" t="n">
-        <v>0.8549921571882522</v>
+        <v>0.8549921545685183</v>
       </c>
       <c r="CL127" t="n">
-        <v>4.502948027597863</v>
+        <v>4.502948028728366</v>
       </c>
       <c r="CM127" t="n">
         <v>11.33513440194061</v>
       </c>
       <c r="CN127" t="n">
-        <v>1.725838691585297</v>
+        <v>1.725838691992438</v>
       </c>
       <c r="CO127" t="n">
-        <v>0.6737065028504394</v>
+        <v>0.6737065028665111</v>
       </c>
       <c r="CP127" t="n">
-        <v>2.204429654082469</v>
+        <v>2.204429654813898</v>
       </c>
       <c r="CQ127" t="n">
         <v>18.60000038146973</v>
@@ -58514,10 +58514,10 @@
         <v>5.199999809265137</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.285816877554555</v>
+        <v>1.28581687790795</v>
       </c>
       <c r="CK128" t="n">
-        <v>2.151989883252669</v>
+        <v>2.151989883844124</v>
       </c>
       <c r="CL128" t="inlineStr"/>
       <c r="CM128" t="inlineStr"/>
@@ -58528,13 +58528,13 @@
         <v>5.739109502577318</v>
       </c>
       <c r="CR128" t="n">
-        <v>1.718903380403612</v>
+        <v>1.718903380876037</v>
       </c>
       <c r="CS128" t="n">
-        <v>1.718903380403612</v>
+        <v>1.718903380876037</v>
       </c>
       <c r="CT128" t="n">
-        <v>1.547013042363251</v>
+        <v>1.547013042788433</v>
       </c>
       <c r="CU128" t="n">
         <v>2</v>
@@ -58546,10 +58546,10 @@
         <v>4.5</v>
       </c>
       <c r="CX128" t="n">
-        <v>-70.24974809408936</v>
+        <v>-70.24974808591278</v>
       </c>
       <c r="CY128" t="n">
-        <v>-66.94416454898817</v>
+        <v>-66.94416453990308</v>
       </c>
       <c r="CZ128" t="inlineStr">
         <is>
@@ -58856,10 +58856,10 @@
         <v>17.1299991607666</v>
       </c>
       <c r="CJ129" t="n">
-        <v>1.320220912227982</v>
+        <v>1.320220912501634</v>
       </c>
       <c r="CK129" t="n">
-        <v>1.922241648203942</v>
+        <v>1.922241648602379</v>
       </c>
       <c r="CL129" t="n">
         <v>1.219133588393709</v>
@@ -59198,37 +59198,37 @@
         <v>17.65999984741211</v>
       </c>
       <c r="CJ130" t="n">
-        <v>2.127790684215423</v>
+        <v>2.127790689949352</v>
       </c>
       <c r="CK130" t="n">
-        <v>3.759843129547795</v>
+        <v>3.759843135055721</v>
       </c>
       <c r="CL130" t="n">
-        <v>9.741985121231609</v>
+        <v>9.741985109250471</v>
       </c>
       <c r="CM130" t="n">
         <v>12.08493439512116</v>
       </c>
       <c r="CN130" t="n">
-        <v>5.648205439350086</v>
+        <v>5.64820543549739</v>
       </c>
       <c r="CO130" t="n">
-        <v>5.613969607102133</v>
+        <v>5.613969606595266</v>
       </c>
       <c r="CP130" t="n">
-        <v>4.793870061121305</v>
+        <v>4.793870056494255</v>
       </c>
       <c r="CQ130" t="n">
         <v>16.0617953943026</v>
       </c>
       <c r="CR130" t="n">
-        <v>6.940467958912347</v>
+        <v>6.94046795633571</v>
       </c>
       <c r="CS130" t="n">
-        <v>5.63108752322611</v>
+        <v>5.631087521046329</v>
       </c>
       <c r="CT130" t="n">
-        <v>5.067978770903498</v>
+        <v>5.067978768941696</v>
       </c>
       <c r="CU130" t="n">
         <v>6</v>
@@ -59240,10 +59240,10 @@
         <v>7.5</v>
       </c>
       <c r="CX130" t="n">
-        <v>-71.30249821804978</v>
+        <v>-71.3024982291585</v>
       </c>
       <c r="CY130" t="n">
-        <v>-60.69950159184514</v>
+        <v>-60.69950160643538</v>
       </c>
       <c r="CZ130" t="inlineStr">
         <is>
@@ -59546,10 +59546,10 @@
         <v>4.309999942779541</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.9059813508621624</v>
+        <v>0.9059813506308048</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.680595405849311</v>
+        <v>1.680595405420143</v>
       </c>
       <c r="CL131" t="inlineStr"/>
       <c r="CM131" t="inlineStr"/>
@@ -59558,13 +59558,13 @@
       <c r="CP131" t="inlineStr"/>
       <c r="CQ131" t="inlineStr"/>
       <c r="CR131" t="n">
-        <v>1.293288378355737</v>
+        <v>1.293288378025474</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.293288378355737</v>
+        <v>1.293288378025474</v>
       </c>
       <c r="CT131" t="n">
-        <v>1.163959540520163</v>
+        <v>1.163959540222927</v>
       </c>
       <c r="CU131" t="n">
         <v>2</v>
@@ -59576,10 +59576,10 @@
         <v>1.9</v>
       </c>
       <c r="CX131" t="n">
-        <v>-72.99397781964889</v>
+        <v>-72.99397782654533</v>
       </c>
       <c r="CY131" t="n">
-        <v>-69.99330868849877</v>
+        <v>-69.99330869616148</v>
       </c>
       <c r="CZ131" t="inlineStr">
         <is>
@@ -59892,10 +59892,10 @@
         <v>1.169999957084656</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.3441507059227179</v>
+        <v>0.3441507060345929</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.6383995594866416</v>
+        <v>0.6383995596941697</v>
       </c>
       <c r="CL132" t="inlineStr"/>
       <c r="CM132" t="inlineStr"/>
@@ -59904,13 +59904,13 @@
       <c r="CP132" t="inlineStr"/>
       <c r="CQ132" t="inlineStr"/>
       <c r="CR132" t="n">
-        <v>0.4912751327046798</v>
+        <v>0.4912751328643813</v>
       </c>
       <c r="CS132" t="n">
-        <v>0.4912751327046798</v>
+        <v>0.4912751328643813</v>
       </c>
       <c r="CT132" t="n">
-        <v>0.4421476194342118</v>
+        <v>0.4421476195779432</v>
       </c>
       <c r="CU132" t="n">
         <v>2</v>
@@ -59922,10 +59922,10 @@
         <v>1.9</v>
       </c>
       <c r="CX132" t="n">
-        <v>-62.20960379041962</v>
+        <v>-62.20960377813489</v>
       </c>
       <c r="CY132" t="n">
-        <v>-58.01067087824403</v>
+        <v>-58.01067086459432</v>
       </c>
       <c r="CZ132" t="inlineStr">
         <is>
@@ -60576,10 +60576,10 @@
         <v>36.66999816894531</v>
       </c>
       <c r="CJ134" t="n">
-        <v>8.259335362740455</v>
+        <v>8.259335398178235</v>
       </c>
       <c r="CK134" t="n">
-        <v>12.0255922881501</v>
+        <v>12.02559233974751</v>
       </c>
       <c r="CL134" t="n">
         <v>7.913840650695814</v>
@@ -60918,10 +60918,10 @@
         <v>5.190000057220459</v>
       </c>
       <c r="CJ135" t="n">
-        <v>0.9904024025802123</v>
+        <v>0.9904024023179506</v>
       </c>
       <c r="CK135" t="n">
-        <v>1.837196456786294</v>
+        <v>1.837196456299798</v>
       </c>
       <c r="CL135" t="inlineStr"/>
       <c r="CM135" t="inlineStr"/>
@@ -60932,13 +60932,13 @@
         <v>2.84152338750234</v>
       </c>
       <c r="CR135" t="n">
-        <v>1.889707415622949</v>
+        <v>1.889707415373363</v>
       </c>
       <c r="CS135" t="n">
-        <v>1.837196456786294</v>
+        <v>1.837196456299798</v>
       </c>
       <c r="CT135" t="n">
-        <v>1.653476811107664</v>
+        <v>1.653476810669818</v>
       </c>
       <c r="CU135" t="n">
         <v>3</v>
@@ -60950,10 +60950,10 @@
         <v>2.9</v>
       </c>
       <c r="CX135" t="n">
-        <v>-68.1411022566887</v>
+        <v>-68.14110226512503</v>
       </c>
       <c r="CY135" t="n">
-        <v>-63.58945289424535</v>
+        <v>-63.58945289905431</v>
       </c>
       <c r="CZ135" t="inlineStr">
         <is>
@@ -61272,25 +61272,25 @@
         <v>4.949999809265137</v>
       </c>
       <c r="CJ136" t="n">
-        <v>1.53709464273051</v>
+        <v>1.53709464148394</v>
       </c>
       <c r="CK136" t="n">
-        <v>1.688537263370283</v>
+        <v>1.688537262309561</v>
       </c>
       <c r="CL136" t="n">
-        <v>2.418475242445044</v>
+        <v>2.418475242887143</v>
       </c>
       <c r="CM136" t="n">
         <v>7.627771328933809</v>
       </c>
       <c r="CN136" t="n">
-        <v>1.683198694266259</v>
+        <v>1.683198693823563</v>
       </c>
       <c r="CO136" t="n">
-        <v>1.780877326903282</v>
+        <v>1.780877326940081</v>
       </c>
       <c r="CP136" t="n">
-        <v>1.039152454836235</v>
+        <v>1.039152455241021</v>
       </c>
       <c r="CQ136" t="n">
         <v>0.3242832207911349</v>
@@ -61616,10 +61616,10 @@
         <v>2.150000095367432</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.6036239000816457</v>
+        <v>0.6036239000495797</v>
       </c>
       <c r="CK137" t="n">
-        <v>0.8788763985188763</v>
+        <v>0.8788763984721881</v>
       </c>
       <c r="CL137" t="n">
         <v>0.3524590320274478</v>
@@ -62274,10 +62274,10 @@
         <v>6.900000095367432</v>
       </c>
       <c r="CJ139" t="n">
-        <v>1.893532161321219</v>
+        <v>1.893532146310335</v>
       </c>
       <c r="CK139" t="n">
-        <v>2.756982826883696</v>
+        <v>2.756982805027848</v>
       </c>
       <c r="CL139" t="n">
         <v>1.700071096702708</v>
@@ -63274,10 +63274,10 @@
         <v>18.26000022888184</v>
       </c>
       <c r="CJ142" t="n">
-        <v>27.71516713193429</v>
+        <v>27.71516703838473</v>
       </c>
       <c r="CK142" t="n">
-        <v>37.07673469649876</v>
+        <v>37.07673457135024</v>
       </c>
       <c r="CL142" t="n">
         <v>2.525466010009227</v>
@@ -63286,7 +63286,7 @@
         <v>7.009520407943455</v>
       </c>
       <c r="CN142" t="n">
-        <v>6.461779426537877</v>
+        <v>6.461779407581533</v>
       </c>
       <c r="CO142" t="n">
         <v>3.155500877947406</v>
@@ -63501,7 +63501,7 @@
         <v>1</v>
       </c>
       <c r="AW143" t="n">
-        <v>3730917120</v>
+        <v>3730954752</v>
       </c>
       <c r="AX143" t="n">
         <v>42.17</v>
@@ -63962,10 +63962,10 @@
         <v>3.900000095367432</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.7054953878133331</v>
+        <v>0.7054953870063031</v>
       </c>
       <c r="CK144" t="n">
-        <v>1.308693944393733</v>
+        <v>1.308693942896692</v>
       </c>
       <c r="CL144" t="inlineStr"/>
       <c r="CM144" t="inlineStr"/>
@@ -63976,13 +63976,13 @@
         <v>3.536464154706048</v>
       </c>
       <c r="CR144" t="n">
-        <v>1.007094666103533</v>
+        <v>1.007094664951498</v>
       </c>
       <c r="CS144" t="n">
-        <v>1.007094666103533</v>
+        <v>1.007094664951498</v>
       </c>
       <c r="CT144" t="n">
-        <v>0.9063851994931796</v>
+        <v>0.9063851984563478</v>
       </c>
       <c r="CU144" t="n">
         <v>2</v>
@@ -63994,10 +63994,10 @@
         <v>5</v>
       </c>
       <c r="CX144" t="n">
-        <v>-76.75935442745711</v>
+        <v>-76.75935445404254</v>
       </c>
       <c r="CY144" t="n">
-        <v>-74.17706047495234</v>
+        <v>-74.17706050449171</v>
       </c>
       <c r="CZ144" t="inlineStr">
         <is>
@@ -64306,10 +64306,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ145" t="n">
-        <v>9.566327508601873</v>
+        <v>9.566327474248439</v>
       </c>
       <c r="CK145" t="n">
-        <v>13.92857285252433</v>
+        <v>13.92857280250573</v>
       </c>
       <c r="CL145" t="n">
         <v>4.670347661304791</v>
@@ -65338,10 +65338,10 @@
         <v>11.1899995803833</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.978835451916871</v>
+        <v>5.978835471266716</v>
       </c>
       <c r="CK148" t="n">
-        <v>10.94348326050858</v>
+        <v>10.94348329592596</v>
       </c>
       <c r="CL148" t="inlineStr"/>
       <c r="CM148" t="inlineStr"/>
@@ -65352,13 +65352,13 @@
         <v>3.360116783680318</v>
       </c>
       <c r="CR148" t="n">
-        <v>6.760811832035258</v>
+        <v>6.760811850290999</v>
       </c>
       <c r="CS148" t="n">
-        <v>5.978835451916871</v>
+        <v>5.978835471266716</v>
       </c>
       <c r="CT148" t="n">
-        <v>5.380951906725184</v>
+        <v>5.380951924140044</v>
       </c>
       <c r="CU148" t="n">
         <v>3</v>
@@ -65370,10 +65370,10 @@
         <v>3.3</v>
       </c>
       <c r="CX148" t="n">
-        <v>-51.91284978992942</v>
+        <v>-51.91284963430065</v>
       </c>
       <c r="CY148" t="n">
-        <v>-39.58166143377394</v>
+        <v>-39.58166127063058</v>
       </c>
       <c r="CZ148" t="inlineStr">
         <is>
@@ -66030,10 +66030,10 @@
         <v>15.25</v>
       </c>
       <c r="CJ150" t="n">
-        <v>3.902183831070954</v>
+        <v>3.902183833199661</v>
       </c>
       <c r="CK150" t="n">
-        <v>5.681579658039309</v>
+        <v>5.681579661138707</v>
       </c>
       <c r="CL150" t="inlineStr"/>
       <c r="CM150" t="inlineStr"/>
@@ -66044,7 +66044,7 @@
         <v>5.478426920725005</v>
       </c>
       <c r="CR150" t="n">
-        <v>5.020730136611757</v>
+        <v>5.020730138354458</v>
       </c>
       <c r="CS150" t="n">
         <v>5.478426920725005</v>
@@ -66065,7 +66065,7 @@
         <v>-67.66830013998357</v>
       </c>
       <c r="CY150" t="n">
-        <v>-67.07717943205405</v>
+        <v>-67.07717942062649</v>
       </c>
       <c r="CZ150" t="inlineStr">
         <is>
